--- a/Random-Forest-main/Random Forest Data.xlsx
+++ b/Random-Forest-main/Random Forest Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10914"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kyliealfaro/Desktop/PhD UHM/Modeling Project/Random-Forest-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{797FA170-5BC8-664E-A02A-2A2FDB72A0B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A107EDDF-727D-EF4E-B196-BB7102EFBC69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1320" yWindow="660" windowWidth="30200" windowHeight="21680" xr2:uid="{6AE4499B-BE9B-4430-8CBB-9E423EAAA4D3}"/>
+    <workbookView xWindow="4360" yWindow="660" windowWidth="30200" windowHeight="21680" xr2:uid="{6AE4499B-BE9B-4430-8CBB-9E423EAAA4D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Combined Manoa Data" sheetId="1" r:id="rId1"/>
@@ -27748,7 +27748,7 @@
         <v>-26.4</v>
       </c>
       <c r="F131" s="19">
-        <f t="shared" ref="F131:F162" si="4">E131 - (8*D131)</f>
+        <f t="shared" ref="F131:F137" si="4">E131 - (8*D131)</f>
         <v>11.200000000000003</v>
       </c>
       <c r="G131" s="19">

--- a/Random-Forest-main/Random Forest Data.xlsx
+++ b/Random-Forest-main/Random Forest Data.xlsx
@@ -1,22 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10914"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kyliealfaro/Desktop/PhD UHM/Modeling Project/Random-Forest-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A107EDDF-727D-EF4E-B196-BB7102EFBC69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CCA8776-0608-C142-9E08-999E3DFA4300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4360" yWindow="660" windowWidth="30200" windowHeight="21680" xr2:uid="{6AE4499B-BE9B-4430-8CBB-9E423EAAA4D3}"/>
+    <workbookView xWindow="3940" yWindow="660" windowWidth="30200" windowHeight="21680" xr2:uid="{6AE4499B-BE9B-4430-8CBB-9E423EAAA4D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Combined Manoa Data" sheetId="1" r:id="rId1"/>
     <sheet name="Hailey's Data" sheetId="3" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="4" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Combined Manoa Data'!$B$2:$N$137</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -22183,6 +22186,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E174FB01-AC8B-4229-B319-63F7FF07E34C}">
+  <sheetPr filterMode="1"/>
   <dimension ref="B1:N148"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
@@ -22247,7 +22251,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="3" spans="2:14">
+    <row r="3" spans="2:14" hidden="1">
       <c r="B3" s="23">
         <v>44970.399305555555</v>
       </c>
@@ -22290,7 +22294,7 @@
         <v>-2.4</v>
       </c>
     </row>
-    <row r="4" spans="2:14">
+    <row r="4" spans="2:14" hidden="1">
       <c r="B4" s="23">
         <v>44970.429166666669</v>
       </c>
@@ -22419,7 +22423,7 @@
         <v>-5.0999999999999996</v>
       </c>
     </row>
-    <row r="7" spans="2:14">
+    <row r="7" spans="2:14" hidden="1">
       <c r="B7" s="23">
         <v>44974.370833333334</v>
       </c>
@@ -22462,7 +22466,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="8" spans="2:14">
+    <row r="8" spans="2:14" hidden="1">
       <c r="B8" s="23">
         <v>44974.385416666664</v>
       </c>
@@ -22505,7 +22509,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="9" spans="2:14">
+    <row r="9" spans="2:14" hidden="1">
       <c r="B9" s="23">
         <v>44974.432638888888</v>
       </c>
@@ -22548,7 +22552,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="10" spans="2:14">
+    <row r="10" spans="2:14" hidden="1">
       <c r="B10" s="23">
         <v>44977.37222222222</v>
       </c>
@@ -22591,7 +22595,7 @@
         <v>-3.6</v>
       </c>
     </row>
-    <row r="11" spans="2:14">
+    <row r="11" spans="2:14" hidden="1">
       <c r="B11" s="23">
         <v>44977.393055555556</v>
       </c>
@@ -22634,7 +22638,7 @@
         <v>-3.6</v>
       </c>
     </row>
-    <row r="12" spans="2:14">
+    <row r="12" spans="2:14" hidden="1">
       <c r="B12" s="23">
         <v>44977.43472222222</v>
       </c>
@@ -22677,7 +22681,7 @@
         <v>-3.6</v>
       </c>
     </row>
-    <row r="13" spans="2:14">
+    <row r="13" spans="2:14" hidden="1">
       <c r="B13" s="23">
         <v>44977.448611111111</v>
       </c>
@@ -22720,7 +22724,7 @@
         <v>-3.6</v>
       </c>
     </row>
-    <row r="14" spans="2:14">
+    <row r="14" spans="2:14" hidden="1">
       <c r="B14" s="23">
         <v>44979.367361111108</v>
       </c>
@@ -22763,7 +22767,7 @@
         <v>-3.8</v>
       </c>
     </row>
-    <row r="15" spans="2:14">
+    <row r="15" spans="2:14" hidden="1">
       <c r="B15" s="23">
         <v>44979.385416666664</v>
       </c>
@@ -22892,7 +22896,7 @@
         <v>-3.8</v>
       </c>
     </row>
-    <row r="18" spans="2:14">
+    <row r="18" spans="2:14" hidden="1">
       <c r="B18" s="23">
         <v>44981.361111111109</v>
       </c>
@@ -22935,7 +22939,7 @@
         <v>-3.1</v>
       </c>
     </row>
-    <row r="19" spans="2:14">
+    <row r="19" spans="2:14" hidden="1">
       <c r="B19" s="23">
         <v>44981.375</v>
       </c>
@@ -22978,7 +22982,7 @@
         <v>-3.1</v>
       </c>
     </row>
-    <row r="20" spans="2:14">
+    <row r="20" spans="2:14" hidden="1">
       <c r="B20" s="23">
         <v>44986.363888888889</v>
       </c>
@@ -23021,7 +23025,7 @@
         <v>-2.5</v>
       </c>
     </row>
-    <row r="21" spans="2:14">
+    <row r="21" spans="2:14" hidden="1">
       <c r="B21" s="23">
         <v>44986.381944444445</v>
       </c>
@@ -23064,7 +23068,7 @@
         <v>-2.5</v>
       </c>
     </row>
-    <row r="22" spans="2:14">
+    <row r="22" spans="2:14" hidden="1">
       <c r="B22" s="23">
         <v>44986.401388888888</v>
       </c>
@@ -23107,7 +23111,7 @@
         <v>-2.5</v>
       </c>
     </row>
-    <row r="23" spans="2:14">
+    <row r="23" spans="2:14" hidden="1">
       <c r="B23" s="23">
         <v>45019.381944444445</v>
       </c>
@@ -23150,7 +23154,7 @@
         <v>-3.7</v>
       </c>
     </row>
-    <row r="24" spans="2:14">
+    <row r="24" spans="2:14" hidden="1">
       <c r="B24" s="23">
         <v>45019.401388888888</v>
       </c>
@@ -23193,7 +23197,7 @@
         <v>-3.7</v>
       </c>
     </row>
-    <row r="25" spans="2:14">
+    <row r="25" spans="2:14" hidden="1">
       <c r="B25" s="23">
         <v>45028.354166666664</v>
       </c>
@@ -23236,7 +23240,7 @@
         <v>-2.6</v>
       </c>
     </row>
-    <row r="26" spans="2:14">
+    <row r="26" spans="2:14" hidden="1">
       <c r="B26" s="23">
         <v>45028.368750000001</v>
       </c>
@@ -23365,7 +23369,7 @@
         <v>-2.6</v>
       </c>
     </row>
-    <row r="29" spans="2:14">
+    <row r="29" spans="2:14" hidden="1">
       <c r="B29" s="23">
         <v>45033.361111111109</v>
       </c>
@@ -23408,7 +23412,7 @@
         <v>-1.5</v>
       </c>
     </row>
-    <row r="30" spans="2:14">
+    <row r="30" spans="2:14" hidden="1">
       <c r="B30" s="23">
         <v>45033.375</v>
       </c>
@@ -23451,7 +23455,7 @@
         <v>-1.5</v>
       </c>
     </row>
-    <row r="31" spans="2:14">
+    <row r="31" spans="2:14" hidden="1">
       <c r="B31" s="23">
         <v>45042.376388888886</v>
       </c>
@@ -23494,7 +23498,7 @@
         <v>-1.9</v>
       </c>
     </row>
-    <row r="32" spans="2:14">
+    <row r="32" spans="2:14" hidden="1">
       <c r="B32" s="23">
         <v>45058.451388888891</v>
       </c>
@@ -23537,7 +23541,7 @@
         <v>-1.7</v>
       </c>
     </row>
-    <row r="33" spans="2:14">
+    <row r="33" spans="2:14" hidden="1">
       <c r="B33" s="23">
         <v>45061.423611111109</v>
       </c>
@@ -23666,7 +23670,7 @@
         <v>-1.7</v>
       </c>
     </row>
-    <row r="36" spans="2:14">
+    <row r="36" spans="2:14" hidden="1">
       <c r="B36" s="23">
         <v>45061.486111111109</v>
       </c>
@@ -23709,7 +23713,7 @@
         <v>-1.7</v>
       </c>
     </row>
-    <row r="37" spans="2:14">
+    <row r="37" spans="2:14" hidden="1">
       <c r="B37" s="23">
         <v>45062.475694444445</v>
       </c>
@@ -23752,7 +23756,7 @@
         <v>-1.7</v>
       </c>
     </row>
-    <row r="38" spans="2:14">
+    <row r="38" spans="2:14" hidden="1">
       <c r="B38" s="23">
         <v>45062.489583333336</v>
       </c>
@@ -23795,7 +23799,7 @@
         <v>-1.7</v>
       </c>
     </row>
-    <row r="39" spans="2:14">
+    <row r="39" spans="2:14" hidden="1">
       <c r="B39" s="23">
         <v>45062.53125</v>
       </c>
@@ -23838,7 +23842,7 @@
         <v>-1.7</v>
       </c>
     </row>
-    <row r="40" spans="2:14">
+    <row r="40" spans="2:14" hidden="1">
       <c r="B40" s="23">
         <v>45063.464583333334</v>
       </c>
@@ -23881,7 +23885,7 @@
         <v>-1.3</v>
       </c>
     </row>
-    <row r="41" spans="2:14">
+    <row r="41" spans="2:14" hidden="1">
       <c r="B41" s="23">
         <v>45063.486111111109</v>
       </c>
@@ -23924,7 +23928,7 @@
         <v>-1.3</v>
       </c>
     </row>
-    <row r="42" spans="2:14">
+    <row r="42" spans="2:14" hidden="1">
       <c r="B42" s="23">
         <v>45077.625</v>
       </c>
@@ -23967,7 +23971,7 @@
         <v>-1.6</v>
       </c>
     </row>
-    <row r="43" spans="2:14">
+    <row r="43" spans="2:14" hidden="1">
       <c r="B43" s="23">
         <v>45077.635416666664</v>
       </c>
@@ -24096,7 +24100,7 @@
         <v>-1.6</v>
       </c>
     </row>
-    <row r="46" spans="2:14">
+    <row r="46" spans="2:14" hidden="1">
       <c r="B46" s="23">
         <v>45078.614583333336</v>
       </c>
@@ -24139,7 +24143,7 @@
         <v>-1.6</v>
       </c>
     </row>
-    <row r="47" spans="2:14">
+    <row r="47" spans="2:14" hidden="1">
       <c r="B47" s="23">
         <v>45078.627083333333</v>
       </c>
@@ -24182,7 +24186,7 @@
         <v>-1.6</v>
       </c>
     </row>
-    <row r="48" spans="2:14">
+    <row r="48" spans="2:14" hidden="1">
       <c r="B48" s="23">
         <v>45078.638194444444</v>
       </c>
@@ -24225,7 +24229,7 @@
         <v>-1.6</v>
       </c>
     </row>
-    <row r="49" spans="2:14">
+    <row r="49" spans="2:14" hidden="1">
       <c r="B49" s="23">
         <v>45079.39166666667</v>
       </c>
@@ -24268,7 +24272,7 @@
         <v>-1.6</v>
       </c>
     </row>
-    <row r="50" spans="2:14">
+    <row r="50" spans="2:14" hidden="1">
       <c r="B50" s="23">
         <v>45079.416666666664</v>
       </c>
@@ -24311,7 +24315,7 @@
         <v>-1.6</v>
       </c>
     </row>
-    <row r="51" spans="2:14">
+    <row r="51" spans="2:14" hidden="1">
       <c r="B51" s="23">
         <v>45121.4375</v>
       </c>
@@ -24354,7 +24358,7 @@
         <v>-1.7</v>
       </c>
     </row>
-    <row r="52" spans="2:14">
+    <row r="52" spans="2:14" hidden="1">
       <c r="B52" s="23">
         <v>45121.458333333336</v>
       </c>
@@ -24440,7 +24444,7 @@
         <v>-1.7</v>
       </c>
     </row>
-    <row r="54" spans="2:14">
+    <row r="54" spans="2:14" hidden="1">
       <c r="B54" s="23">
         <v>45124.368055555555</v>
       </c>
@@ -24483,7 +24487,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="55" spans="2:14">
+    <row r="55" spans="2:14" hidden="1">
       <c r="B55" s="23">
         <v>45124.375</v>
       </c>
@@ -24526,7 +24530,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="56" spans="2:14">
+    <row r="56" spans="2:14" hidden="1">
       <c r="B56" s="23">
         <v>45124.386805555558</v>
       </c>
@@ -24612,7 +24616,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="58" spans="2:14">
+    <row r="58" spans="2:14" hidden="1">
       <c r="B58" s="23">
         <v>45125.416666666664</v>
       </c>
@@ -24655,7 +24659,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="59" spans="2:14">
+    <row r="59" spans="2:14" hidden="1">
       <c r="B59" s="23">
         <v>45125.447916666664</v>
       </c>
@@ -24698,7 +24702,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="60" spans="2:14">
+    <row r="60" spans="2:14" hidden="1">
       <c r="B60" s="23">
         <v>45152.606249999997</v>
       </c>
@@ -24741,7 +24745,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="61" spans="2:14">
+    <row r="61" spans="2:14" hidden="1">
       <c r="B61" s="23">
         <v>45152.62222222222</v>
       </c>
@@ -24827,7 +24831,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="63" spans="2:14">
+    <row r="63" spans="2:14" hidden="1">
       <c r="B63" s="23">
         <v>45153.461805555555</v>
       </c>
@@ -24870,7 +24874,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="64" spans="2:14">
+    <row r="64" spans="2:14" hidden="1">
       <c r="B64" s="23">
         <v>45153.475694444445</v>
       </c>
@@ -24913,7 +24917,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="65" spans="2:14">
+    <row r="65" spans="2:14" hidden="1">
       <c r="B65" s="23">
         <v>45153.489583333336</v>
       </c>
@@ -24999,7 +25003,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="67" spans="2:14">
+    <row r="67" spans="2:14" hidden="1">
       <c r="B67" s="23">
         <v>45154.555555555555</v>
       </c>
@@ -25042,7 +25046,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="68" spans="2:14">
+    <row r="68" spans="2:14" hidden="1">
       <c r="B68" s="23">
         <v>45154.579861111109</v>
       </c>
@@ -25085,7 +25089,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="69" spans="2:14">
+    <row r="69" spans="2:14" hidden="1">
       <c r="B69" s="23">
         <v>45175.631944444445</v>
       </c>
@@ -25128,7 +25132,7 @@
         <v>-1.7</v>
       </c>
     </row>
-    <row r="70" spans="2:14">
+    <row r="70" spans="2:14" hidden="1">
       <c r="B70" s="23">
         <v>45176.5625</v>
       </c>
@@ -25257,7 +25261,7 @@
         <v>-1.7</v>
       </c>
     </row>
-    <row r="73" spans="2:14">
+    <row r="73" spans="2:14" hidden="1">
       <c r="B73" s="23">
         <v>45183.577777777777</v>
       </c>
@@ -25300,7 +25304,7 @@
         <v>-1.7</v>
       </c>
     </row>
-    <row r="74" spans="2:14">
+    <row r="74" spans="2:14" hidden="1">
       <c r="B74" s="23">
         <v>45183.59375</v>
       </c>
@@ -25343,7 +25347,7 @@
         <v>-1.7</v>
       </c>
     </row>
-    <row r="75" spans="2:14">
+    <row r="75" spans="2:14" hidden="1">
       <c r="B75" s="23">
         <v>45187.458333333336</v>
       </c>
@@ -25386,7 +25390,7 @@
         <v>-2.1</v>
       </c>
     </row>
-    <row r="76" spans="2:14">
+    <row r="76" spans="2:14" hidden="1">
       <c r="B76" s="23">
         <v>45187.474999999999</v>
       </c>
@@ -25429,7 +25433,7 @@
         <v>-2.1</v>
       </c>
     </row>
-    <row r="77" spans="2:14">
+    <row r="77" spans="2:14" hidden="1">
       <c r="B77" s="23">
         <v>45187.486805555556</v>
       </c>
@@ -25472,7 +25476,7 @@
         <v>-2.1</v>
       </c>
     </row>
-    <row r="78" spans="2:14">
+    <row r="78" spans="2:14" hidden="1">
       <c r="B78" s="23">
         <v>45238.506944444445</v>
       </c>
@@ -25515,7 +25519,7 @@
         <v>-1.5</v>
       </c>
     </row>
-    <row r="79" spans="2:14">
+    <row r="79" spans="2:14" hidden="1">
       <c r="B79" s="23">
         <v>45238.524305555555</v>
       </c>
@@ -25558,7 +25562,7 @@
         <v>-1.5</v>
       </c>
     </row>
-    <row r="80" spans="2:14">
+    <row r="80" spans="2:14" hidden="1">
       <c r="B80" s="23">
         <v>45238.546527777777</v>
       </c>
@@ -25687,7 +25691,7 @@
         <v>-1.5</v>
       </c>
     </row>
-    <row r="83" spans="2:14">
+    <row r="83" spans="2:14" hidden="1">
       <c r="B83" s="23">
         <v>45240.433333333334</v>
       </c>
@@ -25730,7 +25734,7 @@
         <v>-1.5</v>
       </c>
     </row>
-    <row r="84" spans="2:14">
+    <row r="84" spans="2:14" hidden="1">
       <c r="B84" s="23">
         <v>45240.462500000001</v>
       </c>
@@ -25773,7 +25777,7 @@
         <v>-1.5</v>
       </c>
     </row>
-    <row r="85" spans="2:14">
+    <row r="85" spans="2:14" hidden="1">
       <c r="B85" s="23">
         <v>45240.481944444444</v>
       </c>
@@ -25816,7 +25820,7 @@
         <v>-1.5</v>
       </c>
     </row>
-    <row r="86" spans="2:14">
+    <row r="86" spans="2:14" hidden="1">
       <c r="B86" s="23">
         <v>45240.5</v>
       </c>
@@ -25859,7 +25863,7 @@
         <v>-1.5</v>
       </c>
     </row>
-    <row r="87" spans="2:14">
+    <row r="87" spans="2:14" hidden="1">
       <c r="B87" s="23">
         <v>45259.463194444441</v>
       </c>
@@ -25902,7 +25906,7 @@
         <v>-2.8</v>
       </c>
     </row>
-    <row r="88" spans="2:14">
+    <row r="88" spans="2:14" hidden="1">
       <c r="B88" s="23">
         <v>45260.520833333336</v>
       </c>
@@ -26031,7 +26035,7 @@
         <v>-2.8</v>
       </c>
     </row>
-    <row r="91" spans="2:14">
+    <row r="91" spans="2:14" hidden="1">
       <c r="B91" s="23">
         <v>45260.590277777781</v>
       </c>
@@ -26074,7 +26078,7 @@
         <v>-2.8</v>
       </c>
     </row>
-    <row r="92" spans="2:14">
+    <row r="92" spans="2:14" hidden="1">
       <c r="B92" s="23">
         <v>45261.4375</v>
       </c>
@@ -26117,7 +26121,7 @@
         <v>-2.8</v>
       </c>
     </row>
-    <row r="93" spans="2:14">
+    <row r="93" spans="2:14" hidden="1">
       <c r="B93" s="23">
         <v>45261.45208333333</v>
       </c>
@@ -26160,7 +26164,7 @@
         <v>-2.8</v>
       </c>
     </row>
-    <row r="94" spans="2:14">
+    <row r="94" spans="2:14" hidden="1">
       <c r="B94" s="23">
         <v>45266.4375</v>
       </c>
@@ -26203,7 +26207,7 @@
         <v>-4.5999999999999996</v>
       </c>
     </row>
-    <row r="95" spans="2:14">
+    <row r="95" spans="2:14" hidden="1">
       <c r="B95" s="23">
         <v>45266.468055555553</v>
       </c>
@@ -26246,7 +26250,7 @@
         <v>-4.5999999999999996</v>
       </c>
     </row>
-    <row r="96" spans="2:14">
+    <row r="96" spans="2:14" hidden="1">
       <c r="B96" s="23">
         <v>45344.600694444445</v>
       </c>
@@ -26285,11 +26289,9 @@
       <c r="M96" s="19">
         <v>0.397368</v>
       </c>
-      <c r="N96" s="81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="2:14">
+      <c r="N96" s="81"/>
+    </row>
+    <row r="97" spans="2:14" hidden="1">
       <c r="B97" s="23">
         <v>45344.640277777777</v>
       </c>
@@ -26328,11 +26330,9 @@
       <c r="M97" s="19">
         <v>0.15940199999999999</v>
       </c>
-      <c r="N97" s="81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="2:14">
+      <c r="N97" s="81"/>
+    </row>
+    <row r="98" spans="2:14" hidden="1">
       <c r="B98" s="23">
         <v>45344.663888888892</v>
       </c>
@@ -26371,11 +26371,9 @@
       <c r="M98" s="19">
         <v>5.8161600000000001E-2</v>
       </c>
-      <c r="N98" s="81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="2:14">
+      <c r="N98" s="81"/>
+    </row>
+    <row r="99" spans="2:14" hidden="1">
       <c r="B99" s="23">
         <v>45344.681250000001</v>
       </c>
@@ -26414,9 +26412,7 @@
       <c r="M99" s="19">
         <v>0.16870099999999999</v>
       </c>
-      <c r="N99" s="81">
-        <v>0</v>
-      </c>
+      <c r="N99" s="81"/>
     </row>
     <row r="100" spans="2:14">
       <c r="B100" s="23">
@@ -26457,9 +26453,7 @@
       <c r="M100" s="19">
         <v>5.5910100000000004E-3</v>
       </c>
-      <c r="N100" s="81">
-        <v>0</v>
-      </c>
+      <c r="N100" s="81"/>
     </row>
     <row r="101" spans="2:14">
       <c r="B101" s="23">
@@ -26500,11 +26494,9 @@
       <c r="M101" s="19">
         <v>5.5910100000000004E-3</v>
       </c>
-      <c r="N101" s="81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="2:14">
+      <c r="N101" s="81"/>
+    </row>
+    <row r="102" spans="2:14" hidden="1">
       <c r="B102" s="23">
         <v>45351.558333333334</v>
       </c>
@@ -26543,11 +26535,9 @@
       <c r="M102" s="19">
         <v>2.23054E-2</v>
       </c>
-      <c r="N102" s="81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="2:14">
+      <c r="N102" s="81"/>
+    </row>
+    <row r="103" spans="2:14" hidden="1">
       <c r="B103" s="23">
         <v>45351.579861111109</v>
       </c>
@@ -26586,11 +26576,9 @@
       <c r="M103" s="19">
         <v>2.23054E-2</v>
       </c>
-      <c r="N103" s="81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="2:14">
+      <c r="N103" s="81"/>
+    </row>
+    <row r="104" spans="2:14" hidden="1">
       <c r="B104" s="23">
         <v>45351.611805555556</v>
       </c>
@@ -26629,11 +26617,9 @@
       <c r="M104" s="19">
         <v>6.6970399999999999E-2</v>
       </c>
-      <c r="N104" s="81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="2:14">
+      <c r="N104" s="81"/>
+    </row>
+    <row r="105" spans="2:14" hidden="1">
       <c r="B105" s="26">
         <v>46001.361111111109</v>
       </c>
@@ -26675,7 +26661,7 @@
         <v>-1.4</v>
       </c>
     </row>
-    <row r="106" spans="2:14">
+    <row r="106" spans="2:14" hidden="1">
       <c r="B106" s="26">
         <v>46001.409722222219</v>
       </c>
@@ -26717,7 +26703,7 @@
         <v>-1.4</v>
       </c>
     </row>
-    <row r="107" spans="2:14">
+    <row r="107" spans="2:14" hidden="1">
       <c r="B107" s="26">
         <v>46001.473611111112</v>
       </c>
@@ -26759,7 +26745,7 @@
         <v>-1.4</v>
       </c>
     </row>
-    <row r="108" spans="2:14">
+    <row r="108" spans="2:14" hidden="1">
       <c r="B108" s="26">
         <v>46001.510416666664</v>
       </c>
@@ -26801,7 +26787,7 @@
         <v>-1.4</v>
       </c>
     </row>
-    <row r="109" spans="2:14">
+    <row r="109" spans="2:14" hidden="1">
       <c r="B109" s="26">
         <v>46001.536111111112</v>
       </c>
@@ -26885,7 +26871,7 @@
         <v>-1.4</v>
       </c>
     </row>
-    <row r="111" spans="2:14">
+    <row r="111" spans="2:14" hidden="1">
       <c r="B111" s="28">
         <v>46002</v>
       </c>
@@ -26928,7 +26914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="2:14">
+    <row r="112" spans="2:14" hidden="1">
       <c r="B112" s="28">
         <v>46002</v>
       </c>
@@ -26971,7 +26957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="2:14">
+    <row r="113" spans="2:14" hidden="1">
       <c r="B113" s="26">
         <v>46002.395833333336</v>
       </c>
@@ -27013,7 +26999,7 @@
         <v>-1.4</v>
       </c>
     </row>
-    <row r="114" spans="2:14">
+    <row r="114" spans="2:14" hidden="1">
       <c r="B114" s="28">
         <v>46022</v>
       </c>
@@ -27056,7 +27042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="2:14">
+    <row r="115" spans="2:14" hidden="1">
       <c r="B115" s="28">
         <v>46052</v>
       </c>
@@ -27099,7 +27085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="2:14">
+    <row r="116" spans="2:14" hidden="1">
       <c r="B116" s="28">
         <v>46056</v>
       </c>
@@ -27142,7 +27128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="2:14">
+    <row r="117" spans="2:14" hidden="1">
       <c r="B117" s="26">
         <v>46063.51458333333</v>
       </c>
@@ -27184,7 +27170,7 @@
         <v>-2.8</v>
       </c>
     </row>
-    <row r="118" spans="2:14">
+    <row r="118" spans="2:14" hidden="1">
       <c r="B118" s="26">
         <v>46063.522222222222</v>
       </c>
@@ -27226,7 +27212,7 @@
         <v>-2.8</v>
       </c>
     </row>
-    <row r="119" spans="2:14">
+    <row r="119" spans="2:14" hidden="1">
       <c r="B119" s="26">
         <v>46063.530555555553</v>
       </c>
@@ -27268,7 +27254,7 @@
         <v>-2.8</v>
       </c>
     </row>
-    <row r="120" spans="2:14">
+    <row r="120" spans="2:14" hidden="1">
       <c r="B120" s="26">
         <v>46063.538888888892</v>
       </c>
@@ -27352,7 +27338,7 @@
         <v>-2.8</v>
       </c>
     </row>
-    <row r="122" spans="2:14">
+    <row r="122" spans="2:14" hidden="1">
       <c r="B122" s="26">
         <v>46063.581944444442</v>
       </c>
@@ -27394,7 +27380,7 @@
         <v>-2.8</v>
       </c>
     </row>
-    <row r="123" spans="2:14">
+    <row r="123" spans="2:14" hidden="1">
       <c r="B123" s="28">
         <v>46065</v>
       </c>
@@ -27437,7 +27423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="2:14">
+    <row r="124" spans="2:14" hidden="1">
       <c r="B124" s="28">
         <v>46080</v>
       </c>
@@ -27480,7 +27466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="2:14">
+    <row r="125" spans="2:14" hidden="1">
       <c r="B125" s="28">
         <v>46093</v>
       </c>
@@ -27523,7 +27509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="2:14">
+    <row r="126" spans="2:14" hidden="1">
       <c r="B126" s="28">
         <v>46097</v>
       </c>
@@ -27566,7 +27552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="2:14">
+    <row r="127" spans="2:14" hidden="1">
       <c r="B127" s="26">
         <v>46105.353472222225</v>
       </c>
@@ -27608,7 +27594,7 @@
         <v>-6.4</v>
       </c>
     </row>
-    <row r="128" spans="2:14">
+    <row r="128" spans="2:14" hidden="1">
       <c r="B128" s="26">
         <v>46105.36041666667</v>
       </c>
@@ -27650,7 +27636,7 @@
         <v>-6.4</v>
       </c>
     </row>
-    <row r="129" spans="2:14">
+    <row r="129" spans="2:14" hidden="1">
       <c r="B129" s="26">
         <v>46105.366666666669</v>
       </c>
@@ -27692,7 +27678,7 @@
         <v>-6.4</v>
       </c>
     </row>
-    <row r="130" spans="2:14">
+    <row r="130" spans="2:14" hidden="1">
       <c r="B130" s="26">
         <v>46105.378472222219</v>
       </c>
@@ -27734,7 +27720,7 @@
         <v>-6.4</v>
       </c>
     </row>
-    <row r="131" spans="2:14">
+    <row r="131" spans="2:14" hidden="1">
       <c r="B131" s="28">
         <v>46112</v>
       </c>
@@ -27777,7 +27763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="2:14">
+    <row r="132" spans="2:14" hidden="1">
       <c r="B132" s="26">
         <v>46122.414583333331</v>
       </c>
@@ -27819,7 +27805,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="133" spans="2:14">
+    <row r="133" spans="2:14" hidden="1">
       <c r="B133" s="26">
         <v>46122.421527777777</v>
       </c>
@@ -27861,7 +27847,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="134" spans="2:14">
+    <row r="134" spans="2:14" hidden="1">
       <c r="B134" s="26">
         <v>46122.427777777775</v>
       </c>
@@ -27903,7 +27889,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="135" spans="2:14">
+    <row r="135" spans="2:14" hidden="1">
       <c r="B135" s="26">
         <v>46122.438888888886</v>
       </c>
@@ -27945,7 +27931,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="136" spans="2:14">
+    <row r="136" spans="2:14" hidden="1">
       <c r="B136" s="28">
         <v>46125</v>
       </c>
@@ -27989,7 +27975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="2:14" ht="17" thickBot="1">
+    <row r="137" spans="2:14" ht="17" hidden="1" thickBot="1">
       <c r="B137" s="37">
         <v>46142</v>
       </c>
@@ -28143,6 +28129,13 @@
       <c r="I148" s="18"/>
     </row>
   </sheetData>
+  <autoFilter ref="B2:N137" xr:uid="{E174FB01-AC8B-4229-B319-63F7FF07E34C}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="6"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:N148">
     <sortCondition ref="B1:B148"/>
   </sortState>

--- a/Random-Forest-main/Random Forest Data.xlsx
+++ b/Random-Forest-main/Random Forest Data.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kyliealfaro/Desktop/PhD UHM/Modeling Project/Random-Forest-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CCA8776-0608-C142-9E08-999E3DFA4300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F750A539-E3FE-EA43-A43B-30E7AAA0850C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3940" yWindow="660" windowWidth="30200" windowHeight="21680" xr2:uid="{6AE4499B-BE9B-4430-8CBB-9E423EAAA4D3}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34480" windowHeight="21680" xr2:uid="{6AE4499B-BE9B-4430-8CBB-9E423EAAA4D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Combined Manoa Data" sheetId="1" r:id="rId1"/>
     <sheet name="Hailey's Data" sheetId="3" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Combined Manoa Data'!$B$2:$N$137</definedName>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="309">
   <si>
     <t>Date</t>
   </si>
@@ -1165,6 +1166,59 @@
   <si>
     <t>d-excess</t>
   </si>
+  <si>
+    <t>Groundwater δ18O</t>
+  </si>
+  <si>
+    <t>Rain δ2H</t>
+  </si>
+  <si>
+    <t>Groundwater δ2H</t>
+  </si>
+  <si>
+    <t>Date Collected</t>
+  </si>
+  <si>
+    <r>
+      <t>δ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>18O (‰)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>δ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>2H</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (‰)</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -1177,7 +1231,7 @@
     <numFmt numFmtId="167" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="168" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1378,20 +1432,15 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1592,7 +1641,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1820,31 +1869,45 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -22186,31 +22249,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E174FB01-AC8B-4229-B319-63F7FF07E34C}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="B1:N148"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <dimension ref="B1:X148"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" style="32"/>
+    <col min="1" max="1" width="8.6640625" style="32"/>
     <col min="2" max="2" width="13.83203125" style="32" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.5" style="32" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.5" style="32" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6" style="32" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" style="32" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.1640625" style="32" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.6640625" style="32" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.1640625" style="32" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.83203125" style="32" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17" style="18" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.6640625" style="32" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.83203125" style="32" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.6640625" style="18" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.83203125" style="32"/>
+    <col min="3" max="3" width="11.5" style="32" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" style="32" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5" style="32" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" style="32" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17" style="32" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.6640625" style="32" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.1640625" style="32" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.6640625" style="32" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22" style="18" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14" style="32" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.6640625" style="32" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.6640625" style="18" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.33203125" style="32" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5" style="32" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.33203125" style="32" bestFit="1" customWidth="1"/>
+    <col min="18" max="21" width="8.6640625" style="32"/>
+    <col min="22" max="22" width="11.5" style="32" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.33203125" style="32" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.83203125" style="32" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="8.6640625" style="32"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="17" thickBot="1">
+    <row r="1" spans="2:24" ht="17" thickBot="1">
       <c r="L1" s="18"/>
     </row>
-    <row r="2" spans="2:14">
+    <row r="2" spans="2:24">
       <c r="B2" s="22" t="s">
         <v>0</v>
       </c>
@@ -22247,11 +22316,23 @@
       <c r="M2" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="N2" s="36" t="s">
+      <c r="N2" s="20" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="3" spans="2:14" hidden="1">
+      <c r="O2" s="20" t="s">
+        <v>304</v>
+      </c>
+      <c r="P2" s="20" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q2" s="36" t="s">
+        <v>305</v>
+      </c>
+      <c r="V2" s="83"/>
+      <c r="W2" s="89"/>
+      <c r="X2" s="89"/>
+    </row>
+    <row r="3" spans="2:24">
       <c r="B3" s="23">
         <v>44970.399305555555</v>
       </c>
@@ -22290,11 +22371,23 @@
       <c r="M3" s="19">
         <v>7.7100600000000005E-2</v>
       </c>
-      <c r="N3" s="85">
-        <v>-2.4</v>
-      </c>
-    </row>
-    <row r="4" spans="2:14" hidden="1">
+      <c r="N3" s="95">
+        <v>-2.5</v>
+      </c>
+      <c r="O3" s="95">
+        <v>-7</v>
+      </c>
+      <c r="P3" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q3" s="92">
+        <v>-4.63</v>
+      </c>
+      <c r="V3" s="85"/>
+      <c r="W3" s="86"/>
+      <c r="X3" s="86"/>
+    </row>
+    <row r="4" spans="2:24">
       <c r="B4" s="23">
         <v>44970.429166666669</v>
       </c>
@@ -22333,11 +22426,23 @@
       <c r="M4" s="19">
         <v>0.12563849999999999</v>
       </c>
-      <c r="N4" s="85">
-        <v>-2.4</v>
-      </c>
-    </row>
-    <row r="5" spans="2:14">
+      <c r="N4" s="95">
+        <v>-2.5</v>
+      </c>
+      <c r="O4" s="95">
+        <v>-7</v>
+      </c>
+      <c r="P4" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q4" s="92">
+        <v>-4.63</v>
+      </c>
+      <c r="V4" s="87"/>
+      <c r="W4" s="88"/>
+      <c r="X4" s="88"/>
+    </row>
+    <row r="5" spans="2:24">
       <c r="B5" s="23">
         <v>44972.372916666667</v>
       </c>
@@ -22376,11 +22481,23 @@
       <c r="M5" s="19">
         <v>5.5910100000000004E-3</v>
       </c>
-      <c r="N5" s="86">
-        <v>-5.0999999999999996</v>
-      </c>
-    </row>
-    <row r="6" spans="2:14">
+      <c r="N5" s="95">
+        <v>-6</v>
+      </c>
+      <c r="O5" s="95">
+        <v>-37.1</v>
+      </c>
+      <c r="P5" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q5" s="92">
+        <v>-4.63</v>
+      </c>
+      <c r="V5" s="87"/>
+      <c r="W5" s="88"/>
+      <c r="X5" s="88"/>
+    </row>
+    <row r="6" spans="2:24">
       <c r="B6" s="23">
         <v>44972.397916666669</v>
       </c>
@@ -22419,11 +22536,23 @@
       <c r="M6" s="19">
         <v>5.5910100000000004E-3</v>
       </c>
-      <c r="N6" s="86">
-        <v>-5.0999999999999996</v>
-      </c>
-    </row>
-    <row r="7" spans="2:14" hidden="1">
+      <c r="N6" s="95">
+        <v>-6</v>
+      </c>
+      <c r="O6" s="95">
+        <v>-37.1</v>
+      </c>
+      <c r="P6" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q6" s="92">
+        <v>-4.63</v>
+      </c>
+      <c r="V6" s="87"/>
+      <c r="W6" s="88"/>
+      <c r="X6" s="88"/>
+    </row>
+    <row r="7" spans="2:24">
       <c r="B7" s="23">
         <v>44974.370833333334</v>
       </c>
@@ -22462,11 +22591,23 @@
       <c r="M7" s="19">
         <v>5.2366299999999999E-3</v>
       </c>
-      <c r="N7" s="85">
+      <c r="N7" s="95">
         <v>-6</v>
       </c>
-    </row>
-    <row r="8" spans="2:14" hidden="1">
+      <c r="O7" s="95">
+        <v>-37.1</v>
+      </c>
+      <c r="P7" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q7" s="92">
+        <v>-4.63</v>
+      </c>
+      <c r="V7" s="87"/>
+      <c r="W7" s="88"/>
+      <c r="X7" s="88"/>
+    </row>
+    <row r="8" spans="2:24">
       <c r="B8" s="23">
         <v>44974.385416666664</v>
       </c>
@@ -22505,11 +22646,23 @@
       <c r="M8" s="19">
         <v>5.2366299999999999E-3</v>
       </c>
-      <c r="N8" s="85">
+      <c r="N8" s="95">
         <v>-6</v>
       </c>
-    </row>
-    <row r="9" spans="2:14" hidden="1">
+      <c r="O8" s="95">
+        <v>-37.1</v>
+      </c>
+      <c r="P8" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q8" s="92">
+        <v>-4.63</v>
+      </c>
+      <c r="V8" s="87"/>
+      <c r="W8" s="88"/>
+      <c r="X8" s="88"/>
+    </row>
+    <row r="9" spans="2:24">
       <c r="B9" s="23">
         <v>44974.432638888888</v>
       </c>
@@ -22548,11 +22701,23 @@
       <c r="M9" s="19">
         <v>1.06991E-2</v>
       </c>
-      <c r="N9" s="85">
+      <c r="N9" s="95">
         <v>-6</v>
       </c>
-    </row>
-    <row r="10" spans="2:14" hidden="1">
+      <c r="O9" s="95">
+        <v>-37.1</v>
+      </c>
+      <c r="P9" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q9" s="92">
+        <v>-4.63</v>
+      </c>
+      <c r="V9" s="87"/>
+      <c r="W9" s="88"/>
+      <c r="X9" s="88"/>
+    </row>
+    <row r="10" spans="2:24">
       <c r="B10" s="23">
         <v>44977.37222222222</v>
       </c>
@@ -22591,11 +22756,23 @@
       <c r="M10" s="19">
         <v>0.240284</v>
       </c>
-      <c r="N10" s="86">
-        <v>-3.6</v>
-      </c>
-    </row>
-    <row r="11" spans="2:14" hidden="1">
+      <c r="N10" s="95">
+        <v>-6</v>
+      </c>
+      <c r="O10" s="95">
+        <v>-37.1</v>
+      </c>
+      <c r="P10" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q10" s="92">
+        <v>-4.63</v>
+      </c>
+      <c r="V10" s="87"/>
+      <c r="W10" s="88"/>
+      <c r="X10" s="88"/>
+    </row>
+    <row r="11" spans="2:24">
       <c r="B11" s="23">
         <v>44977.393055555556</v>
       </c>
@@ -22634,11 +22811,23 @@
       <c r="M11" s="19">
         <v>0.240284</v>
       </c>
-      <c r="N11" s="86">
-        <v>-3.6</v>
-      </c>
-    </row>
-    <row r="12" spans="2:14" hidden="1">
+      <c r="N11" s="95">
+        <v>-6</v>
+      </c>
+      <c r="O11" s="95">
+        <v>-37.1</v>
+      </c>
+      <c r="P11" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q11" s="92">
+        <v>-4.63</v>
+      </c>
+      <c r="V11" s="87"/>
+      <c r="W11" s="88"/>
+      <c r="X11" s="88"/>
+    </row>
+    <row r="12" spans="2:24">
       <c r="B12" s="23">
         <v>44977.43472222222</v>
       </c>
@@ -22677,11 +22866,23 @@
       <c r="M12" s="19">
         <v>3.06191E-2</v>
       </c>
-      <c r="N12" s="86">
-        <v>-3.6</v>
-      </c>
-    </row>
-    <row r="13" spans="2:14" hidden="1">
+      <c r="N12" s="95">
+        <v>-6</v>
+      </c>
+      <c r="O12" s="95">
+        <v>-37.1</v>
+      </c>
+      <c r="P12" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q12" s="92">
+        <v>-4.63</v>
+      </c>
+      <c r="V12" s="87"/>
+      <c r="W12" s="88"/>
+      <c r="X12" s="88"/>
+    </row>
+    <row r="13" spans="2:24">
       <c r="B13" s="23">
         <v>44977.448611111111</v>
       </c>
@@ -22720,11 +22921,23 @@
       <c r="M13" s="19">
         <v>7.7100600000000005E-2</v>
       </c>
-      <c r="N13" s="86">
-        <v>-3.6</v>
-      </c>
-    </row>
-    <row r="14" spans="2:14" hidden="1">
+      <c r="N13" s="95">
+        <v>-6</v>
+      </c>
+      <c r="O13" s="95">
+        <v>-37.1</v>
+      </c>
+      <c r="P13" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q13" s="92">
+        <v>-4.63</v>
+      </c>
+      <c r="V13" s="87"/>
+      <c r="W13" s="88"/>
+      <c r="X13" s="88"/>
+    </row>
+    <row r="14" spans="2:24">
       <c r="B14" s="23">
         <v>44979.367361111108</v>
       </c>
@@ -22763,11 +22976,23 @@
       <c r="M14" s="19">
         <v>9.4826599999999997E-2</v>
       </c>
-      <c r="N14" s="85">
-        <v>-3.8</v>
-      </c>
-    </row>
-    <row r="15" spans="2:14" hidden="1">
+      <c r="N14" s="95">
+        <v>-3.1</v>
+      </c>
+      <c r="O14" s="95">
+        <v>-13.6</v>
+      </c>
+      <c r="P14" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q14" s="92">
+        <v>-4.63</v>
+      </c>
+      <c r="V14" s="87"/>
+      <c r="W14" s="88"/>
+      <c r="X14" s="88"/>
+    </row>
+    <row r="15" spans="2:24">
       <c r="B15" s="23">
         <v>44979.385416666664</v>
       </c>
@@ -22806,11 +23031,23 @@
       <c r="M15" s="19">
         <v>3.24406E-2</v>
       </c>
-      <c r="N15" s="85">
-        <v>-3.8</v>
-      </c>
-    </row>
-    <row r="16" spans="2:14">
+      <c r="N15" s="95">
+        <v>-3.1</v>
+      </c>
+      <c r="O15" s="95">
+        <v>-13.6</v>
+      </c>
+      <c r="P15" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q15" s="92">
+        <v>-4.63</v>
+      </c>
+      <c r="V15" s="87"/>
+      <c r="W15" s="88"/>
+      <c r="X15" s="88"/>
+    </row>
+    <row r="16" spans="2:24">
       <c r="B16" s="23">
         <v>44979.541666666664</v>
       </c>
@@ -22849,11 +23086,23 @@
       <c r="M16" s="19">
         <v>2.33487E-2</v>
       </c>
-      <c r="N16" s="85">
-        <v>-3.8</v>
-      </c>
-    </row>
-    <row r="17" spans="2:14">
+      <c r="N16" s="95">
+        <v>-3.1</v>
+      </c>
+      <c r="O16" s="95">
+        <v>-13.6</v>
+      </c>
+      <c r="P16" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q16" s="92">
+        <v>-4.63</v>
+      </c>
+      <c r="V16" s="87"/>
+      <c r="W16" s="88"/>
+      <c r="X16" s="88"/>
+    </row>
+    <row r="17" spans="2:24">
       <c r="B17" s="23">
         <v>44979.5625</v>
       </c>
@@ -22892,11 +23141,23 @@
       <c r="M17" s="19">
         <v>2.33487E-2</v>
       </c>
-      <c r="N17" s="85">
-        <v>-3.8</v>
-      </c>
-    </row>
-    <row r="18" spans="2:14" hidden="1">
+      <c r="N17" s="95">
+        <v>-3.1</v>
+      </c>
+      <c r="O17" s="95">
+        <v>-13.6</v>
+      </c>
+      <c r="P17" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q17" s="92">
+        <v>-4.63</v>
+      </c>
+      <c r="V17" s="87"/>
+      <c r="W17" s="88"/>
+      <c r="X17" s="88"/>
+    </row>
+    <row r="18" spans="2:24">
       <c r="B18" s="23">
         <v>44981.361111111109</v>
       </c>
@@ -22935,11 +23196,23 @@
       <c r="M18" s="19">
         <v>2.23054E-2</v>
       </c>
-      <c r="N18" s="85">
+      <c r="N18" s="95">
         <v>-3.1</v>
       </c>
-    </row>
-    <row r="19" spans="2:14" hidden="1">
+      <c r="O18" s="95">
+        <v>-13.6</v>
+      </c>
+      <c r="P18" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q18" s="92">
+        <v>-4.63</v>
+      </c>
+      <c r="V18" s="87"/>
+      <c r="W18" s="88"/>
+      <c r="X18" s="88"/>
+    </row>
+    <row r="19" spans="2:24">
       <c r="B19" s="23">
         <v>44981.375</v>
       </c>
@@ -22978,11 +23251,23 @@
       <c r="M19" s="19">
         <v>2.23054E-2</v>
       </c>
-      <c r="N19" s="85">
+      <c r="N19" s="95">
         <v>-3.1</v>
       </c>
-    </row>
-    <row r="20" spans="2:14" hidden="1">
+      <c r="O19" s="95">
+        <v>-13.6</v>
+      </c>
+      <c r="P19" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q19" s="92">
+        <v>-4.63</v>
+      </c>
+      <c r="V19" s="87"/>
+      <c r="W19" s="88"/>
+      <c r="X19" s="88"/>
+    </row>
+    <row r="20" spans="2:24">
       <c r="B20" s="23">
         <v>44986.363888888889</v>
       </c>
@@ -23021,11 +23306,23 @@
       <c r="M20" s="19">
         <v>4.1506300000000003E-2</v>
       </c>
-      <c r="N20" s="86">
-        <v>-2.5</v>
-      </c>
-    </row>
-    <row r="21" spans="2:14" hidden="1">
+      <c r="N20" s="95">
+        <v>-3</v>
+      </c>
+      <c r="O20" s="95">
+        <v>-6.7</v>
+      </c>
+      <c r="P20" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q20" s="92">
+        <v>-4.63</v>
+      </c>
+      <c r="V20" s="87"/>
+      <c r="W20" s="88"/>
+      <c r="X20" s="88"/>
+    </row>
+    <row r="21" spans="2:24">
       <c r="B21" s="23">
         <v>44986.381944444445</v>
       </c>
@@ -23064,11 +23361,23 @@
       <c r="M21" s="19">
         <v>0.125691</v>
       </c>
-      <c r="N21" s="86">
-        <v>-2.5</v>
-      </c>
-    </row>
-    <row r="22" spans="2:14" hidden="1">
+      <c r="N21" s="95">
+        <v>-3</v>
+      </c>
+      <c r="O21" s="95">
+        <v>-6.7</v>
+      </c>
+      <c r="P21" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q21" s="92">
+        <v>-4.63</v>
+      </c>
+      <c r="V21" s="87"/>
+      <c r="W21" s="88"/>
+      <c r="X21" s="88"/>
+    </row>
+    <row r="22" spans="2:24">
       <c r="B22" s="23">
         <v>44986.401388888888</v>
       </c>
@@ -23107,11 +23416,23 @@
       <c r="M22" s="19">
         <v>3.8610800000000001E-2</v>
       </c>
-      <c r="N22" s="86">
-        <v>-2.5</v>
-      </c>
-    </row>
-    <row r="23" spans="2:14" hidden="1">
+      <c r="N22" s="95">
+        <v>-3</v>
+      </c>
+      <c r="O22" s="95">
+        <v>-6.7</v>
+      </c>
+      <c r="P22" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q22" s="92">
+        <v>-4.63</v>
+      </c>
+      <c r="V22" s="87"/>
+      <c r="W22" s="88"/>
+      <c r="X22" s="88"/>
+    </row>
+    <row r="23" spans="2:24">
       <c r="B23" s="23">
         <v>45019.381944444445</v>
       </c>
@@ -23150,11 +23471,23 @@
       <c r="M23" s="19">
         <v>2.2294899999999999E-2</v>
       </c>
-      <c r="N23" s="85">
-        <v>-3.7</v>
-      </c>
-    </row>
-    <row r="24" spans="2:14" hidden="1">
+      <c r="N23" s="95">
+        <v>-2.6</v>
+      </c>
+      <c r="O23" s="95">
+        <v>-6.1</v>
+      </c>
+      <c r="P23" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q23" s="92">
+        <v>-4.63</v>
+      </c>
+      <c r="V23" s="87"/>
+      <c r="W23" s="88"/>
+      <c r="X23" s="88"/>
+    </row>
+    <row r="24" spans="2:24">
       <c r="B24" s="23">
         <v>45019.401388888888</v>
       </c>
@@ -23193,11 +23526,23 @@
       <c r="M24" s="19">
         <v>5.8700500000000003E-2</v>
       </c>
-      <c r="N24" s="85">
-        <v>-3.7</v>
-      </c>
-    </row>
-    <row r="25" spans="2:14" hidden="1">
+      <c r="N24" s="95">
+        <v>-2.6</v>
+      </c>
+      <c r="O24" s="95">
+        <v>-6.1</v>
+      </c>
+      <c r="P24" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q24" s="92">
+        <v>-4.63</v>
+      </c>
+      <c r="V24" s="87"/>
+      <c r="W24" s="88"/>
+      <c r="X24" s="88"/>
+    </row>
+    <row r="25" spans="2:24">
       <c r="B25" s="23">
         <v>45028.354166666664</v>
       </c>
@@ -23236,11 +23581,23 @@
       <c r="M25" s="19">
         <v>4.6169500000000002E-2</v>
       </c>
-      <c r="N25" s="85">
+      <c r="N25" s="95">
         <v>-2.6</v>
       </c>
-    </row>
-    <row r="26" spans="2:14" hidden="1">
+      <c r="O25" s="95">
+        <v>-6.1</v>
+      </c>
+      <c r="P25" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q25" s="92">
+        <v>-4.63</v>
+      </c>
+      <c r="V25" s="87"/>
+      <c r="W25" s="88"/>
+      <c r="X25" s="88"/>
+    </row>
+    <row r="26" spans="2:24">
       <c r="B26" s="23">
         <v>45028.368750000001</v>
       </c>
@@ -23279,11 +23636,23 @@
       <c r="M26" s="19">
         <v>2.20571E-2</v>
       </c>
-      <c r="N26" s="85">
+      <c r="N26" s="95">
         <v>-2.6</v>
       </c>
-    </row>
-    <row r="27" spans="2:14">
+      <c r="O26" s="95">
+        <v>-6.1</v>
+      </c>
+      <c r="P26" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q26" s="92">
+        <v>-4.63</v>
+      </c>
+      <c r="V26" s="87"/>
+      <c r="W26" s="88"/>
+      <c r="X26" s="88"/>
+    </row>
+    <row r="27" spans="2:24">
       <c r="B27" s="23">
         <v>45030.337500000001</v>
       </c>
@@ -23322,11 +23691,23 @@
       <c r="M27" s="19">
         <v>1.02437E-2</v>
       </c>
-      <c r="N27" s="85">
+      <c r="N27" s="95">
         <v>-2.6</v>
       </c>
-    </row>
-    <row r="28" spans="2:14">
+      <c r="O27" s="95">
+        <v>-6.1</v>
+      </c>
+      <c r="P27" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q27" s="92">
+        <v>-4.63</v>
+      </c>
+      <c r="V27" s="87"/>
+      <c r="W27" s="88"/>
+      <c r="X27" s="88"/>
+    </row>
+    <row r="28" spans="2:24">
       <c r="B28" s="23">
         <v>45030.351388888892</v>
       </c>
@@ -23365,11 +23746,23 @@
       <c r="M28" s="19">
         <v>1.02437E-2</v>
       </c>
-      <c r="N28" s="85">
+      <c r="N28" s="95">
         <v>-2.6</v>
       </c>
-    </row>
-    <row r="29" spans="2:14" hidden="1">
+      <c r="O28" s="95">
+        <v>-6.1</v>
+      </c>
+      <c r="P28" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q28" s="92">
+        <v>-4.63</v>
+      </c>
+      <c r="V28" s="87"/>
+      <c r="W28" s="88"/>
+      <c r="X28" s="88"/>
+    </row>
+    <row r="29" spans="2:24">
       <c r="B29" s="23">
         <v>45033.361111111109</v>
       </c>
@@ -23408,11 +23801,23 @@
       <c r="M29" s="19">
         <v>9.4680600000000004E-3</v>
       </c>
-      <c r="N29" s="86">
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="30" spans="2:14" hidden="1">
+      <c r="N29" s="95">
+        <v>-2.6</v>
+      </c>
+      <c r="O29" s="95">
+        <v>-6.1</v>
+      </c>
+      <c r="P29" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q29" s="92">
+        <v>-4.63</v>
+      </c>
+      <c r="V29" s="87"/>
+      <c r="W29" s="88"/>
+      <c r="X29" s="88"/>
+    </row>
+    <row r="30" spans="2:24">
       <c r="B30" s="23">
         <v>45033.375</v>
       </c>
@@ -23451,11 +23856,23 @@
       <c r="M30" s="19">
         <v>9.4680600000000004E-3</v>
       </c>
-      <c r="N30" s="86">
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="31" spans="2:14" hidden="1">
+      <c r="N30" s="95">
+        <v>-2.6</v>
+      </c>
+      <c r="O30" s="95">
+        <v>-6.1</v>
+      </c>
+      <c r="P30" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q30" s="92">
+        <v>-4.63</v>
+      </c>
+      <c r="V30" s="87"/>
+      <c r="W30" s="88"/>
+      <c r="X30" s="88"/>
+    </row>
+    <row r="31" spans="2:24">
       <c r="B31" s="23">
         <v>45042.376388888886</v>
       </c>
@@ -23494,11 +23911,23 @@
       <c r="M31" s="19">
         <v>0.10097200000000001</v>
       </c>
-      <c r="N31" s="87">
-        <v>-1.9</v>
-      </c>
-    </row>
-    <row r="32" spans="2:14" hidden="1">
+      <c r="N31" s="95">
+        <v>-1.3</v>
+      </c>
+      <c r="O31" s="95">
+        <v>1.5</v>
+      </c>
+      <c r="P31" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q31" s="92">
+        <v>-4.63</v>
+      </c>
+      <c r="V31" s="87"/>
+      <c r="W31" s="88"/>
+      <c r="X31" s="88"/>
+    </row>
+    <row r="32" spans="2:24">
       <c r="B32" s="23">
         <v>45058.451388888891</v>
       </c>
@@ -23537,11 +23966,23 @@
       <c r="M32" s="19">
         <v>2.3722799999999999E-2</v>
       </c>
-      <c r="N32" s="87">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="33" spans="2:14" hidden="1">
+      <c r="N32" s="95">
+        <v>-1.8</v>
+      </c>
+      <c r="O32" s="95">
+        <v>-0.1</v>
+      </c>
+      <c r="P32" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q32" s="92">
+        <v>-4.63</v>
+      </c>
+      <c r="V32" s="87"/>
+      <c r="W32" s="88"/>
+      <c r="X32" s="88"/>
+    </row>
+    <row r="33" spans="2:24">
       <c r="B33" s="23">
         <v>45061.423611111109</v>
       </c>
@@ -23580,11 +24021,23 @@
       <c r="M33" s="19">
         <v>2.3722799999999999E-2</v>
       </c>
-      <c r="N33" s="87">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="34" spans="2:14">
+      <c r="N33" s="95">
+        <v>-1.8</v>
+      </c>
+      <c r="O33" s="95">
+        <v>-0.1</v>
+      </c>
+      <c r="P33" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q33" s="92">
+        <v>-4.63</v>
+      </c>
+      <c r="V33" s="87"/>
+      <c r="W33" s="88"/>
+      <c r="X33" s="88"/>
+    </row>
+    <row r="34" spans="2:24">
       <c r="B34" s="23">
         <v>45061.453472222223</v>
       </c>
@@ -23623,11 +24076,23 @@
       <c r="M34" s="19">
         <v>2.4759099999999999E-2</v>
       </c>
-      <c r="N34" s="87">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="35" spans="2:14">
+      <c r="N34" s="95">
+        <v>-1.8</v>
+      </c>
+      <c r="O34" s="95">
+        <v>-0.1</v>
+      </c>
+      <c r="P34" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q34" s="92">
+        <v>-4.63</v>
+      </c>
+      <c r="V34" s="87"/>
+      <c r="W34" s="88"/>
+      <c r="X34" s="88"/>
+    </row>
+    <row r="35" spans="2:24">
       <c r="B35" s="23">
         <v>45061.46875</v>
       </c>
@@ -23666,11 +24131,23 @@
       <c r="M35" s="19">
         <v>2.4759099999999999E-2</v>
       </c>
-      <c r="N35" s="87">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="36" spans="2:14" hidden="1">
+      <c r="N35" s="95">
+        <v>-1.8</v>
+      </c>
+      <c r="O35" s="95">
+        <v>-0.1</v>
+      </c>
+      <c r="P35" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q35" s="92">
+        <v>-4.63</v>
+      </c>
+      <c r="V35" s="87"/>
+      <c r="W35" s="88"/>
+      <c r="X35" s="88"/>
+    </row>
+    <row r="36" spans="2:24">
       <c r="B36" s="23">
         <v>45061.486111111109</v>
       </c>
@@ -23709,11 +24186,23 @@
       <c r="M36" s="19">
         <v>6.5966999999999998E-2</v>
       </c>
-      <c r="N36" s="87">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="37" spans="2:14" hidden="1">
+      <c r="N36" s="95">
+        <v>-1.8</v>
+      </c>
+      <c r="O36" s="95">
+        <v>-0.1</v>
+      </c>
+      <c r="P36" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q36" s="92">
+        <v>-4.63</v>
+      </c>
+      <c r="V36" s="87"/>
+      <c r="W36" s="88"/>
+      <c r="X36" s="88"/>
+    </row>
+    <row r="37" spans="2:24">
       <c r="B37" s="23">
         <v>45062.475694444445</v>
       </c>
@@ -23752,11 +24241,23 @@
       <c r="M37" s="19">
         <v>0.168964</v>
       </c>
-      <c r="N37" s="87">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="38" spans="2:14" hidden="1">
+      <c r="N37" s="95">
+        <v>-1.8</v>
+      </c>
+      <c r="O37" s="95">
+        <v>-0.1</v>
+      </c>
+      <c r="P37" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q37" s="92">
+        <v>-4.63</v>
+      </c>
+      <c r="V37" s="87"/>
+      <c r="W37" s="88"/>
+      <c r="X37" s="88"/>
+    </row>
+    <row r="38" spans="2:24">
       <c r="B38" s="23">
         <v>45062.489583333336</v>
       </c>
@@ -23795,11 +24296,23 @@
       <c r="M38" s="19">
         <v>6.5155400000000002E-2</v>
       </c>
-      <c r="N38" s="87">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="39" spans="2:14" hidden="1">
+      <c r="N38" s="95">
+        <v>-1.8</v>
+      </c>
+      <c r="O38" s="95">
+        <v>-0.1</v>
+      </c>
+      <c r="P38" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q38" s="92">
+        <v>-4.63</v>
+      </c>
+      <c r="V38" s="87"/>
+      <c r="W38" s="88"/>
+      <c r="X38" s="88"/>
+    </row>
+    <row r="39" spans="2:24">
       <c r="B39" s="23">
         <v>45062.53125</v>
       </c>
@@ -23838,11 +24351,23 @@
       <c r="M39" s="19">
         <v>0.22280800000000001</v>
       </c>
-      <c r="N39" s="87">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="40" spans="2:14" hidden="1">
+      <c r="N39" s="95">
+        <v>-1.8</v>
+      </c>
+      <c r="O39" s="95">
+        <v>-0.1</v>
+      </c>
+      <c r="P39" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q39" s="92">
+        <v>-4.63</v>
+      </c>
+      <c r="V39" s="87"/>
+      <c r="W39" s="88"/>
+      <c r="X39" s="88"/>
+    </row>
+    <row r="40" spans="2:24">
       <c r="B40" s="23">
         <v>45063.464583333334</v>
       </c>
@@ -23881,11 +24406,23 @@
       <c r="M40" s="19">
         <v>0.43688300000000002</v>
       </c>
-      <c r="N40" s="85">
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="41" spans="2:14" hidden="1">
+      <c r="N40" s="95">
+        <v>-1.8</v>
+      </c>
+      <c r="O40" s="95">
+        <v>-0.1</v>
+      </c>
+      <c r="P40" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q40" s="92">
+        <v>-4.63</v>
+      </c>
+      <c r="V40" s="87"/>
+      <c r="W40" s="88"/>
+      <c r="X40" s="88"/>
+    </row>
+    <row r="41" spans="2:24">
       <c r="B41" s="23">
         <v>45063.486111111109</v>
       </c>
@@ -23924,11 +24461,20 @@
       <c r="M41" s="19">
         <v>0.43688300000000002</v>
       </c>
-      <c r="N41" s="85">
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:14" hidden="1">
+      <c r="N41" s="95">
+        <v>-1.8</v>
+      </c>
+      <c r="O41" s="95">
+        <v>-0.1</v>
+      </c>
+      <c r="P41" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q41" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24">
       <c r="B42" s="23">
         <v>45077.625</v>
       </c>
@@ -23967,11 +24513,20 @@
       <c r="M42" s="19">
         <v>2.53764E-2</v>
       </c>
-      <c r="N42" s="85">
-        <v>-1.6</v>
-      </c>
-    </row>
-    <row r="43" spans="2:14" hidden="1">
+      <c r="N42" s="95">
+        <v>-1.7</v>
+      </c>
+      <c r="O42" s="95">
+        <v>0.1</v>
+      </c>
+      <c r="P42" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q42" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24">
       <c r="B43" s="23">
         <v>45077.635416666664</v>
       </c>
@@ -24010,11 +24565,20 @@
       <c r="M43" s="19">
         <v>2.53764E-2</v>
       </c>
-      <c r="N43" s="85">
-        <v>-1.6</v>
-      </c>
-    </row>
-    <row r="44" spans="2:14">
+      <c r="N43" s="95">
+        <v>-1.7</v>
+      </c>
+      <c r="O43" s="95">
+        <v>0.1</v>
+      </c>
+      <c r="P43" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q43" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24">
       <c r="B44" s="23">
         <v>45077.651388888888</v>
       </c>
@@ -24053,11 +24617,20 @@
       <c r="M44" s="19">
         <v>2.5610000000000001E-2</v>
       </c>
-      <c r="N44" s="85">
-        <v>-1.6</v>
-      </c>
-    </row>
-    <row r="45" spans="2:14">
+      <c r="N44" s="95">
+        <v>-1.7</v>
+      </c>
+      <c r="O44" s="95">
+        <v>0.1</v>
+      </c>
+      <c r="P44" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q44" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24">
       <c r="B45" s="23">
         <v>45078.604166666664</v>
       </c>
@@ -24096,11 +24669,20 @@
       <c r="M45" s="19">
         <v>2.0521899999999999E-2</v>
       </c>
-      <c r="N45" s="85">
+      <c r="N45" s="95">
         <v>-1.6</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" hidden="1">
+      <c r="O45" s="95">
+        <v>0.3</v>
+      </c>
+      <c r="P45" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q45" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24">
       <c r="B46" s="23">
         <v>45078.614583333336</v>
       </c>
@@ -24139,11 +24721,20 @@
       <c r="M46" s="19">
         <v>2.15534E-2</v>
       </c>
-      <c r="N46" s="85">
+      <c r="N46" s="95">
         <v>-1.6</v>
       </c>
-    </row>
-    <row r="47" spans="2:14" hidden="1">
+      <c r="O46" s="95">
+        <v>0.3</v>
+      </c>
+      <c r="P46" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q46" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24">
       <c r="B47" s="23">
         <v>45078.627083333333</v>
       </c>
@@ -24182,11 +24773,20 @@
       <c r="M47" s="19">
         <v>0.204565</v>
       </c>
-      <c r="N47" s="85">
+      <c r="N47" s="95">
         <v>-1.6</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" hidden="1">
+      <c r="O47" s="95">
+        <v>0.3</v>
+      </c>
+      <c r="P47" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q47" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24">
       <c r="B48" s="23">
         <v>45078.638194444444</v>
       </c>
@@ -24225,11 +24825,20 @@
       <c r="M48" s="19">
         <v>5.8530400000000003E-2</v>
       </c>
-      <c r="N48" s="85">
+      <c r="N48" s="95">
         <v>-1.6</v>
       </c>
-    </row>
-    <row r="49" spans="2:14" hidden="1">
+      <c r="O48" s="95">
+        <v>0.3</v>
+      </c>
+      <c r="P48" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q48" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="49" spans="2:17">
       <c r="B49" s="23">
         <v>45079.39166666667</v>
       </c>
@@ -24268,11 +24877,20 @@
       <c r="M49" s="19">
         <v>0.15256500000000001</v>
       </c>
-      <c r="N49" s="85">
+      <c r="N49" s="95">
         <v>-1.6</v>
       </c>
-    </row>
-    <row r="50" spans="2:14" hidden="1">
+      <c r="O49" s="95">
+        <v>0.3</v>
+      </c>
+      <c r="P49" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q49" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="50" spans="2:17">
       <c r="B50" s="23">
         <v>45079.416666666664</v>
       </c>
@@ -24311,11 +24929,20 @@
       <c r="M50" s="19">
         <v>0.31035499999999999</v>
       </c>
-      <c r="N50" s="88">
+      <c r="N50" s="95">
         <v>-1.6</v>
       </c>
-    </row>
-    <row r="51" spans="2:14" hidden="1">
+      <c r="O50" s="95">
+        <v>0.3</v>
+      </c>
+      <c r="P50" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q50" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="51" spans="2:17">
       <c r="B51" s="23">
         <v>45121.4375</v>
       </c>
@@ -24354,11 +24981,20 @@
       <c r="M51" s="19">
         <v>1.1124E-2</v>
       </c>
-      <c r="N51" s="85">
+      <c r="N51" s="95">
         <v>-1.7</v>
       </c>
-    </row>
-    <row r="52" spans="2:14" hidden="1">
+      <c r="O51" s="95">
+        <v>0.8</v>
+      </c>
+      <c r="P51" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q51" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="52" spans="2:17">
       <c r="B52" s="23">
         <v>45121.458333333336</v>
       </c>
@@ -24397,11 +25033,20 @@
       <c r="M52" s="19">
         <v>2.2708599999999999E-2</v>
       </c>
-      <c r="N52" s="85">
+      <c r="N52" s="95">
         <v>-1.7</v>
       </c>
-    </row>
-    <row r="53" spans="2:14">
+      <c r="O52" s="95">
+        <v>0.8</v>
+      </c>
+      <c r="P52" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q52" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="53" spans="2:17">
       <c r="B53" s="23">
         <v>45121.479166666664</v>
       </c>
@@ -24440,11 +25085,20 @@
       <c r="M53" s="19">
         <v>2.4175100000000001E-2</v>
       </c>
-      <c r="N53" s="85">
+      <c r="N53" s="95">
         <v>-1.7</v>
       </c>
-    </row>
-    <row r="54" spans="2:14" hidden="1">
+      <c r="O53" s="95">
+        <v>0.8</v>
+      </c>
+      <c r="P53" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q53" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="54" spans="2:17">
       <c r="B54" s="23">
         <v>45124.368055555555</v>
       </c>
@@ -24483,11 +25137,20 @@
       <c r="M54" s="19">
         <v>7.0259600000000005E-2</v>
       </c>
-      <c r="N54" s="85">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="55" spans="2:14" hidden="1">
+      <c r="N54" s="95">
+        <v>-1.7</v>
+      </c>
+      <c r="O54" s="95">
+        <v>0.8</v>
+      </c>
+      <c r="P54" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q54" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="55" spans="2:17">
       <c r="B55" s="23">
         <v>45124.375</v>
       </c>
@@ -24526,11 +25189,20 @@
       <c r="M55" s="19">
         <v>0.241475</v>
       </c>
-      <c r="N55" s="85">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="56" spans="2:14" hidden="1">
+      <c r="N55" s="95">
+        <v>-1.7</v>
+      </c>
+      <c r="O55" s="95">
+        <v>0.8</v>
+      </c>
+      <c r="P55" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q55" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="56" spans="2:17">
       <c r="B56" s="23">
         <v>45124.386805555558</v>
       </c>
@@ -24569,11 +25241,20 @@
       <c r="M56" s="19">
         <v>7.2402599999999998E-2</v>
       </c>
-      <c r="N56" s="85">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="57" spans="2:14">
+      <c r="N56" s="95">
+        <v>-1.7</v>
+      </c>
+      <c r="O56" s="95">
+        <v>0.8</v>
+      </c>
+      <c r="P56" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q56" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="57" spans="2:17">
       <c r="B57" s="23">
         <v>45124.40625</v>
       </c>
@@ -24612,11 +25293,20 @@
       <c r="M57" s="19">
         <v>2.4175100000000001E-2</v>
       </c>
-      <c r="N57" s="85">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="58" spans="2:14" hidden="1">
+      <c r="N57" s="95">
+        <v>-1.7</v>
+      </c>
+      <c r="O57" s="95">
+        <v>0.8</v>
+      </c>
+      <c r="P57" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q57" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="58" spans="2:17">
       <c r="B58" s="23">
         <v>45125.416666666664</v>
       </c>
@@ -24655,11 +25345,20 @@
       <c r="M58" s="19">
         <v>0.38312099999999999</v>
       </c>
-      <c r="N58" s="85">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="59" spans="2:14" hidden="1">
+      <c r="N58" s="95">
+        <v>-1.3</v>
+      </c>
+      <c r="O58" s="95">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="P58" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q58" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="59" spans="2:17">
       <c r="B59" s="23">
         <v>45125.447916666664</v>
       </c>
@@ -24698,11 +25397,20 @@
       <c r="M59" s="19">
         <v>0.18023800000000001</v>
       </c>
-      <c r="N59" s="85">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="60" spans="2:14" hidden="1">
+      <c r="N59" s="95">
+        <v>-1.3</v>
+      </c>
+      <c r="O59" s="95">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="P59" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q59" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="60" spans="2:17">
       <c r="B60" s="23">
         <v>45152.606249999997</v>
       </c>
@@ -24741,11 +25449,20 @@
       <c r="M60" s="19">
         <v>2.5429199999999999E-2</v>
       </c>
-      <c r="N60" s="85">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="61" spans="2:14" hidden="1">
+      <c r="N60" s="95">
+        <v>-1.4</v>
+      </c>
+      <c r="O60" s="95">
+        <v>-1.3</v>
+      </c>
+      <c r="P60" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q60" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="61" spans="2:17">
       <c r="B61" s="23">
         <v>45152.62222222222</v>
       </c>
@@ -24784,11 +25501,20 @@
       <c r="M61" s="19">
         <v>2.5429199999999999E-2</v>
       </c>
-      <c r="N61" s="85">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="62" spans="2:14">
+      <c r="N61" s="95">
+        <v>-1.4</v>
+      </c>
+      <c r="O61" s="95">
+        <v>-1.3</v>
+      </c>
+      <c r="P61" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q61" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="62" spans="2:17">
       <c r="B62" s="23">
         <v>45152.642361111109</v>
       </c>
@@ -24827,11 +25553,20 @@
       <c r="M62" s="19">
         <v>2.5932400000000001E-2</v>
       </c>
-      <c r="N62" s="85">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="63" spans="2:14" hidden="1">
+      <c r="N62" s="95">
+        <v>-1.4</v>
+      </c>
+      <c r="O62" s="95">
+        <v>-1.3</v>
+      </c>
+      <c r="P62" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q62" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="63" spans="2:17">
       <c r="B63" s="23">
         <v>45153.461805555555</v>
       </c>
@@ -24870,11 +25605,20 @@
       <c r="M63" s="19">
         <v>7.2691500000000006E-2</v>
       </c>
-      <c r="N63" s="85">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="64" spans="2:14" hidden="1">
+      <c r="N63" s="95">
+        <v>-1.4</v>
+      </c>
+      <c r="O63" s="95">
+        <v>-1.3</v>
+      </c>
+      <c r="P63" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q63" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="64" spans="2:17">
       <c r="B64" s="23">
         <v>45153.475694444445</v>
       </c>
@@ -24913,11 +25657,20 @@
       <c r="M64" s="19">
         <v>0.24707599999999999</v>
       </c>
-      <c r="N64" s="85">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="65" spans="2:14" hidden="1">
+      <c r="N64" s="95">
+        <v>-1.4</v>
+      </c>
+      <c r="O64" s="95">
+        <v>-1.3</v>
+      </c>
+      <c r="P64" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q64" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17">
       <c r="B65" s="23">
         <v>45153.489583333336</v>
       </c>
@@ -24956,11 +25709,20 @@
       <c r="M65" s="19">
         <v>7.4904600000000002E-2</v>
       </c>
-      <c r="N65" s="85">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="66" spans="2:14">
+      <c r="N65" s="95">
+        <v>-1.4</v>
+      </c>
+      <c r="O65" s="95">
+        <v>-1.3</v>
+      </c>
+      <c r="P65" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q65" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17">
       <c r="B66" s="23">
         <v>45153.504166666666</v>
       </c>
@@ -24999,11 +25761,20 @@
       <c r="M66" s="19">
         <v>2.6713500000000001E-2</v>
       </c>
-      <c r="N66" s="85">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="67" spans="2:14" hidden="1">
+      <c r="N66" s="95">
+        <v>-1.4</v>
+      </c>
+      <c r="O66" s="95">
+        <v>-1.3</v>
+      </c>
+      <c r="P66" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q66" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17">
       <c r="B67" s="23">
         <v>45154.555555555555</v>
       </c>
@@ -25042,11 +25813,20 @@
       <c r="M67" s="19">
         <v>0.48380299999999998</v>
       </c>
-      <c r="N67" s="85">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="68" spans="2:14" hidden="1">
+      <c r="N67" s="95">
+        <v>-1.4</v>
+      </c>
+      <c r="O67" s="95">
+        <v>-1.3</v>
+      </c>
+      <c r="P67" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q67" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="68" spans="2:17">
       <c r="B68" s="23">
         <v>45154.579861111109</v>
       </c>
@@ -25085,11 +25865,20 @@
       <c r="M68" s="19">
         <v>0.21172099999999999</v>
       </c>
-      <c r="N68" s="85">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="69" spans="2:14" hidden="1">
+      <c r="N68" s="95">
+        <v>-1.4</v>
+      </c>
+      <c r="O68" s="95">
+        <v>-1.3</v>
+      </c>
+      <c r="P68" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q68" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17">
       <c r="B69" s="23">
         <v>45175.631944444445</v>
       </c>
@@ -25128,11 +25917,20 @@
       <c r="M69" s="19">
         <v>2.4729299999999999E-2</v>
       </c>
-      <c r="N69" s="85">
+      <c r="N69" s="95">
         <v>-1.7</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" hidden="1">
+      <c r="O69" s="95">
+        <v>1.2</v>
+      </c>
+      <c r="P69" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q69" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17">
       <c r="B70" s="23">
         <v>45176.5625</v>
       </c>
@@ -25171,11 +25969,20 @@
       <c r="M70" s="19">
         <v>2.6636799999999999E-2</v>
       </c>
-      <c r="N70" s="85">
+      <c r="N70" s="95">
         <v>-1.7</v>
       </c>
-    </row>
-    <row r="71" spans="2:14">
+      <c r="O70" s="95">
+        <v>1.2</v>
+      </c>
+      <c r="P70" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q70" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17">
       <c r="B71" s="23">
         <v>45176.584722222222</v>
       </c>
@@ -25214,11 +26021,20 @@
       <c r="M71" s="19">
         <v>2.8300100000000002E-2</v>
       </c>
-      <c r="N71" s="85">
+      <c r="N71" s="95">
         <v>-1.7</v>
       </c>
-    </row>
-    <row r="72" spans="2:14">
+      <c r="O71" s="95">
+        <v>1.2</v>
+      </c>
+      <c r="P71" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q71" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17">
       <c r="B72" s="23">
         <v>45177.453472222223</v>
       </c>
@@ -25257,11 +26073,20 @@
       <c r="M72" s="19">
         <v>2.35642E-2</v>
       </c>
-      <c r="N72" s="85">
+      <c r="N72" s="95">
         <v>-1.7</v>
       </c>
-    </row>
-    <row r="73" spans="2:14" hidden="1">
+      <c r="O72" s="95">
+        <v>1.2</v>
+      </c>
+      <c r="P72" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q72" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17">
       <c r="B73" s="23">
         <v>45183.577777777777</v>
       </c>
@@ -25300,11 +26125,20 @@
       <c r="M73" s="19">
         <v>0.30014400000000002</v>
       </c>
-      <c r="N73" s="85">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="74" spans="2:14" hidden="1">
+      <c r="N73" s="95">
+        <v>-2.1</v>
+      </c>
+      <c r="O73" s="95">
+        <v>-6.9</v>
+      </c>
+      <c r="P73" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q73" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17">
       <c r="B74" s="23">
         <v>45183.59375</v>
       </c>
@@ -25343,11 +26177,20 @@
       <c r="M74" s="19">
         <v>7.8997700000000004E-2</v>
       </c>
-      <c r="N74" s="85">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="75" spans="2:14" hidden="1">
+      <c r="N74" s="95">
+        <v>-2.1</v>
+      </c>
+      <c r="O74" s="95">
+        <v>-6.9</v>
+      </c>
+      <c r="P74" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q74" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17">
       <c r="B75" s="23">
         <v>45187.458333333336</v>
       </c>
@@ -25386,11 +26229,20 @@
       <c r="M75" s="19">
         <v>0.20494799999999999</v>
       </c>
-      <c r="N75" s="85">
+      <c r="N75" s="95">
         <v>-2.1</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" hidden="1">
+      <c r="O75" s="95">
+        <v>-6.9</v>
+      </c>
+      <c r="P75" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q75" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17">
       <c r="B76" s="23">
         <v>45187.474999999999</v>
       </c>
@@ -25429,11 +26281,20 @@
       <c r="M76" s="19">
         <v>8.1607600000000002E-2</v>
       </c>
-      <c r="N76" s="85">
+      <c r="N76" s="95">
         <v>-2.1</v>
       </c>
-    </row>
-    <row r="77" spans="2:14" hidden="1">
+      <c r="O76" s="95">
+        <v>-6.9</v>
+      </c>
+      <c r="P76" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q76" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17">
       <c r="B77" s="23">
         <v>45187.486805555556</v>
       </c>
@@ -25472,11 +26333,20 @@
       <c r="M77" s="19">
         <v>0.43432599999999999</v>
       </c>
-      <c r="N77" s="85">
+      <c r="N77" s="95">
         <v>-2.1</v>
       </c>
-    </row>
-    <row r="78" spans="2:14" hidden="1">
+      <c r="O77" s="95">
+        <v>-6.9</v>
+      </c>
+      <c r="P77" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q77" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="78" spans="2:17">
       <c r="B78" s="23">
         <v>45238.506944444445</v>
       </c>
@@ -25515,11 +26385,20 @@
       <c r="M78" s="19">
         <v>2.214E-2</v>
       </c>
-      <c r="N78" s="85">
+      <c r="N78" s="95">
         <v>-1.5</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" hidden="1">
+      <c r="O78" s="95">
+        <v>1.9</v>
+      </c>
+      <c r="P78" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q78" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17">
       <c r="B79" s="23">
         <v>45238.524305555555</v>
       </c>
@@ -25558,11 +26437,20 @@
       <c r="M79" s="19">
         <v>2.214E-2</v>
       </c>
-      <c r="N79" s="85">
+      <c r="N79" s="95">
         <v>-1.5</v>
       </c>
-    </row>
-    <row r="80" spans="2:14" hidden="1">
+      <c r="O79" s="95">
+        <v>1.9</v>
+      </c>
+      <c r="P79" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q79" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="80" spans="2:17">
       <c r="B80" s="23">
         <v>45238.546527777777</v>
       </c>
@@ -25601,11 +26489,20 @@
       <c r="M80" s="19">
         <v>7.3910299999999998E-2</v>
       </c>
-      <c r="N80" s="85">
+      <c r="N80" s="95">
         <v>-1.5</v>
       </c>
-    </row>
-    <row r="81" spans="2:14">
+      <c r="O80" s="95">
+        <v>1.9</v>
+      </c>
+      <c r="P80" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q80" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="81" spans="2:17">
       <c r="B81" s="23">
         <v>45239.548611111109</v>
       </c>
@@ -25644,11 +26541,20 @@
       <c r="M81" s="19">
         <v>2.4210300000000001E-2</v>
       </c>
-      <c r="N81" s="85">
+      <c r="N81" s="95">
         <v>-1.5</v>
       </c>
-    </row>
-    <row r="82" spans="2:14">
+      <c r="O81" s="95">
+        <v>1.9</v>
+      </c>
+      <c r="P81" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q81" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="82" spans="2:17">
       <c r="B82" s="23">
         <v>45239.577777777777</v>
       </c>
@@ -25687,11 +26593,20 @@
       <c r="M82" s="19">
         <v>2.4210300000000001E-2</v>
       </c>
-      <c r="N82" s="85">
+      <c r="N82" s="95">
         <v>-1.5</v>
       </c>
-    </row>
-    <row r="83" spans="2:14" hidden="1">
+      <c r="O82" s="95">
+        <v>1.9</v>
+      </c>
+      <c r="P82" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q82" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="83" spans="2:17">
       <c r="B83" s="23">
         <v>45240.433333333334</v>
       </c>
@@ -25730,11 +26645,20 @@
       <c r="M83" s="19">
         <v>0.26539000000000001</v>
       </c>
-      <c r="N83" s="85">
+      <c r="N83" s="95">
         <v>-1.5</v>
       </c>
-    </row>
-    <row r="84" spans="2:14" hidden="1">
+      <c r="O83" s="95">
+        <v>1.9</v>
+      </c>
+      <c r="P83" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q83" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="84" spans="2:17">
       <c r="B84" s="23">
         <v>45240.462500000001</v>
       </c>
@@ -25773,11 +26697,20 @@
       <c r="M84" s="19">
         <v>0.16953599999999999</v>
       </c>
-      <c r="N84" s="85">
+      <c r="N84" s="95">
         <v>-1.5</v>
       </c>
-    </row>
-    <row r="85" spans="2:14" hidden="1">
+      <c r="O84" s="95">
+        <v>1.9</v>
+      </c>
+      <c r="P84" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q84" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="85" spans="2:17">
       <c r="B85" s="23">
         <v>45240.481944444444</v>
       </c>
@@ -25816,11 +26749,20 @@
       <c r="M85" s="19">
         <v>6.7313200000000004E-2</v>
       </c>
-      <c r="N85" s="85">
+      <c r="N85" s="95">
         <v>-1.5</v>
       </c>
-    </row>
-    <row r="86" spans="2:14" hidden="1">
+      <c r="O85" s="95">
+        <v>1.9</v>
+      </c>
+      <c r="P85" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q85" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="86" spans="2:17">
       <c r="B86" s="23">
         <v>45240.5</v>
       </c>
@@ -25859,11 +26801,20 @@
       <c r="M86" s="19">
         <v>0.20750399999999999</v>
       </c>
-      <c r="N86" s="85">
+      <c r="N86" s="95">
         <v>-1.5</v>
       </c>
-    </row>
-    <row r="87" spans="2:14" hidden="1">
+      <c r="O86" s="95">
+        <v>1.9</v>
+      </c>
+      <c r="P86" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q86" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="87" spans="2:17">
       <c r="B87" s="23">
         <v>45259.463194444441</v>
       </c>
@@ -25902,11 +26853,20 @@
       <c r="M87" s="19">
         <v>2.0970800000000001E-2</v>
       </c>
-      <c r="N87" s="85">
-        <v>-2.8</v>
-      </c>
-    </row>
-    <row r="88" spans="2:14" hidden="1">
+      <c r="N87" s="95">
+        <v>0</v>
+      </c>
+      <c r="O87" s="95">
+        <v>6.1</v>
+      </c>
+      <c r="P87" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q87" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="88" spans="2:17">
       <c r="B88" s="23">
         <v>45260.520833333336</v>
       </c>
@@ -25945,11 +26905,20 @@
       <c r="M88" s="19">
         <v>2.214E-2</v>
       </c>
-      <c r="N88" s="85">
-        <v>-2.8</v>
-      </c>
-    </row>
-    <row r="89" spans="2:14">
+      <c r="N88" s="95">
+        <v>0</v>
+      </c>
+      <c r="O88" s="95">
+        <v>6.1</v>
+      </c>
+      <c r="P88" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q88" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="89" spans="2:17">
       <c r="B89" s="23">
         <v>45260.541666666664</v>
       </c>
@@ -25988,11 +26957,20 @@
       <c r="M89" s="19">
         <v>2.4210300000000001E-2</v>
       </c>
-      <c r="N89" s="85">
-        <v>-2.8</v>
-      </c>
-    </row>
-    <row r="90" spans="2:14">
+      <c r="N89" s="95">
+        <v>0</v>
+      </c>
+      <c r="O89" s="95">
+        <v>6.1</v>
+      </c>
+      <c r="P89" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q89" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="90" spans="2:17">
       <c r="B90" s="23">
         <v>45260.5625</v>
       </c>
@@ -26031,11 +27009,20 @@
       <c r="M90" s="19">
         <v>2.4210300000000001E-2</v>
       </c>
-      <c r="N90" s="85">
-        <v>-2.8</v>
-      </c>
-    </row>
-    <row r="91" spans="2:14" hidden="1">
+      <c r="N90" s="95">
+        <v>0</v>
+      </c>
+      <c r="O90" s="95">
+        <v>6.1</v>
+      </c>
+      <c r="P90" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q90" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="91" spans="2:17">
       <c r="B91" s="23">
         <v>45260.590277777781</v>
       </c>
@@ -26074,11 +27061,20 @@
       <c r="M91" s="19">
         <v>6.63469E-2</v>
       </c>
-      <c r="N91" s="85">
-        <v>-2.8</v>
-      </c>
-    </row>
-    <row r="92" spans="2:14" hidden="1">
+      <c r="N91" s="95">
+        <v>0</v>
+      </c>
+      <c r="O91" s="95">
+        <v>6.1</v>
+      </c>
+      <c r="P91" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q91" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="92" spans="2:17">
       <c r="B92" s="23">
         <v>45261.4375</v>
       </c>
@@ -26117,11 +27113,20 @@
       <c r="M92" s="19">
         <v>4.94799E-2</v>
       </c>
-      <c r="N92" s="85">
-        <v>-2.8</v>
-      </c>
-    </row>
-    <row r="93" spans="2:14" hidden="1">
+      <c r="N92" s="95">
+        <v>0</v>
+      </c>
+      <c r="O92" s="95">
+        <v>6.1</v>
+      </c>
+      <c r="P92" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q92" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="93" spans="2:17">
       <c r="B93" s="23">
         <v>45261.45208333333</v>
       </c>
@@ -26160,11 +27165,20 @@
       <c r="M93" s="19">
         <v>0.12698300000000001</v>
       </c>
-      <c r="N93" s="85">
-        <v>-2.8</v>
-      </c>
-    </row>
-    <row r="94" spans="2:14" hidden="1">
+      <c r="N93" s="95">
+        <v>0</v>
+      </c>
+      <c r="O93" s="95">
+        <v>6.1</v>
+      </c>
+      <c r="P93" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q93" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="94" spans="2:17">
       <c r="B94" s="23">
         <v>45266.4375</v>
       </c>
@@ -26203,11 +27217,20 @@
       <c r="M94" s="19">
         <v>0.22950799999999999</v>
       </c>
-      <c r="N94" s="85">
+      <c r="N94" s="95">
         <v>-4.5999999999999996</v>
       </c>
-    </row>
-    <row r="95" spans="2:14" hidden="1">
+      <c r="O94" s="95">
+        <v>-25.2</v>
+      </c>
+      <c r="P94" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q94" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="95" spans="2:17">
       <c r="B95" s="23">
         <v>45266.468055555553</v>
       </c>
@@ -26246,11 +27269,20 @@
       <c r="M95" s="19">
         <v>0.210845</v>
       </c>
-      <c r="N95" s="85">
+      <c r="N95" s="95">
         <v>-4.5999999999999996</v>
       </c>
-    </row>
-    <row r="96" spans="2:14" hidden="1">
+      <c r="O95" s="95">
+        <v>-25.2</v>
+      </c>
+      <c r="P95" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q95" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="96" spans="2:17">
       <c r="B96" s="23">
         <v>45344.600694444445</v>
       </c>
@@ -26289,9 +27321,16 @@
       <c r="M96" s="19">
         <v>0.397368</v>
       </c>
-      <c r="N96" s="81"/>
-    </row>
-    <row r="97" spans="2:14" hidden="1">
+      <c r="N96" s="19"/>
+      <c r="O96" s="91"/>
+      <c r="P96" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q96" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="97" spans="2:17">
       <c r="B97" s="23">
         <v>45344.640277777777</v>
       </c>
@@ -26330,9 +27369,16 @@
       <c r="M97" s="19">
         <v>0.15940199999999999</v>
       </c>
-      <c r="N97" s="81"/>
-    </row>
-    <row r="98" spans="2:14" hidden="1">
+      <c r="N97" s="19"/>
+      <c r="O97" s="91"/>
+      <c r="P97" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q97" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="98" spans="2:17">
       <c r="B98" s="23">
         <v>45344.663888888892</v>
       </c>
@@ -26371,9 +27417,16 @@
       <c r="M98" s="19">
         <v>5.8161600000000001E-2</v>
       </c>
-      <c r="N98" s="81"/>
-    </row>
-    <row r="99" spans="2:14" hidden="1">
+      <c r="N98" s="19"/>
+      <c r="O98" s="91"/>
+      <c r="P98" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q98" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="99" spans="2:17">
       <c r="B99" s="23">
         <v>45344.681250000001</v>
       </c>
@@ -26412,9 +27465,16 @@
       <c r="M99" s="19">
         <v>0.16870099999999999</v>
       </c>
-      <c r="N99" s="81"/>
-    </row>
-    <row r="100" spans="2:14">
+      <c r="N99" s="19"/>
+      <c r="O99" s="91"/>
+      <c r="P99" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q99" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="100" spans="2:17">
       <c r="B100" s="23">
         <v>45345.380555555559</v>
       </c>
@@ -26453,9 +27513,16 @@
       <c r="M100" s="19">
         <v>5.5910100000000004E-3</v>
       </c>
-      <c r="N100" s="81"/>
-    </row>
-    <row r="101" spans="2:14">
+      <c r="N100" s="19"/>
+      <c r="O100" s="91"/>
+      <c r="P100" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q100" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="101" spans="2:17">
       <c r="B101" s="23">
         <v>45345.411111111112</v>
       </c>
@@ -26494,9 +27561,16 @@
       <c r="M101" s="19">
         <v>5.5910100000000004E-3</v>
       </c>
-      <c r="N101" s="81"/>
-    </row>
-    <row r="102" spans="2:14" hidden="1">
+      <c r="N101" s="19"/>
+      <c r="O101" s="91"/>
+      <c r="P101" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q101" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="102" spans="2:17">
       <c r="B102" s="23">
         <v>45351.558333333334</v>
       </c>
@@ -26535,9 +27609,16 @@
       <c r="M102" s="19">
         <v>2.23054E-2</v>
       </c>
-      <c r="N102" s="81"/>
-    </row>
-    <row r="103" spans="2:14" hidden="1">
+      <c r="N102" s="19"/>
+      <c r="O102" s="91"/>
+      <c r="P102" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q102" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="103" spans="2:17">
       <c r="B103" s="23">
         <v>45351.579861111109</v>
       </c>
@@ -26576,9 +27657,16 @@
       <c r="M103" s="19">
         <v>2.23054E-2</v>
       </c>
-      <c r="N103" s="81"/>
-    </row>
-    <row r="104" spans="2:14" hidden="1">
+      <c r="N103" s="19"/>
+      <c r="O103" s="91"/>
+      <c r="P103" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q103" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="104" spans="2:17">
       <c r="B104" s="23">
         <v>45351.611805555556</v>
       </c>
@@ -26617,9 +27705,16 @@
       <c r="M104" s="19">
         <v>6.6970399999999999E-2</v>
       </c>
-      <c r="N104" s="81"/>
-    </row>
-    <row r="105" spans="2:14" hidden="1">
+      <c r="N104" s="19"/>
+      <c r="O104" s="91"/>
+      <c r="P104" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q104" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="105" spans="2:17">
       <c r="B105" s="26">
         <v>46001.361111111109</v>
       </c>
@@ -26657,11 +27752,16 @@
       <c r="M105" s="19">
         <v>1.11231E-2</v>
       </c>
-      <c r="N105" s="83">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="106" spans="2:14" hidden="1">
+      <c r="N105" s="29"/>
+      <c r="O105" s="29"/>
+      <c r="P105" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q105" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="106" spans="2:17">
       <c r="B106" s="26">
         <v>46001.409722222219</v>
       </c>
@@ -26699,11 +27799,16 @@
       <c r="M106" s="19">
         <v>9.0940699999999999E-2</v>
       </c>
-      <c r="N106" s="83">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="107" spans="2:14" hidden="1">
+      <c r="N106" s="29"/>
+      <c r="O106" s="29"/>
+      <c r="P106" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q106" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="107" spans="2:17">
       <c r="B107" s="26">
         <v>46001.473611111112</v>
       </c>
@@ -26741,11 +27846,16 @@
       <c r="M107" s="19">
         <v>0.30540699999999998</v>
       </c>
-      <c r="N107" s="83">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="108" spans="2:14" hidden="1">
+      <c r="N107" s="29"/>
+      <c r="O107" s="29"/>
+      <c r="P107" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q107" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="108" spans="2:17">
       <c r="B108" s="26">
         <v>46001.510416666664</v>
       </c>
@@ -26783,11 +27893,16 @@
       <c r="M108" s="19">
         <v>0.16201399999999999</v>
       </c>
-      <c r="N108" s="83">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="109" spans="2:14" hidden="1">
+      <c r="N108" s="29"/>
+      <c r="O108" s="29"/>
+      <c r="P108" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q108" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="109" spans="2:17">
       <c r="B109" s="26">
         <v>46001.536111111112</v>
       </c>
@@ -26825,11 +27940,16 @@
       <c r="M109" s="19">
         <v>6.0341499999999999E-2</v>
       </c>
-      <c r="N109" s="83">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="110" spans="2:14">
+      <c r="N109" s="29"/>
+      <c r="O109" s="29"/>
+      <c r="P109" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q109" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="110" spans="2:17">
       <c r="B110" s="26">
         <v>46001.600694444445</v>
       </c>
@@ -26867,11 +27987,16 @@
       <c r="M110" s="19">
         <v>2.1567300000000001E-2</v>
       </c>
-      <c r="N110" s="83">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="111" spans="2:14" hidden="1">
+      <c r="N110" s="29"/>
+      <c r="O110" s="29"/>
+      <c r="P110" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q110" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="111" spans="2:17">
       <c r="B111" s="28">
         <v>46002</v>
       </c>
@@ -26904,17 +28029,22 @@
       <c r="K111" s="19">
         <v>11.683999999999999</v>
       </c>
-      <c r="L111" s="19">
-        <v>0</v>
-      </c>
-      <c r="M111" s="19">
-        <v>0</v>
-      </c>
-      <c r="N111" s="81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="2:14" hidden="1">
+      <c r="L111" s="19"/>
+      <c r="M111" s="19"/>
+      <c r="N111" s="29">
+        <v>-1.4</v>
+      </c>
+      <c r="O111" s="29">
+        <v>4</v>
+      </c>
+      <c r="P111" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q111" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="112" spans="2:17">
       <c r="B112" s="28">
         <v>46002</v>
       </c>
@@ -26947,17 +28077,22 @@
       <c r="K112" s="19">
         <v>11.683999999999999</v>
       </c>
-      <c r="L112" s="19">
-        <v>0</v>
-      </c>
-      <c r="M112" s="19">
-        <v>0</v>
-      </c>
-      <c r="N112" s="81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="2:14" hidden="1">
+      <c r="L112" s="19"/>
+      <c r="M112" s="19"/>
+      <c r="N112" s="29">
+        <v>-1.4</v>
+      </c>
+      <c r="O112" s="29">
+        <v>4.2</v>
+      </c>
+      <c r="P112" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q112" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="113" spans="2:17">
       <c r="B113" s="26">
         <v>46002.395833333336</v>
       </c>
@@ -26995,11 +28130,16 @@
       <c r="M113" s="19">
         <v>3.27912E-2</v>
       </c>
-      <c r="N113" s="83">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="114" spans="2:14" hidden="1">
+      <c r="N113" s="29"/>
+      <c r="O113" s="91"/>
+      <c r="P113" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q113" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="114" spans="2:17">
       <c r="B114" s="28">
         <v>46022</v>
       </c>
@@ -27032,17 +28172,22 @@
       <c r="K114" s="19">
         <v>363.47399999999999</v>
       </c>
-      <c r="L114" s="19">
-        <v>0</v>
-      </c>
-      <c r="M114" s="19">
-        <v>0</v>
-      </c>
-      <c r="N114" s="81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="2:14" hidden="1">
+      <c r="L114" s="19"/>
+      <c r="M114" s="19"/>
+      <c r="N114" s="29">
+        <v>-2.2000000000000002</v>
+      </c>
+      <c r="O114" s="29">
+        <v>-4.3</v>
+      </c>
+      <c r="P114" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q114" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="115" spans="2:17">
       <c r="B115" s="28">
         <v>46052</v>
       </c>
@@ -27075,17 +28220,22 @@
       <c r="K115" s="19">
         <v>263.90600000000001</v>
       </c>
-      <c r="L115" s="19">
-        <v>0</v>
-      </c>
-      <c r="M115" s="19">
-        <v>0</v>
-      </c>
-      <c r="N115" s="81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="2:14" hidden="1">
+      <c r="L115" s="19"/>
+      <c r="M115" s="19"/>
+      <c r="N115" s="29">
+        <v>-2.4</v>
+      </c>
+      <c r="O115" s="29">
+        <v>-3.9</v>
+      </c>
+      <c r="P115" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q115" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="116" spans="2:17">
       <c r="B116" s="28">
         <v>46056</v>
       </c>
@@ -27118,17 +28268,22 @@
       <c r="K116" s="19">
         <v>10.16</v>
       </c>
-      <c r="L116" s="19">
-        <v>0</v>
-      </c>
-      <c r="M116" s="19">
-        <v>0</v>
-      </c>
-      <c r="N116" s="81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="2:14" hidden="1">
+      <c r="L116" s="19"/>
+      <c r="M116" s="19"/>
+      <c r="N116" s="29">
+        <v>-1.6</v>
+      </c>
+      <c r="O116" s="29">
+        <v>0.3</v>
+      </c>
+      <c r="P116" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q116" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="117" spans="2:17">
       <c r="B117" s="26">
         <v>46063.51458333333</v>
       </c>
@@ -27166,11 +28321,20 @@
       <c r="M117" s="19">
         <v>0.172401</v>
       </c>
-      <c r="N117" s="83">
+      <c r="N117" s="29">
         <v>-2.8</v>
       </c>
-    </row>
-    <row r="118" spans="2:14" hidden="1">
+      <c r="O117" s="29">
+        <v>-7.5</v>
+      </c>
+      <c r="P117" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q117" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="118" spans="2:17">
       <c r="B118" s="26">
         <v>46063.522222222222</v>
       </c>
@@ -27208,11 +28372,20 @@
       <c r="M118" s="19">
         <v>6.3673300000000002E-2</v>
       </c>
-      <c r="N118" s="83">
+      <c r="N118" s="29">
         <v>-2.8</v>
       </c>
-    </row>
-    <row r="119" spans="2:14" hidden="1">
+      <c r="O118" s="29">
+        <v>-7.5</v>
+      </c>
+      <c r="P118" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q118" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="119" spans="2:17">
       <c r="B119" s="26">
         <v>46063.530555555553</v>
       </c>
@@ -27250,11 +28423,20 @@
       <c r="M119" s="19">
         <v>0.2293</v>
       </c>
-      <c r="N119" s="83">
+      <c r="N119" s="29">
         <v>-2.8</v>
       </c>
-    </row>
-    <row r="120" spans="2:14" hidden="1">
+      <c r="O119" s="29">
+        <v>-7.5</v>
+      </c>
+      <c r="P119" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q119" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="120" spans="2:17">
       <c r="B120" s="26">
         <v>46063.538888888892</v>
       </c>
@@ -27292,11 +28474,20 @@
       <c r="M120" s="19">
         <v>6.7744299999999993E-2</v>
       </c>
-      <c r="N120" s="83">
+      <c r="N120" s="29">
         <v>-2.8</v>
       </c>
-    </row>
-    <row r="121" spans="2:14">
+      <c r="O120" s="29">
+        <v>-7.5</v>
+      </c>
+      <c r="P120" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q120" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="121" spans="2:17">
       <c r="B121" s="26">
         <v>46063.563194444447</v>
       </c>
@@ -27334,11 +28525,20 @@
       <c r="M121" s="19">
         <v>2.33487E-2</v>
       </c>
-      <c r="N121" s="83">
+      <c r="N121" s="29">
         <v>-2.8</v>
       </c>
-    </row>
-    <row r="122" spans="2:14" hidden="1">
+      <c r="O121" s="29">
+        <v>-7.5</v>
+      </c>
+      <c r="P121" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q121" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="122" spans="2:17">
       <c r="B122" s="26">
         <v>46063.581944444442</v>
       </c>
@@ -27376,11 +28576,20 @@
       <c r="M122" s="19">
         <v>2.23054E-2</v>
       </c>
-      <c r="N122" s="83">
+      <c r="N122" s="29">
         <v>-2.8</v>
       </c>
-    </row>
-    <row r="123" spans="2:14" hidden="1">
+      <c r="O122" s="29">
+        <v>-7.5</v>
+      </c>
+      <c r="P122" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q122" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="123" spans="2:17">
       <c r="B123" s="28">
         <v>46065</v>
       </c>
@@ -27413,17 +28622,22 @@
       <c r="K123" s="19">
         <v>58.673999999999999</v>
       </c>
-      <c r="L123" s="19">
-        <v>0</v>
-      </c>
-      <c r="M123" s="19">
-        <v>0</v>
-      </c>
-      <c r="N123" s="81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="2:14" hidden="1">
+      <c r="L123" s="19"/>
+      <c r="M123" s="19"/>
+      <c r="N123" s="29">
+        <v>-2.8</v>
+      </c>
+      <c r="O123" s="29">
+        <v>-7.5</v>
+      </c>
+      <c r="P123" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q123" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="124" spans="2:17">
       <c r="B124" s="28">
         <v>46080</v>
       </c>
@@ -27456,17 +28670,22 @@
       <c r="K124" s="19">
         <v>474.726</v>
       </c>
-      <c r="L124" s="19">
-        <v>0</v>
-      </c>
-      <c r="M124" s="19">
-        <v>0</v>
-      </c>
-      <c r="N124" s="81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="2:14" hidden="1">
+      <c r="L124" s="19"/>
+      <c r="M124" s="19"/>
+      <c r="N124" s="29">
+        <v>-2.7</v>
+      </c>
+      <c r="O124" s="29">
+        <v>-7.6</v>
+      </c>
+      <c r="P124" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q124" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="125" spans="2:17">
       <c r="B125" s="28">
         <v>46093</v>
       </c>
@@ -27499,17 +28718,22 @@
       <c r="K125" s="19">
         <v>101.854</v>
       </c>
-      <c r="L125" s="19">
-        <v>0</v>
-      </c>
-      <c r="M125" s="19">
-        <v>0</v>
-      </c>
-      <c r="N125" s="81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="2:14" hidden="1">
+      <c r="L125" s="19"/>
+      <c r="M125" s="19"/>
+      <c r="N125" s="30">
+        <v>-3.8</v>
+      </c>
+      <c r="O125" s="30">
+        <v>-17.5</v>
+      </c>
+      <c r="P125" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q125" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="126" spans="2:17">
       <c r="B126" s="28">
         <v>46097</v>
       </c>
@@ -27542,17 +28766,22 @@
       <c r="K126" s="19">
         <v>276.09800000000001</v>
       </c>
-      <c r="L126" s="19">
-        <v>0</v>
-      </c>
-      <c r="M126" s="19">
-        <v>0</v>
-      </c>
-      <c r="N126" s="81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="2:14" hidden="1">
+      <c r="L126" s="19"/>
+      <c r="M126" s="19"/>
+      <c r="N126" s="30">
+        <v>-6.4</v>
+      </c>
+      <c r="O126" s="30">
+        <v>-41.6</v>
+      </c>
+      <c r="P126" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q126" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="127" spans="2:17">
       <c r="B127" s="26">
         <v>46105.353472222225</v>
       </c>
@@ -27590,11 +28819,20 @@
       <c r="M127" s="19">
         <v>2.79311E-2</v>
       </c>
-      <c r="N127" s="84">
+      <c r="N127" s="30">
         <v>-6.4</v>
       </c>
-    </row>
-    <row r="128" spans="2:14" hidden="1">
+      <c r="O127" s="30">
+        <v>-41.6</v>
+      </c>
+      <c r="P127" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q127" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="128" spans="2:17">
       <c r="B128" s="26">
         <v>46105.36041666667</v>
       </c>
@@ -27632,11 +28870,20 @@
       <c r="M128" s="19">
         <v>3.42866E-2</v>
       </c>
-      <c r="N128" s="84">
+      <c r="N128" s="30">
         <v>-6.4</v>
       </c>
-    </row>
-    <row r="129" spans="2:14" hidden="1">
+      <c r="O128" s="30">
+        <v>-41.6</v>
+      </c>
+      <c r="P128" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q128" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="129" spans="2:17">
       <c r="B129" s="26">
         <v>46105.366666666669</v>
       </c>
@@ -27674,11 +28921,20 @@
       <c r="M129" s="19">
         <v>1.8465700000000002E-2</v>
       </c>
-      <c r="N129" s="84">
+      <c r="N129" s="30">
         <v>-6.4</v>
       </c>
-    </row>
-    <row r="130" spans="2:14" hidden="1">
+      <c r="O129" s="30">
+        <v>-41.6</v>
+      </c>
+      <c r="P129" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q129" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="130" spans="2:17">
       <c r="B130" s="26">
         <v>46105.378472222219</v>
       </c>
@@ -27716,11 +28972,20 @@
       <c r="M130" s="19">
         <v>1.27665E-2</v>
       </c>
-      <c r="N130" s="84">
+      <c r="N130" s="30">
         <v>-6.4</v>
       </c>
-    </row>
-    <row r="131" spans="2:14" hidden="1">
+      <c r="O130" s="30">
+        <v>-41.6</v>
+      </c>
+      <c r="P130" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q130" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="131" spans="2:17">
       <c r="B131" s="28">
         <v>46112</v>
       </c>
@@ -27753,17 +29018,22 @@
       <c r="K131" s="19">
         <v>869.44</v>
       </c>
-      <c r="L131" s="19">
-        <v>0</v>
-      </c>
-      <c r="M131" s="19">
-        <v>0</v>
-      </c>
-      <c r="N131" s="81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="2:14" hidden="1">
+      <c r="L131" s="19"/>
+      <c r="M131" s="19"/>
+      <c r="N131" s="30">
+        <v>-4.7</v>
+      </c>
+      <c r="O131" s="30">
+        <v>-26.4</v>
+      </c>
+      <c r="P131" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q131" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="132" spans="2:17">
       <c r="B132" s="26">
         <v>46122.414583333331</v>
       </c>
@@ -27801,11 +29071,20 @@
       <c r="M132" s="19">
         <v>0.10782600000000001</v>
       </c>
-      <c r="N132" s="84">
+      <c r="N132" s="30">
         <v>-6</v>
       </c>
-    </row>
-    <row r="133" spans="2:14" hidden="1">
+      <c r="O132" s="30">
+        <v>-40.9</v>
+      </c>
+      <c r="P132" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q132" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="133" spans="2:17">
       <c r="B133" s="26">
         <v>46122.421527777777</v>
       </c>
@@ -27843,11 +29122,20 @@
       <c r="M133" s="19">
         <v>0.197851</v>
       </c>
-      <c r="N133" s="84">
+      <c r="N133" s="30">
         <v>-6</v>
       </c>
-    </row>
-    <row r="134" spans="2:14" hidden="1">
+      <c r="O133" s="30">
+        <v>-40.9</v>
+      </c>
+      <c r="P133" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q133" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="134" spans="2:17">
       <c r="B134" s="26">
         <v>46122.427777777775</v>
       </c>
@@ -27885,11 +29173,20 @@
       <c r="M134" s="19">
         <v>6.1411E-2</v>
       </c>
-      <c r="N134" s="84">
+      <c r="N134" s="30">
         <v>-6</v>
       </c>
-    </row>
-    <row r="135" spans="2:14" hidden="1">
+      <c r="O134" s="30">
+        <v>-40.9</v>
+      </c>
+      <c r="P134" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q134" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="135" spans="2:17">
       <c r="B135" s="26">
         <v>46122.438888888886</v>
       </c>
@@ -27927,11 +29224,20 @@
       <c r="M135" s="19">
         <v>1.8350999999999999E-2</v>
       </c>
-      <c r="N135" s="84">
+      <c r="N135" s="30">
         <v>-6</v>
       </c>
-    </row>
-    <row r="136" spans="2:14" hidden="1">
+      <c r="O135" s="30">
+        <v>-40.9</v>
+      </c>
+      <c r="P135" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q135" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="136" spans="2:17">
       <c r="B136" s="28">
         <v>46125</v>
       </c>
@@ -27965,17 +29271,22 @@
         <f>0.25+0.25+0.25+0.25+0.25+0.25+0.25+0.25+0.51+1.27+0.76+1.02+0.51+1.02+0.51+0.51+0.25+0.51+1.02+0.25+0.51+1.52+1.27+0.76+0.51+0.76+0.25+0.25+0.25+0.25+0.25+1.02+0.76+0.25+0.25+0.25+0.25+0.25+0.51+0.25+0.25+0.25+0.25+0.51+0.25+0.25+0.25+1.02+0.25</f>
         <v>23.790000000000003</v>
       </c>
-      <c r="L136" s="19">
-        <v>0</v>
-      </c>
-      <c r="M136" s="19">
-        <v>0</v>
-      </c>
-      <c r="N136" s="81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="2:14" ht="17" hidden="1" thickBot="1">
+      <c r="L136" s="19"/>
+      <c r="M136" s="19"/>
+      <c r="N136" s="30">
+        <v>-6</v>
+      </c>
+      <c r="O136" s="30">
+        <v>-40.9</v>
+      </c>
+      <c r="P136" s="90">
+        <v>-2.42</v>
+      </c>
+      <c r="Q136" s="92">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="137" spans="2:17" ht="17" thickBot="1">
       <c r="B137" s="37">
         <v>46142</v>
       </c>
@@ -28008,17 +29319,22 @@
       <c r="K137" s="21">
         <v>193.04</v>
       </c>
-      <c r="L137" s="21">
-        <v>0</v>
-      </c>
-      <c r="M137" s="21">
-        <v>0</v>
-      </c>
-      <c r="N137" s="82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="2:14">
+      <c r="L137" s="21"/>
+      <c r="M137" s="21"/>
+      <c r="N137" s="31">
+        <v>-3.6</v>
+      </c>
+      <c r="O137" s="31">
+        <v>-19.2</v>
+      </c>
+      <c r="P137" s="93">
+        <v>-2.42</v>
+      </c>
+      <c r="Q137" s="94">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="138" spans="2:17">
       <c r="B138" s="33"/>
       <c r="C138" s="18"/>
       <c r="D138" s="34"/>
@@ -28028,7 +29344,7 @@
       <c r="H138" s="35"/>
       <c r="I138" s="18"/>
     </row>
-    <row r="139" spans="2:14">
+    <row r="139" spans="2:17">
       <c r="B139" s="33"/>
       <c r="C139" s="18"/>
       <c r="D139" s="34"/>
@@ -28038,7 +29354,7 @@
       <c r="H139" s="35"/>
       <c r="I139" s="18"/>
     </row>
-    <row r="140" spans="2:14">
+    <row r="140" spans="2:17">
       <c r="B140" s="33"/>
       <c r="C140" s="18"/>
       <c r="D140" s="34"/>
@@ -28048,7 +29364,7 @@
       <c r="H140" s="35"/>
       <c r="I140" s="18"/>
     </row>
-    <row r="141" spans="2:14">
+    <row r="141" spans="2:17">
       <c r="B141" s="33"/>
       <c r="C141" s="18"/>
       <c r="D141" s="34"/>
@@ -28058,7 +29374,7 @@
       <c r="H141" s="35"/>
       <c r="I141" s="18"/>
     </row>
-    <row r="142" spans="2:14">
+    <row r="142" spans="2:17">
       <c r="B142" s="33"/>
       <c r="C142" s="18"/>
       <c r="D142" s="34"/>
@@ -28068,7 +29384,7 @@
       <c r="H142" s="35"/>
       <c r="I142" s="18"/>
     </row>
-    <row r="143" spans="2:14">
+    <row r="143" spans="2:17">
       <c r="B143" s="33"/>
       <c r="C143" s="18"/>
       <c r="D143" s="34"/>
@@ -28078,7 +29394,7 @@
       <c r="H143" s="35"/>
       <c r="I143" s="18"/>
     </row>
-    <row r="144" spans="2:14">
+    <row r="144" spans="2:17">
       <c r="B144" s="33"/>
       <c r="C144" s="18"/>
       <c r="D144" s="34"/>
@@ -28129,16 +29445,13 @@
       <c r="I148" s="18"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:N137" xr:uid="{E174FB01-AC8B-4229-B319-63F7FF07E34C}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="6"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="B2:N137" xr:uid="{E174FB01-AC8B-4229-B319-63F7FF07E34C}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:N148">
     <sortCondition ref="B1:B148"/>
   </sortState>
+  <mergeCells count="1">
+    <mergeCell ref="W2:X2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -39315,14 +40628,14 @@
       <c r="I1" s="63" t="s">
         <v>174</v>
       </c>
-      <c r="J1" s="89" t="s">
+      <c r="J1" s="81" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="89"/>
-      <c r="L1" s="89" t="s">
+      <c r="K1" s="81"/>
+      <c r="L1" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="89"/>
+      <c r="M1" s="81"/>
       <c r="N1" s="54"/>
     </row>
     <row r="2" spans="1:14" ht="16">
@@ -43237,4 +44550,5218 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EE49727-5BAE-1446-B48D-603B605EABC1}">
+  <dimension ref="B2:H994"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8">
+      <c r="B2" s="83" t="s">
+        <v>306</v>
+      </c>
+      <c r="C2" s="89" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="89"/>
+    </row>
+    <row r="3" spans="2:8">
+      <c r="B3" s="85"/>
+      <c r="C3" s="86" t="s">
+        <v>307</v>
+      </c>
+      <c r="D3" s="86" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8">
+      <c r="B4" s="87">
+        <v>44967</v>
+      </c>
+      <c r="C4" s="88">
+        <v>-2.5</v>
+      </c>
+      <c r="D4" s="88">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8">
+      <c r="B5" s="87">
+        <v>44974</v>
+      </c>
+      <c r="C5" s="88">
+        <v>-6</v>
+      </c>
+      <c r="D5" s="88">
+        <v>-37.1</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8">
+      <c r="B6" s="87">
+        <v>44981</v>
+      </c>
+      <c r="C6" s="88">
+        <v>-3.1</v>
+      </c>
+      <c r="D6" s="88">
+        <v>-13.6</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8">
+      <c r="B7" s="87">
+        <v>44988</v>
+      </c>
+      <c r="C7" s="88">
+        <v>-3</v>
+      </c>
+      <c r="D7" s="88">
+        <v>-6.7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8">
+      <c r="B8" s="87">
+        <v>44995</v>
+      </c>
+      <c r="C8" s="88">
+        <v>-3.1</v>
+      </c>
+      <c r="D8" s="88">
+        <v>-9.9</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8">
+      <c r="B9" s="87">
+        <v>45002</v>
+      </c>
+      <c r="C9" s="88">
+        <v>-1.3</v>
+      </c>
+      <c r="D9" s="88">
+        <v>-2.2999999999999998</v>
+      </c>
+      <c r="H9" s="84"/>
+    </row>
+    <row r="10" spans="2:8">
+      <c r="B10" s="87">
+        <v>45007</v>
+      </c>
+      <c r="C10" s="88">
+        <v>-1.4</v>
+      </c>
+      <c r="D10" s="88">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8">
+      <c r="B11" s="87">
+        <v>45014</v>
+      </c>
+      <c r="C11" s="88">
+        <v>-1.2</v>
+      </c>
+      <c r="D11" s="88">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8">
+      <c r="B12" s="87">
+        <v>45028</v>
+      </c>
+      <c r="C12" s="88">
+        <v>-2.6</v>
+      </c>
+      <c r="D12" s="88">
+        <v>-6.1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8">
+      <c r="B13" s="87">
+        <v>45036</v>
+      </c>
+      <c r="C13" s="88">
+        <v>-0.8</v>
+      </c>
+      <c r="D13" s="88">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8">
+      <c r="B14" s="87">
+        <v>45044</v>
+      </c>
+      <c r="C14" s="88">
+        <v>-1.3</v>
+      </c>
+      <c r="D14" s="88">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8">
+      <c r="B15" s="87">
+        <v>45049</v>
+      </c>
+      <c r="C15" s="88">
+        <v>-1.9</v>
+      </c>
+      <c r="D15" s="88">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8">
+      <c r="B16" s="87">
+        <v>45056</v>
+      </c>
+      <c r="C16" s="88">
+        <v>-1.8</v>
+      </c>
+      <c r="D16" s="88">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="B17" s="87">
+        <v>45072</v>
+      </c>
+      <c r="C17" s="88">
+        <v>-1.7</v>
+      </c>
+      <c r="D17" s="88">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4">
+      <c r="B18" s="87">
+        <v>45079</v>
+      </c>
+      <c r="C18" s="88">
+        <v>-1.6</v>
+      </c>
+      <c r="D18" s="88">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4">
+      <c r="B19" s="87">
+        <v>45086</v>
+      </c>
+      <c r="C19" s="88">
+        <v>-1.9</v>
+      </c>
+      <c r="D19" s="88">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4">
+      <c r="B20" s="87">
+        <v>45093</v>
+      </c>
+      <c r="C20" s="88">
+        <v>-1.6</v>
+      </c>
+      <c r="D20" s="88">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4">
+      <c r="B21" s="87">
+        <v>45100</v>
+      </c>
+      <c r="C21" s="88">
+        <v>-2</v>
+      </c>
+      <c r="D21" s="88">
+        <v>-2.1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4">
+      <c r="B22" s="87">
+        <v>45107</v>
+      </c>
+      <c r="C22" s="88">
+        <v>-2</v>
+      </c>
+      <c r="D22" s="88">
+        <v>-2.4</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4">
+      <c r="B23" s="87">
+        <v>45114</v>
+      </c>
+      <c r="C23" s="88">
+        <v>-1.6</v>
+      </c>
+      <c r="D23" s="88">
+        <v>-1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4">
+      <c r="B24" s="87">
+        <v>45121</v>
+      </c>
+      <c r="C24" s="88">
+        <v>-1.7</v>
+      </c>
+      <c r="D24" s="88">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4">
+      <c r="B25" s="87">
+        <v>45128</v>
+      </c>
+      <c r="C25" s="88">
+        <v>-1.3</v>
+      </c>
+      <c r="D25" s="88">
+        <v>-1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4">
+      <c r="B26" s="87">
+        <v>45135</v>
+      </c>
+      <c r="C26" s="88">
+        <v>-1.8</v>
+      </c>
+      <c r="D26" s="88">
+        <v>-3.9</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4">
+      <c r="B27" s="87">
+        <v>45142</v>
+      </c>
+      <c r="C27" s="88">
+        <v>-1.6</v>
+      </c>
+      <c r="D27" s="88">
+        <v>-2.1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4">
+      <c r="B28" s="87">
+        <v>45149</v>
+      </c>
+      <c r="C28" s="88">
+        <v>-1.4</v>
+      </c>
+      <c r="D28" s="88">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4">
+      <c r="B29" s="87">
+        <v>45162</v>
+      </c>
+      <c r="C29" s="88">
+        <v>-2.2000000000000002</v>
+      </c>
+      <c r="D29" s="88">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4">
+      <c r="B30" s="87">
+        <v>45176</v>
+      </c>
+      <c r="C30" s="88">
+        <v>-1.7</v>
+      </c>
+      <c r="D30" s="88">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4">
+      <c r="B31" s="87">
+        <v>45183</v>
+      </c>
+      <c r="C31" s="88">
+        <v>-2.1</v>
+      </c>
+      <c r="D31" s="88">
+        <v>-6.9</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4">
+      <c r="B32" s="87">
+        <v>45197</v>
+      </c>
+      <c r="C32" s="88">
+        <v>-1.7</v>
+      </c>
+      <c r="D32" s="88">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4">
+      <c r="B33" s="87">
+        <v>45204</v>
+      </c>
+      <c r="C33" s="88">
+        <v>-1.6</v>
+      </c>
+      <c r="D33" s="88">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4">
+      <c r="B34" s="87">
+        <v>45218</v>
+      </c>
+      <c r="C34" s="88">
+        <v>0</v>
+      </c>
+      <c r="D34" s="88">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4">
+      <c r="B35" s="87">
+        <v>45223</v>
+      </c>
+      <c r="C35" s="88">
+        <v>-2.2000000000000002</v>
+      </c>
+      <c r="D35" s="88">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4">
+      <c r="B36" s="87">
+        <v>45239</v>
+      </c>
+      <c r="C36" s="88">
+        <v>-1.5</v>
+      </c>
+      <c r="D36" s="88">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4">
+      <c r="B37" s="87">
+        <v>45246</v>
+      </c>
+      <c r="C37" s="88">
+        <v>-1.7</v>
+      </c>
+      <c r="D37" s="88">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4">
+      <c r="B38" s="87">
+        <v>45251</v>
+      </c>
+      <c r="C38" s="88">
+        <v>-1.9</v>
+      </c>
+      <c r="D38" s="88">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4">
+      <c r="B39" s="87">
+        <v>45257</v>
+      </c>
+      <c r="C39" s="88">
+        <v>0</v>
+      </c>
+      <c r="D39" s="88">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4">
+      <c r="B40" s="87">
+        <v>45267</v>
+      </c>
+      <c r="C40" s="88">
+        <v>-4.5999999999999996</v>
+      </c>
+      <c r="D40" s="88">
+        <v>-25.2</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4">
+      <c r="B41" s="87"/>
+      <c r="C41" s="85"/>
+      <c r="D41" s="85"/>
+    </row>
+    <row r="42" spans="2:4">
+      <c r="B42" s="87"/>
+      <c r="C42" s="85"/>
+      <c r="D42" s="85"/>
+    </row>
+    <row r="43" spans="2:4">
+      <c r="B43" s="87"/>
+      <c r="C43" s="85"/>
+      <c r="D43" s="85"/>
+    </row>
+    <row r="44" spans="2:4">
+      <c r="B44" s="87"/>
+      <c r="C44" s="85"/>
+      <c r="D44" s="85"/>
+    </row>
+    <row r="45" spans="2:4">
+      <c r="B45" s="87"/>
+      <c r="C45" s="85"/>
+      <c r="D45" s="85"/>
+    </row>
+    <row r="46" spans="2:4">
+      <c r="B46" s="87"/>
+      <c r="C46" s="85"/>
+      <c r="D46" s="85"/>
+    </row>
+    <row r="47" spans="2:4">
+      <c r="B47" s="87"/>
+      <c r="C47" s="85"/>
+      <c r="D47" s="85"/>
+    </row>
+    <row r="48" spans="2:4">
+      <c r="B48" s="87"/>
+      <c r="C48" s="85"/>
+      <c r="D48" s="85"/>
+    </row>
+    <row r="49" spans="2:4">
+      <c r="B49" s="82"/>
+      <c r="C49" s="82"/>
+      <c r="D49" s="82"/>
+    </row>
+    <row r="50" spans="2:4">
+      <c r="B50" s="82"/>
+      <c r="C50" s="82"/>
+      <c r="D50" s="82"/>
+    </row>
+    <row r="51" spans="2:4">
+      <c r="B51" s="82"/>
+      <c r="C51" s="82"/>
+      <c r="D51" s="82"/>
+    </row>
+    <row r="52" spans="2:4">
+      <c r="B52" s="82"/>
+      <c r="C52" s="82"/>
+      <c r="D52" s="82"/>
+    </row>
+    <row r="53" spans="2:4">
+      <c r="B53" s="82"/>
+      <c r="C53" s="82"/>
+      <c r="D53" s="82"/>
+    </row>
+    <row r="54" spans="2:4">
+      <c r="B54" s="82"/>
+      <c r="C54" s="82"/>
+      <c r="D54" s="82"/>
+    </row>
+    <row r="55" spans="2:4">
+      <c r="B55" s="82"/>
+      <c r="C55" s="82"/>
+      <c r="D55" s="82"/>
+    </row>
+    <row r="56" spans="2:4">
+      <c r="B56" s="82"/>
+      <c r="C56" s="82"/>
+      <c r="D56" s="82"/>
+    </row>
+    <row r="57" spans="2:4">
+      <c r="B57" s="82"/>
+      <c r="C57" s="82"/>
+      <c r="D57" s="82"/>
+    </row>
+    <row r="58" spans="2:4">
+      <c r="B58" s="82"/>
+      <c r="C58" s="82"/>
+      <c r="D58" s="82"/>
+    </row>
+    <row r="59" spans="2:4">
+      <c r="B59" s="82"/>
+      <c r="C59" s="82"/>
+      <c r="D59" s="82"/>
+    </row>
+    <row r="60" spans="2:4">
+      <c r="B60" s="82"/>
+      <c r="C60" s="82"/>
+      <c r="D60" s="82"/>
+    </row>
+    <row r="61" spans="2:4">
+      <c r="B61" s="82"/>
+      <c r="C61" s="82"/>
+      <c r="D61" s="82"/>
+    </row>
+    <row r="62" spans="2:4">
+      <c r="B62" s="82"/>
+      <c r="C62" s="82"/>
+      <c r="D62" s="82"/>
+    </row>
+    <row r="63" spans="2:4">
+      <c r="B63" s="82"/>
+      <c r="C63" s="82"/>
+      <c r="D63" s="82"/>
+    </row>
+    <row r="64" spans="2:4">
+      <c r="B64" s="82"/>
+      <c r="C64" s="82"/>
+      <c r="D64" s="82"/>
+    </row>
+    <row r="65" spans="2:4">
+      <c r="B65" s="82"/>
+      <c r="C65" s="82"/>
+      <c r="D65" s="82"/>
+    </row>
+    <row r="66" spans="2:4">
+      <c r="B66" s="82"/>
+      <c r="C66" s="82"/>
+      <c r="D66" s="82"/>
+    </row>
+    <row r="67" spans="2:4">
+      <c r="B67" s="82"/>
+      <c r="C67" s="82"/>
+      <c r="D67" s="82"/>
+    </row>
+    <row r="68" spans="2:4">
+      <c r="B68" s="82"/>
+      <c r="C68" s="82"/>
+      <c r="D68" s="82"/>
+    </row>
+    <row r="69" spans="2:4">
+      <c r="B69" s="82"/>
+      <c r="C69" s="82"/>
+      <c r="D69" s="82"/>
+    </row>
+    <row r="70" spans="2:4">
+      <c r="B70" s="82"/>
+      <c r="C70" s="82"/>
+      <c r="D70" s="82"/>
+    </row>
+    <row r="71" spans="2:4">
+      <c r="B71" s="82"/>
+      <c r="C71" s="82"/>
+      <c r="D71" s="82"/>
+    </row>
+    <row r="72" spans="2:4">
+      <c r="B72" s="82"/>
+      <c r="C72" s="82"/>
+      <c r="D72" s="82"/>
+    </row>
+    <row r="73" spans="2:4">
+      <c r="B73" s="82"/>
+      <c r="C73" s="82"/>
+      <c r="D73" s="82"/>
+    </row>
+    <row r="74" spans="2:4">
+      <c r="B74" s="82"/>
+      <c r="C74" s="82"/>
+      <c r="D74" s="82"/>
+    </row>
+    <row r="75" spans="2:4">
+      <c r="B75" s="82"/>
+      <c r="C75" s="82"/>
+      <c r="D75" s="82"/>
+    </row>
+    <row r="76" spans="2:4">
+      <c r="B76" s="82"/>
+      <c r="C76" s="82"/>
+      <c r="D76" s="82"/>
+    </row>
+    <row r="77" spans="2:4">
+      <c r="B77" s="82"/>
+      <c r="C77" s="82"/>
+      <c r="D77" s="82"/>
+    </row>
+    <row r="78" spans="2:4">
+      <c r="B78" s="82"/>
+      <c r="C78" s="82"/>
+      <c r="D78" s="82"/>
+    </row>
+    <row r="79" spans="2:4">
+      <c r="B79" s="82"/>
+      <c r="C79" s="82"/>
+      <c r="D79" s="82"/>
+    </row>
+    <row r="80" spans="2:4">
+      <c r="B80" s="82"/>
+      <c r="C80" s="82"/>
+      <c r="D80" s="82"/>
+    </row>
+    <row r="81" spans="2:4">
+      <c r="B81" s="82"/>
+      <c r="C81" s="82"/>
+      <c r="D81" s="82"/>
+    </row>
+    <row r="82" spans="2:4">
+      <c r="B82" s="82"/>
+      <c r="C82" s="82"/>
+      <c r="D82" s="82"/>
+    </row>
+    <row r="83" spans="2:4">
+      <c r="B83" s="82"/>
+      <c r="C83" s="82"/>
+      <c r="D83" s="82"/>
+    </row>
+    <row r="84" spans="2:4">
+      <c r="B84" s="82"/>
+      <c r="C84" s="82"/>
+      <c r="D84" s="82"/>
+    </row>
+    <row r="85" spans="2:4">
+      <c r="B85" s="82"/>
+      <c r="C85" s="82"/>
+      <c r="D85" s="82"/>
+    </row>
+    <row r="86" spans="2:4">
+      <c r="B86" s="82"/>
+      <c r="C86" s="82"/>
+      <c r="D86" s="82"/>
+    </row>
+    <row r="87" spans="2:4">
+      <c r="B87" s="82"/>
+      <c r="C87" s="82"/>
+      <c r="D87" s="82"/>
+    </row>
+    <row r="88" spans="2:4">
+      <c r="B88" s="82"/>
+      <c r="C88" s="82"/>
+      <c r="D88" s="82"/>
+    </row>
+    <row r="89" spans="2:4">
+      <c r="B89" s="82"/>
+      <c r="C89" s="82"/>
+      <c r="D89" s="82"/>
+    </row>
+    <row r="90" spans="2:4">
+      <c r="B90" s="82"/>
+      <c r="C90" s="82"/>
+      <c r="D90" s="82"/>
+    </row>
+    <row r="91" spans="2:4">
+      <c r="B91" s="82"/>
+      <c r="C91" s="82"/>
+      <c r="D91" s="82"/>
+    </row>
+    <row r="92" spans="2:4">
+      <c r="B92" s="82"/>
+      <c r="C92" s="82"/>
+      <c r="D92" s="82"/>
+    </row>
+    <row r="93" spans="2:4">
+      <c r="B93" s="82"/>
+      <c r="C93" s="82"/>
+      <c r="D93" s="82"/>
+    </row>
+    <row r="94" spans="2:4">
+      <c r="B94" s="82"/>
+      <c r="C94" s="82"/>
+      <c r="D94" s="82"/>
+    </row>
+    <row r="95" spans="2:4">
+      <c r="B95" s="82"/>
+      <c r="C95" s="82"/>
+      <c r="D95" s="82"/>
+    </row>
+    <row r="96" spans="2:4">
+      <c r="B96" s="82"/>
+      <c r="C96" s="82"/>
+      <c r="D96" s="82"/>
+    </row>
+    <row r="97" spans="2:4">
+      <c r="B97" s="82"/>
+      <c r="C97" s="82"/>
+      <c r="D97" s="82"/>
+    </row>
+    <row r="98" spans="2:4">
+      <c r="B98" s="82"/>
+      <c r="C98" s="82"/>
+      <c r="D98" s="82"/>
+    </row>
+    <row r="99" spans="2:4">
+      <c r="B99" s="82"/>
+      <c r="C99" s="82"/>
+      <c r="D99" s="82"/>
+    </row>
+    <row r="100" spans="2:4">
+      <c r="B100" s="82"/>
+      <c r="C100" s="82"/>
+      <c r="D100" s="82"/>
+    </row>
+    <row r="101" spans="2:4">
+      <c r="B101" s="82"/>
+      <c r="C101" s="82"/>
+      <c r="D101" s="82"/>
+    </row>
+    <row r="102" spans="2:4">
+      <c r="B102" s="82"/>
+      <c r="C102" s="82"/>
+      <c r="D102" s="82"/>
+    </row>
+    <row r="103" spans="2:4">
+      <c r="B103" s="82"/>
+      <c r="C103" s="82"/>
+      <c r="D103" s="82"/>
+    </row>
+    <row r="104" spans="2:4">
+      <c r="B104" s="82"/>
+      <c r="C104" s="82"/>
+      <c r="D104" s="82"/>
+    </row>
+    <row r="105" spans="2:4">
+      <c r="B105" s="82"/>
+      <c r="C105" s="82"/>
+      <c r="D105" s="82"/>
+    </row>
+    <row r="106" spans="2:4">
+      <c r="B106" s="82"/>
+      <c r="C106" s="82"/>
+      <c r="D106" s="82"/>
+    </row>
+    <row r="107" spans="2:4">
+      <c r="B107" s="82"/>
+      <c r="C107" s="82"/>
+      <c r="D107" s="82"/>
+    </row>
+    <row r="108" spans="2:4">
+      <c r="B108" s="82"/>
+      <c r="C108" s="82"/>
+      <c r="D108" s="82"/>
+    </row>
+    <row r="109" spans="2:4">
+      <c r="B109" s="82"/>
+      <c r="C109" s="82"/>
+      <c r="D109" s="82"/>
+    </row>
+    <row r="110" spans="2:4">
+      <c r="B110" s="82"/>
+      <c r="C110" s="82"/>
+      <c r="D110" s="82"/>
+    </row>
+    <row r="111" spans="2:4">
+      <c r="B111" s="82"/>
+      <c r="C111" s="82"/>
+      <c r="D111" s="82"/>
+    </row>
+    <row r="112" spans="2:4">
+      <c r="B112" s="82"/>
+      <c r="C112" s="82"/>
+      <c r="D112" s="82"/>
+    </row>
+    <row r="113" spans="2:4">
+      <c r="B113" s="82"/>
+      <c r="C113" s="82"/>
+      <c r="D113" s="82"/>
+    </row>
+    <row r="114" spans="2:4">
+      <c r="B114" s="82"/>
+      <c r="C114" s="82"/>
+      <c r="D114" s="82"/>
+    </row>
+    <row r="115" spans="2:4">
+      <c r="B115" s="82"/>
+      <c r="C115" s="82"/>
+      <c r="D115" s="82"/>
+    </row>
+    <row r="116" spans="2:4">
+      <c r="B116" s="82"/>
+      <c r="C116" s="82"/>
+      <c r="D116" s="82"/>
+    </row>
+    <row r="117" spans="2:4">
+      <c r="B117" s="82"/>
+      <c r="C117" s="82"/>
+      <c r="D117" s="82"/>
+    </row>
+    <row r="118" spans="2:4">
+      <c r="B118" s="82"/>
+      <c r="C118" s="82"/>
+      <c r="D118" s="82"/>
+    </row>
+    <row r="119" spans="2:4">
+      <c r="B119" s="82"/>
+      <c r="C119" s="82"/>
+      <c r="D119" s="82"/>
+    </row>
+    <row r="120" spans="2:4">
+      <c r="B120" s="82"/>
+      <c r="C120" s="82"/>
+      <c r="D120" s="82"/>
+    </row>
+    <row r="121" spans="2:4">
+      <c r="B121" s="82"/>
+      <c r="C121" s="82"/>
+      <c r="D121" s="82"/>
+    </row>
+    <row r="122" spans="2:4">
+      <c r="B122" s="82"/>
+      <c r="C122" s="82"/>
+      <c r="D122" s="82"/>
+    </row>
+    <row r="123" spans="2:4">
+      <c r="B123" s="82"/>
+      <c r="C123" s="82"/>
+      <c r="D123" s="82"/>
+    </row>
+    <row r="124" spans="2:4">
+      <c r="B124" s="82"/>
+      <c r="C124" s="82"/>
+      <c r="D124" s="82"/>
+    </row>
+    <row r="125" spans="2:4">
+      <c r="B125" s="82"/>
+      <c r="C125" s="82"/>
+      <c r="D125" s="82"/>
+    </row>
+    <row r="126" spans="2:4">
+      <c r="B126" s="82"/>
+      <c r="C126" s="82"/>
+      <c r="D126" s="82"/>
+    </row>
+    <row r="127" spans="2:4">
+      <c r="B127" s="82"/>
+      <c r="C127" s="82"/>
+      <c r="D127" s="82"/>
+    </row>
+    <row r="128" spans="2:4">
+      <c r="B128" s="82"/>
+      <c r="C128" s="82"/>
+      <c r="D128" s="82"/>
+    </row>
+    <row r="129" spans="2:4">
+      <c r="B129" s="82"/>
+      <c r="C129" s="82"/>
+      <c r="D129" s="82"/>
+    </row>
+    <row r="130" spans="2:4">
+      <c r="B130" s="82"/>
+      <c r="C130" s="82"/>
+      <c r="D130" s="82"/>
+    </row>
+    <row r="131" spans="2:4">
+      <c r="B131" s="82"/>
+      <c r="C131" s="82"/>
+      <c r="D131" s="82"/>
+    </row>
+    <row r="132" spans="2:4">
+      <c r="B132" s="82"/>
+      <c r="C132" s="82"/>
+      <c r="D132" s="82"/>
+    </row>
+    <row r="133" spans="2:4">
+      <c r="B133" s="82"/>
+      <c r="C133" s="82"/>
+      <c r="D133" s="82"/>
+    </row>
+    <row r="134" spans="2:4">
+      <c r="B134" s="82"/>
+      <c r="C134" s="82"/>
+      <c r="D134" s="82"/>
+    </row>
+    <row r="135" spans="2:4">
+      <c r="B135" s="82"/>
+      <c r="C135" s="82"/>
+      <c r="D135" s="82"/>
+    </row>
+    <row r="136" spans="2:4">
+      <c r="B136" s="82"/>
+      <c r="C136" s="82"/>
+      <c r="D136" s="82"/>
+    </row>
+    <row r="137" spans="2:4">
+      <c r="B137" s="82"/>
+      <c r="C137" s="82"/>
+      <c r="D137" s="82"/>
+    </row>
+    <row r="138" spans="2:4">
+      <c r="B138" s="82"/>
+      <c r="C138" s="82"/>
+      <c r="D138" s="82"/>
+    </row>
+    <row r="139" spans="2:4">
+      <c r="B139" s="82"/>
+      <c r="C139" s="82"/>
+      <c r="D139" s="82"/>
+    </row>
+    <row r="140" spans="2:4">
+      <c r="B140" s="82"/>
+      <c r="C140" s="82"/>
+      <c r="D140" s="82"/>
+    </row>
+    <row r="141" spans="2:4">
+      <c r="B141" s="82"/>
+      <c r="C141" s="82"/>
+      <c r="D141" s="82"/>
+    </row>
+    <row r="142" spans="2:4">
+      <c r="B142" s="82"/>
+      <c r="C142" s="82"/>
+      <c r="D142" s="82"/>
+    </row>
+    <row r="143" spans="2:4">
+      <c r="B143" s="82"/>
+      <c r="C143" s="82"/>
+      <c r="D143" s="82"/>
+    </row>
+    <row r="144" spans="2:4">
+      <c r="B144" s="82"/>
+      <c r="C144" s="82"/>
+      <c r="D144" s="82"/>
+    </row>
+    <row r="145" spans="2:4">
+      <c r="B145" s="82"/>
+      <c r="C145" s="82"/>
+      <c r="D145" s="82"/>
+    </row>
+    <row r="146" spans="2:4">
+      <c r="B146" s="82"/>
+      <c r="C146" s="82"/>
+      <c r="D146" s="82"/>
+    </row>
+    <row r="147" spans="2:4">
+      <c r="B147" s="82"/>
+      <c r="C147" s="82"/>
+      <c r="D147" s="82"/>
+    </row>
+    <row r="148" spans="2:4">
+      <c r="B148" s="82"/>
+      <c r="C148" s="82"/>
+      <c r="D148" s="82"/>
+    </row>
+    <row r="149" spans="2:4">
+      <c r="B149" s="82"/>
+      <c r="C149" s="82"/>
+      <c r="D149" s="82"/>
+    </row>
+    <row r="150" spans="2:4">
+      <c r="B150" s="82"/>
+      <c r="C150" s="82"/>
+      <c r="D150" s="82"/>
+    </row>
+    <row r="151" spans="2:4">
+      <c r="B151" s="82"/>
+      <c r="C151" s="82"/>
+      <c r="D151" s="82"/>
+    </row>
+    <row r="152" spans="2:4">
+      <c r="B152" s="82"/>
+      <c r="C152" s="82"/>
+      <c r="D152" s="82"/>
+    </row>
+    <row r="153" spans="2:4">
+      <c r="B153" s="82"/>
+      <c r="C153" s="82"/>
+      <c r="D153" s="82"/>
+    </row>
+    <row r="154" spans="2:4">
+      <c r="B154" s="82"/>
+      <c r="C154" s="82"/>
+      <c r="D154" s="82"/>
+    </row>
+    <row r="155" spans="2:4">
+      <c r="B155" s="82"/>
+      <c r="C155" s="82"/>
+      <c r="D155" s="82"/>
+    </row>
+    <row r="156" spans="2:4">
+      <c r="B156" s="82"/>
+      <c r="C156" s="82"/>
+      <c r="D156" s="82"/>
+    </row>
+    <row r="157" spans="2:4">
+      <c r="B157" s="82"/>
+      <c r="C157" s="82"/>
+      <c r="D157" s="82"/>
+    </row>
+    <row r="158" spans="2:4">
+      <c r="B158" s="82"/>
+      <c r="C158" s="82"/>
+      <c r="D158" s="82"/>
+    </row>
+    <row r="159" spans="2:4">
+      <c r="B159" s="82"/>
+      <c r="C159" s="82"/>
+      <c r="D159" s="82"/>
+    </row>
+    <row r="160" spans="2:4">
+      <c r="B160" s="82"/>
+      <c r="C160" s="82"/>
+      <c r="D160" s="82"/>
+    </row>
+    <row r="161" spans="2:4">
+      <c r="B161" s="82"/>
+      <c r="C161" s="82"/>
+      <c r="D161" s="82"/>
+    </row>
+    <row r="162" spans="2:4">
+      <c r="B162" s="82"/>
+      <c r="C162" s="82"/>
+      <c r="D162" s="82"/>
+    </row>
+    <row r="163" spans="2:4">
+      <c r="B163" s="82"/>
+      <c r="C163" s="82"/>
+      <c r="D163" s="82"/>
+    </row>
+    <row r="164" spans="2:4">
+      <c r="B164" s="82"/>
+      <c r="C164" s="82"/>
+      <c r="D164" s="82"/>
+    </row>
+    <row r="165" spans="2:4">
+      <c r="B165" s="82"/>
+      <c r="C165" s="82"/>
+      <c r="D165" s="82"/>
+    </row>
+    <row r="166" spans="2:4">
+      <c r="B166" s="82"/>
+      <c r="C166" s="82"/>
+      <c r="D166" s="82"/>
+    </row>
+    <row r="167" spans="2:4">
+      <c r="B167" s="82"/>
+      <c r="C167" s="82"/>
+      <c r="D167" s="82"/>
+    </row>
+    <row r="168" spans="2:4">
+      <c r="B168" s="82"/>
+      <c r="C168" s="82"/>
+      <c r="D168" s="82"/>
+    </row>
+    <row r="169" spans="2:4">
+      <c r="B169" s="82"/>
+      <c r="C169" s="82"/>
+      <c r="D169" s="82"/>
+    </row>
+    <row r="170" spans="2:4">
+      <c r="B170" s="82"/>
+      <c r="C170" s="82"/>
+      <c r="D170" s="82"/>
+    </row>
+    <row r="171" spans="2:4">
+      <c r="B171" s="82"/>
+      <c r="C171" s="82"/>
+      <c r="D171" s="82"/>
+    </row>
+    <row r="172" spans="2:4">
+      <c r="B172" s="82"/>
+      <c r="C172" s="82"/>
+      <c r="D172" s="82"/>
+    </row>
+    <row r="173" spans="2:4">
+      <c r="B173" s="82"/>
+      <c r="C173" s="82"/>
+      <c r="D173" s="82"/>
+    </row>
+    <row r="174" spans="2:4">
+      <c r="B174" s="82"/>
+      <c r="C174" s="82"/>
+      <c r="D174" s="82"/>
+    </row>
+    <row r="175" spans="2:4">
+      <c r="B175" s="82"/>
+      <c r="C175" s="82"/>
+      <c r="D175" s="82"/>
+    </row>
+    <row r="176" spans="2:4">
+      <c r="B176" s="82"/>
+      <c r="C176" s="82"/>
+      <c r="D176" s="82"/>
+    </row>
+    <row r="177" spans="2:4">
+      <c r="B177" s="82"/>
+      <c r="C177" s="82"/>
+      <c r="D177" s="82"/>
+    </row>
+    <row r="178" spans="2:4">
+      <c r="B178" s="82"/>
+      <c r="C178" s="82"/>
+      <c r="D178" s="82"/>
+    </row>
+    <row r="179" spans="2:4">
+      <c r="B179" s="82"/>
+      <c r="C179" s="82"/>
+      <c r="D179" s="82"/>
+    </row>
+    <row r="180" spans="2:4">
+      <c r="B180" s="82"/>
+      <c r="C180" s="82"/>
+      <c r="D180" s="82"/>
+    </row>
+    <row r="181" spans="2:4">
+      <c r="B181" s="82"/>
+      <c r="C181" s="82"/>
+      <c r="D181" s="82"/>
+    </row>
+    <row r="182" spans="2:4">
+      <c r="B182" s="82"/>
+      <c r="C182" s="82"/>
+      <c r="D182" s="82"/>
+    </row>
+    <row r="183" spans="2:4">
+      <c r="B183" s="82"/>
+      <c r="C183" s="82"/>
+      <c r="D183" s="82"/>
+    </row>
+    <row r="184" spans="2:4">
+      <c r="B184" s="82"/>
+      <c r="C184" s="82"/>
+      <c r="D184" s="82"/>
+    </row>
+    <row r="185" spans="2:4">
+      <c r="B185" s="82"/>
+      <c r="C185" s="82"/>
+      <c r="D185" s="82"/>
+    </row>
+    <row r="186" spans="2:4">
+      <c r="B186" s="82"/>
+      <c r="C186" s="82"/>
+      <c r="D186" s="82"/>
+    </row>
+    <row r="187" spans="2:4">
+      <c r="B187" s="82"/>
+      <c r="C187" s="82"/>
+      <c r="D187" s="82"/>
+    </row>
+    <row r="188" spans="2:4">
+      <c r="B188" s="82"/>
+      <c r="C188" s="82"/>
+      <c r="D188" s="82"/>
+    </row>
+    <row r="189" spans="2:4">
+      <c r="B189" s="82"/>
+      <c r="C189" s="82"/>
+      <c r="D189" s="82"/>
+    </row>
+    <row r="190" spans="2:4">
+      <c r="B190" s="82"/>
+      <c r="C190" s="82"/>
+      <c r="D190" s="82"/>
+    </row>
+    <row r="191" spans="2:4">
+      <c r="B191" s="82"/>
+      <c r="C191" s="82"/>
+      <c r="D191" s="82"/>
+    </row>
+    <row r="192" spans="2:4">
+      <c r="B192" s="82"/>
+      <c r="C192" s="82"/>
+      <c r="D192" s="82"/>
+    </row>
+    <row r="193" spans="2:4">
+      <c r="B193" s="82"/>
+      <c r="C193" s="82"/>
+      <c r="D193" s="82"/>
+    </row>
+    <row r="194" spans="2:4">
+      <c r="B194" s="82"/>
+      <c r="C194" s="82"/>
+      <c r="D194" s="82"/>
+    </row>
+    <row r="195" spans="2:4">
+      <c r="B195" s="82"/>
+      <c r="C195" s="82"/>
+      <c r="D195" s="82"/>
+    </row>
+    <row r="196" spans="2:4">
+      <c r="B196" s="82"/>
+      <c r="C196" s="82"/>
+      <c r="D196" s="82"/>
+    </row>
+    <row r="197" spans="2:4">
+      <c r="B197" s="82"/>
+      <c r="C197" s="82"/>
+      <c r="D197" s="82"/>
+    </row>
+    <row r="198" spans="2:4">
+      <c r="B198" s="82"/>
+      <c r="C198" s="82"/>
+      <c r="D198" s="82"/>
+    </row>
+    <row r="199" spans="2:4">
+      <c r="B199" s="82"/>
+      <c r="C199" s="82"/>
+      <c r="D199" s="82"/>
+    </row>
+    <row r="200" spans="2:4">
+      <c r="B200" s="82"/>
+      <c r="C200" s="82"/>
+      <c r="D200" s="82"/>
+    </row>
+    <row r="201" spans="2:4">
+      <c r="B201" s="82"/>
+      <c r="C201" s="82"/>
+      <c r="D201" s="82"/>
+    </row>
+    <row r="202" spans="2:4">
+      <c r="B202" s="82"/>
+      <c r="C202" s="82"/>
+      <c r="D202" s="82"/>
+    </row>
+    <row r="203" spans="2:4">
+      <c r="B203" s="82"/>
+      <c r="C203" s="82"/>
+      <c r="D203" s="82"/>
+    </row>
+    <row r="204" spans="2:4">
+      <c r="B204" s="82"/>
+      <c r="C204" s="82"/>
+      <c r="D204" s="82"/>
+    </row>
+    <row r="205" spans="2:4">
+      <c r="B205" s="82"/>
+      <c r="C205" s="82"/>
+      <c r="D205" s="82"/>
+    </row>
+    <row r="206" spans="2:4">
+      <c r="B206" s="82"/>
+      <c r="C206" s="82"/>
+      <c r="D206" s="82"/>
+    </row>
+    <row r="207" spans="2:4">
+      <c r="B207" s="82"/>
+      <c r="C207" s="82"/>
+      <c r="D207" s="82"/>
+    </row>
+    <row r="208" spans="2:4">
+      <c r="B208" s="82"/>
+      <c r="C208" s="82"/>
+      <c r="D208" s="82"/>
+    </row>
+    <row r="209" spans="2:4">
+      <c r="B209" s="82"/>
+      <c r="C209" s="82"/>
+      <c r="D209" s="82"/>
+    </row>
+    <row r="210" spans="2:4">
+      <c r="B210" s="82"/>
+      <c r="C210" s="82"/>
+      <c r="D210" s="82"/>
+    </row>
+    <row r="211" spans="2:4">
+      <c r="B211" s="82"/>
+      <c r="C211" s="82"/>
+      <c r="D211" s="82"/>
+    </row>
+    <row r="212" spans="2:4">
+      <c r="B212" s="82"/>
+      <c r="C212" s="82"/>
+      <c r="D212" s="82"/>
+    </row>
+    <row r="213" spans="2:4">
+      <c r="B213" s="82"/>
+      <c r="C213" s="82"/>
+      <c r="D213" s="82"/>
+    </row>
+    <row r="214" spans="2:4">
+      <c r="B214" s="82"/>
+      <c r="C214" s="82"/>
+      <c r="D214" s="82"/>
+    </row>
+    <row r="215" spans="2:4">
+      <c r="B215" s="82"/>
+      <c r="C215" s="82"/>
+      <c r="D215" s="82"/>
+    </row>
+    <row r="216" spans="2:4">
+      <c r="B216" s="82"/>
+      <c r="C216" s="82"/>
+      <c r="D216" s="82"/>
+    </row>
+    <row r="217" spans="2:4">
+      <c r="B217" s="82"/>
+      <c r="C217" s="82"/>
+      <c r="D217" s="82"/>
+    </row>
+    <row r="218" spans="2:4">
+      <c r="B218" s="82"/>
+      <c r="C218" s="82"/>
+      <c r="D218" s="82"/>
+    </row>
+    <row r="219" spans="2:4">
+      <c r="B219" s="82"/>
+      <c r="C219" s="82"/>
+      <c r="D219" s="82"/>
+    </row>
+    <row r="220" spans="2:4">
+      <c r="B220" s="82"/>
+      <c r="C220" s="82"/>
+      <c r="D220" s="82"/>
+    </row>
+    <row r="221" spans="2:4">
+      <c r="B221" s="82"/>
+      <c r="C221" s="82"/>
+      <c r="D221" s="82"/>
+    </row>
+    <row r="222" spans="2:4">
+      <c r="B222" s="82"/>
+      <c r="C222" s="82"/>
+      <c r="D222" s="82"/>
+    </row>
+    <row r="223" spans="2:4">
+      <c r="B223" s="82"/>
+      <c r="C223" s="82"/>
+      <c r="D223" s="82"/>
+    </row>
+    <row r="224" spans="2:4">
+      <c r="B224" s="82"/>
+      <c r="C224" s="82"/>
+      <c r="D224" s="82"/>
+    </row>
+    <row r="225" spans="2:4">
+      <c r="B225" s="82"/>
+      <c r="C225" s="82"/>
+      <c r="D225" s="82"/>
+    </row>
+    <row r="226" spans="2:4">
+      <c r="B226" s="82"/>
+      <c r="C226" s="82"/>
+      <c r="D226" s="82"/>
+    </row>
+    <row r="227" spans="2:4">
+      <c r="B227" s="82"/>
+      <c r="C227" s="82"/>
+      <c r="D227" s="82"/>
+    </row>
+    <row r="228" spans="2:4">
+      <c r="B228" s="82"/>
+      <c r="C228" s="82"/>
+      <c r="D228" s="82"/>
+    </row>
+    <row r="229" spans="2:4">
+      <c r="B229" s="82"/>
+      <c r="C229" s="82"/>
+      <c r="D229" s="82"/>
+    </row>
+    <row r="230" spans="2:4">
+      <c r="B230" s="82"/>
+      <c r="C230" s="82"/>
+      <c r="D230" s="82"/>
+    </row>
+    <row r="231" spans="2:4">
+      <c r="B231" s="82"/>
+      <c r="C231" s="82"/>
+      <c r="D231" s="82"/>
+    </row>
+    <row r="232" spans="2:4">
+      <c r="B232" s="82"/>
+      <c r="C232" s="82"/>
+      <c r="D232" s="82"/>
+    </row>
+    <row r="233" spans="2:4">
+      <c r="B233" s="82"/>
+      <c r="C233" s="82"/>
+      <c r="D233" s="82"/>
+    </row>
+    <row r="234" spans="2:4">
+      <c r="B234" s="82"/>
+      <c r="C234" s="82"/>
+      <c r="D234" s="82"/>
+    </row>
+    <row r="235" spans="2:4">
+      <c r="B235" s="82"/>
+      <c r="C235" s="82"/>
+      <c r="D235" s="82"/>
+    </row>
+    <row r="236" spans="2:4">
+      <c r="B236" s="82"/>
+      <c r="C236" s="82"/>
+      <c r="D236" s="82"/>
+    </row>
+    <row r="237" spans="2:4">
+      <c r="B237" s="82"/>
+      <c r="C237" s="82"/>
+      <c r="D237" s="82"/>
+    </row>
+    <row r="238" spans="2:4">
+      <c r="B238" s="82"/>
+      <c r="C238" s="82"/>
+      <c r="D238" s="82"/>
+    </row>
+    <row r="239" spans="2:4">
+      <c r="B239" s="82"/>
+      <c r="C239" s="82"/>
+      <c r="D239" s="82"/>
+    </row>
+    <row r="240" spans="2:4">
+      <c r="B240" s="82"/>
+      <c r="C240" s="82"/>
+      <c r="D240" s="82"/>
+    </row>
+    <row r="241" spans="2:4">
+      <c r="B241" s="82"/>
+      <c r="C241" s="82"/>
+      <c r="D241" s="82"/>
+    </row>
+    <row r="242" spans="2:4">
+      <c r="B242" s="82"/>
+      <c r="C242" s="82"/>
+      <c r="D242" s="82"/>
+    </row>
+    <row r="243" spans="2:4">
+      <c r="B243" s="82"/>
+      <c r="C243" s="82"/>
+      <c r="D243" s="82"/>
+    </row>
+    <row r="244" spans="2:4">
+      <c r="B244" s="82"/>
+      <c r="C244" s="82"/>
+      <c r="D244" s="82"/>
+    </row>
+    <row r="245" spans="2:4">
+      <c r="B245" s="82"/>
+      <c r="C245" s="82"/>
+      <c r="D245" s="82"/>
+    </row>
+    <row r="246" spans="2:4">
+      <c r="B246" s="82"/>
+      <c r="C246" s="82"/>
+      <c r="D246" s="82"/>
+    </row>
+    <row r="247" spans="2:4">
+      <c r="B247" s="82"/>
+      <c r="C247" s="82"/>
+      <c r="D247" s="82"/>
+    </row>
+    <row r="248" spans="2:4">
+      <c r="B248" s="82"/>
+      <c r="C248" s="82"/>
+      <c r="D248" s="82"/>
+    </row>
+    <row r="249" spans="2:4">
+      <c r="B249" s="82"/>
+      <c r="C249" s="82"/>
+      <c r="D249" s="82"/>
+    </row>
+    <row r="250" spans="2:4">
+      <c r="B250" s="82"/>
+      <c r="C250" s="82"/>
+      <c r="D250" s="82"/>
+    </row>
+    <row r="251" spans="2:4">
+      <c r="B251" s="82"/>
+      <c r="C251" s="82"/>
+      <c r="D251" s="82"/>
+    </row>
+    <row r="252" spans="2:4">
+      <c r="B252" s="82"/>
+      <c r="C252" s="82"/>
+      <c r="D252" s="82"/>
+    </row>
+    <row r="253" spans="2:4">
+      <c r="B253" s="82"/>
+      <c r="C253" s="82"/>
+      <c r="D253" s="82"/>
+    </row>
+    <row r="254" spans="2:4">
+      <c r="B254" s="82"/>
+      <c r="C254" s="82"/>
+      <c r="D254" s="82"/>
+    </row>
+    <row r="255" spans="2:4">
+      <c r="B255" s="82"/>
+      <c r="C255" s="82"/>
+      <c r="D255" s="82"/>
+    </row>
+    <row r="256" spans="2:4">
+      <c r="B256" s="82"/>
+      <c r="C256" s="82"/>
+      <c r="D256" s="82"/>
+    </row>
+    <row r="257" spans="2:4">
+      <c r="B257" s="82"/>
+      <c r="C257" s="82"/>
+      <c r="D257" s="82"/>
+    </row>
+    <row r="258" spans="2:4">
+      <c r="B258" s="82"/>
+      <c r="C258" s="82"/>
+      <c r="D258" s="82"/>
+    </row>
+    <row r="259" spans="2:4">
+      <c r="B259" s="82"/>
+      <c r="C259" s="82"/>
+      <c r="D259" s="82"/>
+    </row>
+    <row r="260" spans="2:4">
+      <c r="B260" s="82"/>
+      <c r="C260" s="82"/>
+      <c r="D260" s="82"/>
+    </row>
+    <row r="261" spans="2:4">
+      <c r="B261" s="82"/>
+      <c r="C261" s="82"/>
+      <c r="D261" s="82"/>
+    </row>
+    <row r="262" spans="2:4">
+      <c r="B262" s="82"/>
+      <c r="C262" s="82"/>
+      <c r="D262" s="82"/>
+    </row>
+    <row r="263" spans="2:4">
+      <c r="B263" s="82"/>
+      <c r="C263" s="82"/>
+      <c r="D263" s="82"/>
+    </row>
+    <row r="264" spans="2:4">
+      <c r="B264" s="82"/>
+      <c r="C264" s="82"/>
+      <c r="D264" s="82"/>
+    </row>
+    <row r="265" spans="2:4">
+      <c r="B265" s="82"/>
+      <c r="C265" s="82"/>
+      <c r="D265" s="82"/>
+    </row>
+    <row r="266" spans="2:4">
+      <c r="B266" s="82"/>
+      <c r="C266" s="82"/>
+      <c r="D266" s="82"/>
+    </row>
+    <row r="267" spans="2:4">
+      <c r="B267" s="82"/>
+      <c r="C267" s="82"/>
+      <c r="D267" s="82"/>
+    </row>
+    <row r="268" spans="2:4">
+      <c r="B268" s="82"/>
+      <c r="C268" s="82"/>
+      <c r="D268" s="82"/>
+    </row>
+    <row r="269" spans="2:4">
+      <c r="B269" s="82"/>
+      <c r="C269" s="82"/>
+      <c r="D269" s="82"/>
+    </row>
+    <row r="270" spans="2:4">
+      <c r="B270" s="82"/>
+      <c r="C270" s="82"/>
+      <c r="D270" s="82"/>
+    </row>
+    <row r="271" spans="2:4">
+      <c r="B271" s="82"/>
+      <c r="C271" s="82"/>
+      <c r="D271" s="82"/>
+    </row>
+    <row r="272" spans="2:4">
+      <c r="B272" s="82"/>
+      <c r="C272" s="82"/>
+      <c r="D272" s="82"/>
+    </row>
+    <row r="273" spans="2:4">
+      <c r="B273" s="82"/>
+      <c r="C273" s="82"/>
+      <c r="D273" s="82"/>
+    </row>
+    <row r="274" spans="2:4">
+      <c r="B274" s="82"/>
+      <c r="C274" s="82"/>
+      <c r="D274" s="82"/>
+    </row>
+    <row r="275" spans="2:4">
+      <c r="B275" s="82"/>
+      <c r="C275" s="82"/>
+      <c r="D275" s="82"/>
+    </row>
+    <row r="276" spans="2:4">
+      <c r="B276" s="82"/>
+      <c r="C276" s="82"/>
+      <c r="D276" s="82"/>
+    </row>
+    <row r="277" spans="2:4">
+      <c r="B277" s="82"/>
+      <c r="C277" s="82"/>
+      <c r="D277" s="82"/>
+    </row>
+    <row r="278" spans="2:4">
+      <c r="B278" s="82"/>
+      <c r="C278" s="82"/>
+      <c r="D278" s="82"/>
+    </row>
+    <row r="279" spans="2:4">
+      <c r="B279" s="82"/>
+      <c r="C279" s="82"/>
+      <c r="D279" s="82"/>
+    </row>
+    <row r="280" spans="2:4">
+      <c r="B280" s="82"/>
+      <c r="C280" s="82"/>
+      <c r="D280" s="82"/>
+    </row>
+    <row r="281" spans="2:4">
+      <c r="B281" s="82"/>
+      <c r="C281" s="82"/>
+      <c r="D281" s="82"/>
+    </row>
+    <row r="282" spans="2:4">
+      <c r="B282" s="82"/>
+      <c r="C282" s="82"/>
+      <c r="D282" s="82"/>
+    </row>
+    <row r="283" spans="2:4">
+      <c r="B283" s="82"/>
+      <c r="C283" s="82"/>
+      <c r="D283" s="82"/>
+    </row>
+    <row r="284" spans="2:4">
+      <c r="B284" s="82"/>
+      <c r="C284" s="82"/>
+      <c r="D284" s="82"/>
+    </row>
+    <row r="285" spans="2:4">
+      <c r="B285" s="82"/>
+      <c r="C285" s="82"/>
+      <c r="D285" s="82"/>
+    </row>
+    <row r="286" spans="2:4">
+      <c r="B286" s="82"/>
+      <c r="C286" s="82"/>
+      <c r="D286" s="82"/>
+    </row>
+    <row r="287" spans="2:4">
+      <c r="B287" s="82"/>
+      <c r="C287" s="82"/>
+      <c r="D287" s="82"/>
+    </row>
+    <row r="288" spans="2:4">
+      <c r="B288" s="82"/>
+      <c r="C288" s="82"/>
+      <c r="D288" s="82"/>
+    </row>
+    <row r="289" spans="2:4">
+      <c r="B289" s="82"/>
+      <c r="C289" s="82"/>
+      <c r="D289" s="82"/>
+    </row>
+    <row r="290" spans="2:4">
+      <c r="B290" s="82"/>
+      <c r="C290" s="82"/>
+      <c r="D290" s="82"/>
+    </row>
+    <row r="291" spans="2:4">
+      <c r="B291" s="82"/>
+      <c r="C291" s="82"/>
+      <c r="D291" s="82"/>
+    </row>
+    <row r="292" spans="2:4">
+      <c r="B292" s="82"/>
+      <c r="C292" s="82"/>
+      <c r="D292" s="82"/>
+    </row>
+    <row r="293" spans="2:4">
+      <c r="B293" s="82"/>
+      <c r="C293" s="82"/>
+      <c r="D293" s="82"/>
+    </row>
+    <row r="294" spans="2:4">
+      <c r="B294" s="82"/>
+      <c r="C294" s="82"/>
+      <c r="D294" s="82"/>
+    </row>
+    <row r="295" spans="2:4">
+      <c r="B295" s="82"/>
+      <c r="C295" s="82"/>
+      <c r="D295" s="82"/>
+    </row>
+    <row r="296" spans="2:4">
+      <c r="B296" s="82"/>
+      <c r="C296" s="82"/>
+      <c r="D296" s="82"/>
+    </row>
+    <row r="297" spans="2:4">
+      <c r="B297" s="82"/>
+      <c r="C297" s="82"/>
+      <c r="D297" s="82"/>
+    </row>
+    <row r="298" spans="2:4">
+      <c r="B298" s="82"/>
+      <c r="C298" s="82"/>
+      <c r="D298" s="82"/>
+    </row>
+    <row r="299" spans="2:4">
+      <c r="B299" s="82"/>
+      <c r="C299" s="82"/>
+      <c r="D299" s="82"/>
+    </row>
+    <row r="300" spans="2:4">
+      <c r="B300" s="82"/>
+      <c r="C300" s="82"/>
+      <c r="D300" s="82"/>
+    </row>
+    <row r="301" spans="2:4">
+      <c r="B301" s="82"/>
+      <c r="C301" s="82"/>
+      <c r="D301" s="82"/>
+    </row>
+    <row r="302" spans="2:4">
+      <c r="B302" s="82"/>
+      <c r="C302" s="82"/>
+      <c r="D302" s="82"/>
+    </row>
+    <row r="303" spans="2:4">
+      <c r="B303" s="82"/>
+      <c r="C303" s="82"/>
+      <c r="D303" s="82"/>
+    </row>
+    <row r="304" spans="2:4">
+      <c r="B304" s="82"/>
+      <c r="C304" s="82"/>
+      <c r="D304" s="82"/>
+    </row>
+    <row r="305" spans="2:4">
+      <c r="B305" s="82"/>
+      <c r="C305" s="82"/>
+      <c r="D305" s="82"/>
+    </row>
+    <row r="306" spans="2:4">
+      <c r="B306" s="82"/>
+      <c r="C306" s="82"/>
+      <c r="D306" s="82"/>
+    </row>
+    <row r="307" spans="2:4">
+      <c r="B307" s="82"/>
+      <c r="C307" s="82"/>
+      <c r="D307" s="82"/>
+    </row>
+    <row r="308" spans="2:4">
+      <c r="B308" s="82"/>
+      <c r="C308" s="82"/>
+      <c r="D308" s="82"/>
+    </row>
+    <row r="309" spans="2:4">
+      <c r="B309" s="82"/>
+      <c r="C309" s="82"/>
+      <c r="D309" s="82"/>
+    </row>
+    <row r="310" spans="2:4">
+      <c r="B310" s="82"/>
+      <c r="C310" s="82"/>
+      <c r="D310" s="82"/>
+    </row>
+    <row r="311" spans="2:4">
+      <c r="B311" s="82"/>
+      <c r="C311" s="82"/>
+      <c r="D311" s="82"/>
+    </row>
+    <row r="312" spans="2:4">
+      <c r="B312" s="82"/>
+      <c r="C312" s="82"/>
+      <c r="D312" s="82"/>
+    </row>
+    <row r="313" spans="2:4">
+      <c r="B313" s="82"/>
+      <c r="C313" s="82"/>
+      <c r="D313" s="82"/>
+    </row>
+    <row r="314" spans="2:4">
+      <c r="B314" s="82"/>
+      <c r="C314" s="82"/>
+      <c r="D314" s="82"/>
+    </row>
+    <row r="315" spans="2:4">
+      <c r="B315" s="82"/>
+      <c r="C315" s="82"/>
+      <c r="D315" s="82"/>
+    </row>
+    <row r="316" spans="2:4">
+      <c r="B316" s="82"/>
+      <c r="C316" s="82"/>
+      <c r="D316" s="82"/>
+    </row>
+    <row r="317" spans="2:4">
+      <c r="B317" s="82"/>
+      <c r="C317" s="82"/>
+      <c r="D317" s="82"/>
+    </row>
+    <row r="318" spans="2:4">
+      <c r="B318" s="82"/>
+      <c r="C318" s="82"/>
+      <c r="D318" s="82"/>
+    </row>
+    <row r="319" spans="2:4">
+      <c r="B319" s="82"/>
+      <c r="C319" s="82"/>
+      <c r="D319" s="82"/>
+    </row>
+    <row r="320" spans="2:4">
+      <c r="B320" s="82"/>
+      <c r="C320" s="82"/>
+      <c r="D320" s="82"/>
+    </row>
+    <row r="321" spans="2:4">
+      <c r="B321" s="82"/>
+      <c r="C321" s="82"/>
+      <c r="D321" s="82"/>
+    </row>
+    <row r="322" spans="2:4">
+      <c r="B322" s="82"/>
+      <c r="C322" s="82"/>
+      <c r="D322" s="82"/>
+    </row>
+    <row r="323" spans="2:4">
+      <c r="B323" s="82"/>
+      <c r="C323" s="82"/>
+      <c r="D323" s="82"/>
+    </row>
+    <row r="324" spans="2:4">
+      <c r="B324" s="82"/>
+      <c r="C324" s="82"/>
+      <c r="D324" s="82"/>
+    </row>
+    <row r="325" spans="2:4">
+      <c r="B325" s="82"/>
+      <c r="C325" s="82"/>
+      <c r="D325" s="82"/>
+    </row>
+    <row r="326" spans="2:4">
+      <c r="B326" s="82"/>
+      <c r="C326" s="82"/>
+      <c r="D326" s="82"/>
+    </row>
+    <row r="327" spans="2:4">
+      <c r="B327" s="82"/>
+      <c r="C327" s="82"/>
+      <c r="D327" s="82"/>
+    </row>
+    <row r="328" spans="2:4">
+      <c r="B328" s="82"/>
+      <c r="C328" s="82"/>
+      <c r="D328" s="82"/>
+    </row>
+    <row r="329" spans="2:4">
+      <c r="B329" s="82"/>
+      <c r="C329" s="82"/>
+      <c r="D329" s="82"/>
+    </row>
+    <row r="330" spans="2:4">
+      <c r="B330" s="82"/>
+      <c r="C330" s="82"/>
+      <c r="D330" s="82"/>
+    </row>
+    <row r="331" spans="2:4">
+      <c r="B331" s="82"/>
+      <c r="C331" s="82"/>
+      <c r="D331" s="82"/>
+    </row>
+    <row r="332" spans="2:4">
+      <c r="B332" s="82"/>
+      <c r="C332" s="82"/>
+      <c r="D332" s="82"/>
+    </row>
+    <row r="333" spans="2:4">
+      <c r="B333" s="82"/>
+      <c r="C333" s="82"/>
+      <c r="D333" s="82"/>
+    </row>
+    <row r="334" spans="2:4">
+      <c r="B334" s="82"/>
+      <c r="C334" s="82"/>
+      <c r="D334" s="82"/>
+    </row>
+    <row r="335" spans="2:4">
+      <c r="B335" s="82"/>
+      <c r="C335" s="82"/>
+      <c r="D335" s="82"/>
+    </row>
+    <row r="336" spans="2:4">
+      <c r="B336" s="82"/>
+      <c r="C336" s="82"/>
+      <c r="D336" s="82"/>
+    </row>
+    <row r="337" spans="2:4">
+      <c r="B337" s="82"/>
+      <c r="C337" s="82"/>
+      <c r="D337" s="82"/>
+    </row>
+    <row r="338" spans="2:4">
+      <c r="B338" s="82"/>
+      <c r="C338" s="82"/>
+      <c r="D338" s="82"/>
+    </row>
+    <row r="339" spans="2:4">
+      <c r="B339" s="82"/>
+      <c r="C339" s="82"/>
+      <c r="D339" s="82"/>
+    </row>
+    <row r="340" spans="2:4">
+      <c r="B340" s="82"/>
+      <c r="C340" s="82"/>
+      <c r="D340" s="82"/>
+    </row>
+    <row r="341" spans="2:4">
+      <c r="B341" s="82"/>
+      <c r="C341" s="82"/>
+      <c r="D341" s="82"/>
+    </row>
+    <row r="342" spans="2:4">
+      <c r="B342" s="82"/>
+      <c r="C342" s="82"/>
+      <c r="D342" s="82"/>
+    </row>
+    <row r="343" spans="2:4">
+      <c r="B343" s="82"/>
+      <c r="C343" s="82"/>
+      <c r="D343" s="82"/>
+    </row>
+    <row r="344" spans="2:4">
+      <c r="B344" s="82"/>
+      <c r="C344" s="82"/>
+      <c r="D344" s="82"/>
+    </row>
+    <row r="345" spans="2:4">
+      <c r="B345" s="82"/>
+      <c r="C345" s="82"/>
+      <c r="D345" s="82"/>
+    </row>
+    <row r="346" spans="2:4">
+      <c r="B346" s="82"/>
+      <c r="C346" s="82"/>
+      <c r="D346" s="82"/>
+    </row>
+    <row r="347" spans="2:4">
+      <c r="B347" s="82"/>
+      <c r="C347" s="82"/>
+      <c r="D347" s="82"/>
+    </row>
+    <row r="348" spans="2:4">
+      <c r="B348" s="82"/>
+      <c r="C348" s="82"/>
+      <c r="D348" s="82"/>
+    </row>
+    <row r="349" spans="2:4">
+      <c r="B349" s="82"/>
+      <c r="C349" s="82"/>
+      <c r="D349" s="82"/>
+    </row>
+    <row r="350" spans="2:4">
+      <c r="B350" s="82"/>
+      <c r="C350" s="82"/>
+      <c r="D350" s="82"/>
+    </row>
+    <row r="351" spans="2:4">
+      <c r="B351" s="82"/>
+      <c r="C351" s="82"/>
+      <c r="D351" s="82"/>
+    </row>
+    <row r="352" spans="2:4">
+      <c r="B352" s="82"/>
+      <c r="C352" s="82"/>
+      <c r="D352" s="82"/>
+    </row>
+    <row r="353" spans="2:4">
+      <c r="B353" s="82"/>
+      <c r="C353" s="82"/>
+      <c r="D353" s="82"/>
+    </row>
+    <row r="354" spans="2:4">
+      <c r="B354" s="82"/>
+      <c r="C354" s="82"/>
+      <c r="D354" s="82"/>
+    </row>
+    <row r="355" spans="2:4">
+      <c r="B355" s="82"/>
+      <c r="C355" s="82"/>
+      <c r="D355" s="82"/>
+    </row>
+    <row r="356" spans="2:4">
+      <c r="B356" s="82"/>
+      <c r="C356" s="82"/>
+      <c r="D356" s="82"/>
+    </row>
+    <row r="357" spans="2:4">
+      <c r="B357" s="82"/>
+      <c r="C357" s="82"/>
+      <c r="D357" s="82"/>
+    </row>
+    <row r="358" spans="2:4">
+      <c r="B358" s="82"/>
+      <c r="C358" s="82"/>
+      <c r="D358" s="82"/>
+    </row>
+    <row r="359" spans="2:4">
+      <c r="B359" s="82"/>
+      <c r="C359" s="82"/>
+      <c r="D359" s="82"/>
+    </row>
+    <row r="360" spans="2:4">
+      <c r="B360" s="82"/>
+      <c r="C360" s="82"/>
+      <c r="D360" s="82"/>
+    </row>
+    <row r="361" spans="2:4">
+      <c r="B361" s="82"/>
+      <c r="C361" s="82"/>
+      <c r="D361" s="82"/>
+    </row>
+    <row r="362" spans="2:4">
+      <c r="B362" s="82"/>
+      <c r="C362" s="82"/>
+      <c r="D362" s="82"/>
+    </row>
+    <row r="363" spans="2:4">
+      <c r="B363" s="82"/>
+      <c r="C363" s="82"/>
+      <c r="D363" s="82"/>
+    </row>
+    <row r="364" spans="2:4">
+      <c r="B364" s="82"/>
+      <c r="C364" s="82"/>
+      <c r="D364" s="82"/>
+    </row>
+    <row r="365" spans="2:4">
+      <c r="B365" s="82"/>
+      <c r="C365" s="82"/>
+      <c r="D365" s="82"/>
+    </row>
+    <row r="366" spans="2:4">
+      <c r="B366" s="82"/>
+      <c r="C366" s="82"/>
+      <c r="D366" s="82"/>
+    </row>
+    <row r="367" spans="2:4">
+      <c r="B367" s="82"/>
+      <c r="C367" s="82"/>
+      <c r="D367" s="82"/>
+    </row>
+    <row r="368" spans="2:4">
+      <c r="B368" s="82"/>
+      <c r="C368" s="82"/>
+      <c r="D368" s="82"/>
+    </row>
+    <row r="369" spans="2:4">
+      <c r="B369" s="82"/>
+      <c r="C369" s="82"/>
+      <c r="D369" s="82"/>
+    </row>
+    <row r="370" spans="2:4">
+      <c r="B370" s="82"/>
+      <c r="C370" s="82"/>
+      <c r="D370" s="82"/>
+    </row>
+    <row r="371" spans="2:4">
+      <c r="B371" s="82"/>
+      <c r="C371" s="82"/>
+      <c r="D371" s="82"/>
+    </row>
+    <row r="372" spans="2:4">
+      <c r="B372" s="82"/>
+      <c r="C372" s="82"/>
+      <c r="D372" s="82"/>
+    </row>
+    <row r="373" spans="2:4">
+      <c r="B373" s="82"/>
+      <c r="C373" s="82"/>
+      <c r="D373" s="82"/>
+    </row>
+    <row r="374" spans="2:4">
+      <c r="B374" s="82"/>
+      <c r="C374" s="82"/>
+      <c r="D374" s="82"/>
+    </row>
+    <row r="375" spans="2:4">
+      <c r="B375" s="82"/>
+      <c r="C375" s="82"/>
+      <c r="D375" s="82"/>
+    </row>
+    <row r="376" spans="2:4">
+      <c r="B376" s="82"/>
+      <c r="C376" s="82"/>
+      <c r="D376" s="82"/>
+    </row>
+    <row r="377" spans="2:4">
+      <c r="B377" s="82"/>
+      <c r="C377" s="82"/>
+      <c r="D377" s="82"/>
+    </row>
+    <row r="378" spans="2:4">
+      <c r="B378" s="82"/>
+      <c r="C378" s="82"/>
+      <c r="D378" s="82"/>
+    </row>
+    <row r="379" spans="2:4">
+      <c r="B379" s="82"/>
+      <c r="C379" s="82"/>
+      <c r="D379" s="82"/>
+    </row>
+    <row r="380" spans="2:4">
+      <c r="B380" s="82"/>
+      <c r="C380" s="82"/>
+      <c r="D380" s="82"/>
+    </row>
+    <row r="381" spans="2:4">
+      <c r="B381" s="82"/>
+      <c r="C381" s="82"/>
+      <c r="D381" s="82"/>
+    </row>
+    <row r="382" spans="2:4">
+      <c r="B382" s="82"/>
+      <c r="C382" s="82"/>
+      <c r="D382" s="82"/>
+    </row>
+    <row r="383" spans="2:4">
+      <c r="B383" s="82"/>
+      <c r="C383" s="82"/>
+      <c r="D383" s="82"/>
+    </row>
+    <row r="384" spans="2:4">
+      <c r="B384" s="82"/>
+      <c r="C384" s="82"/>
+      <c r="D384" s="82"/>
+    </row>
+    <row r="385" spans="2:4">
+      <c r="B385" s="82"/>
+      <c r="C385" s="82"/>
+      <c r="D385" s="82"/>
+    </row>
+    <row r="386" spans="2:4">
+      <c r="B386" s="82"/>
+      <c r="C386" s="82"/>
+      <c r="D386" s="82"/>
+    </row>
+    <row r="387" spans="2:4">
+      <c r="B387" s="82"/>
+      <c r="C387" s="82"/>
+      <c r="D387" s="82"/>
+    </row>
+    <row r="388" spans="2:4">
+      <c r="B388" s="82"/>
+      <c r="C388" s="82"/>
+      <c r="D388" s="82"/>
+    </row>
+    <row r="389" spans="2:4">
+      <c r="B389" s="82"/>
+      <c r="C389" s="82"/>
+      <c r="D389" s="82"/>
+    </row>
+    <row r="390" spans="2:4">
+      <c r="B390" s="82"/>
+      <c r="C390" s="82"/>
+      <c r="D390" s="82"/>
+    </row>
+    <row r="391" spans="2:4">
+      <c r="B391" s="82"/>
+      <c r="C391" s="82"/>
+      <c r="D391" s="82"/>
+    </row>
+    <row r="392" spans="2:4">
+      <c r="B392" s="82"/>
+      <c r="C392" s="82"/>
+      <c r="D392" s="82"/>
+    </row>
+    <row r="393" spans="2:4">
+      <c r="B393" s="82"/>
+      <c r="C393" s="82"/>
+      <c r="D393" s="82"/>
+    </row>
+    <row r="394" spans="2:4">
+      <c r="B394" s="82"/>
+      <c r="C394" s="82"/>
+      <c r="D394" s="82"/>
+    </row>
+    <row r="395" spans="2:4">
+      <c r="B395" s="82"/>
+      <c r="C395" s="82"/>
+      <c r="D395" s="82"/>
+    </row>
+    <row r="396" spans="2:4">
+      <c r="B396" s="82"/>
+      <c r="C396" s="82"/>
+      <c r="D396" s="82"/>
+    </row>
+    <row r="397" spans="2:4">
+      <c r="B397" s="82"/>
+      <c r="C397" s="82"/>
+      <c r="D397" s="82"/>
+    </row>
+    <row r="398" spans="2:4">
+      <c r="B398" s="82"/>
+      <c r="C398" s="82"/>
+      <c r="D398" s="82"/>
+    </row>
+    <row r="399" spans="2:4">
+      <c r="B399" s="82"/>
+      <c r="C399" s="82"/>
+      <c r="D399" s="82"/>
+    </row>
+    <row r="400" spans="2:4">
+      <c r="B400" s="82"/>
+      <c r="C400" s="82"/>
+      <c r="D400" s="82"/>
+    </row>
+    <row r="401" spans="2:4">
+      <c r="B401" s="82"/>
+      <c r="C401" s="82"/>
+      <c r="D401" s="82"/>
+    </row>
+    <row r="402" spans="2:4">
+      <c r="B402" s="82"/>
+      <c r="C402" s="82"/>
+      <c r="D402" s="82"/>
+    </row>
+    <row r="403" spans="2:4">
+      <c r="B403" s="82"/>
+      <c r="C403" s="82"/>
+      <c r="D403" s="82"/>
+    </row>
+    <row r="404" spans="2:4">
+      <c r="B404" s="82"/>
+      <c r="C404" s="82"/>
+      <c r="D404" s="82"/>
+    </row>
+    <row r="405" spans="2:4">
+      <c r="B405" s="82"/>
+      <c r="C405" s="82"/>
+      <c r="D405" s="82"/>
+    </row>
+    <row r="406" spans="2:4">
+      <c r="B406" s="82"/>
+      <c r="C406" s="82"/>
+      <c r="D406" s="82"/>
+    </row>
+    <row r="407" spans="2:4">
+      <c r="B407" s="82"/>
+      <c r="C407" s="82"/>
+      <c r="D407" s="82"/>
+    </row>
+    <row r="408" spans="2:4">
+      <c r="B408" s="82"/>
+      <c r="C408" s="82"/>
+      <c r="D408" s="82"/>
+    </row>
+    <row r="409" spans="2:4">
+      <c r="B409" s="82"/>
+      <c r="C409" s="82"/>
+      <c r="D409" s="82"/>
+    </row>
+    <row r="410" spans="2:4">
+      <c r="B410" s="82"/>
+      <c r="C410" s="82"/>
+      <c r="D410" s="82"/>
+    </row>
+    <row r="411" spans="2:4">
+      <c r="B411" s="82"/>
+      <c r="C411" s="82"/>
+      <c r="D411" s="82"/>
+    </row>
+    <row r="412" spans="2:4">
+      <c r="B412" s="82"/>
+      <c r="C412" s="82"/>
+      <c r="D412" s="82"/>
+    </row>
+    <row r="413" spans="2:4">
+      <c r="B413" s="82"/>
+      <c r="C413" s="82"/>
+      <c r="D413" s="82"/>
+    </row>
+    <row r="414" spans="2:4">
+      <c r="B414" s="82"/>
+      <c r="C414" s="82"/>
+      <c r="D414" s="82"/>
+    </row>
+    <row r="415" spans="2:4">
+      <c r="B415" s="82"/>
+      <c r="C415" s="82"/>
+      <c r="D415" s="82"/>
+    </row>
+    <row r="416" spans="2:4">
+      <c r="B416" s="82"/>
+      <c r="C416" s="82"/>
+      <c r="D416" s="82"/>
+    </row>
+    <row r="417" spans="2:4">
+      <c r="B417" s="82"/>
+      <c r="C417" s="82"/>
+      <c r="D417" s="82"/>
+    </row>
+    <row r="418" spans="2:4">
+      <c r="B418" s="82"/>
+      <c r="C418" s="82"/>
+      <c r="D418" s="82"/>
+    </row>
+    <row r="419" spans="2:4">
+      <c r="B419" s="82"/>
+      <c r="C419" s="82"/>
+      <c r="D419" s="82"/>
+    </row>
+    <row r="420" spans="2:4">
+      <c r="B420" s="82"/>
+      <c r="C420" s="82"/>
+      <c r="D420" s="82"/>
+    </row>
+    <row r="421" spans="2:4">
+      <c r="B421" s="82"/>
+      <c r="C421" s="82"/>
+      <c r="D421" s="82"/>
+    </row>
+    <row r="422" spans="2:4">
+      <c r="B422" s="82"/>
+      <c r="C422" s="82"/>
+      <c r="D422" s="82"/>
+    </row>
+    <row r="423" spans="2:4">
+      <c r="B423" s="82"/>
+      <c r="C423" s="82"/>
+      <c r="D423" s="82"/>
+    </row>
+    <row r="424" spans="2:4">
+      <c r="B424" s="82"/>
+      <c r="C424" s="82"/>
+      <c r="D424" s="82"/>
+    </row>
+    <row r="425" spans="2:4">
+      <c r="B425" s="82"/>
+      <c r="C425" s="82"/>
+      <c r="D425" s="82"/>
+    </row>
+    <row r="426" spans="2:4">
+      <c r="B426" s="82"/>
+      <c r="C426" s="82"/>
+      <c r="D426" s="82"/>
+    </row>
+    <row r="427" spans="2:4">
+      <c r="B427" s="82"/>
+      <c r="C427" s="82"/>
+      <c r="D427" s="82"/>
+    </row>
+    <row r="428" spans="2:4">
+      <c r="B428" s="82"/>
+      <c r="C428" s="82"/>
+      <c r="D428" s="82"/>
+    </row>
+    <row r="429" spans="2:4">
+      <c r="B429" s="82"/>
+      <c r="C429" s="82"/>
+      <c r="D429" s="82"/>
+    </row>
+    <row r="430" spans="2:4">
+      <c r="B430" s="82"/>
+      <c r="C430" s="82"/>
+      <c r="D430" s="82"/>
+    </row>
+    <row r="431" spans="2:4">
+      <c r="B431" s="82"/>
+      <c r="C431" s="82"/>
+      <c r="D431" s="82"/>
+    </row>
+    <row r="432" spans="2:4">
+      <c r="B432" s="82"/>
+      <c r="C432" s="82"/>
+      <c r="D432" s="82"/>
+    </row>
+    <row r="433" spans="2:4">
+      <c r="B433" s="82"/>
+      <c r="C433" s="82"/>
+      <c r="D433" s="82"/>
+    </row>
+    <row r="434" spans="2:4">
+      <c r="B434" s="82"/>
+      <c r="C434" s="82"/>
+      <c r="D434" s="82"/>
+    </row>
+    <row r="435" spans="2:4">
+      <c r="B435" s="82"/>
+      <c r="C435" s="82"/>
+      <c r="D435" s="82"/>
+    </row>
+    <row r="436" spans="2:4">
+      <c r="B436" s="82"/>
+      <c r="C436" s="82"/>
+      <c r="D436" s="82"/>
+    </row>
+    <row r="437" spans="2:4">
+      <c r="B437" s="82"/>
+      <c r="C437" s="82"/>
+      <c r="D437" s="82"/>
+    </row>
+    <row r="438" spans="2:4">
+      <c r="B438" s="82"/>
+      <c r="C438" s="82"/>
+      <c r="D438" s="82"/>
+    </row>
+    <row r="439" spans="2:4">
+      <c r="B439" s="82"/>
+      <c r="C439" s="82"/>
+      <c r="D439" s="82"/>
+    </row>
+    <row r="440" spans="2:4">
+      <c r="B440" s="82"/>
+      <c r="C440" s="82"/>
+      <c r="D440" s="82"/>
+    </row>
+    <row r="441" spans="2:4">
+      <c r="B441" s="82"/>
+      <c r="C441" s="82"/>
+      <c r="D441" s="82"/>
+    </row>
+    <row r="442" spans="2:4">
+      <c r="B442" s="82"/>
+      <c r="C442" s="82"/>
+      <c r="D442" s="82"/>
+    </row>
+    <row r="443" spans="2:4">
+      <c r="B443" s="82"/>
+      <c r="C443" s="82"/>
+      <c r="D443" s="82"/>
+    </row>
+    <row r="444" spans="2:4">
+      <c r="B444" s="82"/>
+      <c r="C444" s="82"/>
+      <c r="D444" s="82"/>
+    </row>
+    <row r="445" spans="2:4">
+      <c r="B445" s="82"/>
+      <c r="C445" s="82"/>
+      <c r="D445" s="82"/>
+    </row>
+    <row r="446" spans="2:4">
+      <c r="B446" s="82"/>
+      <c r="C446" s="82"/>
+      <c r="D446" s="82"/>
+    </row>
+    <row r="447" spans="2:4">
+      <c r="B447" s="82"/>
+      <c r="C447" s="82"/>
+      <c r="D447" s="82"/>
+    </row>
+    <row r="448" spans="2:4">
+      <c r="B448" s="82"/>
+      <c r="C448" s="82"/>
+      <c r="D448" s="82"/>
+    </row>
+    <row r="449" spans="2:4">
+      <c r="B449" s="82"/>
+      <c r="C449" s="82"/>
+      <c r="D449" s="82"/>
+    </row>
+    <row r="450" spans="2:4">
+      <c r="B450" s="82"/>
+      <c r="C450" s="82"/>
+      <c r="D450" s="82"/>
+    </row>
+    <row r="451" spans="2:4">
+      <c r="B451" s="82"/>
+      <c r="C451" s="82"/>
+      <c r="D451" s="82"/>
+    </row>
+    <row r="452" spans="2:4">
+      <c r="B452" s="82"/>
+      <c r="C452" s="82"/>
+      <c r="D452" s="82"/>
+    </row>
+    <row r="453" spans="2:4">
+      <c r="B453" s="82"/>
+      <c r="C453" s="82"/>
+      <c r="D453" s="82"/>
+    </row>
+    <row r="454" spans="2:4">
+      <c r="B454" s="82"/>
+      <c r="C454" s="82"/>
+      <c r="D454" s="82"/>
+    </row>
+    <row r="455" spans="2:4">
+      <c r="B455" s="82"/>
+      <c r="C455" s="82"/>
+      <c r="D455" s="82"/>
+    </row>
+    <row r="456" spans="2:4">
+      <c r="B456" s="82"/>
+      <c r="C456" s="82"/>
+      <c r="D456" s="82"/>
+    </row>
+    <row r="457" spans="2:4">
+      <c r="B457" s="82"/>
+      <c r="C457" s="82"/>
+      <c r="D457" s="82"/>
+    </row>
+    <row r="458" spans="2:4">
+      <c r="B458" s="82"/>
+      <c r="C458" s="82"/>
+      <c r="D458" s="82"/>
+    </row>
+    <row r="459" spans="2:4">
+      <c r="B459" s="82"/>
+      <c r="C459" s="82"/>
+      <c r="D459" s="82"/>
+    </row>
+    <row r="460" spans="2:4">
+      <c r="B460" s="82"/>
+      <c r="C460" s="82"/>
+      <c r="D460" s="82"/>
+    </row>
+    <row r="461" spans="2:4">
+      <c r="B461" s="82"/>
+      <c r="C461" s="82"/>
+      <c r="D461" s="82"/>
+    </row>
+    <row r="462" spans="2:4">
+      <c r="B462" s="82"/>
+      <c r="C462" s="82"/>
+      <c r="D462" s="82"/>
+    </row>
+    <row r="463" spans="2:4">
+      <c r="B463" s="82"/>
+      <c r="C463" s="82"/>
+      <c r="D463" s="82"/>
+    </row>
+    <row r="464" spans="2:4">
+      <c r="B464" s="82"/>
+      <c r="C464" s="82"/>
+      <c r="D464" s="82"/>
+    </row>
+    <row r="465" spans="2:4">
+      <c r="B465" s="82"/>
+      <c r="C465" s="82"/>
+      <c r="D465" s="82"/>
+    </row>
+    <row r="466" spans="2:4">
+      <c r="B466" s="82"/>
+      <c r="C466" s="82"/>
+      <c r="D466" s="82"/>
+    </row>
+    <row r="467" spans="2:4">
+      <c r="B467" s="82"/>
+      <c r="C467" s="82"/>
+      <c r="D467" s="82"/>
+    </row>
+    <row r="468" spans="2:4">
+      <c r="B468" s="82"/>
+      <c r="C468" s="82"/>
+      <c r="D468" s="82"/>
+    </row>
+    <row r="469" spans="2:4">
+      <c r="B469" s="82"/>
+      <c r="C469" s="82"/>
+      <c r="D469" s="82"/>
+    </row>
+    <row r="470" spans="2:4">
+      <c r="B470" s="82"/>
+      <c r="C470" s="82"/>
+      <c r="D470" s="82"/>
+    </row>
+    <row r="471" spans="2:4">
+      <c r="B471" s="82"/>
+      <c r="C471" s="82"/>
+      <c r="D471" s="82"/>
+    </row>
+    <row r="472" spans="2:4">
+      <c r="B472" s="82"/>
+      <c r="C472" s="82"/>
+      <c r="D472" s="82"/>
+    </row>
+    <row r="473" spans="2:4">
+      <c r="B473" s="82"/>
+      <c r="C473" s="82"/>
+      <c r="D473" s="82"/>
+    </row>
+    <row r="474" spans="2:4">
+      <c r="B474" s="82"/>
+      <c r="C474" s="82"/>
+      <c r="D474" s="82"/>
+    </row>
+    <row r="475" spans="2:4">
+      <c r="B475" s="82"/>
+      <c r="C475" s="82"/>
+      <c r="D475" s="82"/>
+    </row>
+    <row r="476" spans="2:4">
+      <c r="B476" s="82"/>
+      <c r="C476" s="82"/>
+      <c r="D476" s="82"/>
+    </row>
+    <row r="477" spans="2:4">
+      <c r="B477" s="82"/>
+      <c r="C477" s="82"/>
+      <c r="D477" s="82"/>
+    </row>
+    <row r="478" spans="2:4">
+      <c r="B478" s="82"/>
+      <c r="C478" s="82"/>
+      <c r="D478" s="82"/>
+    </row>
+    <row r="479" spans="2:4">
+      <c r="B479" s="82"/>
+      <c r="C479" s="82"/>
+      <c r="D479" s="82"/>
+    </row>
+    <row r="480" spans="2:4">
+      <c r="B480" s="82"/>
+      <c r="C480" s="82"/>
+      <c r="D480" s="82"/>
+    </row>
+    <row r="481" spans="2:4">
+      <c r="B481" s="82"/>
+      <c r="C481" s="82"/>
+      <c r="D481" s="82"/>
+    </row>
+    <row r="482" spans="2:4">
+      <c r="B482" s="82"/>
+      <c r="C482" s="82"/>
+      <c r="D482" s="82"/>
+    </row>
+    <row r="483" spans="2:4">
+      <c r="B483" s="82"/>
+      <c r="C483" s="82"/>
+      <c r="D483" s="82"/>
+    </row>
+    <row r="484" spans="2:4">
+      <c r="B484" s="82"/>
+      <c r="C484" s="82"/>
+      <c r="D484" s="82"/>
+    </row>
+    <row r="485" spans="2:4">
+      <c r="B485" s="82"/>
+      <c r="C485" s="82"/>
+      <c r="D485" s="82"/>
+    </row>
+    <row r="486" spans="2:4">
+      <c r="B486" s="82"/>
+      <c r="C486" s="82"/>
+      <c r="D486" s="82"/>
+    </row>
+    <row r="487" spans="2:4">
+      <c r="B487" s="82"/>
+      <c r="C487" s="82"/>
+      <c r="D487" s="82"/>
+    </row>
+    <row r="488" spans="2:4">
+      <c r="B488" s="82"/>
+      <c r="C488" s="82"/>
+      <c r="D488" s="82"/>
+    </row>
+    <row r="489" spans="2:4">
+      <c r="B489" s="82"/>
+      <c r="C489" s="82"/>
+      <c r="D489" s="82"/>
+    </row>
+    <row r="490" spans="2:4">
+      <c r="B490" s="82"/>
+      <c r="C490" s="82"/>
+      <c r="D490" s="82"/>
+    </row>
+    <row r="491" spans="2:4">
+      <c r="B491" s="82"/>
+      <c r="C491" s="82"/>
+      <c r="D491" s="82"/>
+    </row>
+    <row r="492" spans="2:4">
+      <c r="B492" s="82"/>
+      <c r="C492" s="82"/>
+      <c r="D492" s="82"/>
+    </row>
+    <row r="493" spans="2:4">
+      <c r="B493" s="82"/>
+      <c r="C493" s="82"/>
+      <c r="D493" s="82"/>
+    </row>
+    <row r="494" spans="2:4">
+      <c r="B494" s="82"/>
+      <c r="C494" s="82"/>
+      <c r="D494" s="82"/>
+    </row>
+    <row r="495" spans="2:4">
+      <c r="B495" s="82"/>
+      <c r="C495" s="82"/>
+      <c r="D495" s="82"/>
+    </row>
+    <row r="496" spans="2:4">
+      <c r="B496" s="82"/>
+      <c r="C496" s="82"/>
+      <c r="D496" s="82"/>
+    </row>
+    <row r="497" spans="2:4">
+      <c r="B497" s="82"/>
+      <c r="C497" s="82"/>
+      <c r="D497" s="82"/>
+    </row>
+    <row r="498" spans="2:4">
+      <c r="B498" s="82"/>
+      <c r="C498" s="82"/>
+      <c r="D498" s="82"/>
+    </row>
+    <row r="499" spans="2:4">
+      <c r="B499" s="82"/>
+      <c r="C499" s="82"/>
+      <c r="D499" s="82"/>
+    </row>
+    <row r="500" spans="2:4">
+      <c r="B500" s="82"/>
+      <c r="C500" s="82"/>
+      <c r="D500" s="82"/>
+    </row>
+    <row r="501" spans="2:4">
+      <c r="B501" s="82"/>
+      <c r="C501" s="82"/>
+      <c r="D501" s="82"/>
+    </row>
+    <row r="502" spans="2:4">
+      <c r="B502" s="82"/>
+      <c r="C502" s="82"/>
+      <c r="D502" s="82"/>
+    </row>
+    <row r="503" spans="2:4">
+      <c r="B503" s="82"/>
+      <c r="C503" s="82"/>
+      <c r="D503" s="82"/>
+    </row>
+    <row r="504" spans="2:4">
+      <c r="B504" s="82"/>
+      <c r="C504" s="82"/>
+      <c r="D504" s="82"/>
+    </row>
+    <row r="505" spans="2:4">
+      <c r="B505" s="82"/>
+      <c r="C505" s="82"/>
+      <c r="D505" s="82"/>
+    </row>
+    <row r="506" spans="2:4">
+      <c r="B506" s="82"/>
+      <c r="C506" s="82"/>
+      <c r="D506" s="82"/>
+    </row>
+    <row r="507" spans="2:4">
+      <c r="B507" s="82"/>
+      <c r="C507" s="82"/>
+      <c r="D507" s="82"/>
+    </row>
+    <row r="508" spans="2:4">
+      <c r="B508" s="82"/>
+      <c r="C508" s="82"/>
+      <c r="D508" s="82"/>
+    </row>
+    <row r="509" spans="2:4">
+      <c r="B509" s="82"/>
+      <c r="C509" s="82"/>
+      <c r="D509" s="82"/>
+    </row>
+    <row r="510" spans="2:4">
+      <c r="B510" s="82"/>
+      <c r="C510" s="82"/>
+      <c r="D510" s="82"/>
+    </row>
+    <row r="511" spans="2:4">
+      <c r="B511" s="82"/>
+      <c r="C511" s="82"/>
+      <c r="D511" s="82"/>
+    </row>
+    <row r="512" spans="2:4">
+      <c r="B512" s="82"/>
+      <c r="C512" s="82"/>
+      <c r="D512" s="82"/>
+    </row>
+    <row r="513" spans="2:4">
+      <c r="B513" s="82"/>
+      <c r="C513" s="82"/>
+      <c r="D513" s="82"/>
+    </row>
+    <row r="514" spans="2:4">
+      <c r="B514" s="82"/>
+      <c r="C514" s="82"/>
+      <c r="D514" s="82"/>
+    </row>
+    <row r="515" spans="2:4">
+      <c r="B515" s="82"/>
+      <c r="C515" s="82"/>
+      <c r="D515" s="82"/>
+    </row>
+    <row r="516" spans="2:4">
+      <c r="B516" s="82"/>
+      <c r="C516" s="82"/>
+      <c r="D516" s="82"/>
+    </row>
+    <row r="517" spans="2:4">
+      <c r="B517" s="82"/>
+      <c r="C517" s="82"/>
+      <c r="D517" s="82"/>
+    </row>
+    <row r="518" spans="2:4">
+      <c r="B518" s="82"/>
+      <c r="C518" s="82"/>
+      <c r="D518" s="82"/>
+    </row>
+    <row r="519" spans="2:4">
+      <c r="B519" s="82"/>
+      <c r="C519" s="82"/>
+      <c r="D519" s="82"/>
+    </row>
+    <row r="520" spans="2:4">
+      <c r="B520" s="82"/>
+      <c r="C520" s="82"/>
+      <c r="D520" s="82"/>
+    </row>
+    <row r="521" spans="2:4">
+      <c r="B521" s="82"/>
+      <c r="C521" s="82"/>
+      <c r="D521" s="82"/>
+    </row>
+    <row r="522" spans="2:4">
+      <c r="B522" s="82"/>
+      <c r="C522" s="82"/>
+      <c r="D522" s="82"/>
+    </row>
+    <row r="523" spans="2:4">
+      <c r="B523" s="82"/>
+      <c r="C523" s="82"/>
+      <c r="D523" s="82"/>
+    </row>
+    <row r="524" spans="2:4">
+      <c r="B524" s="82"/>
+      <c r="C524" s="82"/>
+      <c r="D524" s="82"/>
+    </row>
+    <row r="525" spans="2:4">
+      <c r="B525" s="82"/>
+      <c r="C525" s="82"/>
+      <c r="D525" s="82"/>
+    </row>
+    <row r="526" spans="2:4">
+      <c r="B526" s="82"/>
+      <c r="C526" s="82"/>
+      <c r="D526" s="82"/>
+    </row>
+    <row r="527" spans="2:4">
+      <c r="B527" s="82"/>
+      <c r="C527" s="82"/>
+      <c r="D527" s="82"/>
+    </row>
+    <row r="528" spans="2:4">
+      <c r="B528" s="82"/>
+      <c r="C528" s="82"/>
+      <c r="D528" s="82"/>
+    </row>
+    <row r="529" spans="2:4">
+      <c r="B529" s="82"/>
+      <c r="C529" s="82"/>
+      <c r="D529" s="82"/>
+    </row>
+    <row r="530" spans="2:4">
+      <c r="B530" s="82"/>
+      <c r="C530" s="82"/>
+      <c r="D530" s="82"/>
+    </row>
+    <row r="531" spans="2:4">
+      <c r="B531" s="82"/>
+      <c r="C531" s="82"/>
+      <c r="D531" s="82"/>
+    </row>
+    <row r="532" spans="2:4">
+      <c r="B532" s="82"/>
+      <c r="C532" s="82"/>
+      <c r="D532" s="82"/>
+    </row>
+    <row r="533" spans="2:4">
+      <c r="B533" s="82"/>
+      <c r="C533" s="82"/>
+      <c r="D533" s="82"/>
+    </row>
+    <row r="534" spans="2:4">
+      <c r="B534" s="82"/>
+      <c r="C534" s="82"/>
+      <c r="D534" s="82"/>
+    </row>
+    <row r="535" spans="2:4">
+      <c r="B535" s="82"/>
+      <c r="C535" s="82"/>
+      <c r="D535" s="82"/>
+    </row>
+    <row r="536" spans="2:4">
+      <c r="B536" s="82"/>
+      <c r="C536" s="82"/>
+      <c r="D536" s="82"/>
+    </row>
+    <row r="537" spans="2:4">
+      <c r="B537" s="82"/>
+      <c r="C537" s="82"/>
+      <c r="D537" s="82"/>
+    </row>
+    <row r="538" spans="2:4">
+      <c r="B538" s="82"/>
+      <c r="C538" s="82"/>
+      <c r="D538" s="82"/>
+    </row>
+    <row r="539" spans="2:4">
+      <c r="B539" s="82"/>
+      <c r="C539" s="82"/>
+      <c r="D539" s="82"/>
+    </row>
+    <row r="540" spans="2:4">
+      <c r="B540" s="82"/>
+      <c r="C540" s="82"/>
+      <c r="D540" s="82"/>
+    </row>
+    <row r="541" spans="2:4">
+      <c r="B541" s="82"/>
+      <c r="C541" s="82"/>
+      <c r="D541" s="82"/>
+    </row>
+    <row r="542" spans="2:4">
+      <c r="B542" s="82"/>
+      <c r="C542" s="82"/>
+      <c r="D542" s="82"/>
+    </row>
+    <row r="543" spans="2:4">
+      <c r="B543" s="82"/>
+      <c r="C543" s="82"/>
+      <c r="D543" s="82"/>
+    </row>
+    <row r="544" spans="2:4">
+      <c r="B544" s="82"/>
+      <c r="C544" s="82"/>
+      <c r="D544" s="82"/>
+    </row>
+    <row r="545" spans="2:4">
+      <c r="B545" s="82"/>
+      <c r="C545" s="82"/>
+      <c r="D545" s="82"/>
+    </row>
+    <row r="546" spans="2:4">
+      <c r="B546" s="82"/>
+      <c r="C546" s="82"/>
+      <c r="D546" s="82"/>
+    </row>
+    <row r="547" spans="2:4">
+      <c r="B547" s="82"/>
+      <c r="C547" s="82"/>
+      <c r="D547" s="82"/>
+    </row>
+    <row r="548" spans="2:4">
+      <c r="B548" s="82"/>
+      <c r="C548" s="82"/>
+      <c r="D548" s="82"/>
+    </row>
+    <row r="549" spans="2:4">
+      <c r="B549" s="82"/>
+      <c r="C549" s="82"/>
+      <c r="D549" s="82"/>
+    </row>
+    <row r="550" spans="2:4">
+      <c r="B550" s="82"/>
+      <c r="C550" s="82"/>
+      <c r="D550" s="82"/>
+    </row>
+    <row r="551" spans="2:4">
+      <c r="B551" s="82"/>
+      <c r="C551" s="82"/>
+      <c r="D551" s="82"/>
+    </row>
+    <row r="552" spans="2:4">
+      <c r="B552" s="82"/>
+      <c r="C552" s="82"/>
+      <c r="D552" s="82"/>
+    </row>
+    <row r="553" spans="2:4">
+      <c r="B553" s="82"/>
+      <c r="C553" s="82"/>
+      <c r="D553" s="82"/>
+    </row>
+    <row r="554" spans="2:4">
+      <c r="B554" s="82"/>
+      <c r="C554" s="82"/>
+      <c r="D554" s="82"/>
+    </row>
+    <row r="555" spans="2:4">
+      <c r="B555" s="82"/>
+      <c r="C555" s="82"/>
+      <c r="D555" s="82"/>
+    </row>
+    <row r="556" spans="2:4">
+      <c r="B556" s="82"/>
+      <c r="C556" s="82"/>
+      <c r="D556" s="82"/>
+    </row>
+    <row r="557" spans="2:4">
+      <c r="B557" s="82"/>
+      <c r="C557" s="82"/>
+      <c r="D557" s="82"/>
+    </row>
+    <row r="558" spans="2:4">
+      <c r="B558" s="82"/>
+      <c r="C558" s="82"/>
+      <c r="D558" s="82"/>
+    </row>
+    <row r="559" spans="2:4">
+      <c r="B559" s="82"/>
+      <c r="C559" s="82"/>
+      <c r="D559" s="82"/>
+    </row>
+    <row r="560" spans="2:4">
+      <c r="B560" s="82"/>
+      <c r="C560" s="82"/>
+      <c r="D560" s="82"/>
+    </row>
+    <row r="561" spans="2:4">
+      <c r="B561" s="82"/>
+      <c r="C561" s="82"/>
+      <c r="D561" s="82"/>
+    </row>
+    <row r="562" spans="2:4">
+      <c r="B562" s="82"/>
+      <c r="C562" s="82"/>
+      <c r="D562" s="82"/>
+    </row>
+    <row r="563" spans="2:4">
+      <c r="B563" s="82"/>
+      <c r="C563" s="82"/>
+      <c r="D563" s="82"/>
+    </row>
+    <row r="564" spans="2:4">
+      <c r="B564" s="82"/>
+      <c r="C564" s="82"/>
+      <c r="D564" s="82"/>
+    </row>
+    <row r="565" spans="2:4">
+      <c r="B565" s="82"/>
+      <c r="C565" s="82"/>
+      <c r="D565" s="82"/>
+    </row>
+    <row r="566" spans="2:4">
+      <c r="B566" s="82"/>
+      <c r="C566" s="82"/>
+      <c r="D566" s="82"/>
+    </row>
+    <row r="567" spans="2:4">
+      <c r="B567" s="82"/>
+      <c r="C567" s="82"/>
+      <c r="D567" s="82"/>
+    </row>
+    <row r="568" spans="2:4">
+      <c r="B568" s="82"/>
+      <c r="C568" s="82"/>
+      <c r="D568" s="82"/>
+    </row>
+    <row r="569" spans="2:4">
+      <c r="B569" s="82"/>
+      <c r="C569" s="82"/>
+      <c r="D569" s="82"/>
+    </row>
+    <row r="570" spans="2:4">
+      <c r="B570" s="82"/>
+      <c r="C570" s="82"/>
+      <c r="D570" s="82"/>
+    </row>
+    <row r="571" spans="2:4">
+      <c r="B571" s="82"/>
+      <c r="C571" s="82"/>
+      <c r="D571" s="82"/>
+    </row>
+    <row r="572" spans="2:4">
+      <c r="B572" s="82"/>
+      <c r="C572" s="82"/>
+      <c r="D572" s="82"/>
+    </row>
+    <row r="573" spans="2:4">
+      <c r="B573" s="82"/>
+      <c r="C573" s="82"/>
+      <c r="D573" s="82"/>
+    </row>
+    <row r="574" spans="2:4">
+      <c r="B574" s="82"/>
+      <c r="C574" s="82"/>
+      <c r="D574" s="82"/>
+    </row>
+    <row r="575" spans="2:4">
+      <c r="B575" s="82"/>
+      <c r="C575" s="82"/>
+      <c r="D575" s="82"/>
+    </row>
+    <row r="576" spans="2:4">
+      <c r="B576" s="82"/>
+      <c r="C576" s="82"/>
+      <c r="D576" s="82"/>
+    </row>
+    <row r="577" spans="2:4">
+      <c r="B577" s="82"/>
+      <c r="C577" s="82"/>
+      <c r="D577" s="82"/>
+    </row>
+    <row r="578" spans="2:4">
+      <c r="B578" s="82"/>
+      <c r="C578" s="82"/>
+      <c r="D578" s="82"/>
+    </row>
+    <row r="579" spans="2:4">
+      <c r="B579" s="82"/>
+      <c r="C579" s="82"/>
+      <c r="D579" s="82"/>
+    </row>
+    <row r="580" spans="2:4">
+      <c r="B580" s="82"/>
+      <c r="C580" s="82"/>
+      <c r="D580" s="82"/>
+    </row>
+    <row r="581" spans="2:4">
+      <c r="B581" s="82"/>
+      <c r="C581" s="82"/>
+      <c r="D581" s="82"/>
+    </row>
+    <row r="582" spans="2:4">
+      <c r="B582" s="82"/>
+      <c r="C582" s="82"/>
+      <c r="D582" s="82"/>
+    </row>
+    <row r="583" spans="2:4">
+      <c r="B583" s="82"/>
+      <c r="C583" s="82"/>
+      <c r="D583" s="82"/>
+    </row>
+    <row r="584" spans="2:4">
+      <c r="B584" s="82"/>
+      <c r="C584" s="82"/>
+      <c r="D584" s="82"/>
+    </row>
+    <row r="585" spans="2:4">
+      <c r="B585" s="82"/>
+      <c r="C585" s="82"/>
+      <c r="D585" s="82"/>
+    </row>
+    <row r="586" spans="2:4">
+      <c r="B586" s="82"/>
+      <c r="C586" s="82"/>
+      <c r="D586" s="82"/>
+    </row>
+    <row r="587" spans="2:4">
+      <c r="B587" s="82"/>
+      <c r="C587" s="82"/>
+      <c r="D587" s="82"/>
+    </row>
+    <row r="588" spans="2:4">
+      <c r="B588" s="82"/>
+      <c r="C588" s="82"/>
+      <c r="D588" s="82"/>
+    </row>
+    <row r="589" spans="2:4">
+      <c r="B589" s="82"/>
+      <c r="C589" s="82"/>
+      <c r="D589" s="82"/>
+    </row>
+    <row r="590" spans="2:4">
+      <c r="B590" s="82"/>
+      <c r="C590" s="82"/>
+      <c r="D590" s="82"/>
+    </row>
+    <row r="591" spans="2:4">
+      <c r="B591" s="82"/>
+      <c r="C591" s="82"/>
+      <c r="D591" s="82"/>
+    </row>
+    <row r="592" spans="2:4">
+      <c r="B592" s="82"/>
+      <c r="C592" s="82"/>
+      <c r="D592" s="82"/>
+    </row>
+    <row r="593" spans="2:4">
+      <c r="B593" s="82"/>
+      <c r="C593" s="82"/>
+      <c r="D593" s="82"/>
+    </row>
+    <row r="594" spans="2:4">
+      <c r="B594" s="82"/>
+      <c r="C594" s="82"/>
+      <c r="D594" s="82"/>
+    </row>
+    <row r="595" spans="2:4">
+      <c r="B595" s="82"/>
+      <c r="C595" s="82"/>
+      <c r="D595" s="82"/>
+    </row>
+    <row r="596" spans="2:4">
+      <c r="B596" s="82"/>
+      <c r="C596" s="82"/>
+      <c r="D596" s="82"/>
+    </row>
+    <row r="597" spans="2:4">
+      <c r="B597" s="82"/>
+      <c r="C597" s="82"/>
+      <c r="D597" s="82"/>
+    </row>
+    <row r="598" spans="2:4">
+      <c r="B598" s="82"/>
+      <c r="C598" s="82"/>
+      <c r="D598" s="82"/>
+    </row>
+    <row r="599" spans="2:4">
+      <c r="B599" s="82"/>
+      <c r="C599" s="82"/>
+      <c r="D599" s="82"/>
+    </row>
+    <row r="600" spans="2:4">
+      <c r="B600" s="82"/>
+      <c r="C600" s="82"/>
+      <c r="D600" s="82"/>
+    </row>
+    <row r="601" spans="2:4">
+      <c r="B601" s="82"/>
+      <c r="C601" s="82"/>
+      <c r="D601" s="82"/>
+    </row>
+    <row r="602" spans="2:4">
+      <c r="B602" s="82"/>
+      <c r="C602" s="82"/>
+      <c r="D602" s="82"/>
+    </row>
+    <row r="603" spans="2:4">
+      <c r="B603" s="82"/>
+      <c r="C603" s="82"/>
+      <c r="D603" s="82"/>
+    </row>
+    <row r="604" spans="2:4">
+      <c r="B604" s="82"/>
+      <c r="C604" s="82"/>
+      <c r="D604" s="82"/>
+    </row>
+    <row r="605" spans="2:4">
+      <c r="B605" s="82"/>
+      <c r="C605" s="82"/>
+      <c r="D605" s="82"/>
+    </row>
+    <row r="606" spans="2:4">
+      <c r="B606" s="82"/>
+      <c r="C606" s="82"/>
+      <c r="D606" s="82"/>
+    </row>
+    <row r="607" spans="2:4">
+      <c r="B607" s="82"/>
+      <c r="C607" s="82"/>
+      <c r="D607" s="82"/>
+    </row>
+    <row r="608" spans="2:4">
+      <c r="B608" s="82"/>
+      <c r="C608" s="82"/>
+      <c r="D608" s="82"/>
+    </row>
+    <row r="609" spans="2:4">
+      <c r="B609" s="82"/>
+      <c r="C609" s="82"/>
+      <c r="D609" s="82"/>
+    </row>
+    <row r="610" spans="2:4">
+      <c r="B610" s="82"/>
+      <c r="C610" s="82"/>
+      <c r="D610" s="82"/>
+    </row>
+    <row r="611" spans="2:4">
+      <c r="B611" s="82"/>
+      <c r="C611" s="82"/>
+      <c r="D611" s="82"/>
+    </row>
+    <row r="612" spans="2:4">
+      <c r="B612" s="82"/>
+      <c r="C612" s="82"/>
+      <c r="D612" s="82"/>
+    </row>
+    <row r="613" spans="2:4">
+      <c r="B613" s="82"/>
+      <c r="C613" s="82"/>
+      <c r="D613" s="82"/>
+    </row>
+    <row r="614" spans="2:4">
+      <c r="B614" s="82"/>
+      <c r="C614" s="82"/>
+      <c r="D614" s="82"/>
+    </row>
+    <row r="615" spans="2:4">
+      <c r="B615" s="82"/>
+      <c r="C615" s="82"/>
+      <c r="D615" s="82"/>
+    </row>
+    <row r="616" spans="2:4">
+      <c r="B616" s="82"/>
+      <c r="C616" s="82"/>
+      <c r="D616" s="82"/>
+    </row>
+    <row r="617" spans="2:4">
+      <c r="B617" s="82"/>
+      <c r="C617" s="82"/>
+      <c r="D617" s="82"/>
+    </row>
+    <row r="618" spans="2:4">
+      <c r="B618" s="82"/>
+      <c r="C618" s="82"/>
+      <c r="D618" s="82"/>
+    </row>
+    <row r="619" spans="2:4">
+      <c r="B619" s="82"/>
+      <c r="C619" s="82"/>
+      <c r="D619" s="82"/>
+    </row>
+    <row r="620" spans="2:4">
+      <c r="B620" s="82"/>
+      <c r="C620" s="82"/>
+      <c r="D620" s="82"/>
+    </row>
+    <row r="621" spans="2:4">
+      <c r="B621" s="82"/>
+      <c r="C621" s="82"/>
+      <c r="D621" s="82"/>
+    </row>
+    <row r="622" spans="2:4">
+      <c r="B622" s="82"/>
+      <c r="C622" s="82"/>
+      <c r="D622" s="82"/>
+    </row>
+    <row r="623" spans="2:4">
+      <c r="B623" s="82"/>
+      <c r="C623" s="82"/>
+      <c r="D623" s="82"/>
+    </row>
+    <row r="624" spans="2:4">
+      <c r="B624" s="82"/>
+      <c r="C624" s="82"/>
+      <c r="D624" s="82"/>
+    </row>
+    <row r="625" spans="2:4">
+      <c r="B625" s="82"/>
+      <c r="C625" s="82"/>
+      <c r="D625" s="82"/>
+    </row>
+    <row r="626" spans="2:4">
+      <c r="B626" s="82"/>
+      <c r="C626" s="82"/>
+      <c r="D626" s="82"/>
+    </row>
+    <row r="627" spans="2:4">
+      <c r="B627" s="82"/>
+      <c r="C627" s="82"/>
+      <c r="D627" s="82"/>
+    </row>
+    <row r="628" spans="2:4">
+      <c r="B628" s="82"/>
+      <c r="C628" s="82"/>
+      <c r="D628" s="82"/>
+    </row>
+    <row r="629" spans="2:4">
+      <c r="B629" s="82"/>
+      <c r="C629" s="82"/>
+      <c r="D629" s="82"/>
+    </row>
+    <row r="630" spans="2:4">
+      <c r="B630" s="82"/>
+      <c r="C630" s="82"/>
+      <c r="D630" s="82"/>
+    </row>
+    <row r="631" spans="2:4">
+      <c r="B631" s="82"/>
+      <c r="C631" s="82"/>
+      <c r="D631" s="82"/>
+    </row>
+    <row r="632" spans="2:4">
+      <c r="B632" s="82"/>
+      <c r="C632" s="82"/>
+      <c r="D632" s="82"/>
+    </row>
+    <row r="633" spans="2:4">
+      <c r="B633" s="82"/>
+      <c r="C633" s="82"/>
+      <c r="D633" s="82"/>
+    </row>
+    <row r="634" spans="2:4">
+      <c r="B634" s="82"/>
+      <c r="C634" s="82"/>
+      <c r="D634" s="82"/>
+    </row>
+    <row r="635" spans="2:4">
+      <c r="B635" s="82"/>
+      <c r="C635" s="82"/>
+      <c r="D635" s="82"/>
+    </row>
+    <row r="636" spans="2:4">
+      <c r="B636" s="82"/>
+      <c r="C636" s="82"/>
+      <c r="D636" s="82"/>
+    </row>
+    <row r="637" spans="2:4">
+      <c r="B637" s="82"/>
+      <c r="C637" s="82"/>
+      <c r="D637" s="82"/>
+    </row>
+    <row r="638" spans="2:4">
+      <c r="B638" s="82"/>
+      <c r="C638" s="82"/>
+      <c r="D638" s="82"/>
+    </row>
+    <row r="639" spans="2:4">
+      <c r="B639" s="82"/>
+      <c r="C639" s="82"/>
+      <c r="D639" s="82"/>
+    </row>
+    <row r="640" spans="2:4">
+      <c r="B640" s="82"/>
+      <c r="C640" s="82"/>
+      <c r="D640" s="82"/>
+    </row>
+    <row r="641" spans="2:4">
+      <c r="B641" s="82"/>
+      <c r="C641" s="82"/>
+      <c r="D641" s="82"/>
+    </row>
+    <row r="642" spans="2:4">
+      <c r="B642" s="82"/>
+      <c r="C642" s="82"/>
+      <c r="D642" s="82"/>
+    </row>
+    <row r="643" spans="2:4">
+      <c r="B643" s="82"/>
+      <c r="C643" s="82"/>
+      <c r="D643" s="82"/>
+    </row>
+    <row r="644" spans="2:4">
+      <c r="B644" s="82"/>
+      <c r="C644" s="82"/>
+      <c r="D644" s="82"/>
+    </row>
+    <row r="645" spans="2:4">
+      <c r="B645" s="82"/>
+      <c r="C645" s="82"/>
+      <c r="D645" s="82"/>
+    </row>
+    <row r="646" spans="2:4">
+      <c r="B646" s="82"/>
+      <c r="C646" s="82"/>
+      <c r="D646" s="82"/>
+    </row>
+    <row r="647" spans="2:4">
+      <c r="B647" s="82"/>
+      <c r="C647" s="82"/>
+      <c r="D647" s="82"/>
+    </row>
+    <row r="648" spans="2:4">
+      <c r="B648" s="82"/>
+      <c r="C648" s="82"/>
+      <c r="D648" s="82"/>
+    </row>
+    <row r="649" spans="2:4">
+      <c r="B649" s="82"/>
+      <c r="C649" s="82"/>
+      <c r="D649" s="82"/>
+    </row>
+    <row r="650" spans="2:4">
+      <c r="B650" s="82"/>
+      <c r="C650" s="82"/>
+      <c r="D650" s="82"/>
+    </row>
+    <row r="651" spans="2:4">
+      <c r="B651" s="82"/>
+      <c r="C651" s="82"/>
+      <c r="D651" s="82"/>
+    </row>
+    <row r="652" spans="2:4">
+      <c r="B652" s="82"/>
+      <c r="C652" s="82"/>
+      <c r="D652" s="82"/>
+    </row>
+    <row r="653" spans="2:4">
+      <c r="B653" s="82"/>
+      <c r="C653" s="82"/>
+      <c r="D653" s="82"/>
+    </row>
+    <row r="654" spans="2:4">
+      <c r="B654" s="82"/>
+      <c r="C654" s="82"/>
+      <c r="D654" s="82"/>
+    </row>
+    <row r="655" spans="2:4">
+      <c r="B655" s="82"/>
+      <c r="C655" s="82"/>
+      <c r="D655" s="82"/>
+    </row>
+    <row r="656" spans="2:4">
+      <c r="B656" s="82"/>
+      <c r="C656" s="82"/>
+      <c r="D656" s="82"/>
+    </row>
+    <row r="657" spans="2:4">
+      <c r="B657" s="82"/>
+      <c r="C657" s="82"/>
+      <c r="D657" s="82"/>
+    </row>
+    <row r="658" spans="2:4">
+      <c r="B658" s="82"/>
+      <c r="C658" s="82"/>
+      <c r="D658" s="82"/>
+    </row>
+    <row r="659" spans="2:4">
+      <c r="B659" s="82"/>
+      <c r="C659" s="82"/>
+      <c r="D659" s="82"/>
+    </row>
+    <row r="660" spans="2:4">
+      <c r="B660" s="82"/>
+      <c r="C660" s="82"/>
+      <c r="D660" s="82"/>
+    </row>
+    <row r="661" spans="2:4">
+      <c r="B661" s="82"/>
+      <c r="C661" s="82"/>
+      <c r="D661" s="82"/>
+    </row>
+    <row r="662" spans="2:4">
+      <c r="B662" s="82"/>
+      <c r="C662" s="82"/>
+      <c r="D662" s="82"/>
+    </row>
+    <row r="663" spans="2:4">
+      <c r="B663" s="82"/>
+      <c r="C663" s="82"/>
+      <c r="D663" s="82"/>
+    </row>
+    <row r="664" spans="2:4">
+      <c r="B664" s="82"/>
+      <c r="C664" s="82"/>
+      <c r="D664" s="82"/>
+    </row>
+    <row r="665" spans="2:4">
+      <c r="B665" s="82"/>
+      <c r="C665" s="82"/>
+      <c r="D665" s="82"/>
+    </row>
+    <row r="666" spans="2:4">
+      <c r="B666" s="82"/>
+      <c r="C666" s="82"/>
+      <c r="D666" s="82"/>
+    </row>
+    <row r="667" spans="2:4">
+      <c r="B667" s="82"/>
+      <c r="C667" s="82"/>
+      <c r="D667" s="82"/>
+    </row>
+    <row r="668" spans="2:4">
+      <c r="B668" s="82"/>
+      <c r="C668" s="82"/>
+      <c r="D668" s="82"/>
+    </row>
+    <row r="669" spans="2:4">
+      <c r="B669" s="82"/>
+      <c r="C669" s="82"/>
+      <c r="D669" s="82"/>
+    </row>
+    <row r="670" spans="2:4">
+      <c r="B670" s="82"/>
+      <c r="C670" s="82"/>
+      <c r="D670" s="82"/>
+    </row>
+    <row r="671" spans="2:4">
+      <c r="B671" s="82"/>
+      <c r="C671" s="82"/>
+      <c r="D671" s="82"/>
+    </row>
+    <row r="672" spans="2:4">
+      <c r="B672" s="82"/>
+      <c r="C672" s="82"/>
+      <c r="D672" s="82"/>
+    </row>
+    <row r="673" spans="2:4">
+      <c r="B673" s="82"/>
+      <c r="C673" s="82"/>
+      <c r="D673" s="82"/>
+    </row>
+    <row r="674" spans="2:4">
+      <c r="B674" s="82"/>
+      <c r="C674" s="82"/>
+      <c r="D674" s="82"/>
+    </row>
+    <row r="675" spans="2:4">
+      <c r="B675" s="82"/>
+      <c r="C675" s="82"/>
+      <c r="D675" s="82"/>
+    </row>
+    <row r="676" spans="2:4">
+      <c r="B676" s="82"/>
+      <c r="C676" s="82"/>
+      <c r="D676" s="82"/>
+    </row>
+    <row r="677" spans="2:4">
+      <c r="B677" s="82"/>
+      <c r="C677" s="82"/>
+      <c r="D677" s="82"/>
+    </row>
+    <row r="678" spans="2:4">
+      <c r="B678" s="82"/>
+      <c r="C678" s="82"/>
+      <c r="D678" s="82"/>
+    </row>
+    <row r="679" spans="2:4">
+      <c r="B679" s="82"/>
+      <c r="C679" s="82"/>
+      <c r="D679" s="82"/>
+    </row>
+    <row r="680" spans="2:4">
+      <c r="B680" s="82"/>
+      <c r="C680" s="82"/>
+      <c r="D680" s="82"/>
+    </row>
+    <row r="681" spans="2:4">
+      <c r="B681" s="82"/>
+      <c r="C681" s="82"/>
+      <c r="D681" s="82"/>
+    </row>
+    <row r="682" spans="2:4">
+      <c r="B682" s="82"/>
+      <c r="C682" s="82"/>
+      <c r="D682" s="82"/>
+    </row>
+    <row r="683" spans="2:4">
+      <c r="B683" s="82"/>
+      <c r="C683" s="82"/>
+      <c r="D683" s="82"/>
+    </row>
+    <row r="684" spans="2:4">
+      <c r="B684" s="82"/>
+      <c r="C684" s="82"/>
+      <c r="D684" s="82"/>
+    </row>
+    <row r="685" spans="2:4">
+      <c r="B685" s="82"/>
+      <c r="C685" s="82"/>
+      <c r="D685" s="82"/>
+    </row>
+    <row r="686" spans="2:4">
+      <c r="B686" s="82"/>
+      <c r="C686" s="82"/>
+      <c r="D686" s="82"/>
+    </row>
+    <row r="687" spans="2:4">
+      <c r="B687" s="82"/>
+      <c r="C687" s="82"/>
+      <c r="D687" s="82"/>
+    </row>
+    <row r="688" spans="2:4">
+      <c r="B688" s="82"/>
+      <c r="C688" s="82"/>
+      <c r="D688" s="82"/>
+    </row>
+    <row r="689" spans="2:4">
+      <c r="B689" s="82"/>
+      <c r="C689" s="82"/>
+      <c r="D689" s="82"/>
+    </row>
+    <row r="690" spans="2:4">
+      <c r="B690" s="82"/>
+      <c r="C690" s="82"/>
+      <c r="D690" s="82"/>
+    </row>
+    <row r="691" spans="2:4">
+      <c r="B691" s="82"/>
+      <c r="C691" s="82"/>
+      <c r="D691" s="82"/>
+    </row>
+    <row r="692" spans="2:4">
+      <c r="B692" s="82"/>
+      <c r="C692" s="82"/>
+      <c r="D692" s="82"/>
+    </row>
+    <row r="693" spans="2:4">
+      <c r="B693" s="82"/>
+      <c r="C693" s="82"/>
+      <c r="D693" s="82"/>
+    </row>
+    <row r="694" spans="2:4">
+      <c r="B694" s="82"/>
+      <c r="C694" s="82"/>
+      <c r="D694" s="82"/>
+    </row>
+    <row r="695" spans="2:4">
+      <c r="B695" s="82"/>
+      <c r="C695" s="82"/>
+      <c r="D695" s="82"/>
+    </row>
+    <row r="696" spans="2:4">
+      <c r="B696" s="82"/>
+      <c r="C696" s="82"/>
+      <c r="D696" s="82"/>
+    </row>
+    <row r="697" spans="2:4">
+      <c r="B697" s="82"/>
+      <c r="C697" s="82"/>
+      <c r="D697" s="82"/>
+    </row>
+    <row r="698" spans="2:4">
+      <c r="B698" s="82"/>
+      <c r="C698" s="82"/>
+      <c r="D698" s="82"/>
+    </row>
+    <row r="699" spans="2:4">
+      <c r="B699" s="82"/>
+      <c r="C699" s="82"/>
+      <c r="D699" s="82"/>
+    </row>
+    <row r="700" spans="2:4">
+      <c r="B700" s="82"/>
+      <c r="C700" s="82"/>
+      <c r="D700" s="82"/>
+    </row>
+    <row r="701" spans="2:4">
+      <c r="B701" s="82"/>
+      <c r="C701" s="82"/>
+      <c r="D701" s="82"/>
+    </row>
+    <row r="702" spans="2:4">
+      <c r="B702" s="82"/>
+      <c r="C702" s="82"/>
+      <c r="D702" s="82"/>
+    </row>
+    <row r="703" spans="2:4">
+      <c r="B703" s="82"/>
+      <c r="C703" s="82"/>
+      <c r="D703" s="82"/>
+    </row>
+    <row r="704" spans="2:4">
+      <c r="B704" s="82"/>
+      <c r="C704" s="82"/>
+      <c r="D704" s="82"/>
+    </row>
+    <row r="705" spans="2:4">
+      <c r="B705" s="82"/>
+      <c r="C705" s="82"/>
+      <c r="D705" s="82"/>
+    </row>
+    <row r="706" spans="2:4">
+      <c r="B706" s="82"/>
+      <c r="C706" s="82"/>
+      <c r="D706" s="82"/>
+    </row>
+    <row r="707" spans="2:4">
+      <c r="B707" s="82"/>
+      <c r="C707" s="82"/>
+      <c r="D707" s="82"/>
+    </row>
+    <row r="708" spans="2:4">
+      <c r="B708" s="82"/>
+      <c r="C708" s="82"/>
+      <c r="D708" s="82"/>
+    </row>
+    <row r="709" spans="2:4">
+      <c r="B709" s="82"/>
+      <c r="C709" s="82"/>
+      <c r="D709" s="82"/>
+    </row>
+    <row r="710" spans="2:4">
+      <c r="B710" s="82"/>
+      <c r="C710" s="82"/>
+      <c r="D710" s="82"/>
+    </row>
+    <row r="711" spans="2:4">
+      <c r="B711" s="82"/>
+      <c r="C711" s="82"/>
+      <c r="D711" s="82"/>
+    </row>
+    <row r="712" spans="2:4">
+      <c r="B712" s="82"/>
+      <c r="C712" s="82"/>
+      <c r="D712" s="82"/>
+    </row>
+    <row r="713" spans="2:4">
+      <c r="B713" s="82"/>
+      <c r="C713" s="82"/>
+      <c r="D713" s="82"/>
+    </row>
+    <row r="714" spans="2:4">
+      <c r="B714" s="82"/>
+      <c r="C714" s="82"/>
+      <c r="D714" s="82"/>
+    </row>
+    <row r="715" spans="2:4">
+      <c r="B715" s="82"/>
+      <c r="C715" s="82"/>
+      <c r="D715" s="82"/>
+    </row>
+    <row r="716" spans="2:4">
+      <c r="B716" s="82"/>
+      <c r="C716" s="82"/>
+      <c r="D716" s="82"/>
+    </row>
+    <row r="717" spans="2:4">
+      <c r="B717" s="82"/>
+      <c r="C717" s="82"/>
+      <c r="D717" s="82"/>
+    </row>
+    <row r="718" spans="2:4">
+      <c r="B718" s="82"/>
+      <c r="C718" s="82"/>
+      <c r="D718" s="82"/>
+    </row>
+    <row r="719" spans="2:4">
+      <c r="B719" s="82"/>
+      <c r="C719" s="82"/>
+      <c r="D719" s="82"/>
+    </row>
+    <row r="720" spans="2:4">
+      <c r="B720" s="82"/>
+      <c r="C720" s="82"/>
+      <c r="D720" s="82"/>
+    </row>
+    <row r="721" spans="2:4">
+      <c r="B721" s="82"/>
+      <c r="C721" s="82"/>
+      <c r="D721" s="82"/>
+    </row>
+    <row r="722" spans="2:4">
+      <c r="B722" s="82"/>
+      <c r="C722" s="82"/>
+      <c r="D722" s="82"/>
+    </row>
+    <row r="723" spans="2:4">
+      <c r="B723" s="82"/>
+      <c r="C723" s="82"/>
+      <c r="D723" s="82"/>
+    </row>
+    <row r="724" spans="2:4">
+      <c r="B724" s="82"/>
+      <c r="C724" s="82"/>
+      <c r="D724" s="82"/>
+    </row>
+    <row r="725" spans="2:4">
+      <c r="B725" s="82"/>
+      <c r="C725" s="82"/>
+      <c r="D725" s="82"/>
+    </row>
+    <row r="726" spans="2:4">
+      <c r="B726" s="82"/>
+      <c r="C726" s="82"/>
+      <c r="D726" s="82"/>
+    </row>
+    <row r="727" spans="2:4">
+      <c r="B727" s="82"/>
+      <c r="C727" s="82"/>
+      <c r="D727" s="82"/>
+    </row>
+    <row r="728" spans="2:4">
+      <c r="B728" s="82"/>
+      <c r="C728" s="82"/>
+      <c r="D728" s="82"/>
+    </row>
+    <row r="729" spans="2:4">
+      <c r="B729" s="82"/>
+      <c r="C729" s="82"/>
+      <c r="D729" s="82"/>
+    </row>
+    <row r="730" spans="2:4">
+      <c r="B730" s="82"/>
+      <c r="C730" s="82"/>
+      <c r="D730" s="82"/>
+    </row>
+    <row r="731" spans="2:4">
+      <c r="B731" s="82"/>
+      <c r="C731" s="82"/>
+      <c r="D731" s="82"/>
+    </row>
+    <row r="732" spans="2:4">
+      <c r="B732" s="82"/>
+      <c r="C732" s="82"/>
+      <c r="D732" s="82"/>
+    </row>
+    <row r="733" spans="2:4">
+      <c r="B733" s="82"/>
+      <c r="C733" s="82"/>
+      <c r="D733" s="82"/>
+    </row>
+    <row r="734" spans="2:4">
+      <c r="B734" s="82"/>
+      <c r="C734" s="82"/>
+      <c r="D734" s="82"/>
+    </row>
+    <row r="735" spans="2:4">
+      <c r="B735" s="82"/>
+      <c r="C735" s="82"/>
+      <c r="D735" s="82"/>
+    </row>
+    <row r="736" spans="2:4">
+      <c r="B736" s="82"/>
+      <c r="C736" s="82"/>
+      <c r="D736" s="82"/>
+    </row>
+    <row r="737" spans="2:4">
+      <c r="B737" s="82"/>
+      <c r="C737" s="82"/>
+      <c r="D737" s="82"/>
+    </row>
+    <row r="738" spans="2:4">
+      <c r="B738" s="82"/>
+      <c r="C738" s="82"/>
+      <c r="D738" s="82"/>
+    </row>
+    <row r="739" spans="2:4">
+      <c r="B739" s="82"/>
+      <c r="C739" s="82"/>
+      <c r="D739" s="82"/>
+    </row>
+    <row r="740" spans="2:4">
+      <c r="B740" s="82"/>
+      <c r="C740" s="82"/>
+      <c r="D740" s="82"/>
+    </row>
+    <row r="741" spans="2:4">
+      <c r="B741" s="82"/>
+      <c r="C741" s="82"/>
+      <c r="D741" s="82"/>
+    </row>
+    <row r="742" spans="2:4">
+      <c r="B742" s="82"/>
+      <c r="C742" s="82"/>
+      <c r="D742" s="82"/>
+    </row>
+    <row r="743" spans="2:4">
+      <c r="B743" s="82"/>
+      <c r="C743" s="82"/>
+      <c r="D743" s="82"/>
+    </row>
+    <row r="744" spans="2:4">
+      <c r="B744" s="82"/>
+      <c r="C744" s="82"/>
+      <c r="D744" s="82"/>
+    </row>
+    <row r="745" spans="2:4">
+      <c r="B745" s="82"/>
+      <c r="C745" s="82"/>
+      <c r="D745" s="82"/>
+    </row>
+    <row r="746" spans="2:4">
+      <c r="B746" s="82"/>
+      <c r="C746" s="82"/>
+      <c r="D746" s="82"/>
+    </row>
+    <row r="747" spans="2:4">
+      <c r="B747" s="82"/>
+      <c r="C747" s="82"/>
+      <c r="D747" s="82"/>
+    </row>
+    <row r="748" spans="2:4">
+      <c r="B748" s="82"/>
+      <c r="C748" s="82"/>
+      <c r="D748" s="82"/>
+    </row>
+    <row r="749" spans="2:4">
+      <c r="B749" s="82"/>
+      <c r="C749" s="82"/>
+      <c r="D749" s="82"/>
+    </row>
+    <row r="750" spans="2:4">
+      <c r="B750" s="82"/>
+      <c r="C750" s="82"/>
+      <c r="D750" s="82"/>
+    </row>
+    <row r="751" spans="2:4">
+      <c r="B751" s="82"/>
+      <c r="C751" s="82"/>
+      <c r="D751" s="82"/>
+    </row>
+    <row r="752" spans="2:4">
+      <c r="B752" s="82"/>
+      <c r="C752" s="82"/>
+      <c r="D752" s="82"/>
+    </row>
+    <row r="753" spans="2:4">
+      <c r="B753" s="82"/>
+      <c r="C753" s="82"/>
+      <c r="D753" s="82"/>
+    </row>
+    <row r="754" spans="2:4">
+      <c r="B754" s="82"/>
+      <c r="C754" s="82"/>
+      <c r="D754" s="82"/>
+    </row>
+    <row r="755" spans="2:4">
+      <c r="B755" s="82"/>
+      <c r="C755" s="82"/>
+      <c r="D755" s="82"/>
+    </row>
+    <row r="756" spans="2:4">
+      <c r="B756" s="82"/>
+      <c r="C756" s="82"/>
+      <c r="D756" s="82"/>
+    </row>
+    <row r="757" spans="2:4">
+      <c r="B757" s="82"/>
+      <c r="C757" s="82"/>
+      <c r="D757" s="82"/>
+    </row>
+    <row r="758" spans="2:4">
+      <c r="B758" s="82"/>
+      <c r="C758" s="82"/>
+      <c r="D758" s="82"/>
+    </row>
+    <row r="759" spans="2:4">
+      <c r="B759" s="82"/>
+      <c r="C759" s="82"/>
+      <c r="D759" s="82"/>
+    </row>
+    <row r="760" spans="2:4">
+      <c r="B760" s="82"/>
+      <c r="C760" s="82"/>
+      <c r="D760" s="82"/>
+    </row>
+    <row r="761" spans="2:4">
+      <c r="B761" s="82"/>
+      <c r="C761" s="82"/>
+      <c r="D761" s="82"/>
+    </row>
+    <row r="762" spans="2:4">
+      <c r="B762" s="82"/>
+      <c r="C762" s="82"/>
+      <c r="D762" s="82"/>
+    </row>
+    <row r="763" spans="2:4">
+      <c r="B763" s="82"/>
+      <c r="C763" s="82"/>
+      <c r="D763" s="82"/>
+    </row>
+    <row r="764" spans="2:4">
+      <c r="B764" s="82"/>
+      <c r="C764" s="82"/>
+      <c r="D764" s="82"/>
+    </row>
+    <row r="765" spans="2:4">
+      <c r="B765" s="82"/>
+      <c r="C765" s="82"/>
+      <c r="D765" s="82"/>
+    </row>
+    <row r="766" spans="2:4">
+      <c r="B766" s="82"/>
+      <c r="C766" s="82"/>
+      <c r="D766" s="82"/>
+    </row>
+    <row r="767" spans="2:4">
+      <c r="B767" s="82"/>
+      <c r="C767" s="82"/>
+      <c r="D767" s="82"/>
+    </row>
+    <row r="768" spans="2:4">
+      <c r="B768" s="82"/>
+      <c r="C768" s="82"/>
+      <c r="D768" s="82"/>
+    </row>
+    <row r="769" spans="2:4">
+      <c r="B769" s="82"/>
+      <c r="C769" s="82"/>
+      <c r="D769" s="82"/>
+    </row>
+    <row r="770" spans="2:4">
+      <c r="B770" s="82"/>
+      <c r="C770" s="82"/>
+      <c r="D770" s="82"/>
+    </row>
+    <row r="771" spans="2:4">
+      <c r="B771" s="82"/>
+      <c r="C771" s="82"/>
+      <c r="D771" s="82"/>
+    </row>
+    <row r="772" spans="2:4">
+      <c r="B772" s="82"/>
+      <c r="C772" s="82"/>
+      <c r="D772" s="82"/>
+    </row>
+    <row r="773" spans="2:4">
+      <c r="B773" s="82"/>
+      <c r="C773" s="82"/>
+      <c r="D773" s="82"/>
+    </row>
+    <row r="774" spans="2:4">
+      <c r="B774" s="82"/>
+      <c r="C774" s="82"/>
+      <c r="D774" s="82"/>
+    </row>
+    <row r="775" spans="2:4">
+      <c r="B775" s="82"/>
+      <c r="C775" s="82"/>
+      <c r="D775" s="82"/>
+    </row>
+    <row r="776" spans="2:4">
+      <c r="B776" s="82"/>
+      <c r="C776" s="82"/>
+      <c r="D776" s="82"/>
+    </row>
+    <row r="777" spans="2:4">
+      <c r="B777" s="82"/>
+      <c r="C777" s="82"/>
+      <c r="D777" s="82"/>
+    </row>
+    <row r="778" spans="2:4">
+      <c r="B778" s="82"/>
+      <c r="C778" s="82"/>
+      <c r="D778" s="82"/>
+    </row>
+    <row r="779" spans="2:4">
+      <c r="B779" s="82"/>
+      <c r="C779" s="82"/>
+      <c r="D779" s="82"/>
+    </row>
+    <row r="780" spans="2:4">
+      <c r="B780" s="82"/>
+      <c r="C780" s="82"/>
+      <c r="D780" s="82"/>
+    </row>
+    <row r="781" spans="2:4">
+      <c r="B781" s="82"/>
+      <c r="C781" s="82"/>
+      <c r="D781" s="82"/>
+    </row>
+    <row r="782" spans="2:4">
+      <c r="B782" s="82"/>
+      <c r="C782" s="82"/>
+      <c r="D782" s="82"/>
+    </row>
+    <row r="783" spans="2:4">
+      <c r="B783" s="82"/>
+      <c r="C783" s="82"/>
+      <c r="D783" s="82"/>
+    </row>
+    <row r="784" spans="2:4">
+      <c r="B784" s="82"/>
+      <c r="C784" s="82"/>
+      <c r="D784" s="82"/>
+    </row>
+    <row r="785" spans="2:4">
+      <c r="B785" s="82"/>
+      <c r="C785" s="82"/>
+      <c r="D785" s="82"/>
+    </row>
+    <row r="786" spans="2:4">
+      <c r="B786" s="82"/>
+      <c r="C786" s="82"/>
+      <c r="D786" s="82"/>
+    </row>
+    <row r="787" spans="2:4">
+      <c r="B787" s="82"/>
+      <c r="C787" s="82"/>
+      <c r="D787" s="82"/>
+    </row>
+    <row r="788" spans="2:4">
+      <c r="B788" s="82"/>
+      <c r="C788" s="82"/>
+      <c r="D788" s="82"/>
+    </row>
+    <row r="789" spans="2:4">
+      <c r="B789" s="82"/>
+      <c r="C789" s="82"/>
+      <c r="D789" s="82"/>
+    </row>
+    <row r="790" spans="2:4">
+      <c r="B790" s="82"/>
+      <c r="C790" s="82"/>
+      <c r="D790" s="82"/>
+    </row>
+    <row r="791" spans="2:4">
+      <c r="B791" s="82"/>
+      <c r="C791" s="82"/>
+      <c r="D791" s="82"/>
+    </row>
+    <row r="792" spans="2:4">
+      <c r="B792" s="82"/>
+      <c r="C792" s="82"/>
+      <c r="D792" s="82"/>
+    </row>
+    <row r="793" spans="2:4">
+      <c r="B793" s="82"/>
+      <c r="C793" s="82"/>
+      <c r="D793" s="82"/>
+    </row>
+    <row r="794" spans="2:4">
+      <c r="B794" s="82"/>
+      <c r="C794" s="82"/>
+      <c r="D794" s="82"/>
+    </row>
+    <row r="795" spans="2:4">
+      <c r="B795" s="82"/>
+      <c r="C795" s="82"/>
+      <c r="D795" s="82"/>
+    </row>
+    <row r="796" spans="2:4">
+      <c r="B796" s="82"/>
+      <c r="C796" s="82"/>
+      <c r="D796" s="82"/>
+    </row>
+    <row r="797" spans="2:4">
+      <c r="B797" s="82"/>
+      <c r="C797" s="82"/>
+      <c r="D797" s="82"/>
+    </row>
+    <row r="798" spans="2:4">
+      <c r="B798" s="82"/>
+      <c r="C798" s="82"/>
+      <c r="D798" s="82"/>
+    </row>
+    <row r="799" spans="2:4">
+      <c r="B799" s="82"/>
+      <c r="C799" s="82"/>
+      <c r="D799" s="82"/>
+    </row>
+    <row r="800" spans="2:4">
+      <c r="B800" s="82"/>
+      <c r="C800" s="82"/>
+      <c r="D800" s="82"/>
+    </row>
+    <row r="801" spans="2:4">
+      <c r="B801" s="82"/>
+      <c r="C801" s="82"/>
+      <c r="D801" s="82"/>
+    </row>
+    <row r="802" spans="2:4">
+      <c r="B802" s="82"/>
+      <c r="C802" s="82"/>
+      <c r="D802" s="82"/>
+    </row>
+    <row r="803" spans="2:4">
+      <c r="B803" s="82"/>
+      <c r="C803" s="82"/>
+      <c r="D803" s="82"/>
+    </row>
+    <row r="804" spans="2:4">
+      <c r="B804" s="82"/>
+      <c r="C804" s="82"/>
+      <c r="D804" s="82"/>
+    </row>
+    <row r="805" spans="2:4">
+      <c r="B805" s="82"/>
+      <c r="C805" s="82"/>
+      <c r="D805" s="82"/>
+    </row>
+    <row r="806" spans="2:4">
+      <c r="B806" s="82"/>
+      <c r="C806" s="82"/>
+      <c r="D806" s="82"/>
+    </row>
+    <row r="807" spans="2:4">
+      <c r="B807" s="82"/>
+      <c r="C807" s="82"/>
+      <c r="D807" s="82"/>
+    </row>
+    <row r="808" spans="2:4">
+      <c r="B808" s="82"/>
+      <c r="C808" s="82"/>
+      <c r="D808" s="82"/>
+    </row>
+    <row r="809" spans="2:4">
+      <c r="B809" s="82"/>
+      <c r="C809" s="82"/>
+      <c r="D809" s="82"/>
+    </row>
+    <row r="810" spans="2:4">
+      <c r="B810" s="82"/>
+      <c r="C810" s="82"/>
+      <c r="D810" s="82"/>
+    </row>
+    <row r="811" spans="2:4">
+      <c r="B811" s="82"/>
+      <c r="C811" s="82"/>
+      <c r="D811" s="82"/>
+    </row>
+    <row r="812" spans="2:4">
+      <c r="B812" s="82"/>
+      <c r="C812" s="82"/>
+      <c r="D812" s="82"/>
+    </row>
+    <row r="813" spans="2:4">
+      <c r="B813" s="82"/>
+      <c r="C813" s="82"/>
+      <c r="D813" s="82"/>
+    </row>
+    <row r="814" spans="2:4">
+      <c r="B814" s="82"/>
+      <c r="C814" s="82"/>
+      <c r="D814" s="82"/>
+    </row>
+    <row r="815" spans="2:4">
+      <c r="B815" s="82"/>
+      <c r="C815" s="82"/>
+      <c r="D815" s="82"/>
+    </row>
+    <row r="816" spans="2:4">
+      <c r="B816" s="82"/>
+      <c r="C816" s="82"/>
+      <c r="D816" s="82"/>
+    </row>
+    <row r="817" spans="2:4">
+      <c r="B817" s="82"/>
+      <c r="C817" s="82"/>
+      <c r="D817" s="82"/>
+    </row>
+    <row r="818" spans="2:4">
+      <c r="B818" s="82"/>
+      <c r="C818" s="82"/>
+      <c r="D818" s="82"/>
+    </row>
+    <row r="819" spans="2:4">
+      <c r="B819" s="82"/>
+      <c r="C819" s="82"/>
+      <c r="D819" s="82"/>
+    </row>
+    <row r="820" spans="2:4">
+      <c r="B820" s="82"/>
+      <c r="C820" s="82"/>
+      <c r="D820" s="82"/>
+    </row>
+    <row r="821" spans="2:4">
+      <c r="B821" s="82"/>
+      <c r="C821" s="82"/>
+      <c r="D821" s="82"/>
+    </row>
+    <row r="822" spans="2:4">
+      <c r="B822" s="82"/>
+      <c r="C822" s="82"/>
+      <c r="D822" s="82"/>
+    </row>
+    <row r="823" spans="2:4">
+      <c r="B823" s="82"/>
+      <c r="C823" s="82"/>
+      <c r="D823" s="82"/>
+    </row>
+    <row r="824" spans="2:4">
+      <c r="B824" s="82"/>
+      <c r="C824" s="82"/>
+      <c r="D824" s="82"/>
+    </row>
+    <row r="825" spans="2:4">
+      <c r="B825" s="82"/>
+      <c r="C825" s="82"/>
+      <c r="D825" s="82"/>
+    </row>
+    <row r="826" spans="2:4">
+      <c r="B826" s="82"/>
+      <c r="C826" s="82"/>
+      <c r="D826" s="82"/>
+    </row>
+    <row r="827" spans="2:4">
+      <c r="B827" s="82"/>
+      <c r="C827" s="82"/>
+      <c r="D827" s="82"/>
+    </row>
+    <row r="828" spans="2:4">
+      <c r="B828" s="82"/>
+      <c r="C828" s="82"/>
+      <c r="D828" s="82"/>
+    </row>
+    <row r="829" spans="2:4">
+      <c r="B829" s="82"/>
+      <c r="C829" s="82"/>
+      <c r="D829" s="82"/>
+    </row>
+    <row r="830" spans="2:4">
+      <c r="B830" s="82"/>
+      <c r="C830" s="82"/>
+      <c r="D830" s="82"/>
+    </row>
+    <row r="831" spans="2:4">
+      <c r="B831" s="82"/>
+      <c r="C831" s="82"/>
+      <c r="D831" s="82"/>
+    </row>
+    <row r="832" spans="2:4">
+      <c r="B832" s="82"/>
+      <c r="C832" s="82"/>
+      <c r="D832" s="82"/>
+    </row>
+    <row r="833" spans="2:4">
+      <c r="B833" s="82"/>
+      <c r="C833" s="82"/>
+      <c r="D833" s="82"/>
+    </row>
+    <row r="834" spans="2:4">
+      <c r="B834" s="82"/>
+      <c r="C834" s="82"/>
+      <c r="D834" s="82"/>
+    </row>
+    <row r="835" spans="2:4">
+      <c r="B835" s="82"/>
+      <c r="C835" s="82"/>
+      <c r="D835" s="82"/>
+    </row>
+    <row r="836" spans="2:4">
+      <c r="B836" s="82"/>
+      <c r="C836" s="82"/>
+      <c r="D836" s="82"/>
+    </row>
+    <row r="837" spans="2:4">
+      <c r="B837" s="82"/>
+      <c r="C837" s="82"/>
+      <c r="D837" s="82"/>
+    </row>
+    <row r="838" spans="2:4">
+      <c r="B838" s="82"/>
+      <c r="C838" s="82"/>
+      <c r="D838" s="82"/>
+    </row>
+    <row r="839" spans="2:4">
+      <c r="B839" s="82"/>
+      <c r="C839" s="82"/>
+      <c r="D839" s="82"/>
+    </row>
+    <row r="840" spans="2:4">
+      <c r="B840" s="82"/>
+      <c r="C840" s="82"/>
+      <c r="D840" s="82"/>
+    </row>
+    <row r="841" spans="2:4">
+      <c r="B841" s="82"/>
+      <c r="C841" s="82"/>
+      <c r="D841" s="82"/>
+    </row>
+    <row r="842" spans="2:4">
+      <c r="B842" s="82"/>
+      <c r="C842" s="82"/>
+      <c r="D842" s="82"/>
+    </row>
+    <row r="843" spans="2:4">
+      <c r="B843" s="82"/>
+      <c r="C843" s="82"/>
+      <c r="D843" s="82"/>
+    </row>
+    <row r="844" spans="2:4">
+      <c r="B844" s="82"/>
+      <c r="C844" s="82"/>
+      <c r="D844" s="82"/>
+    </row>
+    <row r="845" spans="2:4">
+      <c r="B845" s="82"/>
+      <c r="C845" s="82"/>
+      <c r="D845" s="82"/>
+    </row>
+    <row r="846" spans="2:4">
+      <c r="B846" s="82"/>
+      <c r="C846" s="82"/>
+      <c r="D846" s="82"/>
+    </row>
+    <row r="847" spans="2:4">
+      <c r="B847" s="82"/>
+      <c r="C847" s="82"/>
+      <c r="D847" s="82"/>
+    </row>
+    <row r="848" spans="2:4">
+      <c r="B848" s="82"/>
+      <c r="C848" s="82"/>
+      <c r="D848" s="82"/>
+    </row>
+    <row r="849" spans="2:4">
+      <c r="B849" s="82"/>
+      <c r="C849" s="82"/>
+      <c r="D849" s="82"/>
+    </row>
+    <row r="850" spans="2:4">
+      <c r="B850" s="82"/>
+      <c r="C850" s="82"/>
+      <c r="D850" s="82"/>
+    </row>
+    <row r="851" spans="2:4">
+      <c r="B851" s="82"/>
+      <c r="C851" s="82"/>
+      <c r="D851" s="82"/>
+    </row>
+    <row r="852" spans="2:4">
+      <c r="B852" s="82"/>
+      <c r="C852" s="82"/>
+      <c r="D852" s="82"/>
+    </row>
+    <row r="853" spans="2:4">
+      <c r="B853" s="82"/>
+      <c r="C853" s="82"/>
+      <c r="D853" s="82"/>
+    </row>
+    <row r="854" spans="2:4">
+      <c r="B854" s="82"/>
+      <c r="C854" s="82"/>
+      <c r="D854" s="82"/>
+    </row>
+    <row r="855" spans="2:4">
+      <c r="B855" s="82"/>
+      <c r="C855" s="82"/>
+      <c r="D855" s="82"/>
+    </row>
+    <row r="856" spans="2:4">
+      <c r="B856" s="82"/>
+      <c r="C856" s="82"/>
+      <c r="D856" s="82"/>
+    </row>
+    <row r="857" spans="2:4">
+      <c r="B857" s="82"/>
+      <c r="C857" s="82"/>
+      <c r="D857" s="82"/>
+    </row>
+    <row r="858" spans="2:4">
+      <c r="B858" s="82"/>
+      <c r="C858" s="82"/>
+      <c r="D858" s="82"/>
+    </row>
+    <row r="859" spans="2:4">
+      <c r="B859" s="82"/>
+      <c r="C859" s="82"/>
+      <c r="D859" s="82"/>
+    </row>
+    <row r="860" spans="2:4">
+      <c r="B860" s="82"/>
+      <c r="C860" s="82"/>
+      <c r="D860" s="82"/>
+    </row>
+    <row r="861" spans="2:4">
+      <c r="B861" s="82"/>
+      <c r="C861" s="82"/>
+      <c r="D861" s="82"/>
+    </row>
+    <row r="862" spans="2:4">
+      <c r="B862" s="82"/>
+      <c r="C862" s="82"/>
+      <c r="D862" s="82"/>
+    </row>
+    <row r="863" spans="2:4">
+      <c r="B863" s="82"/>
+      <c r="C863" s="82"/>
+      <c r="D863" s="82"/>
+    </row>
+    <row r="864" spans="2:4">
+      <c r="B864" s="82"/>
+      <c r="C864" s="82"/>
+      <c r="D864" s="82"/>
+    </row>
+    <row r="865" spans="2:4">
+      <c r="B865" s="82"/>
+      <c r="C865" s="82"/>
+      <c r="D865" s="82"/>
+    </row>
+    <row r="866" spans="2:4">
+      <c r="B866" s="82"/>
+      <c r="C866" s="82"/>
+      <c r="D866" s="82"/>
+    </row>
+    <row r="867" spans="2:4">
+      <c r="B867" s="82"/>
+      <c r="C867" s="82"/>
+      <c r="D867" s="82"/>
+    </row>
+    <row r="868" spans="2:4">
+      <c r="B868" s="82"/>
+      <c r="C868" s="82"/>
+      <c r="D868" s="82"/>
+    </row>
+    <row r="869" spans="2:4">
+      <c r="B869" s="82"/>
+      <c r="C869" s="82"/>
+      <c r="D869" s="82"/>
+    </row>
+    <row r="870" spans="2:4">
+      <c r="B870" s="82"/>
+      <c r="C870" s="82"/>
+      <c r="D870" s="82"/>
+    </row>
+    <row r="871" spans="2:4">
+      <c r="B871" s="82"/>
+      <c r="C871" s="82"/>
+      <c r="D871" s="82"/>
+    </row>
+    <row r="872" spans="2:4">
+      <c r="B872" s="82"/>
+      <c r="C872" s="82"/>
+      <c r="D872" s="82"/>
+    </row>
+    <row r="873" spans="2:4">
+      <c r="B873" s="82"/>
+      <c r="C873" s="82"/>
+      <c r="D873" s="82"/>
+    </row>
+    <row r="874" spans="2:4">
+      <c r="B874" s="82"/>
+      <c r="C874" s="82"/>
+      <c r="D874" s="82"/>
+    </row>
+    <row r="875" spans="2:4">
+      <c r="B875" s="82"/>
+      <c r="C875" s="82"/>
+      <c r="D875" s="82"/>
+    </row>
+    <row r="876" spans="2:4">
+      <c r="B876" s="82"/>
+      <c r="C876" s="82"/>
+      <c r="D876" s="82"/>
+    </row>
+    <row r="877" spans="2:4">
+      <c r="B877" s="82"/>
+      <c r="C877" s="82"/>
+      <c r="D877" s="82"/>
+    </row>
+    <row r="878" spans="2:4">
+      <c r="B878" s="82"/>
+      <c r="C878" s="82"/>
+      <c r="D878" s="82"/>
+    </row>
+    <row r="879" spans="2:4">
+      <c r="B879" s="82"/>
+      <c r="C879" s="82"/>
+      <c r="D879" s="82"/>
+    </row>
+    <row r="880" spans="2:4">
+      <c r="B880" s="82"/>
+      <c r="C880" s="82"/>
+      <c r="D880" s="82"/>
+    </row>
+    <row r="881" spans="2:4">
+      <c r="B881" s="82"/>
+      <c r="C881" s="82"/>
+      <c r="D881" s="82"/>
+    </row>
+    <row r="882" spans="2:4">
+      <c r="B882" s="82"/>
+      <c r="C882" s="82"/>
+      <c r="D882" s="82"/>
+    </row>
+    <row r="883" spans="2:4">
+      <c r="B883" s="82"/>
+      <c r="C883" s="82"/>
+      <c r="D883" s="82"/>
+    </row>
+    <row r="884" spans="2:4">
+      <c r="B884" s="82"/>
+      <c r="C884" s="82"/>
+      <c r="D884" s="82"/>
+    </row>
+    <row r="885" spans="2:4">
+      <c r="B885" s="82"/>
+      <c r="C885" s="82"/>
+      <c r="D885" s="82"/>
+    </row>
+    <row r="886" spans="2:4">
+      <c r="B886" s="82"/>
+      <c r="C886" s="82"/>
+      <c r="D886" s="82"/>
+    </row>
+    <row r="887" spans="2:4">
+      <c r="B887" s="82"/>
+      <c r="C887" s="82"/>
+      <c r="D887" s="82"/>
+    </row>
+    <row r="888" spans="2:4">
+      <c r="B888" s="82"/>
+      <c r="C888" s="82"/>
+      <c r="D888" s="82"/>
+    </row>
+    <row r="889" spans="2:4">
+      <c r="B889" s="82"/>
+      <c r="C889" s="82"/>
+      <c r="D889" s="82"/>
+    </row>
+    <row r="890" spans="2:4">
+      <c r="B890" s="82"/>
+      <c r="C890" s="82"/>
+      <c r="D890" s="82"/>
+    </row>
+    <row r="891" spans="2:4">
+      <c r="B891" s="82"/>
+      <c r="C891" s="82"/>
+      <c r="D891" s="82"/>
+    </row>
+    <row r="892" spans="2:4">
+      <c r="B892" s="82"/>
+      <c r="C892" s="82"/>
+      <c r="D892" s="82"/>
+    </row>
+    <row r="893" spans="2:4">
+      <c r="B893" s="82"/>
+      <c r="C893" s="82"/>
+      <c r="D893" s="82"/>
+    </row>
+    <row r="894" spans="2:4">
+      <c r="B894" s="82"/>
+      <c r="C894" s="82"/>
+      <c r="D894" s="82"/>
+    </row>
+    <row r="895" spans="2:4">
+      <c r="B895" s="82"/>
+      <c r="C895" s="82"/>
+      <c r="D895" s="82"/>
+    </row>
+    <row r="896" spans="2:4">
+      <c r="B896" s="82"/>
+      <c r="C896" s="82"/>
+      <c r="D896" s="82"/>
+    </row>
+    <row r="897" spans="2:4">
+      <c r="B897" s="82"/>
+      <c r="C897" s="82"/>
+      <c r="D897" s="82"/>
+    </row>
+    <row r="898" spans="2:4">
+      <c r="B898" s="82"/>
+      <c r="C898" s="82"/>
+      <c r="D898" s="82"/>
+    </row>
+    <row r="899" spans="2:4">
+      <c r="B899" s="82"/>
+      <c r="C899" s="82"/>
+      <c r="D899" s="82"/>
+    </row>
+    <row r="900" spans="2:4">
+      <c r="B900" s="82"/>
+      <c r="C900" s="82"/>
+      <c r="D900" s="82"/>
+    </row>
+    <row r="901" spans="2:4">
+      <c r="B901" s="82"/>
+      <c r="C901" s="82"/>
+      <c r="D901" s="82"/>
+    </row>
+    <row r="902" spans="2:4">
+      <c r="B902" s="82"/>
+      <c r="C902" s="82"/>
+      <c r="D902" s="82"/>
+    </row>
+    <row r="903" spans="2:4">
+      <c r="B903" s="82"/>
+      <c r="C903" s="82"/>
+      <c r="D903" s="82"/>
+    </row>
+    <row r="904" spans="2:4">
+      <c r="B904" s="82"/>
+      <c r="C904" s="82"/>
+      <c r="D904" s="82"/>
+    </row>
+    <row r="905" spans="2:4">
+      <c r="B905" s="82"/>
+      <c r="C905" s="82"/>
+      <c r="D905" s="82"/>
+    </row>
+    <row r="906" spans="2:4">
+      <c r="B906" s="82"/>
+      <c r="C906" s="82"/>
+      <c r="D906" s="82"/>
+    </row>
+    <row r="907" spans="2:4">
+      <c r="B907" s="82"/>
+      <c r="C907" s="82"/>
+      <c r="D907" s="82"/>
+    </row>
+    <row r="908" spans="2:4">
+      <c r="B908" s="82"/>
+      <c r="C908" s="82"/>
+      <c r="D908" s="82"/>
+    </row>
+    <row r="909" spans="2:4">
+      <c r="B909" s="82"/>
+      <c r="C909" s="82"/>
+      <c r="D909" s="82"/>
+    </row>
+    <row r="910" spans="2:4">
+      <c r="B910" s="82"/>
+      <c r="C910" s="82"/>
+      <c r="D910" s="82"/>
+    </row>
+    <row r="911" spans="2:4">
+      <c r="B911" s="82"/>
+      <c r="C911" s="82"/>
+      <c r="D911" s="82"/>
+    </row>
+    <row r="912" spans="2:4">
+      <c r="B912" s="82"/>
+      <c r="C912" s="82"/>
+      <c r="D912" s="82"/>
+    </row>
+    <row r="913" spans="2:4">
+      <c r="B913" s="82"/>
+      <c r="C913" s="82"/>
+      <c r="D913" s="82"/>
+    </row>
+    <row r="914" spans="2:4">
+      <c r="B914" s="82"/>
+      <c r="C914" s="82"/>
+      <c r="D914" s="82"/>
+    </row>
+    <row r="915" spans="2:4">
+      <c r="B915" s="82"/>
+      <c r="C915" s="82"/>
+      <c r="D915" s="82"/>
+    </row>
+    <row r="916" spans="2:4">
+      <c r="B916" s="82"/>
+      <c r="C916" s="82"/>
+      <c r="D916" s="82"/>
+    </row>
+    <row r="917" spans="2:4">
+      <c r="B917" s="82"/>
+      <c r="C917" s="82"/>
+      <c r="D917" s="82"/>
+    </row>
+    <row r="918" spans="2:4">
+      <c r="B918" s="82"/>
+      <c r="C918" s="82"/>
+      <c r="D918" s="82"/>
+    </row>
+    <row r="919" spans="2:4">
+      <c r="B919" s="82"/>
+      <c r="C919" s="82"/>
+      <c r="D919" s="82"/>
+    </row>
+    <row r="920" spans="2:4">
+      <c r="B920" s="82"/>
+      <c r="C920" s="82"/>
+      <c r="D920" s="82"/>
+    </row>
+    <row r="921" spans="2:4">
+      <c r="B921" s="82"/>
+      <c r="C921" s="82"/>
+      <c r="D921" s="82"/>
+    </row>
+    <row r="922" spans="2:4">
+      <c r="B922" s="82"/>
+      <c r="C922" s="82"/>
+      <c r="D922" s="82"/>
+    </row>
+    <row r="923" spans="2:4">
+      <c r="B923" s="82"/>
+      <c r="C923" s="82"/>
+      <c r="D923" s="82"/>
+    </row>
+    <row r="924" spans="2:4">
+      <c r="B924" s="82"/>
+      <c r="C924" s="82"/>
+      <c r="D924" s="82"/>
+    </row>
+    <row r="925" spans="2:4">
+      <c r="B925" s="82"/>
+      <c r="C925" s="82"/>
+      <c r="D925" s="82"/>
+    </row>
+    <row r="926" spans="2:4">
+      <c r="B926" s="82"/>
+      <c r="C926" s="82"/>
+      <c r="D926" s="82"/>
+    </row>
+    <row r="927" spans="2:4">
+      <c r="B927" s="82"/>
+      <c r="C927" s="82"/>
+      <c r="D927" s="82"/>
+    </row>
+    <row r="928" spans="2:4">
+      <c r="B928" s="82"/>
+      <c r="C928" s="82"/>
+      <c r="D928" s="82"/>
+    </row>
+    <row r="929" spans="2:4">
+      <c r="B929" s="82"/>
+      <c r="C929" s="82"/>
+      <c r="D929" s="82"/>
+    </row>
+    <row r="930" spans="2:4">
+      <c r="B930" s="82"/>
+      <c r="C930" s="82"/>
+      <c r="D930" s="82"/>
+    </row>
+    <row r="931" spans="2:4">
+      <c r="B931" s="82"/>
+      <c r="C931" s="82"/>
+      <c r="D931" s="82"/>
+    </row>
+    <row r="932" spans="2:4">
+      <c r="B932" s="82"/>
+      <c r="C932" s="82"/>
+      <c r="D932" s="82"/>
+    </row>
+    <row r="933" spans="2:4">
+      <c r="B933" s="82"/>
+      <c r="C933" s="82"/>
+      <c r="D933" s="82"/>
+    </row>
+    <row r="934" spans="2:4">
+      <c r="B934" s="82"/>
+      <c r="C934" s="82"/>
+      <c r="D934" s="82"/>
+    </row>
+    <row r="935" spans="2:4">
+      <c r="B935" s="82"/>
+      <c r="C935" s="82"/>
+      <c r="D935" s="82"/>
+    </row>
+    <row r="936" spans="2:4">
+      <c r="B936" s="82"/>
+      <c r="C936" s="82"/>
+      <c r="D936" s="82"/>
+    </row>
+    <row r="937" spans="2:4">
+      <c r="B937" s="82"/>
+      <c r="C937" s="82"/>
+      <c r="D937" s="82"/>
+    </row>
+    <row r="938" spans="2:4">
+      <c r="B938" s="82"/>
+      <c r="C938" s="82"/>
+      <c r="D938" s="82"/>
+    </row>
+    <row r="939" spans="2:4">
+      <c r="B939" s="82"/>
+      <c r="C939" s="82"/>
+      <c r="D939" s="82"/>
+    </row>
+    <row r="940" spans="2:4">
+      <c r="B940" s="82"/>
+      <c r="C940" s="82"/>
+      <c r="D940" s="82"/>
+    </row>
+    <row r="941" spans="2:4">
+      <c r="B941" s="82"/>
+      <c r="C941" s="82"/>
+      <c r="D941" s="82"/>
+    </row>
+    <row r="942" spans="2:4">
+      <c r="B942" s="82"/>
+      <c r="C942" s="82"/>
+      <c r="D942" s="82"/>
+    </row>
+    <row r="943" spans="2:4">
+      <c r="B943" s="82"/>
+      <c r="C943" s="82"/>
+      <c r="D943" s="82"/>
+    </row>
+    <row r="944" spans="2:4">
+      <c r="B944" s="82"/>
+      <c r="C944" s="82"/>
+      <c r="D944" s="82"/>
+    </row>
+    <row r="945" spans="2:4">
+      <c r="B945" s="82"/>
+      <c r="C945" s="82"/>
+      <c r="D945" s="82"/>
+    </row>
+    <row r="946" spans="2:4">
+      <c r="B946" s="82"/>
+      <c r="C946" s="82"/>
+      <c r="D946" s="82"/>
+    </row>
+    <row r="947" spans="2:4">
+      <c r="B947" s="82"/>
+      <c r="C947" s="82"/>
+      <c r="D947" s="82"/>
+    </row>
+    <row r="948" spans="2:4">
+      <c r="B948" s="82"/>
+      <c r="C948" s="82"/>
+      <c r="D948" s="82"/>
+    </row>
+    <row r="949" spans="2:4">
+      <c r="B949" s="82"/>
+      <c r="C949" s="82"/>
+      <c r="D949" s="82"/>
+    </row>
+    <row r="950" spans="2:4">
+      <c r="B950" s="82"/>
+      <c r="C950" s="82"/>
+      <c r="D950" s="82"/>
+    </row>
+    <row r="951" spans="2:4">
+      <c r="B951" s="82"/>
+      <c r="C951" s="82"/>
+      <c r="D951" s="82"/>
+    </row>
+    <row r="952" spans="2:4">
+      <c r="B952" s="82"/>
+      <c r="C952" s="82"/>
+      <c r="D952" s="82"/>
+    </row>
+    <row r="953" spans="2:4">
+      <c r="B953" s="82"/>
+      <c r="C953" s="82"/>
+      <c r="D953" s="82"/>
+    </row>
+    <row r="954" spans="2:4">
+      <c r="B954" s="82"/>
+      <c r="C954" s="82"/>
+      <c r="D954" s="82"/>
+    </row>
+    <row r="955" spans="2:4">
+      <c r="B955" s="82"/>
+      <c r="C955" s="82"/>
+      <c r="D955" s="82"/>
+    </row>
+    <row r="956" spans="2:4">
+      <c r="B956" s="82"/>
+      <c r="C956" s="82"/>
+      <c r="D956" s="82"/>
+    </row>
+    <row r="957" spans="2:4">
+      <c r="B957" s="82"/>
+      <c r="C957" s="82"/>
+      <c r="D957" s="82"/>
+    </row>
+    <row r="958" spans="2:4">
+      <c r="B958" s="82"/>
+      <c r="C958" s="82"/>
+      <c r="D958" s="82"/>
+    </row>
+    <row r="959" spans="2:4">
+      <c r="B959" s="82"/>
+      <c r="C959" s="82"/>
+      <c r="D959" s="82"/>
+    </row>
+    <row r="960" spans="2:4">
+      <c r="B960" s="82"/>
+      <c r="C960" s="82"/>
+      <c r="D960" s="82"/>
+    </row>
+    <row r="961" spans="2:4">
+      <c r="B961" s="82"/>
+      <c r="C961" s="82"/>
+      <c r="D961" s="82"/>
+    </row>
+    <row r="962" spans="2:4">
+      <c r="B962" s="82"/>
+      <c r="C962" s="82"/>
+      <c r="D962" s="82"/>
+    </row>
+    <row r="963" spans="2:4">
+      <c r="B963" s="82"/>
+      <c r="C963" s="82"/>
+      <c r="D963" s="82"/>
+    </row>
+    <row r="964" spans="2:4">
+      <c r="B964" s="82"/>
+      <c r="C964" s="82"/>
+      <c r="D964" s="82"/>
+    </row>
+    <row r="965" spans="2:4">
+      <c r="B965" s="82"/>
+      <c r="C965" s="82"/>
+      <c r="D965" s="82"/>
+    </row>
+    <row r="966" spans="2:4">
+      <c r="B966" s="82"/>
+      <c r="C966" s="82"/>
+      <c r="D966" s="82"/>
+    </row>
+    <row r="967" spans="2:4">
+      <c r="B967" s="82"/>
+      <c r="C967" s="82"/>
+      <c r="D967" s="82"/>
+    </row>
+    <row r="968" spans="2:4">
+      <c r="B968" s="82"/>
+      <c r="C968" s="82"/>
+      <c r="D968" s="82"/>
+    </row>
+    <row r="969" spans="2:4">
+      <c r="B969" s="82"/>
+      <c r="C969" s="82"/>
+      <c r="D969" s="82"/>
+    </row>
+    <row r="970" spans="2:4">
+      <c r="B970" s="82"/>
+      <c r="C970" s="82"/>
+      <c r="D970" s="82"/>
+    </row>
+    <row r="971" spans="2:4">
+      <c r="B971" s="82"/>
+      <c r="C971" s="82"/>
+      <c r="D971" s="82"/>
+    </row>
+    <row r="972" spans="2:4">
+      <c r="B972" s="82"/>
+      <c r="C972" s="82"/>
+      <c r="D972" s="82"/>
+    </row>
+    <row r="973" spans="2:4">
+      <c r="B973" s="82"/>
+      <c r="C973" s="82"/>
+      <c r="D973" s="82"/>
+    </row>
+    <row r="974" spans="2:4">
+      <c r="B974" s="82"/>
+      <c r="C974" s="82"/>
+      <c r="D974" s="82"/>
+    </row>
+    <row r="975" spans="2:4">
+      <c r="B975" s="82"/>
+      <c r="C975" s="82"/>
+      <c r="D975" s="82"/>
+    </row>
+    <row r="976" spans="2:4">
+      <c r="B976" s="82"/>
+      <c r="C976" s="82"/>
+      <c r="D976" s="82"/>
+    </row>
+    <row r="977" spans="2:4">
+      <c r="B977" s="82"/>
+      <c r="C977" s="82"/>
+      <c r="D977" s="82"/>
+    </row>
+    <row r="978" spans="2:4">
+      <c r="B978" s="82"/>
+      <c r="C978" s="82"/>
+      <c r="D978" s="82"/>
+    </row>
+    <row r="979" spans="2:4">
+      <c r="B979" s="82"/>
+      <c r="C979" s="82"/>
+      <c r="D979" s="82"/>
+    </row>
+    <row r="980" spans="2:4">
+      <c r="B980" s="82"/>
+      <c r="C980" s="82"/>
+      <c r="D980" s="82"/>
+    </row>
+    <row r="981" spans="2:4">
+      <c r="B981" s="82"/>
+      <c r="C981" s="82"/>
+      <c r="D981" s="82"/>
+    </row>
+    <row r="982" spans="2:4">
+      <c r="B982" s="82"/>
+      <c r="C982" s="82"/>
+      <c r="D982" s="82"/>
+    </row>
+    <row r="983" spans="2:4">
+      <c r="B983" s="82"/>
+      <c r="C983" s="82"/>
+      <c r="D983" s="82"/>
+    </row>
+    <row r="984" spans="2:4">
+      <c r="B984" s="82"/>
+      <c r="C984" s="82"/>
+      <c r="D984" s="82"/>
+    </row>
+    <row r="985" spans="2:4">
+      <c r="B985" s="82"/>
+      <c r="C985" s="82"/>
+      <c r="D985" s="82"/>
+    </row>
+    <row r="986" spans="2:4">
+      <c r="B986" s="82"/>
+      <c r="C986" s="82"/>
+      <c r="D986" s="82"/>
+    </row>
+    <row r="987" spans="2:4">
+      <c r="B987" s="82"/>
+      <c r="C987" s="82"/>
+      <c r="D987" s="82"/>
+    </row>
+    <row r="988" spans="2:4">
+      <c r="B988" s="82"/>
+      <c r="C988" s="82"/>
+      <c r="D988" s="82"/>
+    </row>
+    <row r="989" spans="2:4">
+      <c r="B989" s="82"/>
+      <c r="C989" s="82"/>
+      <c r="D989" s="82"/>
+    </row>
+    <row r="990" spans="2:4">
+      <c r="B990" s="82"/>
+      <c r="C990" s="82"/>
+      <c r="D990" s="82"/>
+    </row>
+    <row r="991" spans="2:4">
+      <c r="B991" s="82"/>
+      <c r="C991" s="82"/>
+      <c r="D991" s="82"/>
+    </row>
+    <row r="992" spans="2:4">
+      <c r="B992" s="82"/>
+      <c r="C992" s="82"/>
+      <c r="D992" s="82"/>
+    </row>
+    <row r="993" spans="2:4">
+      <c r="B993" s="82"/>
+      <c r="C993" s="82"/>
+      <c r="D993" s="82"/>
+    </row>
+    <row r="994" spans="2:4">
+      <c r="B994" s="82"/>
+      <c r="C994" s="82"/>
+      <c r="D994" s="82"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Random-Forest-main/Random Forest Data.xlsx
+++ b/Random-Forest-main/Random Forest Data.xlsx
@@ -1,27 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kyliealfaro/Desktop/PhD UHM/Modeling Project/Random-Forest-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23BFB68F-C735-CC47-8CB5-E1250D950598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22B6B4AE-3E6B-8A4A-8888-BD572F685013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4360" yWindow="660" windowWidth="30200" windowHeight="21680" xr2:uid="{6AE4499B-BE9B-4430-8CBB-9E423EAAA4D3}"/>
+    <workbookView xWindow="16940" yWindow="3460" windowWidth="30200" windowHeight="21680" activeTab="1" xr2:uid="{6AE4499B-BE9B-4430-8CBB-9E423EAAA4D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Combined Manoa Data" sheetId="1" r:id="rId1"/>
-    <sheet name="Hailey's Data" sheetId="3" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="4" r:id="rId3"/>
-    <sheet name="Sheet2" sheetId="5" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="6" r:id="rId2"/>
+    <sheet name="Hailey's Data" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Combined Manoa Data'!$B$2:$N$137</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -33,7 +34,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="311">
   <si>
     <t>Date</t>
   </si>
@@ -1219,6 +1219,12 @@
       <t xml:space="preserve"> (‰)</t>
     </r>
   </si>
+  <si>
+    <t xml:space="preserve">3H </t>
+  </si>
+  <si>
+    <t>3H</t>
+  </si>
 </sst>
 </file>
 
@@ -1484,7 +1490,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1546,13 +1552,103 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1763,41 +1859,75 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -22137,93 +22267,95 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E174FB01-AC8B-4229-B319-63F7FF07E34C}">
-  <dimension ref="A1:X148"/>
+  <dimension ref="B1:X148"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="88"/>
-    <col min="2" max="2" width="13.83203125" style="75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5" style="75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5" style="75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5" style="75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.33203125" style="75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17" style="75" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.6640625" style="75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.1640625" style="75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.6640625" style="75" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22" style="18" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14" style="75" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="27.6640625" style="75" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.6640625" style="18" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.33203125" style="75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5" style="75" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.33203125" style="75" bestFit="1" customWidth="1"/>
-    <col min="18" max="21" width="8.6640625" style="75"/>
-    <col min="22" max="22" width="11.5" style="75" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.33203125" style="75" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.83203125" style="75" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="8.6640625" style="75"/>
+    <col min="1" max="1" width="8.6640625" style="77"/>
+    <col min="2" max="2" width="13.83203125" style="77" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5" style="77" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" style="77" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5" style="77" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" style="77" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17" style="77" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.6640625" style="77" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.1640625" style="77" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.6640625" style="77" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22" style="78" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14" style="77" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.6640625" style="77" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.6640625" style="78" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.33203125" style="77" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5" style="77" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.33203125" style="77" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.1640625" style="77" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="8.6640625" style="77"/>
+    <col min="22" max="22" width="11.5" style="77" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.33203125" style="77" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.83203125" style="77" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="8.6640625" style="77"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:24" s="86" customFormat="1">
-      <c r="K1" s="87"/>
-      <c r="L1" s="87"/>
-      <c r="N1" s="87"/>
-    </row>
-    <row r="2" spans="2:24" s="75" customFormat="1">
-      <c r="B2" s="79" t="s">
+    <row r="1" spans="2:24" ht="17" thickBot="1">
+      <c r="L1" s="78"/>
+    </row>
+    <row r="2" spans="2:24">
+      <c r="B2" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="79" t="s">
+      <c r="C2" s="86" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="79" t="s">
+      <c r="D2" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="79" t="s">
+      <c r="E2" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="79" t="s">
+      <c r="F2" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="79" t="s">
+      <c r="G2" s="86" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="79" t="s">
+      <c r="H2" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="79" t="s">
+      <c r="I2" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="79" t="s">
+      <c r="J2" s="86" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="79" t="s">
+      <c r="K2" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="79" t="s">
+      <c r="L2" s="86" t="s">
         <v>163</v>
       </c>
-      <c r="M2" s="79" t="s">
+      <c r="M2" s="86" t="s">
         <v>164</v>
       </c>
-      <c r="N2" s="79" t="s">
+      <c r="N2" s="86" t="s">
         <v>165</v>
       </c>
-      <c r="O2" s="79" t="s">
+      <c r="O2" s="86" t="s">
         <v>304</v>
       </c>
-      <c r="P2" s="79" t="s">
+      <c r="P2" s="86" t="s">
         <v>303</v>
       </c>
-      <c r="Q2" s="79" t="s">
+      <c r="Q2" s="86" t="s">
         <v>305</v>
       </c>
-      <c r="V2" s="80"/>
-      <c r="W2" s="81"/>
-      <c r="X2" s="81"/>
-    </row>
-    <row r="3" spans="2:24" s="75" customFormat="1">
-      <c r="B3" s="82">
+      <c r="R2" s="87" t="s">
+        <v>309</v>
+      </c>
+      <c r="V2" s="79"/>
+      <c r="W2" s="98"/>
+      <c r="X2" s="98"/>
+    </row>
+    <row r="3" spans="2:24">
+      <c r="B3" s="88">
         <v>44970.399305555555</v>
       </c>
       <c r="C3" s="18">
@@ -22261,10 +22393,10 @@
       <c r="M3" s="18">
         <v>7.7100600000000005E-2</v>
       </c>
-      <c r="N3" s="78">
+      <c r="N3" s="76">
         <v>-2.5</v>
       </c>
-      <c r="O3" s="78">
+      <c r="O3" s="76">
         <v>-7</v>
       </c>
       <c r="P3" s="74">
@@ -22273,12 +22405,13 @@
       <c r="Q3" s="74">
         <v>-4.63</v>
       </c>
-      <c r="V3" s="18"/>
+      <c r="R3" s="89"/>
+      <c r="V3" s="78"/>
       <c r="W3" s="83"/>
       <c r="X3" s="83"/>
     </row>
-    <row r="4" spans="2:24" s="75" customFormat="1">
-      <c r="B4" s="82">
+    <row r="4" spans="2:24">
+      <c r="B4" s="88">
         <v>44970.429166666669</v>
       </c>
       <c r="C4" s="18">
@@ -22316,10 +22449,10 @@
       <c r="M4" s="18">
         <v>0.12563849999999999</v>
       </c>
-      <c r="N4" s="78">
+      <c r="N4" s="76">
         <v>-2.5</v>
       </c>
-      <c r="O4" s="78">
+      <c r="O4" s="76">
         <v>-7</v>
       </c>
       <c r="P4" s="74">
@@ -22328,12 +22461,13 @@
       <c r="Q4" s="74">
         <v>-4.63</v>
       </c>
+      <c r="R4" s="89"/>
       <c r="V4" s="84"/>
       <c r="W4" s="83"/>
       <c r="X4" s="83"/>
     </row>
-    <row r="5" spans="2:24" s="75" customFormat="1">
-      <c r="B5" s="82">
+    <row r="5" spans="2:24">
+      <c r="B5" s="88">
         <v>44972.372916666667</v>
       </c>
       <c r="C5" s="18">
@@ -22371,10 +22505,10 @@
       <c r="M5" s="18">
         <v>5.5910100000000004E-3</v>
       </c>
-      <c r="N5" s="78">
+      <c r="N5" s="76">
         <v>-6</v>
       </c>
-      <c r="O5" s="78">
+      <c r="O5" s="76">
         <v>-37.1</v>
       </c>
       <c r="P5" s="74">
@@ -22383,12 +22517,13 @@
       <c r="Q5" s="74">
         <v>-4.63</v>
       </c>
+      <c r="R5" s="89"/>
       <c r="V5" s="84"/>
       <c r="W5" s="83"/>
       <c r="X5" s="83"/>
     </row>
-    <row r="6" spans="2:24" s="75" customFormat="1">
-      <c r="B6" s="82">
+    <row r="6" spans="2:24">
+      <c r="B6" s="88">
         <v>44972.397916666669</v>
       </c>
       <c r="C6" s="18">
@@ -22426,10 +22561,10 @@
       <c r="M6" s="18">
         <v>5.5910100000000004E-3</v>
       </c>
-      <c r="N6" s="78">
+      <c r="N6" s="76">
         <v>-6</v>
       </c>
-      <c r="O6" s="78">
+      <c r="O6" s="76">
         <v>-37.1</v>
       </c>
       <c r="P6" s="74">
@@ -22438,12 +22573,13 @@
       <c r="Q6" s="74">
         <v>-4.63</v>
       </c>
+      <c r="R6" s="89"/>
       <c r="V6" s="84"/>
       <c r="W6" s="83"/>
       <c r="X6" s="83"/>
     </row>
-    <row r="7" spans="2:24" s="75" customFormat="1">
-      <c r="B7" s="82">
+    <row r="7" spans="2:24">
+      <c r="B7" s="88">
         <v>44974.370833333334</v>
       </c>
       <c r="C7" s="18">
@@ -22481,10 +22617,10 @@
       <c r="M7" s="18">
         <v>5.2366299999999999E-3</v>
       </c>
-      <c r="N7" s="78">
+      <c r="N7" s="76">
         <v>-6</v>
       </c>
-      <c r="O7" s="78">
+      <c r="O7" s="76">
         <v>-37.1</v>
       </c>
       <c r="P7" s="74">
@@ -22493,12 +22629,13 @@
       <c r="Q7" s="74">
         <v>-4.63</v>
       </c>
+      <c r="R7" s="89"/>
       <c r="V7" s="84"/>
       <c r="W7" s="83"/>
       <c r="X7" s="83"/>
     </row>
-    <row r="8" spans="2:24" s="75" customFormat="1">
-      <c r="B8" s="82">
+    <row r="8" spans="2:24">
+      <c r="B8" s="88">
         <v>44974.385416666664</v>
       </c>
       <c r="C8" s="18">
@@ -22536,10 +22673,10 @@
       <c r="M8" s="18">
         <v>5.2366299999999999E-3</v>
       </c>
-      <c r="N8" s="78">
+      <c r="N8" s="76">
         <v>-6</v>
       </c>
-      <c r="O8" s="78">
+      <c r="O8" s="76">
         <v>-37.1</v>
       </c>
       <c r="P8" s="74">
@@ -22548,12 +22685,13 @@
       <c r="Q8" s="74">
         <v>-4.63</v>
       </c>
+      <c r="R8" s="89"/>
       <c r="V8" s="84"/>
       <c r="W8" s="83"/>
       <c r="X8" s="83"/>
     </row>
-    <row r="9" spans="2:24" s="75" customFormat="1">
-      <c r="B9" s="82">
+    <row r="9" spans="2:24">
+      <c r="B9" s="88">
         <v>44974.432638888888</v>
       </c>
       <c r="C9" s="18">
@@ -22591,10 +22729,10 @@
       <c r="M9" s="18">
         <v>1.06991E-2</v>
       </c>
-      <c r="N9" s="78">
+      <c r="N9" s="76">
         <v>-6</v>
       </c>
-      <c r="O9" s="78">
+      <c r="O9" s="76">
         <v>-37.1</v>
       </c>
       <c r="P9" s="74">
@@ -22603,12 +22741,13 @@
       <c r="Q9" s="74">
         <v>-4.63</v>
       </c>
+      <c r="R9" s="89"/>
       <c r="V9" s="84"/>
       <c r="W9" s="83"/>
       <c r="X9" s="83"/>
     </row>
-    <row r="10" spans="2:24" s="75" customFormat="1">
-      <c r="B10" s="82">
+    <row r="10" spans="2:24">
+      <c r="B10" s="88">
         <v>44977.37222222222</v>
       </c>
       <c r="C10" s="18">
@@ -22646,10 +22785,10 @@
       <c r="M10" s="18">
         <v>0.240284</v>
       </c>
-      <c r="N10" s="78">
+      <c r="N10" s="76">
         <v>-6</v>
       </c>
-      <c r="O10" s="78">
+      <c r="O10" s="76">
         <v>-37.1</v>
       </c>
       <c r="P10" s="74">
@@ -22658,12 +22797,13 @@
       <c r="Q10" s="74">
         <v>-4.63</v>
       </c>
+      <c r="R10" s="89"/>
       <c r="V10" s="84"/>
       <c r="W10" s="83"/>
       <c r="X10" s="83"/>
     </row>
-    <row r="11" spans="2:24" s="75" customFormat="1">
-      <c r="B11" s="82">
+    <row r="11" spans="2:24">
+      <c r="B11" s="88">
         <v>44977.393055555556</v>
       </c>
       <c r="C11" s="18">
@@ -22701,10 +22841,10 @@
       <c r="M11" s="18">
         <v>0.240284</v>
       </c>
-      <c r="N11" s="78">
+      <c r="N11" s="76">
         <v>-6</v>
       </c>
-      <c r="O11" s="78">
+      <c r="O11" s="76">
         <v>-37.1</v>
       </c>
       <c r="P11" s="74">
@@ -22713,12 +22853,13 @@
       <c r="Q11" s="74">
         <v>-4.63</v>
       </c>
+      <c r="R11" s="89"/>
       <c r="V11" s="84"/>
       <c r="W11" s="83"/>
       <c r="X11" s="83"/>
     </row>
-    <row r="12" spans="2:24" s="75" customFormat="1">
-      <c r="B12" s="82">
+    <row r="12" spans="2:24">
+      <c r="B12" s="88">
         <v>44977.43472222222</v>
       </c>
       <c r="C12" s="18">
@@ -22756,10 +22897,10 @@
       <c r="M12" s="18">
         <v>3.06191E-2</v>
       </c>
-      <c r="N12" s="78">
+      <c r="N12" s="76">
         <v>-6</v>
       </c>
-      <c r="O12" s="78">
+      <c r="O12" s="76">
         <v>-37.1</v>
       </c>
       <c r="P12" s="74">
@@ -22768,12 +22909,13 @@
       <c r="Q12" s="74">
         <v>-4.63</v>
       </c>
+      <c r="R12" s="89"/>
       <c r="V12" s="84"/>
       <c r="W12" s="83"/>
       <c r="X12" s="83"/>
     </row>
-    <row r="13" spans="2:24" s="75" customFormat="1">
-      <c r="B13" s="82">
+    <row r="13" spans="2:24">
+      <c r="B13" s="88">
         <v>44977.448611111111</v>
       </c>
       <c r="C13" s="18">
@@ -22811,10 +22953,10 @@
       <c r="M13" s="18">
         <v>7.7100600000000005E-2</v>
       </c>
-      <c r="N13" s="78">
+      <c r="N13" s="76">
         <v>-6</v>
       </c>
-      <c r="O13" s="78">
+      <c r="O13" s="76">
         <v>-37.1</v>
       </c>
       <c r="P13" s="74">
@@ -22823,12 +22965,13 @@
       <c r="Q13" s="74">
         <v>-4.63</v>
       </c>
+      <c r="R13" s="89"/>
       <c r="V13" s="84"/>
       <c r="W13" s="83"/>
       <c r="X13" s="83"/>
     </row>
-    <row r="14" spans="2:24" s="75" customFormat="1">
-      <c r="B14" s="82">
+    <row r="14" spans="2:24">
+      <c r="B14" s="88">
         <v>44979.367361111108</v>
       </c>
       <c r="C14" s="18">
@@ -22866,10 +23009,10 @@
       <c r="M14" s="18">
         <v>9.4826599999999997E-2</v>
       </c>
-      <c r="N14" s="78">
+      <c r="N14" s="76">
         <v>-3.1</v>
       </c>
-      <c r="O14" s="78">
+      <c r="O14" s="76">
         <v>-13.6</v>
       </c>
       <c r="P14" s="74">
@@ -22878,12 +23021,13 @@
       <c r="Q14" s="74">
         <v>-4.63</v>
       </c>
+      <c r="R14" s="89"/>
       <c r="V14" s="84"/>
       <c r="W14" s="83"/>
       <c r="X14" s="83"/>
     </row>
-    <row r="15" spans="2:24" s="75" customFormat="1">
-      <c r="B15" s="82">
+    <row r="15" spans="2:24">
+      <c r="B15" s="88">
         <v>44979.385416666664</v>
       </c>
       <c r="C15" s="18">
@@ -22921,10 +23065,10 @@
       <c r="M15" s="18">
         <v>3.24406E-2</v>
       </c>
-      <c r="N15" s="78">
+      <c r="N15" s="76">
         <v>-3.1</v>
       </c>
-      <c r="O15" s="78">
+      <c r="O15" s="76">
         <v>-13.6</v>
       </c>
       <c r="P15" s="74">
@@ -22933,12 +23077,13 @@
       <c r="Q15" s="74">
         <v>-4.63</v>
       </c>
+      <c r="R15" s="89"/>
       <c r="V15" s="84"/>
       <c r="W15" s="83"/>
       <c r="X15" s="83"/>
     </row>
-    <row r="16" spans="2:24" s="75" customFormat="1">
-      <c r="B16" s="82">
+    <row r="16" spans="2:24">
+      <c r="B16" s="88">
         <v>44979.541666666664</v>
       </c>
       <c r="C16" s="18">
@@ -22976,10 +23121,10 @@
       <c r="M16" s="18">
         <v>2.33487E-2</v>
       </c>
-      <c r="N16" s="78">
+      <c r="N16" s="76">
         <v>-3.1</v>
       </c>
-      <c r="O16" s="78">
+      <c r="O16" s="76">
         <v>-13.6</v>
       </c>
       <c r="P16" s="74">
@@ -22988,12 +23133,13 @@
       <c r="Q16" s="74">
         <v>-4.63</v>
       </c>
+      <c r="R16" s="89"/>
       <c r="V16" s="84"/>
       <c r="W16" s="83"/>
       <c r="X16" s="83"/>
     </row>
-    <row r="17" spans="2:24" s="75" customFormat="1">
-      <c r="B17" s="82">
+    <row r="17" spans="2:24">
+      <c r="B17" s="88">
         <v>44979.5625</v>
       </c>
       <c r="C17" s="18">
@@ -23031,10 +23177,10 @@
       <c r="M17" s="18">
         <v>2.33487E-2</v>
       </c>
-      <c r="N17" s="78">
+      <c r="N17" s="76">
         <v>-3.1</v>
       </c>
-      <c r="O17" s="78">
+      <c r="O17" s="76">
         <v>-13.6</v>
       </c>
       <c r="P17" s="74">
@@ -23043,12 +23189,13 @@
       <c r="Q17" s="74">
         <v>-4.63</v>
       </c>
+      <c r="R17" s="89"/>
       <c r="V17" s="84"/>
       <c r="W17" s="83"/>
       <c r="X17" s="83"/>
     </row>
-    <row r="18" spans="2:24" s="75" customFormat="1">
-      <c r="B18" s="82">
+    <row r="18" spans="2:24">
+      <c r="B18" s="88">
         <v>44981.361111111109</v>
       </c>
       <c r="C18" s="18">
@@ -23086,10 +23233,10 @@
       <c r="M18" s="18">
         <v>2.23054E-2</v>
       </c>
-      <c r="N18" s="78">
+      <c r="N18" s="76">
         <v>-3.1</v>
       </c>
-      <c r="O18" s="78">
+      <c r="O18" s="76">
         <v>-13.6</v>
       </c>
       <c r="P18" s="74">
@@ -23098,12 +23245,13 @@
       <c r="Q18" s="74">
         <v>-4.63</v>
       </c>
+      <c r="R18" s="89"/>
       <c r="V18" s="84"/>
       <c r="W18" s="83"/>
       <c r="X18" s="83"/>
     </row>
-    <row r="19" spans="2:24" s="75" customFormat="1">
-      <c r="B19" s="82">
+    <row r="19" spans="2:24">
+      <c r="B19" s="88">
         <v>44981.375</v>
       </c>
       <c r="C19" s="18">
@@ -23141,10 +23289,10 @@
       <c r="M19" s="18">
         <v>2.23054E-2</v>
       </c>
-      <c r="N19" s="78">
+      <c r="N19" s="76">
         <v>-3.1</v>
       </c>
-      <c r="O19" s="78">
+      <c r="O19" s="76">
         <v>-13.6</v>
       </c>
       <c r="P19" s="74">
@@ -23153,12 +23301,13 @@
       <c r="Q19" s="74">
         <v>-4.63</v>
       </c>
+      <c r="R19" s="89"/>
       <c r="V19" s="84"/>
       <c r="W19" s="83"/>
       <c r="X19" s="83"/>
     </row>
-    <row r="20" spans="2:24" s="75" customFormat="1">
-      <c r="B20" s="82">
+    <row r="20" spans="2:24">
+      <c r="B20" s="88">
         <v>44986.363888888889</v>
       </c>
       <c r="C20" s="18">
@@ -23196,10 +23345,10 @@
       <c r="M20" s="18">
         <v>4.1506300000000003E-2</v>
       </c>
-      <c r="N20" s="78">
+      <c r="N20" s="76">
         <v>-3</v>
       </c>
-      <c r="O20" s="78">
+      <c r="O20" s="76">
         <v>-6.7</v>
       </c>
       <c r="P20" s="74">
@@ -23208,12 +23357,13 @@
       <c r="Q20" s="74">
         <v>-4.63</v>
       </c>
+      <c r="R20" s="89"/>
       <c r="V20" s="84"/>
       <c r="W20" s="83"/>
       <c r="X20" s="83"/>
     </row>
-    <row r="21" spans="2:24" s="75" customFormat="1">
-      <c r="B21" s="82">
+    <row r="21" spans="2:24">
+      <c r="B21" s="88">
         <v>44986.381944444445</v>
       </c>
       <c r="C21" s="18">
@@ -23251,10 +23401,10 @@
       <c r="M21" s="18">
         <v>0.125691</v>
       </c>
-      <c r="N21" s="78">
+      <c r="N21" s="76">
         <v>-3</v>
       </c>
-      <c r="O21" s="78">
+      <c r="O21" s="76">
         <v>-6.7</v>
       </c>
       <c r="P21" s="74">
@@ -23263,12 +23413,13 @@
       <c r="Q21" s="74">
         <v>-4.63</v>
       </c>
+      <c r="R21" s="89"/>
       <c r="V21" s="84"/>
       <c r="W21" s="83"/>
       <c r="X21" s="83"/>
     </row>
-    <row r="22" spans="2:24" s="75" customFormat="1">
-      <c r="B22" s="82">
+    <row r="22" spans="2:24">
+      <c r="B22" s="88">
         <v>44986.401388888888</v>
       </c>
       <c r="C22" s="18">
@@ -23306,10 +23457,10 @@
       <c r="M22" s="18">
         <v>3.8610800000000001E-2</v>
       </c>
-      <c r="N22" s="78">
+      <c r="N22" s="76">
         <v>-3</v>
       </c>
-      <c r="O22" s="78">
+      <c r="O22" s="76">
         <v>-6.7</v>
       </c>
       <c r="P22" s="74">
@@ -23318,12 +23469,13 @@
       <c r="Q22" s="74">
         <v>-4.63</v>
       </c>
+      <c r="R22" s="89"/>
       <c r="V22" s="84"/>
       <c r="W22" s="83"/>
       <c r="X22" s="83"/>
     </row>
-    <row r="23" spans="2:24" s="75" customFormat="1">
-      <c r="B23" s="82">
+    <row r="23" spans="2:24">
+      <c r="B23" s="88">
         <v>45019.381944444445</v>
       </c>
       <c r="C23" s="18">
@@ -23361,10 +23513,10 @@
       <c r="M23" s="18">
         <v>2.2294899999999999E-2</v>
       </c>
-      <c r="N23" s="78">
+      <c r="N23" s="76">
         <v>-2.6</v>
       </c>
-      <c r="O23" s="78">
+      <c r="O23" s="76">
         <v>-6.1</v>
       </c>
       <c r="P23" s="74">
@@ -23373,12 +23525,13 @@
       <c r="Q23" s="74">
         <v>-4.63</v>
       </c>
+      <c r="R23" s="89"/>
       <c r="V23" s="84"/>
       <c r="W23" s="83"/>
       <c r="X23" s="83"/>
     </row>
-    <row r="24" spans="2:24" s="75" customFormat="1">
-      <c r="B24" s="82">
+    <row r="24" spans="2:24">
+      <c r="B24" s="88">
         <v>45019.401388888888</v>
       </c>
       <c r="C24" s="18">
@@ -23416,10 +23569,10 @@
       <c r="M24" s="18">
         <v>5.8700500000000003E-2</v>
       </c>
-      <c r="N24" s="78">
+      <c r="N24" s="76">
         <v>-2.6</v>
       </c>
-      <c r="O24" s="78">
+      <c r="O24" s="76">
         <v>-6.1</v>
       </c>
       <c r="P24" s="74">
@@ -23428,12 +23581,13 @@
       <c r="Q24" s="74">
         <v>-4.63</v>
       </c>
+      <c r="R24" s="89"/>
       <c r="V24" s="84"/>
       <c r="W24" s="83"/>
       <c r="X24" s="83"/>
     </row>
-    <row r="25" spans="2:24" s="75" customFormat="1">
-      <c r="B25" s="82">
+    <row r="25" spans="2:24">
+      <c r="B25" s="88">
         <v>45028.354166666664</v>
       </c>
       <c r="C25" s="18">
@@ -23471,10 +23625,10 @@
       <c r="M25" s="18">
         <v>4.6169500000000002E-2</v>
       </c>
-      <c r="N25" s="78">
+      <c r="N25" s="76">
         <v>-2.6</v>
       </c>
-      <c r="O25" s="78">
+      <c r="O25" s="76">
         <v>-6.1</v>
       </c>
       <c r="P25" s="74">
@@ -23483,12 +23637,13 @@
       <c r="Q25" s="74">
         <v>-4.63</v>
       </c>
+      <c r="R25" s="89"/>
       <c r="V25" s="84"/>
       <c r="W25" s="83"/>
       <c r="X25" s="83"/>
     </row>
-    <row r="26" spans="2:24" s="75" customFormat="1">
-      <c r="B26" s="82">
+    <row r="26" spans="2:24">
+      <c r="B26" s="88">
         <v>45028.368750000001</v>
       </c>
       <c r="C26" s="18">
@@ -23526,10 +23681,10 @@
       <c r="M26" s="18">
         <v>2.20571E-2</v>
       </c>
-      <c r="N26" s="78">
+      <c r="N26" s="76">
         <v>-2.6</v>
       </c>
-      <c r="O26" s="78">
+      <c r="O26" s="76">
         <v>-6.1</v>
       </c>
       <c r="P26" s="74">
@@ -23538,12 +23693,13 @@
       <c r="Q26" s="74">
         <v>-4.63</v>
       </c>
+      <c r="R26" s="89"/>
       <c r="V26" s="84"/>
       <c r="W26" s="83"/>
       <c r="X26" s="83"/>
     </row>
-    <row r="27" spans="2:24" s="75" customFormat="1">
-      <c r="B27" s="82">
+    <row r="27" spans="2:24">
+      <c r="B27" s="88">
         <v>45030.337500000001</v>
       </c>
       <c r="C27" s="18">
@@ -23581,10 +23737,10 @@
       <c r="M27" s="18">
         <v>1.02437E-2</v>
       </c>
-      <c r="N27" s="78">
+      <c r="N27" s="76">
         <v>-2.6</v>
       </c>
-      <c r="O27" s="78">
+      <c r="O27" s="76">
         <v>-6.1</v>
       </c>
       <c r="P27" s="74">
@@ -23593,12 +23749,13 @@
       <c r="Q27" s="74">
         <v>-4.63</v>
       </c>
+      <c r="R27" s="89"/>
       <c r="V27" s="84"/>
       <c r="W27" s="83"/>
       <c r="X27" s="83"/>
     </row>
-    <row r="28" spans="2:24" s="75" customFormat="1">
-      <c r="B28" s="82">
+    <row r="28" spans="2:24">
+      <c r="B28" s="88">
         <v>45030.351388888892</v>
       </c>
       <c r="C28" s="18">
@@ -23636,10 +23793,10 @@
       <c r="M28" s="18">
         <v>1.02437E-2</v>
       </c>
-      <c r="N28" s="78">
+      <c r="N28" s="76">
         <v>-2.6</v>
       </c>
-      <c r="O28" s="78">
+      <c r="O28" s="76">
         <v>-6.1</v>
       </c>
       <c r="P28" s="74">
@@ -23648,12 +23805,13 @@
       <c r="Q28" s="74">
         <v>-4.63</v>
       </c>
+      <c r="R28" s="89"/>
       <c r="V28" s="84"/>
       <c r="W28" s="83"/>
       <c r="X28" s="83"/>
     </row>
-    <row r="29" spans="2:24" s="75" customFormat="1">
-      <c r="B29" s="82">
+    <row r="29" spans="2:24">
+      <c r="B29" s="88">
         <v>45033.361111111109</v>
       </c>
       <c r="C29" s="18">
@@ -23691,10 +23849,10 @@
       <c r="M29" s="18">
         <v>9.4680600000000004E-3</v>
       </c>
-      <c r="N29" s="78">
+      <c r="N29" s="76">
         <v>-2.6</v>
       </c>
-      <c r="O29" s="78">
+      <c r="O29" s="76">
         <v>-6.1</v>
       </c>
       <c r="P29" s="74">
@@ -23703,12 +23861,13 @@
       <c r="Q29" s="74">
         <v>-4.63</v>
       </c>
+      <c r="R29" s="89"/>
       <c r="V29" s="84"/>
       <c r="W29" s="83"/>
       <c r="X29" s="83"/>
     </row>
-    <row r="30" spans="2:24" s="75" customFormat="1">
-      <c r="B30" s="82">
+    <row r="30" spans="2:24">
+      <c r="B30" s="88">
         <v>45033.375</v>
       </c>
       <c r="C30" s="18">
@@ -23746,10 +23905,10 @@
       <c r="M30" s="18">
         <v>9.4680600000000004E-3</v>
       </c>
-      <c r="N30" s="78">
+      <c r="N30" s="76">
         <v>-2.6</v>
       </c>
-      <c r="O30" s="78">
+      <c r="O30" s="76">
         <v>-6.1</v>
       </c>
       <c r="P30" s="74">
@@ -23758,12 +23917,13 @@
       <c r="Q30" s="74">
         <v>-4.63</v>
       </c>
+      <c r="R30" s="89"/>
       <c r="V30" s="84"/>
       <c r="W30" s="83"/>
       <c r="X30" s="83"/>
     </row>
-    <row r="31" spans="2:24" s="75" customFormat="1">
-      <c r="B31" s="82">
+    <row r="31" spans="2:24">
+      <c r="B31" s="88">
         <v>45042.376388888886</v>
       </c>
       <c r="C31" s="18">
@@ -23801,10 +23961,10 @@
       <c r="M31" s="18">
         <v>0.10097200000000001</v>
       </c>
-      <c r="N31" s="78">
+      <c r="N31" s="76">
         <v>-1.3</v>
       </c>
-      <c r="O31" s="78">
+      <c r="O31" s="76">
         <v>1.5</v>
       </c>
       <c r="P31" s="74">
@@ -23813,12 +23973,13 @@
       <c r="Q31" s="74">
         <v>-4.63</v>
       </c>
+      <c r="R31" s="89"/>
       <c r="V31" s="84"/>
       <c r="W31" s="83"/>
       <c r="X31" s="83"/>
     </row>
-    <row r="32" spans="2:24" s="75" customFormat="1">
-      <c r="B32" s="82">
+    <row r="32" spans="2:24">
+      <c r="B32" s="88">
         <v>45058.451388888891</v>
       </c>
       <c r="C32" s="18">
@@ -23856,10 +24017,10 @@
       <c r="M32" s="18">
         <v>2.3722799999999999E-2</v>
       </c>
-      <c r="N32" s="78">
+      <c r="N32" s="76">
         <v>-1.8</v>
       </c>
-      <c r="O32" s="78">
+      <c r="O32" s="76">
         <v>-0.1</v>
       </c>
       <c r="P32" s="74">
@@ -23868,12 +24029,13 @@
       <c r="Q32" s="74">
         <v>-4.63</v>
       </c>
+      <c r="R32" s="89"/>
       <c r="V32" s="84"/>
       <c r="W32" s="83"/>
       <c r="X32" s="83"/>
     </row>
-    <row r="33" spans="2:24" s="75" customFormat="1">
-      <c r="B33" s="82">
+    <row r="33" spans="2:24">
+      <c r="B33" s="88">
         <v>45061.423611111109</v>
       </c>
       <c r="C33" s="18">
@@ -23911,10 +24073,10 @@
       <c r="M33" s="18">
         <v>2.3722799999999999E-2</v>
       </c>
-      <c r="N33" s="78">
+      <c r="N33" s="76">
         <v>-1.8</v>
       </c>
-      <c r="O33" s="78">
+      <c r="O33" s="76">
         <v>-0.1</v>
       </c>
       <c r="P33" s="74">
@@ -23923,12 +24085,13 @@
       <c r="Q33" s="74">
         <v>-4.63</v>
       </c>
+      <c r="R33" s="89"/>
       <c r="V33" s="84"/>
       <c r="W33" s="83"/>
       <c r="X33" s="83"/>
     </row>
-    <row r="34" spans="2:24" s="75" customFormat="1">
-      <c r="B34" s="82">
+    <row r="34" spans="2:24">
+      <c r="B34" s="88">
         <v>45061.453472222223</v>
       </c>
       <c r="C34" s="18">
@@ -23966,10 +24129,10 @@
       <c r="M34" s="18">
         <v>2.4759099999999999E-2</v>
       </c>
-      <c r="N34" s="78">
+      <c r="N34" s="76">
         <v>-1.8</v>
       </c>
-      <c r="O34" s="78">
+      <c r="O34" s="76">
         <v>-0.1</v>
       </c>
       <c r="P34" s="74">
@@ -23978,12 +24141,13 @@
       <c r="Q34" s="74">
         <v>-4.63</v>
       </c>
+      <c r="R34" s="89"/>
       <c r="V34" s="84"/>
       <c r="W34" s="83"/>
       <c r="X34" s="83"/>
     </row>
-    <row r="35" spans="2:24" s="75" customFormat="1">
-      <c r="B35" s="82">
+    <row r="35" spans="2:24">
+      <c r="B35" s="88">
         <v>45061.46875</v>
       </c>
       <c r="C35" s="18">
@@ -24021,10 +24185,10 @@
       <c r="M35" s="18">
         <v>2.4759099999999999E-2</v>
       </c>
-      <c r="N35" s="78">
+      <c r="N35" s="76">
         <v>-1.8</v>
       </c>
-      <c r="O35" s="78">
+      <c r="O35" s="76">
         <v>-0.1</v>
       </c>
       <c r="P35" s="74">
@@ -24033,12 +24197,13 @@
       <c r="Q35" s="74">
         <v>-4.63</v>
       </c>
+      <c r="R35" s="89"/>
       <c r="V35" s="84"/>
       <c r="W35" s="83"/>
       <c r="X35" s="83"/>
     </row>
-    <row r="36" spans="2:24" s="75" customFormat="1">
-      <c r="B36" s="82">
+    <row r="36" spans="2:24">
+      <c r="B36" s="88">
         <v>45061.486111111109</v>
       </c>
       <c r="C36" s="18">
@@ -24076,10 +24241,10 @@
       <c r="M36" s="18">
         <v>6.5966999999999998E-2</v>
       </c>
-      <c r="N36" s="78">
+      <c r="N36" s="76">
         <v>-1.8</v>
       </c>
-      <c r="O36" s="78">
+      <c r="O36" s="76">
         <v>-0.1</v>
       </c>
       <c r="P36" s="74">
@@ -24088,12 +24253,13 @@
       <c r="Q36" s="74">
         <v>-4.63</v>
       </c>
+      <c r="R36" s="89"/>
       <c r="V36" s="84"/>
       <c r="W36" s="83"/>
       <c r="X36" s="83"/>
     </row>
-    <row r="37" spans="2:24" s="75" customFormat="1">
-      <c r="B37" s="82">
+    <row r="37" spans="2:24">
+      <c r="B37" s="88">
         <v>45062.475694444445</v>
       </c>
       <c r="C37" s="18">
@@ -24131,10 +24297,10 @@
       <c r="M37" s="18">
         <v>0.168964</v>
       </c>
-      <c r="N37" s="78">
+      <c r="N37" s="76">
         <v>-1.8</v>
       </c>
-      <c r="O37" s="78">
+      <c r="O37" s="76">
         <v>-0.1</v>
       </c>
       <c r="P37" s="74">
@@ -24143,12 +24309,13 @@
       <c r="Q37" s="74">
         <v>-4.63</v>
       </c>
+      <c r="R37" s="89"/>
       <c r="V37" s="84"/>
       <c r="W37" s="83"/>
       <c r="X37" s="83"/>
     </row>
-    <row r="38" spans="2:24" s="75" customFormat="1">
-      <c r="B38" s="82">
+    <row r="38" spans="2:24">
+      <c r="B38" s="88">
         <v>45062.489583333336</v>
       </c>
       <c r="C38" s="18">
@@ -24186,10 +24353,10 @@
       <c r="M38" s="18">
         <v>6.5155400000000002E-2</v>
       </c>
-      <c r="N38" s="78">
+      <c r="N38" s="76">
         <v>-1.8</v>
       </c>
-      <c r="O38" s="78">
+      <c r="O38" s="76">
         <v>-0.1</v>
       </c>
       <c r="P38" s="74">
@@ -24198,12 +24365,13 @@
       <c r="Q38" s="74">
         <v>-4.63</v>
       </c>
+      <c r="R38" s="89"/>
       <c r="V38" s="84"/>
       <c r="W38" s="83"/>
       <c r="X38" s="83"/>
     </row>
-    <row r="39" spans="2:24" s="75" customFormat="1">
-      <c r="B39" s="82">
+    <row r="39" spans="2:24">
+      <c r="B39" s="88">
         <v>45062.53125</v>
       </c>
       <c r="C39" s="18">
@@ -24241,10 +24409,10 @@
       <c r="M39" s="18">
         <v>0.22280800000000001</v>
       </c>
-      <c r="N39" s="78">
+      <c r="N39" s="76">
         <v>-1.8</v>
       </c>
-      <c r="O39" s="78">
+      <c r="O39" s="76">
         <v>-0.1</v>
       </c>
       <c r="P39" s="74">
@@ -24253,12 +24421,13 @@
       <c r="Q39" s="74">
         <v>-4.63</v>
       </c>
+      <c r="R39" s="89"/>
       <c r="V39" s="84"/>
       <c r="W39" s="83"/>
       <c r="X39" s="83"/>
     </row>
-    <row r="40" spans="2:24" s="75" customFormat="1">
-      <c r="B40" s="82">
+    <row r="40" spans="2:24">
+      <c r="B40" s="88">
         <v>45063.464583333334</v>
       </c>
       <c r="C40" s="18">
@@ -24296,10 +24465,10 @@
       <c r="M40" s="18">
         <v>0.43688300000000002</v>
       </c>
-      <c r="N40" s="78">
+      <c r="N40" s="76">
         <v>-1.8</v>
       </c>
-      <c r="O40" s="78">
+      <c r="O40" s="76">
         <v>-0.1</v>
       </c>
       <c r="P40" s="74">
@@ -24308,12 +24477,13 @@
       <c r="Q40" s="74">
         <v>-4.63</v>
       </c>
+      <c r="R40" s="89"/>
       <c r="V40" s="84"/>
       <c r="W40" s="83"/>
       <c r="X40" s="83"/>
     </row>
-    <row r="41" spans="2:24" s="75" customFormat="1">
-      <c r="B41" s="82">
+    <row r="41" spans="2:24">
+      <c r="B41" s="88">
         <v>45063.486111111109</v>
       </c>
       <c r="C41" s="18">
@@ -24351,10 +24521,10 @@
       <c r="M41" s="18">
         <v>0.43688300000000002</v>
       </c>
-      <c r="N41" s="78">
+      <c r="N41" s="76">
         <v>-1.8</v>
       </c>
-      <c r="O41" s="78">
+      <c r="O41" s="76">
         <v>-0.1</v>
       </c>
       <c r="P41" s="74">
@@ -24363,9 +24533,10 @@
       <c r="Q41" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" s="75" customFormat="1">
-      <c r="B42" s="82">
+      <c r="R41" s="89"/>
+    </row>
+    <row r="42" spans="2:24">
+      <c r="B42" s="88">
         <v>45077.625</v>
       </c>
       <c r="C42" s="18">
@@ -24403,10 +24574,10 @@
       <c r="M42" s="18">
         <v>2.53764E-2</v>
       </c>
-      <c r="N42" s="78">
+      <c r="N42" s="76">
         <v>-1.7</v>
       </c>
-      <c r="O42" s="78">
+      <c r="O42" s="76">
         <v>0.1</v>
       </c>
       <c r="P42" s="74">
@@ -24415,9 +24586,10 @@
       <c r="Q42" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" s="75" customFormat="1">
-      <c r="B43" s="82">
+      <c r="R42" s="89"/>
+    </row>
+    <row r="43" spans="2:24">
+      <c r="B43" s="88">
         <v>45077.635416666664</v>
       </c>
       <c r="C43" s="18">
@@ -24455,10 +24627,10 @@
       <c r="M43" s="18">
         <v>2.53764E-2</v>
       </c>
-      <c r="N43" s="78">
+      <c r="N43" s="76">
         <v>-1.7</v>
       </c>
-      <c r="O43" s="78">
+      <c r="O43" s="76">
         <v>0.1</v>
       </c>
       <c r="P43" s="74">
@@ -24467,9 +24639,10 @@
       <c r="Q43" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" s="75" customFormat="1">
-      <c r="B44" s="82">
+      <c r="R43" s="89"/>
+    </row>
+    <row r="44" spans="2:24">
+      <c r="B44" s="88">
         <v>45077.651388888888</v>
       </c>
       <c r="C44" s="18">
@@ -24507,10 +24680,10 @@
       <c r="M44" s="18">
         <v>2.5610000000000001E-2</v>
       </c>
-      <c r="N44" s="78">
+      <c r="N44" s="76">
         <v>-1.7</v>
       </c>
-      <c r="O44" s="78">
+      <c r="O44" s="76">
         <v>0.1</v>
       </c>
       <c r="P44" s="74">
@@ -24519,9 +24692,10 @@
       <c r="Q44" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" s="75" customFormat="1">
-      <c r="B45" s="82">
+      <c r="R44" s="89"/>
+    </row>
+    <row r="45" spans="2:24">
+      <c r="B45" s="88">
         <v>45078.604166666664</v>
       </c>
       <c r="C45" s="18">
@@ -24559,10 +24733,10 @@
       <c r="M45" s="18">
         <v>2.0521899999999999E-2</v>
       </c>
-      <c r="N45" s="78">
+      <c r="N45" s="76">
         <v>-1.6</v>
       </c>
-      <c r="O45" s="78">
+      <c r="O45" s="76">
         <v>0.3</v>
       </c>
       <c r="P45" s="74">
@@ -24571,9 +24745,10 @@
       <c r="Q45" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" s="75" customFormat="1">
-      <c r="B46" s="82">
+      <c r="R45" s="89"/>
+    </row>
+    <row r="46" spans="2:24">
+      <c r="B46" s="88">
         <v>45078.614583333336</v>
       </c>
       <c r="C46" s="18">
@@ -24611,10 +24786,10 @@
       <c r="M46" s="18">
         <v>2.15534E-2</v>
       </c>
-      <c r="N46" s="78">
+      <c r="N46" s="76">
         <v>-1.6</v>
       </c>
-      <c r="O46" s="78">
+      <c r="O46" s="76">
         <v>0.3</v>
       </c>
       <c r="P46" s="74">
@@ -24623,9 +24798,10 @@
       <c r="Q46" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" s="75" customFormat="1">
-      <c r="B47" s="82">
+      <c r="R46" s="89"/>
+    </row>
+    <row r="47" spans="2:24">
+      <c r="B47" s="88">
         <v>45078.627083333333</v>
       </c>
       <c r="C47" s="18">
@@ -24663,10 +24839,10 @@
       <c r="M47" s="18">
         <v>0.204565</v>
       </c>
-      <c r="N47" s="78">
+      <c r="N47" s="76">
         <v>-1.6</v>
       </c>
-      <c r="O47" s="78">
+      <c r="O47" s="76">
         <v>0.3</v>
       </c>
       <c r="P47" s="74">
@@ -24675,9 +24851,10 @@
       <c r="Q47" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" s="75" customFormat="1">
-      <c r="B48" s="82">
+      <c r="R47" s="89"/>
+    </row>
+    <row r="48" spans="2:24">
+      <c r="B48" s="88">
         <v>45078.638194444444</v>
       </c>
       <c r="C48" s="18">
@@ -24715,10 +24892,10 @@
       <c r="M48" s="18">
         <v>5.8530400000000003E-2</v>
       </c>
-      <c r="N48" s="78">
+      <c r="N48" s="76">
         <v>-1.6</v>
       </c>
-      <c r="O48" s="78">
+      <c r="O48" s="76">
         <v>0.3</v>
       </c>
       <c r="P48" s="74">
@@ -24727,9 +24904,10 @@
       <c r="Q48" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="49" spans="2:17" s="75" customFormat="1">
-      <c r="B49" s="82">
+      <c r="R48" s="89"/>
+    </row>
+    <row r="49" spans="2:18">
+      <c r="B49" s="88">
         <v>45079.39166666667</v>
       </c>
       <c r="C49" s="18">
@@ -24767,10 +24945,10 @@
       <c r="M49" s="18">
         <v>0.15256500000000001</v>
       </c>
-      <c r="N49" s="78">
+      <c r="N49" s="76">
         <v>-1.6</v>
       </c>
-      <c r="O49" s="78">
+      <c r="O49" s="76">
         <v>0.3</v>
       </c>
       <c r="P49" s="74">
@@ -24779,9 +24957,10 @@
       <c r="Q49" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="50" spans="2:17" s="75" customFormat="1">
-      <c r="B50" s="82">
+      <c r="R49" s="89"/>
+    </row>
+    <row r="50" spans="2:18">
+      <c r="B50" s="88">
         <v>45079.416666666664</v>
       </c>
       <c r="C50" s="18">
@@ -24819,10 +24998,10 @@
       <c r="M50" s="18">
         <v>0.31035499999999999</v>
       </c>
-      <c r="N50" s="78">
+      <c r="N50" s="76">
         <v>-1.6</v>
       </c>
-      <c r="O50" s="78">
+      <c r="O50" s="76">
         <v>0.3</v>
       </c>
       <c r="P50" s="74">
@@ -24831,9 +25010,10 @@
       <c r="Q50" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="51" spans="2:17" s="75" customFormat="1">
-      <c r="B51" s="82">
+      <c r="R50" s="89"/>
+    </row>
+    <row r="51" spans="2:18">
+      <c r="B51" s="88">
         <v>45121.4375</v>
       </c>
       <c r="C51" s="18">
@@ -24871,10 +25051,10 @@
       <c r="M51" s="18">
         <v>1.1124E-2</v>
       </c>
-      <c r="N51" s="78">
+      <c r="N51" s="76">
         <v>-1.7</v>
       </c>
-      <c r="O51" s="78">
+      <c r="O51" s="76">
         <v>0.8</v>
       </c>
       <c r="P51" s="74">
@@ -24883,9 +25063,10 @@
       <c r="Q51" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="52" spans="2:17" s="75" customFormat="1">
-      <c r="B52" s="82">
+      <c r="R51" s="89"/>
+    </row>
+    <row r="52" spans="2:18">
+      <c r="B52" s="88">
         <v>45121.458333333336</v>
       </c>
       <c r="C52" s="18">
@@ -24923,10 +25104,10 @@
       <c r="M52" s="18">
         <v>2.2708599999999999E-2</v>
       </c>
-      <c r="N52" s="78">
+      <c r="N52" s="76">
         <v>-1.7</v>
       </c>
-      <c r="O52" s="78">
+      <c r="O52" s="76">
         <v>0.8</v>
       </c>
       <c r="P52" s="74">
@@ -24935,9 +25116,10 @@
       <c r="Q52" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="53" spans="2:17" s="75" customFormat="1">
-      <c r="B53" s="82">
+      <c r="R52" s="89"/>
+    </row>
+    <row r="53" spans="2:18">
+      <c r="B53" s="88">
         <v>45121.479166666664</v>
       </c>
       <c r="C53" s="18">
@@ -24975,10 +25157,10 @@
       <c r="M53" s="18">
         <v>2.4175100000000001E-2</v>
       </c>
-      <c r="N53" s="78">
+      <c r="N53" s="76">
         <v>-1.7</v>
       </c>
-      <c r="O53" s="78">
+      <c r="O53" s="76">
         <v>0.8</v>
       </c>
       <c r="P53" s="74">
@@ -24987,9 +25169,10 @@
       <c r="Q53" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="54" spans="2:17" s="75" customFormat="1">
-      <c r="B54" s="82">
+      <c r="R53" s="89"/>
+    </row>
+    <row r="54" spans="2:18">
+      <c r="B54" s="88">
         <v>45124.368055555555</v>
       </c>
       <c r="C54" s="18">
@@ -25027,10 +25210,10 @@
       <c r="M54" s="18">
         <v>7.0259600000000005E-2</v>
       </c>
-      <c r="N54" s="78">
+      <c r="N54" s="76">
         <v>-1.7</v>
       </c>
-      <c r="O54" s="78">
+      <c r="O54" s="76">
         <v>0.8</v>
       </c>
       <c r="P54" s="74">
@@ -25039,9 +25222,10 @@
       <c r="Q54" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="55" spans="2:17" s="75" customFormat="1">
-      <c r="B55" s="82">
+      <c r="R54" s="89"/>
+    </row>
+    <row r="55" spans="2:18">
+      <c r="B55" s="88">
         <v>45124.375</v>
       </c>
       <c r="C55" s="18">
@@ -25079,10 +25263,10 @@
       <c r="M55" s="18">
         <v>0.241475</v>
       </c>
-      <c r="N55" s="78">
+      <c r="N55" s="76">
         <v>-1.7</v>
       </c>
-      <c r="O55" s="78">
+      <c r="O55" s="76">
         <v>0.8</v>
       </c>
       <c r="P55" s="74">
@@ -25091,9 +25275,10 @@
       <c r="Q55" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="56" spans="2:17" s="75" customFormat="1">
-      <c r="B56" s="82">
+      <c r="R55" s="89"/>
+    </row>
+    <row r="56" spans="2:18">
+      <c r="B56" s="88">
         <v>45124.386805555558</v>
       </c>
       <c r="C56" s="18">
@@ -25131,10 +25316,10 @@
       <c r="M56" s="18">
         <v>7.2402599999999998E-2</v>
       </c>
-      <c r="N56" s="78">
+      <c r="N56" s="76">
         <v>-1.7</v>
       </c>
-      <c r="O56" s="78">
+      <c r="O56" s="76">
         <v>0.8</v>
       </c>
       <c r="P56" s="74">
@@ -25143,9 +25328,10 @@
       <c r="Q56" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="57" spans="2:17" s="75" customFormat="1">
-      <c r="B57" s="82">
+      <c r="R56" s="89"/>
+    </row>
+    <row r="57" spans="2:18">
+      <c r="B57" s="88">
         <v>45124.40625</v>
       </c>
       <c r="C57" s="18">
@@ -25183,10 +25369,10 @@
       <c r="M57" s="18">
         <v>2.4175100000000001E-2</v>
       </c>
-      <c r="N57" s="78">
+      <c r="N57" s="76">
         <v>-1.7</v>
       </c>
-      <c r="O57" s="78">
+      <c r="O57" s="76">
         <v>0.8</v>
       </c>
       <c r="P57" s="74">
@@ -25195,9 +25381,10 @@
       <c r="Q57" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="58" spans="2:17" s="75" customFormat="1">
-      <c r="B58" s="82">
+      <c r="R57" s="89"/>
+    </row>
+    <row r="58" spans="2:18">
+      <c r="B58" s="88">
         <v>45125.416666666664</v>
       </c>
       <c r="C58" s="18">
@@ -25235,10 +25422,10 @@
       <c r="M58" s="18">
         <v>0.38312099999999999</v>
       </c>
-      <c r="N58" s="78">
+      <c r="N58" s="76">
         <v>-1.3</v>
       </c>
-      <c r="O58" s="78">
+      <c r="O58" s="76">
         <v>-1.1000000000000001</v>
       </c>
       <c r="P58" s="74">
@@ -25247,9 +25434,10 @@
       <c r="Q58" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="59" spans="2:17" s="75" customFormat="1">
-      <c r="B59" s="82">
+      <c r="R58" s="89"/>
+    </row>
+    <row r="59" spans="2:18">
+      <c r="B59" s="88">
         <v>45125.447916666664</v>
       </c>
       <c r="C59" s="18">
@@ -25287,10 +25475,10 @@
       <c r="M59" s="18">
         <v>0.18023800000000001</v>
       </c>
-      <c r="N59" s="78">
+      <c r="N59" s="76">
         <v>-1.3</v>
       </c>
-      <c r="O59" s="78">
+      <c r="O59" s="76">
         <v>-1.1000000000000001</v>
       </c>
       <c r="P59" s="74">
@@ -25299,9 +25487,10 @@
       <c r="Q59" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="60" spans="2:17" s="75" customFormat="1">
-      <c r="B60" s="82">
+      <c r="R59" s="89"/>
+    </row>
+    <row r="60" spans="2:18">
+      <c r="B60" s="88">
         <v>45152.606249999997</v>
       </c>
       <c r="C60" s="18">
@@ -25339,10 +25528,10 @@
       <c r="M60" s="18">
         <v>2.5429199999999999E-2</v>
       </c>
-      <c r="N60" s="78">
+      <c r="N60" s="76">
         <v>-1.4</v>
       </c>
-      <c r="O60" s="78">
+      <c r="O60" s="76">
         <v>-1.3</v>
       </c>
       <c r="P60" s="74">
@@ -25351,9 +25540,10 @@
       <c r="Q60" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="61" spans="2:17" s="75" customFormat="1">
-      <c r="B61" s="82">
+      <c r="R60" s="89"/>
+    </row>
+    <row r="61" spans="2:18">
+      <c r="B61" s="88">
         <v>45152.62222222222</v>
       </c>
       <c r="C61" s="18">
@@ -25391,10 +25581,10 @@
       <c r="M61" s="18">
         <v>2.5429199999999999E-2</v>
       </c>
-      <c r="N61" s="78">
+      <c r="N61" s="76">
         <v>-1.4</v>
       </c>
-      <c r="O61" s="78">
+      <c r="O61" s="76">
         <v>-1.3</v>
       </c>
       <c r="P61" s="74">
@@ -25403,9 +25593,10 @@
       <c r="Q61" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="62" spans="2:17" s="75" customFormat="1">
-      <c r="B62" s="82">
+      <c r="R61" s="89"/>
+    </row>
+    <row r="62" spans="2:18">
+      <c r="B62" s="88">
         <v>45152.642361111109</v>
       </c>
       <c r="C62" s="18">
@@ -25443,10 +25634,10 @@
       <c r="M62" s="18">
         <v>2.5932400000000001E-2</v>
       </c>
-      <c r="N62" s="78">
+      <c r="N62" s="76">
         <v>-1.4</v>
       </c>
-      <c r="O62" s="78">
+      <c r="O62" s="76">
         <v>-1.3</v>
       </c>
       <c r="P62" s="74">
@@ -25455,9 +25646,10 @@
       <c r="Q62" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="63" spans="2:17" s="75" customFormat="1">
-      <c r="B63" s="82">
+      <c r="R62" s="89"/>
+    </row>
+    <row r="63" spans="2:18">
+      <c r="B63" s="88">
         <v>45153.461805555555</v>
       </c>
       <c r="C63" s="18">
@@ -25495,10 +25687,10 @@
       <c r="M63" s="18">
         <v>7.2691500000000006E-2</v>
       </c>
-      <c r="N63" s="78">
+      <c r="N63" s="76">
         <v>-1.4</v>
       </c>
-      <c r="O63" s="78">
+      <c r="O63" s="76">
         <v>-1.3</v>
       </c>
       <c r="P63" s="74">
@@ -25507,9 +25699,10 @@
       <c r="Q63" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="64" spans="2:17" s="75" customFormat="1">
-      <c r="B64" s="82">
+      <c r="R63" s="89"/>
+    </row>
+    <row r="64" spans="2:18">
+      <c r="B64" s="88">
         <v>45153.475694444445</v>
       </c>
       <c r="C64" s="18">
@@ -25547,10 +25740,10 @@
       <c r="M64" s="18">
         <v>0.24707599999999999</v>
       </c>
-      <c r="N64" s="78">
+      <c r="N64" s="76">
         <v>-1.4</v>
       </c>
-      <c r="O64" s="78">
+      <c r="O64" s="76">
         <v>-1.3</v>
       </c>
       <c r="P64" s="74">
@@ -25559,9 +25752,10 @@
       <c r="Q64" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" s="75" customFormat="1">
-      <c r="B65" s="82">
+      <c r="R64" s="89"/>
+    </row>
+    <row r="65" spans="2:18">
+      <c r="B65" s="88">
         <v>45153.489583333336</v>
       </c>
       <c r="C65" s="18">
@@ -25599,10 +25793,10 @@
       <c r="M65" s="18">
         <v>7.4904600000000002E-2</v>
       </c>
-      <c r="N65" s="78">
+      <c r="N65" s="76">
         <v>-1.4</v>
       </c>
-      <c r="O65" s="78">
+      <c r="O65" s="76">
         <v>-1.3</v>
       </c>
       <c r="P65" s="74">
@@ -25611,9 +25805,10 @@
       <c r="Q65" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" s="75" customFormat="1">
-      <c r="B66" s="82">
+      <c r="R65" s="89"/>
+    </row>
+    <row r="66" spans="2:18">
+      <c r="B66" s="88">
         <v>45153.504166666666</v>
       </c>
       <c r="C66" s="18">
@@ -25651,10 +25846,10 @@
       <c r="M66" s="18">
         <v>2.6713500000000001E-2</v>
       </c>
-      <c r="N66" s="78">
+      <c r="N66" s="76">
         <v>-1.4</v>
       </c>
-      <c r="O66" s="78">
+      <c r="O66" s="76">
         <v>-1.3</v>
       </c>
       <c r="P66" s="74">
@@ -25663,9 +25858,10 @@
       <c r="Q66" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" s="75" customFormat="1">
-      <c r="B67" s="82">
+      <c r="R66" s="89"/>
+    </row>
+    <row r="67" spans="2:18">
+      <c r="B67" s="88">
         <v>45154.555555555555</v>
       </c>
       <c r="C67" s="18">
@@ -25703,10 +25899,10 @@
       <c r="M67" s="18">
         <v>0.48380299999999998</v>
       </c>
-      <c r="N67" s="78">
+      <c r="N67" s="76">
         <v>-1.4</v>
       </c>
-      <c r="O67" s="78">
+      <c r="O67" s="76">
         <v>-1.3</v>
       </c>
       <c r="P67" s="74">
@@ -25715,9 +25911,10 @@
       <c r="Q67" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="68" spans="2:17" s="75" customFormat="1">
-      <c r="B68" s="82">
+      <c r="R67" s="89"/>
+    </row>
+    <row r="68" spans="2:18">
+      <c r="B68" s="88">
         <v>45154.579861111109</v>
       </c>
       <c r="C68" s="18">
@@ -25755,10 +25952,10 @@
       <c r="M68" s="18">
         <v>0.21172099999999999</v>
       </c>
-      <c r="N68" s="78">
+      <c r="N68" s="76">
         <v>-1.4</v>
       </c>
-      <c r="O68" s="78">
+      <c r="O68" s="76">
         <v>-1.3</v>
       </c>
       <c r="P68" s="74">
@@ -25767,9 +25964,10 @@
       <c r="Q68" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" s="75" customFormat="1">
-      <c r="B69" s="82">
+      <c r="R68" s="89"/>
+    </row>
+    <row r="69" spans="2:18">
+      <c r="B69" s="88">
         <v>45175.631944444445</v>
       </c>
       <c r="C69" s="18">
@@ -25807,10 +26005,10 @@
       <c r="M69" s="18">
         <v>2.4729299999999999E-2</v>
       </c>
-      <c r="N69" s="78">
+      <c r="N69" s="76">
         <v>-1.7</v>
       </c>
-      <c r="O69" s="78">
+      <c r="O69" s="76">
         <v>1.2</v>
       </c>
       <c r="P69" s="74">
@@ -25819,9 +26017,10 @@
       <c r="Q69" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" s="75" customFormat="1">
-      <c r="B70" s="82">
+      <c r="R69" s="89"/>
+    </row>
+    <row r="70" spans="2:18">
+      <c r="B70" s="88">
         <v>45176.5625</v>
       </c>
       <c r="C70" s="18">
@@ -25859,10 +26058,10 @@
       <c r="M70" s="18">
         <v>2.6636799999999999E-2</v>
       </c>
-      <c r="N70" s="78">
+      <c r="N70" s="76">
         <v>-1.7</v>
       </c>
-      <c r="O70" s="78">
+      <c r="O70" s="76">
         <v>1.2</v>
       </c>
       <c r="P70" s="74">
@@ -25871,9 +26070,10 @@
       <c r="Q70" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" s="75" customFormat="1">
-      <c r="B71" s="82">
+      <c r="R70" s="89"/>
+    </row>
+    <row r="71" spans="2:18">
+      <c r="B71" s="88">
         <v>45176.584722222222</v>
       </c>
       <c r="C71" s="18">
@@ -25911,10 +26111,10 @@
       <c r="M71" s="18">
         <v>2.8300100000000002E-2</v>
       </c>
-      <c r="N71" s="78">
+      <c r="N71" s="76">
         <v>-1.7</v>
       </c>
-      <c r="O71" s="78">
+      <c r="O71" s="76">
         <v>1.2</v>
       </c>
       <c r="P71" s="74">
@@ -25923,9 +26123,10 @@
       <c r="Q71" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" s="75" customFormat="1">
-      <c r="B72" s="82">
+      <c r="R71" s="89"/>
+    </row>
+    <row r="72" spans="2:18">
+      <c r="B72" s="88">
         <v>45177.453472222223</v>
       </c>
       <c r="C72" s="18">
@@ -25963,10 +26164,10 @@
       <c r="M72" s="18">
         <v>2.35642E-2</v>
       </c>
-      <c r="N72" s="78">
+      <c r="N72" s="76">
         <v>-1.7</v>
       </c>
-      <c r="O72" s="78">
+      <c r="O72" s="76">
         <v>1.2</v>
       </c>
       <c r="P72" s="74">
@@ -25975,9 +26176,10 @@
       <c r="Q72" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" s="75" customFormat="1">
-      <c r="B73" s="82">
+      <c r="R72" s="89"/>
+    </row>
+    <row r="73" spans="2:18">
+      <c r="B73" s="88">
         <v>45183.577777777777</v>
       </c>
       <c r="C73" s="18">
@@ -26015,10 +26217,10 @@
       <c r="M73" s="18">
         <v>0.30014400000000002</v>
       </c>
-      <c r="N73" s="78">
+      <c r="N73" s="76">
         <v>-2.1</v>
       </c>
-      <c r="O73" s="78">
+      <c r="O73" s="76">
         <v>-6.9</v>
       </c>
       <c r="P73" s="74">
@@ -26027,9 +26229,10 @@
       <c r="Q73" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" s="75" customFormat="1">
-      <c r="B74" s="82">
+      <c r="R73" s="89"/>
+    </row>
+    <row r="74" spans="2:18">
+      <c r="B74" s="88">
         <v>45183.59375</v>
       </c>
       <c r="C74" s="18">
@@ -26067,10 +26270,10 @@
       <c r="M74" s="18">
         <v>7.8997700000000004E-2</v>
       </c>
-      <c r="N74" s="78">
+      <c r="N74" s="76">
         <v>-2.1</v>
       </c>
-      <c r="O74" s="78">
+      <c r="O74" s="76">
         <v>-6.9</v>
       </c>
       <c r="P74" s="74">
@@ -26079,9 +26282,10 @@
       <c r="Q74" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" s="75" customFormat="1">
-      <c r="B75" s="82">
+      <c r="R74" s="89"/>
+    </row>
+    <row r="75" spans="2:18">
+      <c r="B75" s="88">
         <v>45187.458333333336</v>
       </c>
       <c r="C75" s="18">
@@ -26119,10 +26323,10 @@
       <c r="M75" s="18">
         <v>0.20494799999999999</v>
       </c>
-      <c r="N75" s="78">
+      <c r="N75" s="76">
         <v>-2.1</v>
       </c>
-      <c r="O75" s="78">
+      <c r="O75" s="76">
         <v>-6.9</v>
       </c>
       <c r="P75" s="74">
@@ -26131,9 +26335,10 @@
       <c r="Q75" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" s="75" customFormat="1">
-      <c r="B76" s="82">
+      <c r="R75" s="89"/>
+    </row>
+    <row r="76" spans="2:18">
+      <c r="B76" s="88">
         <v>45187.474999999999</v>
       </c>
       <c r="C76" s="18">
@@ -26171,10 +26376,10 @@
       <c r="M76" s="18">
         <v>8.1607600000000002E-2</v>
       </c>
-      <c r="N76" s="78">
+      <c r="N76" s="76">
         <v>-2.1</v>
       </c>
-      <c r="O76" s="78">
+      <c r="O76" s="76">
         <v>-6.9</v>
       </c>
       <c r="P76" s="74">
@@ -26183,9 +26388,10 @@
       <c r="Q76" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" s="75" customFormat="1">
-      <c r="B77" s="82">
+      <c r="R76" s="89"/>
+    </row>
+    <row r="77" spans="2:18">
+      <c r="B77" s="88">
         <v>45187.486805555556</v>
       </c>
       <c r="C77" s="18">
@@ -26223,10 +26429,10 @@
       <c r="M77" s="18">
         <v>0.43432599999999999</v>
       </c>
-      <c r="N77" s="78">
+      <c r="N77" s="76">
         <v>-2.1</v>
       </c>
-      <c r="O77" s="78">
+      <c r="O77" s="76">
         <v>-6.9</v>
       </c>
       <c r="P77" s="74">
@@ -26235,9 +26441,10 @@
       <c r="Q77" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="78" spans="2:17" s="75" customFormat="1">
-      <c r="B78" s="82">
+      <c r="R77" s="89"/>
+    </row>
+    <row r="78" spans="2:18">
+      <c r="B78" s="88">
         <v>45238.506944444445</v>
       </c>
       <c r="C78" s="18">
@@ -26275,10 +26482,10 @@
       <c r="M78" s="18">
         <v>2.214E-2</v>
       </c>
-      <c r="N78" s="78">
+      <c r="N78" s="76">
         <v>-1.5</v>
       </c>
-      <c r="O78" s="78">
+      <c r="O78" s="76">
         <v>1.9</v>
       </c>
       <c r="P78" s="74">
@@ -26287,9 +26494,10 @@
       <c r="Q78" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" s="75" customFormat="1">
-      <c r="B79" s="82">
+      <c r="R78" s="89"/>
+    </row>
+    <row r="79" spans="2:18">
+      <c r="B79" s="88">
         <v>45238.524305555555</v>
       </c>
       <c r="C79" s="18">
@@ -26327,10 +26535,10 @@
       <c r="M79" s="18">
         <v>2.214E-2</v>
       </c>
-      <c r="N79" s="78">
+      <c r="N79" s="76">
         <v>-1.5</v>
       </c>
-      <c r="O79" s="78">
+      <c r="O79" s="76">
         <v>1.9</v>
       </c>
       <c r="P79" s="74">
@@ -26339,9 +26547,10 @@
       <c r="Q79" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="80" spans="2:17" s="75" customFormat="1">
-      <c r="B80" s="82">
+      <c r="R79" s="89"/>
+    </row>
+    <row r="80" spans="2:18">
+      <c r="B80" s="88">
         <v>45238.546527777777</v>
       </c>
       <c r="C80" s="18">
@@ -26379,10 +26588,10 @@
       <c r="M80" s="18">
         <v>7.3910299999999998E-2</v>
       </c>
-      <c r="N80" s="78">
+      <c r="N80" s="76">
         <v>-1.5</v>
       </c>
-      <c r="O80" s="78">
+      <c r="O80" s="76">
         <v>1.9</v>
       </c>
       <c r="P80" s="74">
@@ -26391,9 +26600,10 @@
       <c r="Q80" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="81" spans="2:17" s="75" customFormat="1">
-      <c r="B81" s="82">
+      <c r="R80" s="89"/>
+    </row>
+    <row r="81" spans="2:18">
+      <c r="B81" s="88">
         <v>45239.548611111109</v>
       </c>
       <c r="C81" s="18">
@@ -26431,10 +26641,10 @@
       <c r="M81" s="18">
         <v>2.4210300000000001E-2</v>
       </c>
-      <c r="N81" s="78">
+      <c r="N81" s="76">
         <v>-1.5</v>
       </c>
-      <c r="O81" s="78">
+      <c r="O81" s="76">
         <v>1.9</v>
       </c>
       <c r="P81" s="74">
@@ -26443,9 +26653,10 @@
       <c r="Q81" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="82" spans="2:17" s="75" customFormat="1">
-      <c r="B82" s="82">
+      <c r="R81" s="89"/>
+    </row>
+    <row r="82" spans="2:18">
+      <c r="B82" s="88">
         <v>45239.577777777777</v>
       </c>
       <c r="C82" s="18">
@@ -26483,10 +26694,10 @@
       <c r="M82" s="18">
         <v>2.4210300000000001E-2</v>
       </c>
-      <c r="N82" s="78">
+      <c r="N82" s="76">
         <v>-1.5</v>
       </c>
-      <c r="O82" s="78">
+      <c r="O82" s="76">
         <v>1.9</v>
       </c>
       <c r="P82" s="74">
@@ -26495,9 +26706,10 @@
       <c r="Q82" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="83" spans="2:17" s="75" customFormat="1">
-      <c r="B83" s="82">
+      <c r="R82" s="89"/>
+    </row>
+    <row r="83" spans="2:18">
+      <c r="B83" s="88">
         <v>45240.433333333334</v>
       </c>
       <c r="C83" s="18">
@@ -26535,10 +26747,10 @@
       <c r="M83" s="18">
         <v>0.26539000000000001</v>
       </c>
-      <c r="N83" s="78">
+      <c r="N83" s="76">
         <v>-1.5</v>
       </c>
-      <c r="O83" s="78">
+      <c r="O83" s="76">
         <v>1.9</v>
       </c>
       <c r="P83" s="74">
@@ -26547,9 +26759,10 @@
       <c r="Q83" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="84" spans="2:17" s="75" customFormat="1">
-      <c r="B84" s="82">
+      <c r="R83" s="89"/>
+    </row>
+    <row r="84" spans="2:18">
+      <c r="B84" s="88">
         <v>45240.462500000001</v>
       </c>
       <c r="C84" s="18">
@@ -26587,10 +26800,10 @@
       <c r="M84" s="18">
         <v>0.16953599999999999</v>
       </c>
-      <c r="N84" s="78">
+      <c r="N84" s="76">
         <v>-1.5</v>
       </c>
-      <c r="O84" s="78">
+      <c r="O84" s="76">
         <v>1.9</v>
       </c>
       <c r="P84" s="74">
@@ -26599,9 +26812,10 @@
       <c r="Q84" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="85" spans="2:17" s="75" customFormat="1">
-      <c r="B85" s="82">
+      <c r="R84" s="89"/>
+    </row>
+    <row r="85" spans="2:18">
+      <c r="B85" s="88">
         <v>45240.481944444444</v>
       </c>
       <c r="C85" s="18">
@@ -26639,10 +26853,10 @@
       <c r="M85" s="18">
         <v>6.7313200000000004E-2</v>
       </c>
-      <c r="N85" s="78">
+      <c r="N85" s="76">
         <v>-1.5</v>
       </c>
-      <c r="O85" s="78">
+      <c r="O85" s="76">
         <v>1.9</v>
       </c>
       <c r="P85" s="74">
@@ -26651,9 +26865,10 @@
       <c r="Q85" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="86" spans="2:17" s="75" customFormat="1">
-      <c r="B86" s="82">
+      <c r="R85" s="89"/>
+    </row>
+    <row r="86" spans="2:18">
+      <c r="B86" s="88">
         <v>45240.5</v>
       </c>
       <c r="C86" s="18">
@@ -26691,10 +26906,10 @@
       <c r="M86" s="18">
         <v>0.20750399999999999</v>
       </c>
-      <c r="N86" s="78">
+      <c r="N86" s="76">
         <v>-1.5</v>
       </c>
-      <c r="O86" s="78">
+      <c r="O86" s="76">
         <v>1.9</v>
       </c>
       <c r="P86" s="74">
@@ -26703,9 +26918,10 @@
       <c r="Q86" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="87" spans="2:17" s="75" customFormat="1">
-      <c r="B87" s="82">
+      <c r="R86" s="89"/>
+    </row>
+    <row r="87" spans="2:18">
+      <c r="B87" s="88">
         <v>45259.463194444441</v>
       </c>
       <c r="C87" s="18">
@@ -26743,10 +26959,10 @@
       <c r="M87" s="18">
         <v>2.0970800000000001E-2</v>
       </c>
-      <c r="N87" s="78">
+      <c r="N87" s="76">
         <v>0</v>
       </c>
-      <c r="O87" s="78">
+      <c r="O87" s="76">
         <v>6.1</v>
       </c>
       <c r="P87" s="74">
@@ -26755,9 +26971,10 @@
       <c r="Q87" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="88" spans="2:17" s="75" customFormat="1">
-      <c r="B88" s="82">
+      <c r="R87" s="89"/>
+    </row>
+    <row r="88" spans="2:18">
+      <c r="B88" s="88">
         <v>45260.520833333336</v>
       </c>
       <c r="C88" s="18">
@@ -26795,10 +27012,10 @@
       <c r="M88" s="18">
         <v>2.214E-2</v>
       </c>
-      <c r="N88" s="78">
+      <c r="N88" s="76">
         <v>0</v>
       </c>
-      <c r="O88" s="78">
+      <c r="O88" s="76">
         <v>6.1</v>
       </c>
       <c r="P88" s="74">
@@ -26807,9 +27024,10 @@
       <c r="Q88" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="89" spans="2:17" s="75" customFormat="1">
-      <c r="B89" s="82">
+      <c r="R88" s="89"/>
+    </row>
+    <row r="89" spans="2:18">
+      <c r="B89" s="88">
         <v>45260.541666666664</v>
       </c>
       <c r="C89" s="18">
@@ -26847,10 +27065,10 @@
       <c r="M89" s="18">
         <v>2.4210300000000001E-2</v>
       </c>
-      <c r="N89" s="78">
+      <c r="N89" s="76">
         <v>0</v>
       </c>
-      <c r="O89" s="78">
+      <c r="O89" s="76">
         <v>6.1</v>
       </c>
       <c r="P89" s="74">
@@ -26859,9 +27077,10 @@
       <c r="Q89" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="90" spans="2:17" s="75" customFormat="1">
-      <c r="B90" s="82">
+      <c r="R89" s="89"/>
+    </row>
+    <row r="90" spans="2:18">
+      <c r="B90" s="88">
         <v>45260.5625</v>
       </c>
       <c r="C90" s="18">
@@ -26899,10 +27118,10 @@
       <c r="M90" s="18">
         <v>2.4210300000000001E-2</v>
       </c>
-      <c r="N90" s="78">
+      <c r="N90" s="76">
         <v>0</v>
       </c>
-      <c r="O90" s="78">
+      <c r="O90" s="76">
         <v>6.1</v>
       </c>
       <c r="P90" s="74">
@@ -26911,9 +27130,10 @@
       <c r="Q90" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="91" spans="2:17" s="75" customFormat="1">
-      <c r="B91" s="82">
+      <c r="R90" s="89"/>
+    </row>
+    <row r="91" spans="2:18">
+      <c r="B91" s="88">
         <v>45260.590277777781</v>
       </c>
       <c r="C91" s="18">
@@ -26951,10 +27171,10 @@
       <c r="M91" s="18">
         <v>6.63469E-2</v>
       </c>
-      <c r="N91" s="78">
+      <c r="N91" s="76">
         <v>0</v>
       </c>
-      <c r="O91" s="78">
+      <c r="O91" s="76">
         <v>6.1</v>
       </c>
       <c r="P91" s="74">
@@ -26963,9 +27183,10 @@
       <c r="Q91" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="92" spans="2:17" s="75" customFormat="1">
-      <c r="B92" s="82">
+      <c r="R91" s="89"/>
+    </row>
+    <row r="92" spans="2:18">
+      <c r="B92" s="88">
         <v>45261.4375</v>
       </c>
       <c r="C92" s="18">
@@ -27003,10 +27224,10 @@
       <c r="M92" s="18">
         <v>4.94799E-2</v>
       </c>
-      <c r="N92" s="78">
+      <c r="N92" s="76">
         <v>0</v>
       </c>
-      <c r="O92" s="78">
+      <c r="O92" s="76">
         <v>6.1</v>
       </c>
       <c r="P92" s="74">
@@ -27015,9 +27236,10 @@
       <c r="Q92" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="93" spans="2:17" s="75" customFormat="1">
-      <c r="B93" s="82">
+      <c r="R92" s="89"/>
+    </row>
+    <row r="93" spans="2:18">
+      <c r="B93" s="88">
         <v>45261.45208333333</v>
       </c>
       <c r="C93" s="18">
@@ -27055,10 +27277,10 @@
       <c r="M93" s="18">
         <v>0.12698300000000001</v>
       </c>
-      <c r="N93" s="78">
+      <c r="N93" s="76">
         <v>0</v>
       </c>
-      <c r="O93" s="78">
+      <c r="O93" s="76">
         <v>6.1</v>
       </c>
       <c r="P93" s="74">
@@ -27067,9 +27289,10 @@
       <c r="Q93" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="94" spans="2:17" s="75" customFormat="1">
-      <c r="B94" s="82">
+      <c r="R93" s="89"/>
+    </row>
+    <row r="94" spans="2:18">
+      <c r="B94" s="88">
         <v>45266.4375</v>
       </c>
       <c r="C94" s="18">
@@ -27107,10 +27330,10 @@
       <c r="M94" s="18">
         <v>0.22950799999999999</v>
       </c>
-      <c r="N94" s="78">
+      <c r="N94" s="76">
         <v>-4.5999999999999996</v>
       </c>
-      <c r="O94" s="78">
+      <c r="O94" s="76">
         <v>-25.2</v>
       </c>
       <c r="P94" s="74">
@@ -27119,9 +27342,10 @@
       <c r="Q94" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="95" spans="2:17" s="75" customFormat="1">
-      <c r="B95" s="82">
+      <c r="R94" s="89"/>
+    </row>
+    <row r="95" spans="2:18">
+      <c r="B95" s="88">
         <v>45266.468055555553</v>
       </c>
       <c r="C95" s="18">
@@ -27159,10 +27383,10 @@
       <c r="M95" s="18">
         <v>0.210845</v>
       </c>
-      <c r="N95" s="78">
+      <c r="N95" s="76">
         <v>-4.5999999999999996</v>
       </c>
-      <c r="O95" s="78">
+      <c r="O95" s="76">
         <v>-25.2</v>
       </c>
       <c r="P95" s="74">
@@ -27171,9 +27395,10 @@
       <c r="Q95" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="96" spans="2:17" s="75" customFormat="1">
-      <c r="B96" s="82">
+      <c r="R95" s="89"/>
+    </row>
+    <row r="96" spans="2:18">
+      <c r="B96" s="88">
         <v>45344.600694444445</v>
       </c>
       <c r="C96" s="18">
@@ -27212,15 +27437,17 @@
         <v>0.397368</v>
       </c>
       <c r="N96" s="18"/>
+      <c r="O96" s="75"/>
       <c r="P96" s="74">
         <v>-2.42</v>
       </c>
       <c r="Q96" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="97" spans="2:17" s="75" customFormat="1">
-      <c r="B97" s="82">
+      <c r="R96" s="89"/>
+    </row>
+    <row r="97" spans="2:18">
+      <c r="B97" s="88">
         <v>45344.640277777777</v>
       </c>
       <c r="C97" s="18">
@@ -27259,15 +27486,17 @@
         <v>0.15940199999999999</v>
       </c>
       <c r="N97" s="18"/>
+      <c r="O97" s="75"/>
       <c r="P97" s="74">
         <v>-2.42</v>
       </c>
       <c r="Q97" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="98" spans="2:17" s="75" customFormat="1">
-      <c r="B98" s="82">
+      <c r="R97" s="89"/>
+    </row>
+    <row r="98" spans="2:18">
+      <c r="B98" s="88">
         <v>45344.663888888892</v>
       </c>
       <c r="C98" s="18">
@@ -27306,15 +27535,17 @@
         <v>5.8161600000000001E-2</v>
       </c>
       <c r="N98" s="18"/>
+      <c r="O98" s="75"/>
       <c r="P98" s="74">
         <v>-2.42</v>
       </c>
       <c r="Q98" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="99" spans="2:17" s="75" customFormat="1">
-      <c r="B99" s="82">
+      <c r="R98" s="89"/>
+    </row>
+    <row r="99" spans="2:18">
+      <c r="B99" s="88">
         <v>45344.681250000001</v>
       </c>
       <c r="C99" s="18">
@@ -27353,15 +27584,17 @@
         <v>0.16870099999999999</v>
       </c>
       <c r="N99" s="18"/>
+      <c r="O99" s="75"/>
       <c r="P99" s="74">
         <v>-2.42</v>
       </c>
       <c r="Q99" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="100" spans="2:17" s="75" customFormat="1">
-      <c r="B100" s="82">
+      <c r="R99" s="89"/>
+    </row>
+    <row r="100" spans="2:18">
+      <c r="B100" s="88">
         <v>45345.380555555559</v>
       </c>
       <c r="C100" s="18">
@@ -27400,15 +27633,17 @@
         <v>5.5910100000000004E-3</v>
       </c>
       <c r="N100" s="18"/>
+      <c r="O100" s="75"/>
       <c r="P100" s="74">
         <v>-2.42</v>
       </c>
       <c r="Q100" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="101" spans="2:17" s="75" customFormat="1">
-      <c r="B101" s="82">
+      <c r="R100" s="89"/>
+    </row>
+    <row r="101" spans="2:18">
+      <c r="B101" s="88">
         <v>45345.411111111112</v>
       </c>
       <c r="C101" s="18">
@@ -27447,15 +27682,17 @@
         <v>5.5910100000000004E-3</v>
       </c>
       <c r="N101" s="18"/>
+      <c r="O101" s="75"/>
       <c r="P101" s="74">
         <v>-2.42</v>
       </c>
       <c r="Q101" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="102" spans="2:17" s="75" customFormat="1">
-      <c r="B102" s="82">
+      <c r="R101" s="89"/>
+    </row>
+    <row r="102" spans="2:18">
+      <c r="B102" s="88">
         <v>45351.558333333334</v>
       </c>
       <c r="C102" s="18">
@@ -27494,15 +27731,17 @@
         <v>2.23054E-2</v>
       </c>
       <c r="N102" s="18"/>
+      <c r="O102" s="75"/>
       <c r="P102" s="74">
         <v>-2.42</v>
       </c>
       <c r="Q102" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="103" spans="2:17" s="75" customFormat="1">
-      <c r="B103" s="82">
+      <c r="R102" s="89"/>
+    </row>
+    <row r="103" spans="2:18">
+      <c r="B103" s="88">
         <v>45351.579861111109</v>
       </c>
       <c r="C103" s="18">
@@ -27541,15 +27780,17 @@
         <v>2.23054E-2</v>
       </c>
       <c r="N103" s="18"/>
+      <c r="O103" s="75"/>
       <c r="P103" s="74">
         <v>-2.42</v>
       </c>
       <c r="Q103" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="104" spans="2:17" s="75" customFormat="1">
-      <c r="B104" s="82">
+      <c r="R103" s="89"/>
+    </row>
+    <row r="104" spans="2:18">
+      <c r="B104" s="88">
         <v>45351.611805555556</v>
       </c>
       <c r="C104" s="18">
@@ -27588,15 +27829,17 @@
         <v>6.6970399999999999E-2</v>
       </c>
       <c r="N104" s="18"/>
+      <c r="O104" s="75"/>
       <c r="P104" s="74">
         <v>-2.42</v>
       </c>
       <c r="Q104" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="105" spans="2:17" s="75" customFormat="1">
-      <c r="B105" s="85">
+      <c r="R104" s="89"/>
+    </row>
+    <row r="105" spans="2:18">
+      <c r="B105" s="90">
         <v>46001.361111111109</v>
       </c>
       <c r="C105" s="18">
@@ -27641,9 +27884,12 @@
       <c r="Q105" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="106" spans="2:17" s="75" customFormat="1">
-      <c r="B106" s="85">
+      <c r="R105" s="91">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="106" spans="2:18">
+      <c r="B106" s="90">
         <v>46001.409722222219</v>
       </c>
       <c r="C106" s="18">
@@ -27688,9 +27934,12 @@
       <c r="Q106" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="107" spans="2:17" s="75" customFormat="1">
-      <c r="B107" s="85">
+      <c r="R106" s="91">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="107" spans="2:18">
+      <c r="B107" s="90">
         <v>46001.473611111112</v>
       </c>
       <c r="C107" s="18">
@@ -27735,9 +27984,12 @@
       <c r="Q107" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="108" spans="2:17" s="75" customFormat="1">
-      <c r="B108" s="85">
+      <c r="R107" s="91">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="108" spans="2:18">
+      <c r="B108" s="90">
         <v>46001.510416666664</v>
       </c>
       <c r="C108" s="18">
@@ -27782,9 +28034,12 @@
       <c r="Q108" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="109" spans="2:17" s="75" customFormat="1">
-      <c r="B109" s="85">
+      <c r="R108" s="91">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="109" spans="2:18">
+      <c r="B109" s="90">
         <v>46001.536111111112</v>
       </c>
       <c r="C109" s="18">
@@ -27829,9 +28084,12 @@
       <c r="Q109" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="110" spans="2:17" s="75" customFormat="1">
-      <c r="B110" s="85">
+      <c r="R109" s="91">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="110" spans="2:18">
+      <c r="B110" s="90">
         <v>46001.600694444445</v>
       </c>
       <c r="C110" s="18">
@@ -27876,9 +28134,12 @@
       <c r="Q110" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="111" spans="2:17" s="75" customFormat="1">
-      <c r="B111" s="84">
+      <c r="R110" s="91">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="111" spans="2:18">
+      <c r="B111" s="92">
         <v>46002</v>
       </c>
       <c r="C111" s="18">
@@ -27924,9 +28185,10 @@
       <c r="Q111" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="112" spans="2:17" s="75" customFormat="1">
-      <c r="B112" s="84">
+      <c r="R111" s="89"/>
+    </row>
+    <row r="112" spans="2:18">
+      <c r="B112" s="92">
         <v>46002</v>
       </c>
       <c r="C112" s="18">
@@ -27972,9 +28234,10 @@
       <c r="Q112" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="113" spans="2:17" s="75" customFormat="1">
-      <c r="B113" s="85">
+      <c r="R112" s="89"/>
+    </row>
+    <row r="113" spans="2:18">
+      <c r="B113" s="90">
         <v>46002.395833333336</v>
       </c>
       <c r="C113" s="18">
@@ -28012,15 +28275,19 @@
         <v>3.27912E-2</v>
       </c>
       <c r="N113" s="22"/>
+      <c r="O113" s="75"/>
       <c r="P113" s="74">
         <v>-2.42</v>
       </c>
       <c r="Q113" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="114" spans="2:17" s="75" customFormat="1">
-      <c r="B114" s="84">
+      <c r="R113" s="91">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="114" spans="2:18">
+      <c r="B114" s="92">
         <v>46022</v>
       </c>
       <c r="C114" s="18">
@@ -28066,9 +28333,10 @@
       <c r="Q114" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="115" spans="2:17" s="75" customFormat="1">
-      <c r="B115" s="84">
+      <c r="R114" s="89"/>
+    </row>
+    <row r="115" spans="2:18">
+      <c r="B115" s="92">
         <v>46052</v>
       </c>
       <c r="C115" s="18">
@@ -28114,9 +28382,10 @@
       <c r="Q115" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="116" spans="2:17" s="75" customFormat="1">
-      <c r="B116" s="84">
+      <c r="R115" s="89"/>
+    </row>
+    <row r="116" spans="2:18">
+      <c r="B116" s="92">
         <v>46056</v>
       </c>
       <c r="C116" s="18">
@@ -28162,9 +28431,10 @@
       <c r="Q116" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="117" spans="2:17" s="75" customFormat="1">
-      <c r="B117" s="85">
+      <c r="R116" s="89"/>
+    </row>
+    <row r="117" spans="2:18">
+      <c r="B117" s="90">
         <v>46063.51458333333</v>
       </c>
       <c r="C117" s="18">
@@ -28213,9 +28483,12 @@
       <c r="Q117" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="118" spans="2:17" s="75" customFormat="1">
-      <c r="B118" s="85">
+      <c r="R117" s="91">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="118" spans="2:18">
+      <c r="B118" s="90">
         <v>46063.522222222222</v>
       </c>
       <c r="C118" s="18">
@@ -28264,9 +28537,12 @@
       <c r="Q118" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="119" spans="2:17" s="75" customFormat="1">
-      <c r="B119" s="85">
+      <c r="R118" s="91">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="119" spans="2:18">
+      <c r="B119" s="90">
         <v>46063.530555555553</v>
       </c>
       <c r="C119" s="18">
@@ -28315,9 +28591,12 @@
       <c r="Q119" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="120" spans="2:17" s="75" customFormat="1">
-      <c r="B120" s="85">
+      <c r="R119" s="91">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="120" spans="2:18">
+      <c r="B120" s="90">
         <v>46063.538888888892</v>
       </c>
       <c r="C120" s="18">
@@ -28366,9 +28645,12 @@
       <c r="Q120" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="121" spans="2:17" s="75" customFormat="1">
-      <c r="B121" s="85">
+      <c r="R120" s="91">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="121" spans="2:18">
+      <c r="B121" s="90">
         <v>46063.563194444447</v>
       </c>
       <c r="C121" s="18">
@@ -28417,9 +28699,12 @@
       <c r="Q121" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="122" spans="2:17" s="75" customFormat="1">
-      <c r="B122" s="85">
+      <c r="R121" s="91">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="122" spans="2:18">
+      <c r="B122" s="90">
         <v>46063.581944444442</v>
       </c>
       <c r="C122" s="18">
@@ -28468,9 +28753,12 @@
       <c r="Q122" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="123" spans="2:17" s="75" customFormat="1">
-      <c r="B123" s="84">
+      <c r="R122" s="91">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="123" spans="2:18">
+      <c r="B123" s="92">
         <v>46065</v>
       </c>
       <c r="C123" s="18">
@@ -28516,9 +28804,10 @@
       <c r="Q123" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="124" spans="2:17" s="75" customFormat="1">
-      <c r="B124" s="84">
+      <c r="R123" s="89"/>
+    </row>
+    <row r="124" spans="2:18">
+      <c r="B124" s="92">
         <v>46080</v>
       </c>
       <c r="C124" s="18">
@@ -28564,9 +28853,10 @@
       <c r="Q124" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="125" spans="2:17" s="75" customFormat="1">
-      <c r="B125" s="84">
+      <c r="R124" s="89"/>
+    </row>
+    <row r="125" spans="2:18">
+      <c r="B125" s="92">
         <v>46093</v>
       </c>
       <c r="C125" s="18">
@@ -28612,9 +28902,10 @@
       <c r="Q125" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="126" spans="2:17" s="75" customFormat="1">
-      <c r="B126" s="84">
+      <c r="R125" s="89"/>
+    </row>
+    <row r="126" spans="2:18">
+      <c r="B126" s="92">
         <v>46097</v>
       </c>
       <c r="C126" s="18">
@@ -28660,9 +28951,10 @@
       <c r="Q126" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="127" spans="2:17" s="75" customFormat="1">
-      <c r="B127" s="85">
+      <c r="R126" s="89"/>
+    </row>
+    <row r="127" spans="2:18">
+      <c r="B127" s="90">
         <v>46105.353472222225</v>
       </c>
       <c r="C127" s="18">
@@ -28711,9 +29003,10 @@
       <c r="Q127" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="128" spans="2:17" s="75" customFormat="1">
-      <c r="B128" s="85">
+      <c r="R127" s="89"/>
+    </row>
+    <row r="128" spans="2:18">
+      <c r="B128" s="90">
         <v>46105.36041666667</v>
       </c>
       <c r="C128" s="18">
@@ -28762,9 +29055,10 @@
       <c r="Q128" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="129" spans="2:17" s="75" customFormat="1">
-      <c r="B129" s="85">
+      <c r="R128" s="89"/>
+    </row>
+    <row r="129" spans="2:18">
+      <c r="B129" s="90">
         <v>46105.366666666669</v>
       </c>
       <c r="C129" s="18">
@@ -28813,9 +29107,10 @@
       <c r="Q129" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="130" spans="2:17" s="75" customFormat="1">
-      <c r="B130" s="85">
+      <c r="R129" s="89"/>
+    </row>
+    <row r="130" spans="2:18">
+      <c r="B130" s="90">
         <v>46105.378472222219</v>
       </c>
       <c r="C130" s="18">
@@ -28864,9 +29159,10 @@
       <c r="Q130" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="131" spans="2:17" s="75" customFormat="1">
-      <c r="B131" s="84">
+      <c r="R130" s="89"/>
+    </row>
+    <row r="131" spans="2:18">
+      <c r="B131" s="92">
         <v>46112</v>
       </c>
       <c r="C131" s="18">
@@ -28912,9 +29208,10 @@
       <c r="Q131" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="132" spans="2:17" s="75" customFormat="1">
-      <c r="B132" s="85">
+      <c r="R131" s="89"/>
+    </row>
+    <row r="132" spans="2:18">
+      <c r="B132" s="90">
         <v>46122.414583333331</v>
       </c>
       <c r="C132" s="18">
@@ -28963,9 +29260,10 @@
       <c r="Q132" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="133" spans="2:17" s="75" customFormat="1">
-      <c r="B133" s="85">
+      <c r="R132" s="89"/>
+    </row>
+    <row r="133" spans="2:18">
+      <c r="B133" s="90">
         <v>46122.421527777777</v>
       </c>
       <c r="C133" s="18">
@@ -29014,9 +29312,10 @@
       <c r="Q133" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="134" spans="2:17" s="75" customFormat="1">
-      <c r="B134" s="85">
+      <c r="R133" s="89"/>
+    </row>
+    <row r="134" spans="2:18">
+      <c r="B134" s="90">
         <v>46122.427777777775</v>
       </c>
       <c r="C134" s="18">
@@ -29065,9 +29364,10 @@
       <c r="Q134" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="135" spans="2:17" s="75" customFormat="1">
-      <c r="B135" s="85">
+      <c r="R134" s="89"/>
+    </row>
+    <row r="135" spans="2:18">
+      <c r="B135" s="90">
         <v>46122.438888888886</v>
       </c>
       <c r="C135" s="18">
@@ -29116,9 +29416,10 @@
       <c r="Q135" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="136" spans="2:17" s="75" customFormat="1">
-      <c r="B136" s="84">
+      <c r="R135" s="89"/>
+    </row>
+    <row r="136" spans="2:18">
+      <c r="B136" s="92">
         <v>46125</v>
       </c>
       <c r="C136" s="18">
@@ -29165,186 +29466,166 @@
       <c r="Q136" s="74">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="137" spans="2:17" s="75" customFormat="1">
-      <c r="B137" s="84">
+      <c r="R136" s="89"/>
+    </row>
+    <row r="137" spans="2:18" ht="17" thickBot="1">
+      <c r="B137" s="93">
         <v>46142</v>
       </c>
-      <c r="C137" s="18">
+      <c r="C137" s="94">
         <v>1</v>
       </c>
-      <c r="D137" s="23">
+      <c r="D137" s="95">
         <v>-3.6</v>
       </c>
-      <c r="E137" s="23">
+      <c r="E137" s="95">
         <v>-19.2</v>
       </c>
-      <c r="F137" s="18">
+      <c r="F137" s="94">
         <f t="shared" si="4"/>
         <v>9.6000000000000014</v>
       </c>
-      <c r="G137" s="18">
+      <c r="G137" s="94">
         <v>23.5</v>
       </c>
-      <c r="H137" s="18">
+      <c r="H137" s="94">
         <f>0.02832*5.69</f>
         <v>0.16114080000000003</v>
       </c>
-      <c r="I137" s="18" t="s">
+      <c r="I137" s="94" t="s">
         <v>9</v>
       </c>
-      <c r="J137" s="18">
+      <c r="J137" s="94">
         <v>460</v>
       </c>
-      <c r="K137" s="18">
+      <c r="K137" s="94">
         <v>193.04</v>
       </c>
-      <c r="L137" s="18"/>
-      <c r="M137" s="18"/>
-      <c r="N137" s="23">
+      <c r="L137" s="94"/>
+      <c r="M137" s="94"/>
+      <c r="N137" s="95">
         <v>-3.6</v>
       </c>
-      <c r="O137" s="23">
+      <c r="O137" s="95">
         <v>-19.2</v>
       </c>
-      <c r="P137" s="74">
+      <c r="P137" s="96">
         <v>-2.42</v>
       </c>
-      <c r="Q137" s="74">
+      <c r="Q137" s="96">
         <v>-4.63</v>
       </c>
-    </row>
-    <row r="138" spans="2:17" s="75" customFormat="1">
-      <c r="B138" s="82"/>
-      <c r="C138" s="18"/>
-      <c r="D138" s="19"/>
-      <c r="E138" s="19"/>
-      <c r="F138" s="18"/>
-      <c r="G138" s="20"/>
-      <c r="H138" s="20"/>
-      <c r="I138" s="18"/>
-      <c r="K138" s="18"/>
-      <c r="N138" s="18"/>
-    </row>
-    <row r="139" spans="2:17" s="75" customFormat="1">
-      <c r="B139" s="82"/>
-      <c r="C139" s="18"/>
-      <c r="D139" s="19"/>
-      <c r="E139" s="19"/>
-      <c r="F139" s="18"/>
-      <c r="G139" s="20"/>
-      <c r="H139" s="20"/>
-      <c r="I139" s="18"/>
-      <c r="K139" s="18"/>
-      <c r="N139" s="18"/>
-    </row>
-    <row r="140" spans="2:17" s="75" customFormat="1">
-      <c r="B140" s="82"/>
-      <c r="C140" s="18"/>
-      <c r="D140" s="19"/>
-      <c r="E140" s="19"/>
-      <c r="F140" s="18"/>
-      <c r="G140" s="20"/>
-      <c r="H140" s="20"/>
-      <c r="I140" s="18"/>
-      <c r="K140" s="18"/>
-      <c r="N140" s="18"/>
-    </row>
-    <row r="141" spans="2:17" s="75" customFormat="1">
-      <c r="B141" s="82"/>
-      <c r="C141" s="18"/>
-      <c r="D141" s="19"/>
-      <c r="E141" s="19"/>
-      <c r="F141" s="18"/>
-      <c r="G141" s="20"/>
-      <c r="H141" s="20"/>
-      <c r="I141" s="18"/>
-      <c r="K141" s="18"/>
-      <c r="N141" s="18"/>
-    </row>
-    <row r="142" spans="2:17" s="75" customFormat="1">
-      <c r="B142" s="82"/>
-      <c r="C142" s="18"/>
-      <c r="D142" s="19"/>
-      <c r="E142" s="19"/>
-      <c r="F142" s="18"/>
-      <c r="G142" s="20"/>
-      <c r="H142" s="20"/>
-      <c r="I142" s="18"/>
-      <c r="K142" s="18"/>
-      <c r="N142" s="18"/>
-    </row>
-    <row r="143" spans="2:17" s="75" customFormat="1">
-      <c r="B143" s="82"/>
-      <c r="C143" s="18"/>
-      <c r="D143" s="19"/>
-      <c r="E143" s="19"/>
-      <c r="F143" s="18"/>
-      <c r="G143" s="20"/>
-      <c r="H143" s="20"/>
-      <c r="I143" s="18"/>
-      <c r="K143" s="18"/>
-      <c r="N143" s="18"/>
-    </row>
-    <row r="144" spans="2:17" s="75" customFormat="1">
-      <c r="B144" s="82"/>
-      <c r="C144" s="18"/>
-      <c r="D144" s="19"/>
-      <c r="E144" s="19"/>
-      <c r="F144" s="18"/>
-      <c r="G144" s="20"/>
-      <c r="H144" s="20"/>
-      <c r="I144" s="18"/>
-      <c r="K144" s="18"/>
-      <c r="N144" s="18"/>
-    </row>
-    <row r="145" spans="2:14" s="75" customFormat="1">
-      <c r="B145" s="82"/>
-      <c r="C145" s="18"/>
-      <c r="D145" s="19"/>
-      <c r="E145" s="19"/>
-      <c r="F145" s="18"/>
-      <c r="G145" s="20"/>
-      <c r="H145" s="20"/>
-      <c r="I145" s="18"/>
-      <c r="K145" s="18"/>
-      <c r="N145" s="18"/>
-    </row>
-    <row r="146" spans="2:14" s="75" customFormat="1">
-      <c r="B146" s="82"/>
-      <c r="C146" s="18"/>
-      <c r="D146" s="19"/>
-      <c r="E146" s="19"/>
-      <c r="F146" s="18"/>
-      <c r="G146" s="20"/>
-      <c r="H146" s="20"/>
-      <c r="I146" s="18"/>
-      <c r="K146" s="18"/>
-      <c r="N146" s="18"/>
-    </row>
-    <row r="147" spans="2:14" s="75" customFormat="1">
-      <c r="B147" s="82"/>
-      <c r="C147" s="18"/>
-      <c r="D147" s="19"/>
-      <c r="E147" s="19"/>
-      <c r="F147" s="18"/>
-      <c r="G147" s="20"/>
-      <c r="H147" s="20"/>
-      <c r="I147" s="18"/>
-      <c r="K147" s="18"/>
-      <c r="N147" s="18"/>
-    </row>
-    <row r="148" spans="2:14" s="75" customFormat="1">
-      <c r="B148" s="82"/>
-      <c r="C148" s="18"/>
-      <c r="D148" s="20"/>
-      <c r="E148" s="20"/>
-      <c r="F148" s="18"/>
-      <c r="G148" s="20"/>
-      <c r="H148" s="20"/>
-      <c r="I148" s="18"/>
-      <c r="K148" s="18"/>
-      <c r="N148" s="18"/>
+      <c r="R137" s="97"/>
+    </row>
+    <row r="138" spans="2:18">
+      <c r="B138" s="80"/>
+      <c r="C138" s="78"/>
+      <c r="D138" s="81"/>
+      <c r="E138" s="81"/>
+      <c r="F138" s="78"/>
+      <c r="G138" s="82"/>
+      <c r="H138" s="82"/>
+      <c r="I138" s="78"/>
+    </row>
+    <row r="139" spans="2:18">
+      <c r="B139" s="80"/>
+      <c r="C139" s="78"/>
+      <c r="D139" s="81"/>
+      <c r="E139" s="81"/>
+      <c r="F139" s="78"/>
+      <c r="G139" s="82"/>
+      <c r="H139" s="82"/>
+      <c r="I139" s="78"/>
+    </row>
+    <row r="140" spans="2:18">
+      <c r="B140" s="80"/>
+      <c r="C140" s="78"/>
+      <c r="D140" s="81"/>
+      <c r="E140" s="81"/>
+      <c r="F140" s="78"/>
+      <c r="G140" s="82"/>
+      <c r="H140" s="82"/>
+      <c r="I140" s="78"/>
+    </row>
+    <row r="141" spans="2:18">
+      <c r="B141" s="80"/>
+      <c r="C141" s="78"/>
+      <c r="D141" s="81"/>
+      <c r="E141" s="81"/>
+      <c r="F141" s="78"/>
+      <c r="G141" s="82"/>
+      <c r="H141" s="82"/>
+      <c r="I141" s="78"/>
+    </row>
+    <row r="142" spans="2:18">
+      <c r="B142" s="80"/>
+      <c r="C142" s="78"/>
+      <c r="D142" s="81"/>
+      <c r="E142" s="81"/>
+      <c r="F142" s="78"/>
+      <c r="G142" s="82"/>
+      <c r="H142" s="82"/>
+      <c r="I142" s="78"/>
+    </row>
+    <row r="143" spans="2:18">
+      <c r="B143" s="80"/>
+      <c r="C143" s="78"/>
+      <c r="D143" s="81"/>
+      <c r="E143" s="81"/>
+      <c r="F143" s="78"/>
+      <c r="G143" s="82"/>
+      <c r="H143" s="82"/>
+      <c r="I143" s="78"/>
+    </row>
+    <row r="144" spans="2:18">
+      <c r="B144" s="80"/>
+      <c r="C144" s="78"/>
+      <c r="D144" s="81"/>
+      <c r="E144" s="81"/>
+      <c r="F144" s="78"/>
+      <c r="G144" s="82"/>
+      <c r="H144" s="82"/>
+      <c r="I144" s="78"/>
+    </row>
+    <row r="145" spans="2:9">
+      <c r="B145" s="80"/>
+      <c r="C145" s="78"/>
+      <c r="D145" s="81"/>
+      <c r="E145" s="81"/>
+      <c r="F145" s="78"/>
+      <c r="G145" s="82"/>
+      <c r="H145" s="82"/>
+      <c r="I145" s="78"/>
+    </row>
+    <row r="146" spans="2:9">
+      <c r="B146" s="80"/>
+      <c r="C146" s="78"/>
+      <c r="D146" s="81"/>
+      <c r="E146" s="81"/>
+      <c r="F146" s="78"/>
+      <c r="G146" s="82"/>
+      <c r="H146" s="82"/>
+      <c r="I146" s="78"/>
+    </row>
+    <row r="147" spans="2:9">
+      <c r="B147" s="80"/>
+      <c r="C147" s="78"/>
+      <c r="D147" s="81"/>
+      <c r="E147" s="81"/>
+      <c r="F147" s="78"/>
+      <c r="G147" s="82"/>
+      <c r="H147" s="82"/>
+      <c r="I147" s="78"/>
+    </row>
+    <row r="148" spans="2:9">
+      <c r="B148" s="80"/>
+      <c r="C148" s="78"/>
+      <c r="D148" s="82"/>
+      <c r="E148" s="82"/>
+      <c r="F148" s="78"/>
+      <c r="G148" s="82"/>
+      <c r="H148" s="82"/>
+      <c r="I148" s="78"/>
     </row>
   </sheetData>
   <autoFilter ref="B2:N137" xr:uid="{E174FB01-AC8B-4229-B319-63F7FF07E34C}"/>
@@ -29360,6 +29641,1008 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{357DA256-30D5-CE4A-B419-F4D79195044A}">
+  <dimension ref="B1:R20"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:18" ht="16" thickBot="1"/>
+    <row r="2" spans="2:18" ht="16">
+      <c r="B2" s="85" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="86" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="86" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="86" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="86" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="86" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="86" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="86" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="86" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="86" t="s">
+        <v>163</v>
+      </c>
+      <c r="M2" s="86" t="s">
+        <v>164</v>
+      </c>
+      <c r="N2" s="86" t="s">
+        <v>165</v>
+      </c>
+      <c r="O2" s="86" t="s">
+        <v>304</v>
+      </c>
+      <c r="P2" s="86" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q2" s="86" t="s">
+        <v>305</v>
+      </c>
+      <c r="R2" s="87" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="3" spans="2:18" ht="16">
+      <c r="B3" s="90">
+        <v>46001.361111111109</v>
+      </c>
+      <c r="C3" s="18">
+        <v>5</v>
+      </c>
+      <c r="D3" s="21">
+        <v>-2.2999999999999998</v>
+      </c>
+      <c r="E3" s="21">
+        <v>-3.8</v>
+      </c>
+      <c r="F3" s="18">
+        <f t="shared" ref="F3:F20" si="0">E3 - (8*D3)</f>
+        <v>14.599999999999998</v>
+      </c>
+      <c r="G3" s="18">
+        <v>21.6</v>
+      </c>
+      <c r="H3" s="18">
+        <v>9.6818425000000014E-2</v>
+      </c>
+      <c r="I3" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="18">
+        <v>80</v>
+      </c>
+      <c r="K3" s="18">
+        <v>0</v>
+      </c>
+      <c r="L3" s="18">
+        <v>13.077484395006453</v>
+      </c>
+      <c r="M3" s="18">
+        <v>1.11231E-2</v>
+      </c>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="74">
+        <v>-2.42</v>
+      </c>
+      <c r="Q3" s="74">
+        <v>-4.63</v>
+      </c>
+      <c r="R3" s="91">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="4" spans="2:18" ht="16">
+      <c r="B4" s="90">
+        <v>46001.409722222219</v>
+      </c>
+      <c r="C4" s="18">
+        <v>4</v>
+      </c>
+      <c r="D4" s="21">
+        <v>-2.4</v>
+      </c>
+      <c r="E4" s="21">
+        <v>-4.0999999999999996</v>
+      </c>
+      <c r="F4" s="18">
+        <f t="shared" si="0"/>
+        <v>15.1</v>
+      </c>
+      <c r="G4" s="18">
+        <v>21.4</v>
+      </c>
+      <c r="H4" s="18">
+        <v>7.3870850000000002E-2</v>
+      </c>
+      <c r="I4" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" s="18">
+        <v>80</v>
+      </c>
+      <c r="K4" s="18">
+        <v>0</v>
+      </c>
+      <c r="L4" s="18">
+        <v>32.712148647331908</v>
+      </c>
+      <c r="M4" s="18">
+        <v>9.0940699999999999E-2</v>
+      </c>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="74">
+        <v>-2.42</v>
+      </c>
+      <c r="Q4" s="74">
+        <v>-4.63</v>
+      </c>
+      <c r="R4" s="91">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="5" spans="2:18" ht="16">
+      <c r="B5" s="90">
+        <v>46001.473611111112</v>
+      </c>
+      <c r="C5" s="18">
+        <v>1</v>
+      </c>
+      <c r="D5" s="21">
+        <v>-2.1</v>
+      </c>
+      <c r="E5" s="21">
+        <v>-3.3</v>
+      </c>
+      <c r="F5" s="18">
+        <f t="shared" si="0"/>
+        <v>13.5</v>
+      </c>
+      <c r="G5" s="21">
+        <v>22</v>
+      </c>
+      <c r="H5" s="18">
+        <v>3.1959000000000002E-3</v>
+      </c>
+      <c r="I5" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="J5" s="18">
+        <v>460</v>
+      </c>
+      <c r="K5" s="18">
+        <v>0</v>
+      </c>
+      <c r="L5" s="18">
+        <v>10.281100270273566</v>
+      </c>
+      <c r="M5" s="18">
+        <v>0.30540699999999998</v>
+      </c>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="74">
+        <v>-2.42</v>
+      </c>
+      <c r="Q5" s="74">
+        <v>-4.63</v>
+      </c>
+      <c r="R5" s="91">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:18" ht="16">
+      <c r="B6" s="90">
+        <v>46001.510416666664</v>
+      </c>
+      <c r="C6" s="18">
+        <v>2</v>
+      </c>
+      <c r="D6" s="21">
+        <v>-2.1</v>
+      </c>
+      <c r="E6" s="21">
+        <v>-2.7</v>
+      </c>
+      <c r="F6" s="18">
+        <f t="shared" si="0"/>
+        <v>14.100000000000001</v>
+      </c>
+      <c r="G6" s="18">
+        <v>21.9</v>
+      </c>
+      <c r="H6" s="18">
+        <v>1.5066890000000001E-2</v>
+      </c>
+      <c r="I6" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="J6" s="18">
+        <v>270</v>
+      </c>
+      <c r="K6" s="18">
+        <v>0</v>
+      </c>
+      <c r="L6" s="18">
+        <v>7.0312998488008001</v>
+      </c>
+      <c r="M6" s="18">
+        <v>0.16201399999999999</v>
+      </c>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="74">
+        <v>-2.42</v>
+      </c>
+      <c r="Q6" s="74">
+        <v>-4.63</v>
+      </c>
+      <c r="R6" s="91">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="7" spans="2:18" ht="16">
+      <c r="B7" s="90">
+        <v>46001.536111111112</v>
+      </c>
+      <c r="C7" s="18">
+        <v>3</v>
+      </c>
+      <c r="D7" s="21">
+        <v>-2.4</v>
+      </c>
+      <c r="E7" s="21">
+        <v>-4.0999999999999996</v>
+      </c>
+      <c r="F7" s="18">
+        <f t="shared" si="0"/>
+        <v>15.1</v>
+      </c>
+      <c r="G7" s="18">
+        <v>24</v>
+      </c>
+      <c r="H7" s="18">
+        <v>7.3870850000000002E-2</v>
+      </c>
+      <c r="I7" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="J7" s="18">
+        <v>230</v>
+      </c>
+      <c r="K7" s="18">
+        <v>0</v>
+      </c>
+      <c r="L7" s="18">
+        <v>10.034530750663777</v>
+      </c>
+      <c r="M7" s="18">
+        <v>6.0341499999999999E-2</v>
+      </c>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="74">
+        <v>-2.42</v>
+      </c>
+      <c r="Q7" s="74">
+        <v>-4.63</v>
+      </c>
+      <c r="R7" s="91">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="8" spans="2:18" ht="16">
+      <c r="B8" s="90">
+        <v>46001.600694444445</v>
+      </c>
+      <c r="C8" s="18">
+        <v>6</v>
+      </c>
+      <c r="D8" s="21">
+        <v>-2.1</v>
+      </c>
+      <c r="E8" s="21">
+        <v>-3.3</v>
+      </c>
+      <c r="F8" s="18">
+        <f t="shared" si="0"/>
+        <v>13.5</v>
+      </c>
+      <c r="G8" s="18">
+        <v>24.7</v>
+      </c>
+      <c r="H8" s="18">
+        <v>0.10129350000000001</v>
+      </c>
+      <c r="I8" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="18">
+        <v>80</v>
+      </c>
+      <c r="K8" s="18">
+        <v>0</v>
+      </c>
+      <c r="L8" s="18">
+        <v>8.0372760653336979</v>
+      </c>
+      <c r="M8" s="18">
+        <v>2.1567300000000001E-2</v>
+      </c>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="74">
+        <v>-2.42</v>
+      </c>
+      <c r="Q8" s="74">
+        <v>-4.63</v>
+      </c>
+      <c r="R8" s="91">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="9" spans="2:18" ht="16">
+      <c r="B9" s="92">
+        <v>46002</v>
+      </c>
+      <c r="C9" s="18">
+        <v>1</v>
+      </c>
+      <c r="D9" s="22">
+        <v>-1.4</v>
+      </c>
+      <c r="E9" s="22">
+        <v>4</v>
+      </c>
+      <c r="F9" s="18">
+        <f t="shared" si="0"/>
+        <v>15.2</v>
+      </c>
+      <c r="G9" s="18">
+        <v>20</v>
+      </c>
+      <c r="H9" s="18">
+        <f>0.02832*1.76</f>
+        <v>4.9843200000000004E-2</v>
+      </c>
+      <c r="I9" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J9" s="18">
+        <v>460</v>
+      </c>
+      <c r="K9" s="18">
+        <v>11.683999999999999</v>
+      </c>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+      <c r="N9" s="22">
+        <v>-1.4</v>
+      </c>
+      <c r="O9" s="22">
+        <v>4</v>
+      </c>
+      <c r="P9" s="74">
+        <v>-2.42</v>
+      </c>
+      <c r="Q9" s="74">
+        <v>-4.63</v>
+      </c>
+      <c r="R9" s="89"/>
+    </row>
+    <row r="10" spans="2:18" ht="16">
+      <c r="B10" s="92">
+        <v>46002</v>
+      </c>
+      <c r="C10" s="18">
+        <v>1</v>
+      </c>
+      <c r="D10" s="22">
+        <v>-1.4</v>
+      </c>
+      <c r="E10" s="22">
+        <v>4.2</v>
+      </c>
+      <c r="F10" s="18">
+        <f t="shared" si="0"/>
+        <v>15.399999999999999</v>
+      </c>
+      <c r="G10" s="18">
+        <v>20</v>
+      </c>
+      <c r="H10" s="18">
+        <f>0.02832*1.76</f>
+        <v>4.9843200000000004E-2</v>
+      </c>
+      <c r="I10" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" s="18">
+        <v>460</v>
+      </c>
+      <c r="K10" s="18">
+        <v>11.683999999999999</v>
+      </c>
+      <c r="L10" s="18"/>
+      <c r="M10" s="18"/>
+      <c r="N10" s="22">
+        <v>-1.4</v>
+      </c>
+      <c r="O10" s="22">
+        <v>4.2</v>
+      </c>
+      <c r="P10" s="74">
+        <v>-2.42</v>
+      </c>
+      <c r="Q10" s="74">
+        <v>-4.63</v>
+      </c>
+      <c r="R10" s="89"/>
+    </row>
+    <row r="11" spans="2:18" ht="16">
+      <c r="B11" s="90">
+        <v>46002.395833333336</v>
+      </c>
+      <c r="C11" s="18">
+        <v>5</v>
+      </c>
+      <c r="D11" s="21">
+        <v>-2.2999999999999998</v>
+      </c>
+      <c r="E11" s="21">
+        <v>-3.6</v>
+      </c>
+      <c r="F11" s="18">
+        <f t="shared" si="0"/>
+        <v>14.799999999999999</v>
+      </c>
+      <c r="G11" s="18">
+        <v>22.1</v>
+      </c>
+      <c r="H11" s="18">
+        <v>0.10892949999999998</v>
+      </c>
+      <c r="I11" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11" s="18">
+        <v>80</v>
+      </c>
+      <c r="K11" s="18">
+        <v>0</v>
+      </c>
+      <c r="L11" s="18">
+        <v>1.27165588456704</v>
+      </c>
+      <c r="M11" s="18">
+        <v>3.27912E-2</v>
+      </c>
+      <c r="N11" s="22"/>
+      <c r="O11" s="75"/>
+      <c r="P11" s="74">
+        <v>-2.42</v>
+      </c>
+      <c r="Q11" s="74">
+        <v>-4.63</v>
+      </c>
+      <c r="R11" s="91">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="12" spans="2:18" ht="16">
+      <c r="B12" s="92">
+        <v>46022</v>
+      </c>
+      <c r="C12" s="18">
+        <v>1</v>
+      </c>
+      <c r="D12" s="22">
+        <v>-2.2000000000000002</v>
+      </c>
+      <c r="E12" s="22">
+        <v>-4.3</v>
+      </c>
+      <c r="F12" s="18">
+        <f t="shared" si="0"/>
+        <v>13.3</v>
+      </c>
+      <c r="G12" s="18">
+        <v>22</v>
+      </c>
+      <c r="H12" s="18">
+        <f>0.02832*6.01</f>
+        <v>0.1702032</v>
+      </c>
+      <c r="I12" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J12" s="18">
+        <v>460</v>
+      </c>
+      <c r="K12" s="18">
+        <v>363.47399999999999</v>
+      </c>
+      <c r="L12" s="18"/>
+      <c r="M12" s="18"/>
+      <c r="N12" s="22">
+        <v>-2.2000000000000002</v>
+      </c>
+      <c r="O12" s="22">
+        <v>-4.3</v>
+      </c>
+      <c r="P12" s="74">
+        <v>-2.42</v>
+      </c>
+      <c r="Q12" s="74">
+        <v>-4.63</v>
+      </c>
+      <c r="R12" s="89"/>
+    </row>
+    <row r="13" spans="2:18" ht="16">
+      <c r="B13" s="92">
+        <v>46052</v>
+      </c>
+      <c r="C13" s="18">
+        <v>1</v>
+      </c>
+      <c r="D13" s="22">
+        <v>-2.4</v>
+      </c>
+      <c r="E13" s="22">
+        <v>-3.9</v>
+      </c>
+      <c r="F13" s="18">
+        <f t="shared" si="0"/>
+        <v>15.299999999999999</v>
+      </c>
+      <c r="G13" s="18">
+        <v>21</v>
+      </c>
+      <c r="H13" s="18">
+        <f>0.02832*6.64</f>
+        <v>0.18804480000000001</v>
+      </c>
+      <c r="I13" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J13" s="18">
+        <v>460</v>
+      </c>
+      <c r="K13" s="18">
+        <v>263.90600000000001</v>
+      </c>
+      <c r="L13" s="18"/>
+      <c r="M13" s="18"/>
+      <c r="N13" s="22">
+        <v>-2.4</v>
+      </c>
+      <c r="O13" s="22">
+        <v>-3.9</v>
+      </c>
+      <c r="P13" s="74">
+        <v>-2.42</v>
+      </c>
+      <c r="Q13" s="74">
+        <v>-4.63</v>
+      </c>
+      <c r="R13" s="89"/>
+    </row>
+    <row r="14" spans="2:18" ht="16">
+      <c r="B14" s="92">
+        <v>46056</v>
+      </c>
+      <c r="C14" s="18">
+        <v>1</v>
+      </c>
+      <c r="D14" s="22">
+        <v>-1.6</v>
+      </c>
+      <c r="E14" s="22">
+        <v>0.3</v>
+      </c>
+      <c r="F14" s="18">
+        <f t="shared" si="0"/>
+        <v>13.100000000000001</v>
+      </c>
+      <c r="G14" s="18">
+        <v>24</v>
+      </c>
+      <c r="H14" s="18">
+        <f>0.02832*2.31</f>
+        <v>6.5419200000000011E-2</v>
+      </c>
+      <c r="I14" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J14" s="18">
+        <v>460</v>
+      </c>
+      <c r="K14" s="18">
+        <v>10.16</v>
+      </c>
+      <c r="L14" s="18"/>
+      <c r="M14" s="18"/>
+      <c r="N14" s="22">
+        <v>-1.6</v>
+      </c>
+      <c r="O14" s="22">
+        <v>0.3</v>
+      </c>
+      <c r="P14" s="74">
+        <v>-2.42</v>
+      </c>
+      <c r="Q14" s="74">
+        <v>-4.63</v>
+      </c>
+      <c r="R14" s="89"/>
+    </row>
+    <row r="15" spans="2:18" ht="16">
+      <c r="B15" s="90">
+        <v>46063.51458333333</v>
+      </c>
+      <c r="C15" s="18">
+        <v>2</v>
+      </c>
+      <c r="D15" s="21">
+        <v>-2.4</v>
+      </c>
+      <c r="E15" s="21">
+        <v>-3.5</v>
+      </c>
+      <c r="F15" s="18">
+        <f t="shared" si="0"/>
+        <v>15.7</v>
+      </c>
+      <c r="G15" s="18">
+        <v>20.7</v>
+      </c>
+      <c r="H15" s="18">
+        <v>0.44147607795698929</v>
+      </c>
+      <c r="I15" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="18">
+        <v>270</v>
+      </c>
+      <c r="K15" s="18">
+        <v>25.4</v>
+      </c>
+      <c r="L15" s="18">
+        <v>2.6882586224509724</v>
+      </c>
+      <c r="M15" s="18">
+        <v>0.172401</v>
+      </c>
+      <c r="N15" s="22">
+        <v>-2.8</v>
+      </c>
+      <c r="O15" s="22">
+        <v>-7.5</v>
+      </c>
+      <c r="P15" s="74">
+        <v>-2.42</v>
+      </c>
+      <c r="Q15" s="74">
+        <v>-4.63</v>
+      </c>
+      <c r="R15" s="91">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="16" spans="2:18" ht="16">
+      <c r="B16" s="90">
+        <v>46063.522222222222</v>
+      </c>
+      <c r="C16" s="18">
+        <v>3</v>
+      </c>
+      <c r="D16" s="21">
+        <v>-2.4</v>
+      </c>
+      <c r="E16" s="21">
+        <v>-3.6</v>
+      </c>
+      <c r="F16" s="18">
+        <f t="shared" si="0"/>
+        <v>15.6</v>
+      </c>
+      <c r="G16" s="18">
+        <v>21</v>
+      </c>
+      <c r="H16" s="18">
+        <v>2.1644953360215053</v>
+      </c>
+      <c r="I16" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" s="18">
+        <v>230</v>
+      </c>
+      <c r="K16" s="18">
+        <v>25.4</v>
+      </c>
+      <c r="L16" s="18">
+        <v>4.9054900269077422</v>
+      </c>
+      <c r="M16" s="18">
+        <v>6.3673300000000002E-2</v>
+      </c>
+      <c r="N16" s="22">
+        <v>-2.8</v>
+      </c>
+      <c r="O16" s="22">
+        <v>-7.5</v>
+      </c>
+      <c r="P16" s="74">
+        <v>-2.42</v>
+      </c>
+      <c r="Q16" s="74">
+        <v>-4.63</v>
+      </c>
+      <c r="R16" s="91">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="17" spans="2:18" ht="16">
+      <c r="B17" s="90">
+        <v>46063.530555555553</v>
+      </c>
+      <c r="C17" s="18">
+        <v>4</v>
+      </c>
+      <c r="D17" s="21">
+        <v>-2.2000000000000002</v>
+      </c>
+      <c r="E17" s="21">
+        <v>-2.8</v>
+      </c>
+      <c r="F17" s="18">
+        <f t="shared" si="0"/>
+        <v>14.8</v>
+      </c>
+      <c r="G17" s="18">
+        <v>22.1</v>
+      </c>
+      <c r="H17" s="18">
+        <v>2.1644953360215053</v>
+      </c>
+      <c r="I17" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="18">
+        <v>80</v>
+      </c>
+      <c r="K17" s="18">
+        <v>25.4</v>
+      </c>
+      <c r="L17" s="18">
+        <v>5.3351094517973552</v>
+      </c>
+      <c r="M17" s="18">
+        <v>0.2293</v>
+      </c>
+      <c r="N17" s="22">
+        <v>-2.8</v>
+      </c>
+      <c r="O17" s="22">
+        <v>-7.5</v>
+      </c>
+      <c r="P17" s="74">
+        <v>-2.42</v>
+      </c>
+      <c r="Q17" s="74">
+        <v>-4.63</v>
+      </c>
+      <c r="R17" s="91">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="18" spans="2:18" ht="16">
+      <c r="B18" s="90">
+        <v>46063.538888888892</v>
+      </c>
+      <c r="C18" s="18">
+        <v>5</v>
+      </c>
+      <c r="D18" s="21">
+        <v>-2.2000000000000002</v>
+      </c>
+      <c r="E18" s="21">
+        <v>-2.7</v>
+      </c>
+      <c r="F18" s="18">
+        <f t="shared" si="0"/>
+        <v>14.900000000000002</v>
+      </c>
+      <c r="G18" s="18">
+        <v>22.4</v>
+      </c>
+      <c r="H18" s="18">
+        <v>2.8368839583333334</v>
+      </c>
+      <c r="I18" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="18">
+        <v>80</v>
+      </c>
+      <c r="K18" s="18">
+        <v>25.4</v>
+      </c>
+      <c r="L18" s="18">
+        <v>4.2030931992580207</v>
+      </c>
+      <c r="M18" s="18">
+        <v>6.7744299999999993E-2</v>
+      </c>
+      <c r="N18" s="22">
+        <v>-2.8</v>
+      </c>
+      <c r="O18" s="22">
+        <v>-7.5</v>
+      </c>
+      <c r="P18" s="74">
+        <v>-2.42</v>
+      </c>
+      <c r="Q18" s="74">
+        <v>-4.63</v>
+      </c>
+      <c r="R18" s="91">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="19" spans="2:18" ht="16">
+      <c r="B19" s="90">
+        <v>46063.563194444447</v>
+      </c>
+      <c r="C19" s="18">
+        <v>6</v>
+      </c>
+      <c r="D19" s="21">
+        <v>-2.1</v>
+      </c>
+      <c r="E19" s="21">
+        <v>-2.7</v>
+      </c>
+      <c r="F19" s="18">
+        <f t="shared" si="0"/>
+        <v>14.100000000000001</v>
+      </c>
+      <c r="G19" s="18">
+        <v>22.3</v>
+      </c>
+      <c r="H19" s="18">
+        <v>3.191751478494623</v>
+      </c>
+      <c r="I19" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="J19" s="18">
+        <v>80</v>
+      </c>
+      <c r="K19" s="18">
+        <v>25.4</v>
+      </c>
+      <c r="L19" s="18">
+        <v>2.021642864177855</v>
+      </c>
+      <c r="M19" s="18">
+        <v>2.33487E-2</v>
+      </c>
+      <c r="N19" s="22">
+        <v>-2.8</v>
+      </c>
+      <c r="O19" s="22">
+        <v>-7.5</v>
+      </c>
+      <c r="P19" s="74">
+        <v>-2.42</v>
+      </c>
+      <c r="Q19" s="74">
+        <v>-4.63</v>
+      </c>
+      <c r="R19" s="91">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="20" spans="2:18" ht="16">
+      <c r="B20" s="90">
+        <v>46063.581944444442</v>
+      </c>
+      <c r="C20" s="18">
+        <v>7</v>
+      </c>
+      <c r="D20" s="21">
+        <v>-2.1</v>
+      </c>
+      <c r="E20" s="21">
+        <v>-3</v>
+      </c>
+      <c r="F20" s="18">
+        <f t="shared" si="0"/>
+        <v>13.8</v>
+      </c>
+      <c r="G20" s="18">
+        <v>22.7</v>
+      </c>
+      <c r="H20" s="18">
+        <v>2.9680084677419356</v>
+      </c>
+      <c r="I20" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="18">
+        <v>5</v>
+      </c>
+      <c r="K20" s="18">
+        <v>25.4</v>
+      </c>
+      <c r="L20" s="18">
+        <v>1.6028538685766356</v>
+      </c>
+      <c r="M20" s="18">
+        <v>2.23054E-2</v>
+      </c>
+      <c r="N20" s="22">
+        <v>-2.8</v>
+      </c>
+      <c r="O20" s="22">
+        <v>-7.5</v>
+      </c>
+      <c r="P20" s="74">
+        <v>-2.42</v>
+      </c>
+      <c r="Q20" s="74">
+        <v>-4.63</v>
+      </c>
+      <c r="R20" s="91">
+        <v>0.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7725347B-6589-43A9-892E-0097DC5F2940}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -40490,7 +41773,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1CD757B-7BB1-654C-93A0-663733BA707E}">
   <dimension ref="A1:O112"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
@@ -40530,14 +41813,14 @@
       <c r="I1" s="49" t="s">
         <v>174</v>
       </c>
-      <c r="J1" s="77" t="s">
+      <c r="J1" s="99" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77" t="s">
+      <c r="K1" s="99"/>
+      <c r="L1" s="99" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="77"/>
+      <c r="M1" s="99"/>
       <c r="N1" s="40"/>
     </row>
     <row r="2" spans="1:14" ht="16">
@@ -44454,7 +45737,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EE49727-5BAE-1446-B48D-603B605EABC1}">
   <dimension ref="B2:H994"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
@@ -44468,10 +45751,10 @@
       <c r="B2" s="68" t="s">
         <v>306</v>
       </c>
-      <c r="C2" s="76" t="s">
+      <c r="C2" s="100" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="76"/>
+      <c r="D2" s="100"/>
     </row>
     <row r="3" spans="2:8">
       <c r="B3" s="70"/>
